--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.381837565105401</v>
+        <v>1.454045195182068</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5717603453601734</v>
+        <v>0.6315082818181326</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.738854033415441</v>
+        <v>0.8011720164171648</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.2186252040736006</v>
+        <v>-0.1710340861837486</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.194381592418162</v>
+        <v>1.263705986267777</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3826470747827959</v>
+        <v>0.1594595153023725</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.263096312523885</v>
+        <v>1.33800827413888</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.762696233538968</v>
+        <v>1.417199902504285</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2196075207408087</v>
+        <v>0.2739390398563569</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2505806547720013</v>
+        <v>0.3053885676819106</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8553208515671425</v>
+        <v>0.9194301957324015</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.9365415623831419</v>
+        <v>1.001900151864273</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.4278023588469198</v>
+        <v>0.4853360960135009</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.569666024302258</v>
+        <v>1.523321734102833</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.493337065756498</v>
+        <v>0.4185630758398887</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.06994183256607481</v>
+        <v>-0.020063834845479</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.440455026231926</v>
+        <v>-0.3962758443306636</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.1422182178713154</v>
+        <v>-0.09345189394529217</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.8116816981862757</v>
+        <v>-0.2280857826590073</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.08362409927990096</v>
+        <v>-0.03395654674540401</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.1142099662234878</v>
+        <v>-0.3156872501229944</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.0873110945706123</v>
+        <v>-0.037700251236888</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9337742060004742</v>
+        <v>-0.9700813361779281</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8763529648194739</v>
+        <v>-0.8388782730969818</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.003056772115929</v>
+        <v>-1.531949491583592</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.46006006290979</v>
+        <v>-1.431563295054306</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.333277656196829</v>
+        <v>-1.302830864435745</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.057823184484106</v>
+        <v>-1.02313966289062</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.001744303458295</v>
+        <v>-1.981579111298077</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.64239283897248</v>
+        <v>-1.616700508115119</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.454045195182068</v>
+        <v>1.442592641354352</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6315082818181326</v>
+        <v>0.6178923898995194</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.8011720164171648</v>
+        <v>0.7880023537360954</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1710340861837486</v>
+        <v>-0.1867607289343902</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.263705986267777</v>
+        <v>1.251752825045857</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1594595153023725</v>
+        <v>0.4253653591460073</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33800827413888</v>
+        <v>1.326250533896834</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.417199902504285</v>
+        <v>1.405650442599984</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2739390398563569</v>
+        <v>0.2593827121363821</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3053885676819106</v>
+        <v>0.2909149547439477</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.9194301957324015</v>
+        <v>0.9065715615531734</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.001900151864273</v>
+        <v>0.9892584202879016</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.4853360960135009</v>
+        <v>0.4713357595158749</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.523321734102833</v>
+        <v>1.512051383131934</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.4185630758398887</v>
+        <v>0.404387120940658</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.020063834845479</v>
+        <v>-0.03539341371970848</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.3962758443306636</v>
+        <v>-0.4125948909809272</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.09345189394529217</v>
+        <v>-0.1089744893043604</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2280857826590073</v>
+        <v>-0.2439624759497888</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.03395654674540401</v>
+        <v>-0.04932266456682316</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3156872501229944</v>
+        <v>-0.2516185441934098</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.037700251236888</v>
+        <v>-0.05307621530155279</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9700813361779281</v>
+        <v>-0.9879095373197542</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8388782730969818</v>
+        <v>-0.8563613996538332</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.531949491583592</v>
+        <v>-1.551255451064166</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.431563295054306</v>
+        <v>-1.353240009438239</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.302830864435745</v>
+        <v>-1.321534223540104</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.02313966289062</v>
+        <v>-1.041107411689641</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.981579111298077</v>
+        <v>-2.002067632761365</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.616700508115119</v>
+        <v>-1.636229369570456</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.442592641354352</v>
+        <v>1.315987785987079</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6178923898995194</v>
+        <v>0.9869771457329588</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.7880023537360954</v>
+        <v>0.6893509242168948</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1867607289343902</v>
+        <v>-0.2437861703106713</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.251752825045857</v>
+        <v>1.133297535529079</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.4253653591460073</v>
+        <v>0.342199870267517</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.326250533896834</v>
+        <v>1.361527234042971</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.405650442599984</v>
+        <v>1.687163825500734</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2593827121363821</v>
+        <v>0.1833052960616181</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2909149547439477</v>
+        <v>0.2134909953088153</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.9065715615531734</v>
+        <v>0.8028567884108356</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.9892584202879016</v>
+        <v>1.013568027894907</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.4713357595158749</v>
+        <v>0.3862071645506431</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.512051383131934</v>
+        <v>1.573507126016638</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.404387120940658</v>
+        <v>0.4500757724555945</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.03539341371970848</v>
+        <v>-0.09888279918698861</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.4125948909809272</v>
+        <v>-0.4599763785403882</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.1089744893043604</v>
+        <v>-0.1693216907535109</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2439624759497888</v>
+        <v>-0.2985451912058992</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.04932266456682316</v>
+        <v>-0.1122172195148624</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.2516185441934098</v>
+        <v>-0.3058743170246417</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.05307621530155279</v>
+        <v>-0.1158104797532084</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9879095373197542</v>
+        <v>-0.8229713505736566</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8563613996538332</v>
+        <v>-1.034626841282074</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.551255451064166</v>
+        <v>-1.073146226809086</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.353240009438239</v>
+        <v>-1.331019063224665</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.321534223540104</v>
+        <v>-1.330100640491755</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.041107411689641</v>
+        <v>-1.061649090479343</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.002067632761365</v>
+        <v>-2.212228073427188</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.636229369570456</v>
+        <v>-1.469359959398348</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -607,76 +607,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>1753.354</v>
+        <v>1756.874</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5562</v>
+        <v>3.2415</v>
       </c>
       <c r="I2" t="n">
-        <v>1494.016671428571</v>
+        <v>1493.682464788732</v>
       </c>
       <c r="J2" t="n">
-        <v>116.9386515415007</v>
+        <v>116.7726225147858</v>
       </c>
       <c r="K2" t="n">
-        <v>105.3659322613714</v>
+        <v>105.8193320275637</v>
       </c>
       <c r="L2" t="n">
-        <v>11.57271928012938</v>
+        <v>10.95329048722205</v>
       </c>
       <c r="M2" t="n">
-        <v>114.8725636035466</v>
+        <v>116.1281386355679</v>
       </c>
       <c r="N2" t="n">
-        <v>102.3325667215449</v>
+        <v>105.424126099685</v>
       </c>
       <c r="O2" t="n">
-        <v>12.53999688200164</v>
+        <v>10.70401253588286</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5627183124667726</v>
+        <v>0.5612808692774636</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1081645753969181</v>
+        <v>0.1066908381652615</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2198041638481379</v>
+        <v>0.2159234099063693</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5490749817310749</v>
+        <v>0.5537199092673066</v>
       </c>
       <c r="T2" t="n">
-        <v>0.262674917941201</v>
+        <v>0.2667331386116227</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4252838192444485</v>
+        <v>0.4258528382251876</v>
       </c>
       <c r="V2" t="n">
-        <v>101.8754789915966</v>
+        <v>101.7688575899844</v>
       </c>
       <c r="W2" t="n">
-        <v>118.9373949579832</v>
+        <v>118.5989827856025</v>
       </c>
       <c r="X2" t="n">
-        <v>11.58361344537815</v>
+        <v>10.85485133020344</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.600907045577183</v>
+        <v>0.599994776910475</v>
       </c>
       <c r="Z2" t="n">
-        <v>114.72</v>
+        <v>115.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.36</v>
+        <v>8.989999999999998</v>
       </c>
       <c r="AB2" t="n">
         <v>11.54061896828745</v>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.315987785987079</v>
+        <v>1.33508470800633</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>1722.37</v>
+        <v>1728.821</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9455</v>
+        <v>1.8856</v>
       </c>
       <c r="I3" t="n">
-        <v>1512.105657142857</v>
+        <v>1512.470591549296</v>
       </c>
       <c r="J3" t="n">
-        <v>117.2617210546893</v>
+        <v>117.3877812581318</v>
       </c>
       <c r="K3" t="n">
-        <v>109.2662603450949</v>
+        <v>108.9043843197315</v>
       </c>
       <c r="L3" t="n">
-        <v>7.995460709594358</v>
+        <v>8.483396938400279</v>
       </c>
       <c r="M3" t="n">
-        <v>124.1434533907008</v>
+        <v>124.0575328453496</v>
       </c>
       <c r="N3" t="n">
-        <v>111.5102760830591</v>
+        <v>110.014448718639</v>
       </c>
       <c r="O3" t="n">
-        <v>12.63317730764172</v>
+        <v>14.04308412671063</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5588220185439347</v>
+        <v>0.5603876192810846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1121575795182626</v>
+        <v>0.1124661740932666</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2577055753063973</v>
+        <v>0.2578826853122713</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5793827313942118</v>
+        <v>0.5825975534783464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2815031209362703</v>
+        <v>0.2805154394961951</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4231188426401386</v>
+        <v>0.4259273397239809</v>
       </c>
       <c r="V3" t="n">
-        <v>102.1330977443609</v>
+        <v>102.0246265471618</v>
       </c>
       <c r="W3" t="n">
-        <v>119.5447368421053</v>
+        <v>119.4489970123773</v>
       </c>
       <c r="X3" t="n">
-        <v>7.863157894736842</v>
+        <v>8.173708920187794</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5953947167387815</v>
+        <v>0.5961811490629734</v>
       </c>
       <c r="Z3" t="n">
-        <v>125.11</v>
+        <v>125.16</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.31</v>
+        <v>13.21</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -802,214 +802,214 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9869771457329588</v>
+        <v>1.003702297275551</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>1661.046</v>
+        <v>1673.754</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4937</v>
+        <v>0.2338</v>
       </c>
       <c r="I4" t="n">
-        <v>1486.000197183099</v>
+        <v>1491.511126760563</v>
       </c>
       <c r="J4" t="n">
-        <v>117.7514429497014</v>
+        <v>114.9760603792054</v>
       </c>
       <c r="K4" t="n">
-        <v>110.5643345855821</v>
+        <v>107.7466008376071</v>
       </c>
       <c r="L4" t="n">
-        <v>7.187108364119367</v>
+        <v>7.229459541598239</v>
       </c>
       <c r="M4" t="n">
-        <v>120.4513770239545</v>
+        <v>120.8864718420659</v>
       </c>
       <c r="N4" t="n">
-        <v>110.4421261636559</v>
+        <v>109.3482686233348</v>
       </c>
       <c r="O4" t="n">
-        <v>10.00925086029851</v>
+        <v>11.53820321873111</v>
       </c>
       <c r="P4" t="n">
-        <v>0.555309965953557</v>
+        <v>0.5458134423745101</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1146948371657094</v>
+        <v>0.1224513214693638</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2922428885321953</v>
+        <v>0.3033694647116994</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5611470539521123</v>
+        <v>0.5717910382819438</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2414692037213116</v>
+        <v>0.2946597194465311</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4307237049699405</v>
+        <v>0.3476755456258619</v>
       </c>
       <c r="V4" t="n">
-        <v>99.68718309859155</v>
+        <v>102.2082299200609</v>
       </c>
       <c r="W4" t="n">
-        <v>117.106103286385</v>
+        <v>117.7217358203274</v>
       </c>
       <c r="X4" t="n">
-        <v>6.674647887323943</v>
+        <v>7.953939855348307</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5888285134000125</v>
+        <v>0.5824674183157785</v>
       </c>
       <c r="Z4" t="n">
-        <v>117.94</v>
+        <v>122.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.770000000000001</v>
+        <v>11.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.775420617465777</v>
+        <v>1.549391602834736</v>
       </c>
       <c r="AC4" t="n">
-        <v>115.1107166171038</v>
+        <v>112.5216901085732</v>
       </c>
       <c r="AD4" t="n">
-        <v>112.335295999638</v>
+        <v>110.9722985057385</v>
       </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6893509242168948</v>
+        <v>-0.2359333400233777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>1677.716</v>
+        <v>1652.324</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8929</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1490.191420289855</v>
+        <v>1484.803605633803</v>
       </c>
       <c r="J5" t="n">
-        <v>114.6967783772711</v>
+        <v>117.2478973082106</v>
       </c>
       <c r="K5" t="n">
-        <v>107.8880588794505</v>
+        <v>110.3650030182045</v>
       </c>
       <c r="L5" t="n">
-        <v>6.808719497820561</v>
+        <v>6.882894290006084</v>
       </c>
       <c r="M5" t="n">
-        <v>118.5242979109732</v>
+        <v>113.0671486090455</v>
       </c>
       <c r="N5" t="n">
-        <v>110.848927558386</v>
+        <v>111.3724579958304</v>
       </c>
       <c r="O5" t="n">
-        <v>7.675370352587169</v>
+        <v>1.694690613215108</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5423284643438895</v>
+        <v>0.5486463484273284</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1214779954249772</v>
+        <v>0.1044215648656459</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3047673055734159</v>
+        <v>0.2898507213136685</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5476399918131996</v>
+        <v>0.5218839621574175</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2965556051985</v>
+        <v>0.2123075857171958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3478085202192765</v>
+        <v>0.4682678535189928</v>
       </c>
       <c r="V5" t="n">
-        <v>101.9351851851851</v>
+        <v>97.25119304059652</v>
       </c>
       <c r="W5" t="n">
-        <v>117.1847826086957</v>
+        <v>114.2700911350456</v>
       </c>
       <c r="X5" t="n">
-        <v>7.64975845410628</v>
+        <v>7.252278376139188</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5796560979167548</v>
+        <v>0.5795621378020794</v>
       </c>
       <c r="Z5" t="n">
-        <v>118.04</v>
+        <v>110.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.039999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.549391602834736</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC5" t="n">
-        <v>112.5216901085732</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD5" t="n">
-        <v>110.9722985057385</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1021,103 +1021,103 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.2437861703106713</v>
+        <v>1.151077480863093</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612738</v>
+        <v>1610612752</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46103</v>
+        <v>46107</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>1659.163</v>
+        <v>1661.885</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4931</v>
+        <v>0.0692</v>
       </c>
       <c r="I6" t="n">
-        <v>1483.551114285714</v>
+        <v>1484.587111111111</v>
       </c>
       <c r="J6" t="n">
-        <v>116.8246721983145</v>
+        <v>117.4055805175939</v>
       </c>
       <c r="K6" t="n">
-        <v>110.1035414288288</v>
+        <v>110.7868648411097</v>
       </c>
       <c r="L6" t="n">
-        <v>6.721130769485597</v>
+        <v>6.618715676484227</v>
       </c>
       <c r="M6" t="n">
-        <v>112.8549351933639</v>
+        <v>121.3766576228191</v>
       </c>
       <c r="N6" t="n">
-        <v>109.0128473046101</v>
+        <v>111.9795146550886</v>
       </c>
       <c r="O6" t="n">
-        <v>3.842087888753789</v>
+        <v>9.39714296773052</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5457106222432236</v>
+        <v>0.5553539830452668</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1037940000336703</v>
+        <v>0.1148876370982657</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2921494148452223</v>
+        <v>0.2880838594247036</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5162276918520243</v>
+        <v>0.5701781612952713</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2076361070765312</v>
+        <v>0.2367413216275416</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4654560120726629</v>
+        <v>0.4289810295681382</v>
       </c>
       <c r="V6" t="n">
-        <v>97.2975</v>
+        <v>99.50724999999998</v>
       </c>
       <c r="W6" t="n">
-        <v>113.8194444444444</v>
+        <v>116.5601851851852</v>
       </c>
       <c r="X6" t="n">
-        <v>6.930555555555555</v>
+        <v>6.118055555555555</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5760756705431612</v>
+        <v>0.5881959753234444</v>
       </c>
       <c r="Z6" t="n">
-        <v>109.28</v>
+        <v>118.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.67</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.220352523846751</v>
+        <v>2.775420617465777</v>
       </c>
       <c r="AC6" t="n">
-        <v>117.8084737243045</v>
+        <v>115.1107166171038</v>
       </c>
       <c r="AD6" t="n">
-        <v>108.5881212004577</v>
+        <v>112.335295999638</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1129,211 +1129,211 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.133297535529079</v>
+        <v>0.7039305491445247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612750</v>
+        <v>1610612743</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46103</v>
+        <v>46106</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>1572.478</v>
+        <v>1593.941</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.8066</v>
+        <v>2.6025</v>
       </c>
       <c r="I7" t="n">
-        <v>1496.53176056338</v>
+        <v>1506.298506849315</v>
       </c>
       <c r="J7" t="n">
-        <v>115.2444275310869</v>
+        <v>120.0217941041301</v>
       </c>
       <c r="K7" t="n">
-        <v>110.6615931535083</v>
+        <v>115.5284268665138</v>
       </c>
       <c r="L7" t="n">
-        <v>4.582834377578638</v>
+        <v>4.49336723761634</v>
       </c>
       <c r="M7" t="n">
-        <v>112.6740778551731</v>
+        <v>121.7922458677627</v>
       </c>
       <c r="N7" t="n">
-        <v>112.5253193438116</v>
+        <v>116.8255697660083</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1487585113614742</v>
+        <v>4.9666761017544</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5610522441894443</v>
+        <v>0.5775798132358746</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1252255446033865</v>
+        <v>0.1093900356585961</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2592269001558693</v>
+        <v>0.2305477551151635</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5520154437364804</v>
+        <v>0.5910041138839821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2923632021821821</v>
+        <v>0.3048379750978497</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4183301671813572</v>
+        <v>0.4059178653494889</v>
       </c>
       <c r="V7" t="n">
-        <v>102.8640093896714</v>
+        <v>101.3255375674554</v>
       </c>
       <c r="W7" t="n">
-        <v>118.0657276995306</v>
+        <v>121.5035284350352</v>
       </c>
       <c r="X7" t="n">
-        <v>3.982159624413145</v>
+        <v>4.449564134495642</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5946419142282087</v>
+        <v>0.6171076494744393</v>
       </c>
       <c r="Z7" t="n">
-        <v>114.15</v>
+        <v>125.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1000000000000001</v>
+        <v>4.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.250350764022217</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC7" t="n">
-        <v>114.1383305986051</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD7" t="n">
-        <v>109.8879798345829</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.342199870267517</v>
+        <v>1.686465288119215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>1645.228</v>
+        <v>1579.316</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7993</v>
+        <v>-2.4482</v>
       </c>
       <c r="I8" t="n">
-        <v>1489.187788732394</v>
+        <v>1498.790527777778</v>
       </c>
       <c r="J8" t="n">
-        <v>117.1840132002113</v>
+        <v>114.9947400564755</v>
       </c>
       <c r="K8" t="n">
-        <v>112.741828286195</v>
+        <v>110.7471958471358</v>
       </c>
       <c r="L8" t="n">
-        <v>4.442184914016339</v>
+        <v>4.247544209339688</v>
       </c>
       <c r="M8" t="n">
-        <v>121.2050580754658</v>
+        <v>111.196728777161</v>
       </c>
       <c r="N8" t="n">
-        <v>115.7178251620435</v>
+        <v>112.1659150925616</v>
       </c>
       <c r="O8" t="n">
-        <v>5.48723291342225</v>
+        <v>-0.9691863154006422</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5621765465134173</v>
+        <v>0.5597987380413881</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1162964868595602</v>
+        <v>0.1249943522007503</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2655051801748356</v>
+        <v>0.2610747023556211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5787385317755277</v>
+        <v>0.5465412882623248</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2671916793341491</v>
+        <v>0.2887970325747766</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4434845566380923</v>
+        <v>0.4171213995273137</v>
       </c>
       <c r="V8" t="n">
-        <v>102.137965571205</v>
+        <v>103.1068013468014</v>
       </c>
       <c r="W8" t="n">
-        <v>119.4448356807512</v>
+        <v>118.1346801346801</v>
       </c>
       <c r="X8" t="n">
-        <v>4.301643192488262</v>
+        <v>3.804713804713805</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.595383622176326</v>
+        <v>0.5928568149437025</v>
       </c>
       <c r="Z8" t="n">
-        <v>118.09</v>
+        <v>113.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>-0.4299999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.967224035556209</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC8" t="n">
-        <v>120.0962116764131</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD8" t="n">
-        <v>110.1289876408569</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1345,319 +1345,319 @@
         <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.361527234042971</v>
+        <v>0.392707937915488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>1590.521</v>
+        <v>1647.27</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5018</v>
+        <v>-0.6692</v>
       </c>
       <c r="I9" t="n">
-        <v>1506.280097222222</v>
+        <v>1489.691555555556</v>
       </c>
       <c r="J9" t="n">
-        <v>119.7829146040073</v>
+        <v>116.5250500726224</v>
       </c>
       <c r="K9" t="n">
-        <v>115.3562172451138</v>
+        <v>112.6994946632939</v>
       </c>
       <c r="L9" t="n">
-        <v>4.42669735889349</v>
+        <v>3.82555540932849</v>
       </c>
       <c r="M9" t="n">
-        <v>120.5040163170924</v>
+        <v>120.1151737145579</v>
       </c>
       <c r="N9" t="n">
-        <v>115.7565211331056</v>
+        <v>117.2619092348234</v>
       </c>
       <c r="O9" t="n">
-        <v>4.74749518398691</v>
+        <v>2.853264479734493</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5749461560609834</v>
+        <v>0.5590389603124643</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1096998580954748</v>
+        <v>0.1172615642326015</v>
       </c>
       <c r="R9" t="n">
-        <v>0.235073850230154</v>
+        <v>0.2644418904790862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5852024540269851</v>
+        <v>0.5704942636979263</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3049127271214951</v>
+        <v>0.2667157468069255</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4044314812947749</v>
+        <v>0.4448604255118168</v>
       </c>
       <c r="V9" t="n">
-        <v>101.1053240740741</v>
+        <v>102.0978378378378</v>
       </c>
       <c r="W9" t="n">
-        <v>120.9453703703704</v>
+        <v>118.7702702702702</v>
       </c>
       <c r="X9" t="n">
-        <v>4.322685185185184</v>
+        <v>3.716216216216216</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.614648240237066</v>
+        <v>0.5926889621431041</v>
       </c>
       <c r="Z9" t="n">
-        <v>123.2</v>
+        <v>117.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.43</v>
+        <v>2.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.722616812266775</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC9" t="n">
-        <v>116.5392386763017</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD9" t="n">
-        <v>113.8166218640349</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.687163825500734</v>
+        <v>1.359097128978686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1583.587</v>
+        <v>1575.02</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9649</v>
+        <v>-2.6455</v>
       </c>
       <c r="I10" t="n">
-        <v>1495.617690140845</v>
+        <v>1497.89823943662</v>
       </c>
       <c r="J10" t="n">
-        <v>115.9553514075589</v>
+        <v>114.5081402177387</v>
       </c>
       <c r="K10" t="n">
-        <v>112.0263341533761</v>
+        <v>110.9840662922424</v>
       </c>
       <c r="L10" t="n">
-        <v>3.929017254182764</v>
+        <v>3.524073925496332</v>
       </c>
       <c r="M10" t="n">
-        <v>118.6730137541692</v>
+        <v>110.2315068362509</v>
       </c>
       <c r="N10" t="n">
-        <v>106.6179784180848</v>
+        <v>115.3463986822449</v>
       </c>
       <c r="O10" t="n">
-        <v>12.05503533608447</v>
+        <v>-5.114891845994104</v>
       </c>
       <c r="P10" t="n">
-        <v>0.555648856162369</v>
+        <v>0.5397833453443341</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1293704052379693</v>
+        <v>0.1301250193768773</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3033903613160999</v>
+        <v>0.3456255813831912</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5695931485011393</v>
+        <v>0.5391079959108015</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2487399210748749</v>
+        <v>0.2642288216034025</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4830601372664774</v>
+        <v>0.3456852676299191</v>
       </c>
       <c r="V10" t="n">
-        <v>100.0783538732394</v>
+        <v>99.55902688860435</v>
       </c>
       <c r="W10" t="n">
-        <v>116.6852992957747</v>
+        <v>113.9684165599659</v>
       </c>
       <c r="X10" t="n">
-        <v>5.318221830985916</v>
+        <v>3.736235595390525</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5920223269359435</v>
+        <v>0.573471010969931</v>
       </c>
       <c r="Z10" t="n">
-        <v>118.34</v>
+        <v>110.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.85</v>
+        <v>-3.71</v>
       </c>
       <c r="AB10" t="n">
-        <v>-10.13717477219789</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC10" t="n">
-        <v>104.7204689341547</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD10" t="n">
-        <v>114.8576437063525</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1833052960616181</v>
+        <v>0.2246402432445732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>1579.242</v>
+        <v>1585.81</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8869</v>
+        <v>1.3874</v>
       </c>
       <c r="I11" t="n">
-        <v>1499.567957142857</v>
+        <v>1493.130958333333</v>
       </c>
       <c r="J11" t="n">
-        <v>114.8664777467995</v>
+        <v>115.9229240571725</v>
       </c>
       <c r="K11" t="n">
-        <v>111.5299009901896</v>
+        <v>112.4097813148812</v>
       </c>
       <c r="L11" t="n">
-        <v>3.336576756609883</v>
+        <v>3.513142742291282</v>
       </c>
       <c r="M11" t="n">
-        <v>111.1618390956935</v>
+        <v>118.9625739102969</v>
       </c>
       <c r="N11" t="n">
-        <v>116.8665441307296</v>
+        <v>108.8794278261441</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.704705035036057</v>
+        <v>10.0831460841528</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5432415560391709</v>
+        <v>0.5560978430042903</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1293780857253464</v>
+        <v>0.1306211069524975</v>
       </c>
       <c r="R11" t="n">
-        <v>0.342808682071236</v>
+        <v>0.305417531360279</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5471454842230969</v>
+        <v>0.5727424814377063</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2640294440603316</v>
+        <v>0.2503261617229583</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3484653825819483</v>
+        <v>0.4825001993335964</v>
       </c>
       <c r="V11" t="n">
-        <v>99.4524375</v>
+        <v>99.83223809523807</v>
       </c>
       <c r="W11" t="n">
-        <v>114.3263392857143</v>
+        <v>116.3071428571429</v>
       </c>
       <c r="X11" t="n">
-        <v>3.708035714285714</v>
+        <v>4.807142857142857</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5756771651025279</v>
+        <v>0.592632282845572</v>
       </c>
       <c r="Z11" t="n">
-        <v>111.4</v>
+        <v>117.87</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.77</v>
+        <v>12.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.413694058608522</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC11" t="n">
-        <v>112.3850185369902</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD11" t="n">
-        <v>108.9713244783817</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1666,106 +1666,106 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2134909953088153</v>
+        <v>0.1942369414595478</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612737</v>
+        <v>1610612748</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>1507.101</v>
+        <v>1531.564</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1571</v>
+        <v>-1.4609</v>
       </c>
       <c r="I12" t="n">
-        <v>1482.085253521127</v>
+        <v>1504.285833333333</v>
       </c>
       <c r="J12" t="n">
-        <v>114.2451679434539</v>
+        <v>113.7311431173802</v>
       </c>
       <c r="K12" t="n">
-        <v>111.8776487518716</v>
+        <v>110.9652149369016</v>
       </c>
       <c r="L12" t="n">
-        <v>2.367519191582394</v>
+        <v>2.76592818047858</v>
       </c>
       <c r="M12" t="n">
-        <v>122.3843472297877</v>
+        <v>117.5980674011579</v>
       </c>
       <c r="N12" t="n">
-        <v>106.6101181936673</v>
+        <v>115.6839366586612</v>
       </c>
       <c r="O12" t="n">
-        <v>15.77422903612032</v>
+        <v>1.914130742496657</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5551870756949181</v>
+        <v>0.5383662577126558</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1165671956334055</v>
+        <v>0.1130664434951674</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2387733200297679</v>
+        <v>0.2504140221540508</v>
       </c>
       <c r="S12" t="n">
-        <v>0.587426084001258</v>
+        <v>0.5450276515356729</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2391024938682699</v>
+        <v>0.271398840497824</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4298009091911338</v>
+        <v>0.4052222903025458</v>
       </c>
       <c r="V12" t="n">
-        <v>103.9231814415907</v>
+        <v>105.6261904761905</v>
       </c>
       <c r="W12" t="n">
-        <v>118.6868268434135</v>
+        <v>120.1753968253969</v>
       </c>
       <c r="X12" t="n">
-        <v>2.445733222866612</v>
+        <v>3.116666666666667</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5863667053068362</v>
+        <v>0.5766628789699688</v>
       </c>
       <c r="Z12" t="n">
-        <v>124.85</v>
+        <v>121.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.42</v>
+        <v>1.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.981113782848854</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC12" t="n">
-        <v>112.8029837792552</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD12" t="n">
-        <v>113.7840975621041</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8028567884108356</v>
+        <v>0.3986014880582209</v>
       </c>
     </row>
     <row r="13">
@@ -1795,76 +1795,76 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>1546.739</v>
+        <v>1550.449</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0443</v>
+        <v>-0.8964</v>
       </c>
       <c r="I13" t="n">
-        <v>1501.074352112676</v>
+        <v>1499.719291666667</v>
       </c>
       <c r="J13" t="n">
-        <v>115.9655162090404</v>
+        <v>116.0594839796474</v>
       </c>
       <c r="K13" t="n">
-        <v>113.6904745105796</v>
+        <v>113.4927422178393</v>
       </c>
       <c r="L13" t="n">
-        <v>2.275041698460828</v>
+        <v>2.566741761808119</v>
       </c>
       <c r="M13" t="n">
-        <v>121.4925103411196</v>
+        <v>122.6048180628484</v>
       </c>
       <c r="N13" t="n">
-        <v>116.009316462159</v>
+        <v>114.110263470885</v>
       </c>
       <c r="O13" t="n">
-        <v>5.483193878960551</v>
+        <v>8.494554591963418</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5618168741797257</v>
+        <v>0.5614500059833608</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1261066591771781</v>
+        <v>0.1254986889428335</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2331700340041289</v>
+        <v>0.2347284689840954</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5862580369844335</v>
+        <v>0.5901492367491442</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3024871468785147</v>
+        <v>0.3032474363324933</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4057320630769585</v>
+        <v>0.4054571589269671</v>
       </c>
       <c r="V13" t="n">
-        <v>98.75899184581171</v>
+        <v>98.67018970189702</v>
       </c>
       <c r="W13" t="n">
-        <v>113.9421793921423</v>
+        <v>113.8780487804878</v>
       </c>
       <c r="X13" t="n">
-        <v>1.403261675315048</v>
+        <v>1.585365853658537</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6059642399630348</v>
+        <v>0.6053765220982654</v>
       </c>
       <c r="Z13" t="n">
-        <v>121.17</v>
+        <v>121.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.74</v>
+        <v>7.27</v>
       </c>
       <c r="AB13" t="n">
         <v>4.815266446541752</v>
@@ -1885,103 +1885,103 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.013568027894907</v>
+        <v>1.052033216741718</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>1538.016</v>
+        <v>1560.408</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1772</v>
+        <v>4.9923</v>
       </c>
       <c r="I14" t="n">
-        <v>1501.214225352113</v>
+        <v>1498.311388888889</v>
       </c>
       <c r="J14" t="n">
-        <v>113.3017986901711</v>
+        <v>116.6602495758146</v>
       </c>
       <c r="K14" t="n">
-        <v>111.27930553659</v>
+        <v>114.6082226687074</v>
       </c>
       <c r="L14" t="n">
-        <v>2.022493153580982</v>
+        <v>2.05202690710708</v>
       </c>
       <c r="M14" t="n">
-        <v>117.5425967168357</v>
+        <v>121.4787552661077</v>
       </c>
       <c r="N14" t="n">
-        <v>114.5756462208918</v>
+        <v>112.6611401571135</v>
       </c>
       <c r="O14" t="n">
-        <v>2.966950495943939</v>
+        <v>8.817615108994094</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5349570899820502</v>
+        <v>0.5721434326640716</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1128232588563916</v>
+        <v>0.1248167872560072</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2521258566258857</v>
+        <v>0.2392673504996769</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5378408597699338</v>
+        <v>0.5800995330512867</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2705355046717062</v>
+        <v>0.3200507259875529</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4028650574433048</v>
+        <v>0.3984966982904639</v>
       </c>
       <c r="V14" t="n">
-        <v>105.9207981220657</v>
+        <v>100.3966913580247</v>
       </c>
       <c r="W14" t="n">
-        <v>120.0512519561816</v>
+        <v>116.8197530864198</v>
       </c>
       <c r="X14" t="n">
-        <v>2.318075117370892</v>
+        <v>1.567901234567901</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5736066802395121</v>
+        <v>0.6085856308650595</v>
       </c>
       <c r="Z14" t="n">
-        <v>121.98</v>
+        <v>121.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>7.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.094669144490311</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC14" t="n">
-        <v>111.6804548463295</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD14" t="n">
-        <v>112.7751239908198</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -1990,106 +1990,106 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.3862071645506431</v>
+        <v>1.477489013729737</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>1562.706</v>
+        <v>1511.376</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5802</v>
+        <v>2.6406</v>
       </c>
       <c r="I15" t="n">
-        <v>1495.784563380282</v>
+        <v>1480.827708333333</v>
       </c>
       <c r="J15" t="n">
-        <v>116.4668767560661</v>
+        <v>113.7766280849965</v>
       </c>
       <c r="K15" t="n">
-        <v>114.5066489638546</v>
+        <v>112.2400374758675</v>
       </c>
       <c r="L15" t="n">
-        <v>1.960227792211604</v>
+        <v>1.53659060912899</v>
       </c>
       <c r="M15" t="n">
-        <v>120.5899075879412</v>
+        <v>120.4109026661776</v>
       </c>
       <c r="N15" t="n">
-        <v>112.7331806350083</v>
+        <v>108.7814087274484</v>
       </c>
       <c r="O15" t="n">
-        <v>7.856726952932928</v>
+        <v>11.62949393872914</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5708746450645391</v>
+        <v>0.5536188819862715</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1250337675846658</v>
+        <v>0.117861930427064</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2404371382232494</v>
+        <v>0.2419422373926377</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5774558957602749</v>
+        <v>0.5797035167134733</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3193034033401732</v>
+        <v>0.2363897912998568</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4013700622944356</v>
+        <v>0.4292289238933412</v>
       </c>
       <c r="V15" t="n">
-        <v>100.1612035851473</v>
+        <v>104.1380317460317</v>
       </c>
       <c r="W15" t="n">
-        <v>116.3040973111395</v>
+        <v>118.5857142857143</v>
       </c>
       <c r="X15" t="n">
-        <v>1.404609475032011</v>
+        <v>1.836507936507936</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6073187542483937</v>
+        <v>0.5842230457083195</v>
       </c>
       <c r="Z15" t="n">
-        <v>119.27</v>
+        <v>124.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>6</v>
+        <v>12.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.827913300592181</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC15" t="n">
-        <v>114.1496737878887</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD15" t="n">
-        <v>112.3217604872965</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2101,211 +2101,211 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.573507126016638</v>
+        <v>0.8585147979180038</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>1507.767</v>
+        <v>1507.624</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9552</v>
+        <v>-0.2525</v>
       </c>
       <c r="I16" t="n">
-        <v>1498.606842857143</v>
+        <v>1516.454152777778</v>
       </c>
       <c r="J16" t="n">
-        <v>113.4147506688892</v>
+        <v>113.2866827538334</v>
       </c>
       <c r="K16" t="n">
-        <v>111.6457906087347</v>
+        <v>112.1392926130768</v>
       </c>
       <c r="L16" t="n">
-        <v>1.768960060154494</v>
+        <v>1.147390140756679</v>
       </c>
       <c r="M16" t="n">
-        <v>115.9921061882838</v>
+        <v>118.7196042868246</v>
       </c>
       <c r="N16" t="n">
-        <v>114.9475689705509</v>
+        <v>115.5101813717958</v>
       </c>
       <c r="O16" t="n">
-        <v>1.044537217732861</v>
+        <v>3.209422915028772</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5456955292848021</v>
+        <v>0.5386739885194024</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.116607668047129</v>
+        <v>0.1182585643998592</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2515287319409977</v>
+        <v>0.2845045285103836</v>
       </c>
       <c r="S16" t="n">
-        <v>0.569270479087245</v>
+        <v>0.5549428707731872</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2642636892549037</v>
+        <v>0.2310536443479878</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3729360100924466</v>
+        <v>0.4569015087700092</v>
       </c>
       <c r="V16" t="n">
-        <v>100.9620897959183</v>
+        <v>99.40384469696968</v>
       </c>
       <c r="W16" t="n">
-        <v>114.6204081632653</v>
+        <v>112.4807449494949</v>
       </c>
       <c r="X16" t="n">
-        <v>2.108571428571429</v>
+        <v>1.176136363636364</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5799580283469715</v>
+        <v>0.5706535010178025</v>
       </c>
       <c r="Z16" t="n">
-        <v>115.73</v>
+        <v>114.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>2.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.536933640611859</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC16" t="n">
-        <v>108.3888858603967</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD16" t="n">
-        <v>112.9258195010085</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.4500757724555945</v>
+        <v>-0.1108154562546669</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>1507.624</v>
+        <v>1523.417</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2525</v>
+        <v>-1.9164</v>
       </c>
       <c r="I17" t="n">
-        <v>1516.454152777778</v>
+        <v>1492.514652173913</v>
       </c>
       <c r="J17" t="n">
-        <v>113.2998233323481</v>
+        <v>113.4568142054788</v>
       </c>
       <c r="K17" t="n">
-        <v>112.1590028426721</v>
+        <v>112.8190945895778</v>
       </c>
       <c r="L17" t="n">
-        <v>1.140820489676101</v>
+        <v>0.6377196159009948</v>
       </c>
       <c r="M17" t="n">
-        <v>118.7196042868246</v>
+        <v>117.545021261121</v>
       </c>
       <c r="N17" t="n">
-        <v>115.5101813717958</v>
+        <v>119.2147304854601</v>
       </c>
       <c r="O17" t="n">
-        <v>3.209422915028772</v>
+        <v>-1.669709224339038</v>
       </c>
       <c r="P17" t="n">
-        <v>0.538668488936511</v>
+        <v>0.5350509465278205</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1181582846469728</v>
+        <v>0.1151056882291826</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2844302060030054</v>
+        <v>0.2453037725407861</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5549428707731872</v>
+        <v>0.5540849780805727</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2312581589578777</v>
+        <v>0.315402177160877</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4569803441840407</v>
+        <v>0.3882862478687213</v>
       </c>
       <c r="V17" t="n">
-        <v>99.40144841269841</v>
+        <v>101.9763812033377</v>
       </c>
       <c r="W17" t="n">
-        <v>112.4923941798942</v>
+        <v>115.8142292490119</v>
       </c>
       <c r="X17" t="n">
-        <v>1.172619047619048</v>
+        <v>1.31576635924462</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5706684545437566</v>
+        <v>0.5804581042604025</v>
       </c>
       <c r="Z17" t="n">
-        <v>114.63</v>
+        <v>120.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.375203171419814</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC17" t="n">
-        <v>114.7034977739938</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD17" t="n">
-        <v>117.0787009454136</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -2317,211 +2317,211 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.09888279918698861</v>
+        <v>-0.4536820192886385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>1525.459</v>
+        <v>1510.298</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2716</v>
+        <v>1.1304</v>
       </c>
       <c r="I18" t="n">
-        <v>1490.268867647059</v>
+        <v>1496.039746478873</v>
       </c>
       <c r="J18" t="n">
-        <v>113.2433170133823</v>
+        <v>112.6678395395337</v>
       </c>
       <c r="K18" t="n">
-        <v>112.8956232676691</v>
+        <v>112.0712437861321</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3476937457131365</v>
+        <v>0.5965957534014882</v>
       </c>
       <c r="M18" t="n">
-        <v>116.2337240788888</v>
+        <v>115.2326549049742</v>
       </c>
       <c r="N18" t="n">
-        <v>116.4707406900348</v>
+        <v>116.2513101342109</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2370166111460345</v>
+        <v>-1.018655229236692</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5326641642562735</v>
+        <v>0.5407380408991779</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1145118459790797</v>
+        <v>0.1158598294236353</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2474010853932448</v>
+        <v>0.25355135622668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5429504369460316</v>
+        <v>0.5632883362301022</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3136408097200016</v>
+        <v>0.258948205539726</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3900328021539879</v>
+        <v>0.3701017890782413</v>
       </c>
       <c r="V18" t="n">
-        <v>102.1431045751634</v>
+        <v>100.6615877080666</v>
       </c>
       <c r="W18" t="n">
-        <v>115.859068627451</v>
+        <v>113.5851472471191</v>
       </c>
       <c r="X18" t="n">
-        <v>1.147875816993464</v>
+        <v>1.086214255228339</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5781191231041731</v>
+        <v>0.5745874533393589</v>
       </c>
       <c r="Z18" t="n">
-        <v>120.65</v>
+        <v>115.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.28</v>
+        <v>0.4699999999999998</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC18" t="n">
-        <v>107.6152962364644</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD18" t="n">
-        <v>108.1384073962044</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.4599763785403882</v>
+        <v>0.294204686436984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>1477.303</v>
+        <v>1466.767</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.1065</v>
+        <v>-0.0474</v>
       </c>
       <c r="I19" t="n">
-        <v>1510.289591549296</v>
+        <v>1498.779</v>
       </c>
       <c r="J19" t="n">
-        <v>112.6018217165064</v>
+        <v>113.4572304016832</v>
       </c>
       <c r="K19" t="n">
-        <v>112.6693933341195</v>
+        <v>113.1555451692424</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.06757161761302077</v>
+        <v>0.3016852324407445</v>
       </c>
       <c r="M19" t="n">
-        <v>110.3250337170559</v>
+        <v>113.6079435006834</v>
       </c>
       <c r="N19" t="n">
-        <v>116.4490234798927</v>
+        <v>115.4468774267562</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.123989762836737</v>
+        <v>-1.838933926072703</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5505423885852961</v>
+        <v>0.5321602185382215</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1324787003910661</v>
+        <v>0.114130259174332</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2615353240409742</v>
+        <v>0.2612642510733914</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5327838380999267</v>
+        <v>0.5413927720632195</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2355810240336734</v>
+        <v>0.2812339030142152</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5025366037380323</v>
+        <v>0.3949267448455321</v>
       </c>
       <c r="V19" t="n">
-        <v>102.3044913928013</v>
+        <v>103.0025925925926</v>
       </c>
       <c r="W19" t="n">
-        <v>115.3646322378716</v>
+        <v>116.6452991452991</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2625195618153364</v>
+        <v>-0.1232193732193733</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.583946786594648</v>
+        <v>0.5744636725259946</v>
       </c>
       <c r="Z19" t="n">
-        <v>113.69</v>
+        <v>118.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>-5.7</v>
+        <v>-1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.402868486532558</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC19" t="n">
-        <v>112.5227430890375</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD19" t="n">
-        <v>110.1198746025049</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -2530,106 +2530,106 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.1693216907535109</v>
+        <v>-0.3119367214951564</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>1470.288</v>
+        <v>1479.562</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3205</v>
+        <v>-2.6566</v>
       </c>
       <c r="I20" t="n">
-        <v>1495.193436619718</v>
+        <v>1508.360041666667</v>
       </c>
       <c r="J20" t="n">
-        <v>112.6209966021631</v>
+        <v>112.4016856116114</v>
       </c>
       <c r="K20" t="n">
-        <v>113.1999371256172</v>
+        <v>112.3499792560339</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5789405234540922</v>
+        <v>0.05170635557735945</v>
       </c>
       <c r="M20" t="n">
-        <v>110.4978228434437</v>
+        <v>109.6855564088347</v>
       </c>
       <c r="N20" t="n">
-        <v>114.1753474154772</v>
+        <v>115.7327696649611</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.677524572033542</v>
+        <v>-6.047213256126416</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5287522567315109</v>
+        <v>0.5512942038959984</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1158662085599083</v>
+        <v>0.1348382300776007</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2627799662953647</v>
+        <v>0.25910302554522</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5261506756706635</v>
+        <v>0.5366643384778743</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2782109829378432</v>
+        <v>0.2439478398473092</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3950024049719088</v>
+        <v>0.5000390599561023</v>
       </c>
       <c r="V20" t="n">
-        <v>102.6561795774648</v>
+        <v>102.118253968254</v>
       </c>
       <c r="W20" t="n">
-        <v>115.3617957746479</v>
+        <v>114.8825396825397</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9933978873239437</v>
+        <v>0.2611111111111112</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.570858744920842</v>
+        <v>0.5854180507076207</v>
       </c>
       <c r="Z20" t="n">
-        <v>113.35</v>
+        <v>112.87</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.35</v>
+        <v>-5.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>-6.382503892565079</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC20" t="n">
-        <v>109.8789897646453</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD20" t="n">
-        <v>116.2614936572104</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -2638,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2985451912058992</v>
+        <v>-0.1414072364241386</v>
       </c>
     </row>
     <row r="21">
@@ -2659,76 +2659,76 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>1457.857</v>
+        <v>1460.365</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6612</v>
+        <v>1.0113</v>
       </c>
       <c r="I21" t="n">
-        <v>1512.701930555556</v>
+        <v>1509.740164383562</v>
       </c>
       <c r="J21" t="n">
-        <v>111.1529191044272</v>
+        <v>111.5535802956328</v>
       </c>
       <c r="K21" t="n">
-        <v>112.9445501794095</v>
+        <v>112.8552661388475</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.791631074982341</v>
+        <v>-1.301685843214741</v>
       </c>
       <c r="M21" t="n">
-        <v>113.2035572443342</v>
+        <v>113.9656626732359</v>
       </c>
       <c r="N21" t="n">
-        <v>106.1963767156836</v>
+        <v>105.384268953207</v>
       </c>
       <c r="O21" t="n">
-        <v>7.007180528650684</v>
+        <v>8.581393720028856</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5340009834212796</v>
+        <v>0.5351566194002902</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1411658045894082</v>
+        <v>0.14146778552269</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3079851464183359</v>
+        <v>0.3119467028213384</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5476178369247923</v>
+        <v>0.5527888895563711</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2868918402396836</v>
+        <v>0.2872839572269039</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4684684037401181</v>
+        <v>0.4695664165631555</v>
       </c>
       <c r="V21" t="n">
-        <v>103.6971682098765</v>
+        <v>103.5102258422807</v>
       </c>
       <c r="W21" t="n">
-        <v>115.6087962962963</v>
+        <v>115.7386153276565</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.120756172839506</v>
+        <v>-0.7615697889670491</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.570534357755778</v>
+        <v>0.5720669835831984</v>
       </c>
       <c r="Z21" t="n">
-        <v>116.09</v>
+        <v>116.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.92</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AB21" t="n">
         <v>-3.840928550668963</v>
@@ -2740,16 +2740,16 @@
         <v>113.1404693910572</v>
       </c>
       <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.1122172195148624</v>
+        <v>-0.1034159355456411</v>
       </c>
     </row>
     <row r="22">
@@ -2767,76 +2767,76 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>1381.018</v>
+        <v>1385.239</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0897</v>
+        <v>0.0027</v>
       </c>
       <c r="I22" t="n">
-        <v>1492.571785714286</v>
+        <v>1493.792492957747</v>
       </c>
       <c r="J22" t="n">
-        <v>111.9075230016125</v>
+        <v>111.9903979357038</v>
       </c>
       <c r="K22" t="n">
-        <v>115.1802858363683</v>
+        <v>115.8540815857431</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.272762834755738</v>
+        <v>-3.863683650039318</v>
       </c>
       <c r="M22" t="n">
-        <v>111.3383490438546</v>
+        <v>111.8073657100563</v>
       </c>
       <c r="N22" t="n">
-        <v>112.1341936130722</v>
+        <v>116.8541814037627</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7958445692176035</v>
+        <v>-5.046815693706469</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5510574778085431</v>
+        <v>0.5506914637643898</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1264658975756351</v>
+        <v>0.1259387511251726</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2282646482007521</v>
+        <v>0.2287348820757405</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5537193999564878</v>
+        <v>0.548582211747871</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2433320571716941</v>
+        <v>0.2443769693842713</v>
       </c>
       <c r="U22" t="n">
-        <v>0.445533226647087</v>
+        <v>0.446817279743916</v>
       </c>
       <c r="V22" t="n">
-        <v>104.2184163265306</v>
+        <v>104.413255086072</v>
       </c>
       <c r="W22" t="n">
-        <v>116.2628571428571</v>
+        <v>116.6107198748044</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.059591836734694</v>
+        <v>-4.677230046948357</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5832875869610011</v>
+        <v>0.5832337617466857</v>
       </c>
       <c r="Z22" t="n">
-        <v>117.78</v>
+        <v>119.36</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.54</v>
+        <v>-5.69</v>
       </c>
       <c r="AB22" t="n">
         <v>-0.9433805425336231</v>
@@ -2848,7 +2848,7 @@
         <v>113.5078075941239</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3058743170246417</v>
+        <v>-0.2767517143077139</v>
       </c>
     </row>
     <row r="23">
@@ -2875,76 +2875,76 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>1384.258</v>
+        <v>1383.419</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6361</v>
+        <v>2.5076</v>
       </c>
       <c r="I23" t="n">
-        <v>1503.629194444444</v>
+        <v>1505.785589041096</v>
       </c>
       <c r="J23" t="n">
-        <v>112.6471335269735</v>
+        <v>112.2958640990509</v>
       </c>
       <c r="K23" t="n">
-        <v>116.1441997252851</v>
+        <v>116.1987057338638</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.49706619831156</v>
+        <v>-3.902841634812923</v>
       </c>
       <c r="M23" t="n">
-        <v>116.6707098046145</v>
+        <v>117.2285993147765</v>
       </c>
       <c r="N23" t="n">
-        <v>112.4950153616689</v>
+        <v>114.1274500933177</v>
       </c>
       <c r="O23" t="n">
-        <v>4.175694442945603</v>
+        <v>3.101149221458858</v>
       </c>
       <c r="P23" t="n">
-        <v>0.53071721628351</v>
+        <v>0.529425236519333</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1165039262283043</v>
+        <v>0.1172635260041805</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2665440333922451</v>
+        <v>0.2687259888794437</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5508299008220187</v>
+        <v>0.553916623310057</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2819404758930381</v>
+        <v>0.2828116351150145</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3625170464152275</v>
+        <v>0.3597480948558597</v>
       </c>
       <c r="V23" t="n">
-        <v>102.6258689458689</v>
+        <v>102.7634383561644</v>
       </c>
       <c r="W23" t="n">
-        <v>115.485754985755</v>
+        <v>115.2924657534247</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.714387464387464</v>
+        <v>-4.131164383561644</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5707762965649407</v>
+        <v>0.5687211557574223</v>
       </c>
       <c r="Z23" t="n">
-        <v>117.71</v>
+        <v>118.26</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.08</v>
+        <v>3.839999999999999</v>
       </c>
       <c r="AB23" t="n">
         <v>-9.447870926461551</v>
@@ -2956,7 +2956,7 @@
         <v>117.8388903788833</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -2965,103 +2965,103 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.1158104797532084</v>
+        <v>-0.1269298318492404</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>1371.362</v>
+        <v>1387.267</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1368</v>
+        <v>-2.0318</v>
       </c>
       <c r="I24" t="n">
-        <v>1504.481528571428</v>
+        <v>1492.156739130435</v>
       </c>
       <c r="J24" t="n">
-        <v>108.9844317086595</v>
+        <v>110.1850361530908</v>
       </c>
       <c r="K24" t="n">
-        <v>114.2659109722026</v>
+        <v>115.6136673111742</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.281479263543045</v>
+        <v>-5.428631158083402</v>
       </c>
       <c r="M24" t="n">
-        <v>111.014802780115</v>
+        <v>108.1227798172251</v>
       </c>
       <c r="N24" t="n">
-        <v>120.4815970338388</v>
+        <v>124.3346594522542</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.466794253723792</v>
+        <v>-16.21187963502906</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5334067459290003</v>
+        <v>0.5328556870653992</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1257593246252751</v>
+        <v>0.1263135833008181</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2293591294386801</v>
+        <v>0.2464948354270139</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5376790545612083</v>
+        <v>0.5226552280287723</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2844172512599166</v>
+        <v>0.2585946150139702</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3494151372250878</v>
+        <v>0.4351180897508055</v>
       </c>
       <c r="V24" t="n">
-        <v>104.5858907563025</v>
+        <v>103.6906688963211</v>
       </c>
       <c r="W24" t="n">
-        <v>114.0701680672269</v>
+        <v>114.5830546265329</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.154201680672269</v>
+        <v>-4.779821627647714</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5682726557021605</v>
+        <v>0.5698821067033008</v>
       </c>
       <c r="Z24" t="n">
-        <v>115.25</v>
+        <v>112.22</v>
       </c>
       <c r="AA24" t="n">
-        <v>-11.22</v>
+        <v>-14.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.6658146557452705</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC24" t="n">
-        <v>113.1126313914285</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD24" t="n">
-        <v>113.7784460471737</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -3070,106 +3070,106 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.8229713505736566</v>
+        <v>-0.8815604690768023</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>1391.542</v>
+        <v>1369.103</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.259</v>
+        <v>-1.0388</v>
       </c>
       <c r="I25" t="n">
-        <v>1491.936970588235</v>
+        <v>1504.098732394366</v>
       </c>
       <c r="J25" t="n">
-        <v>110.498661826104</v>
+        <v>109.4007429319452</v>
       </c>
       <c r="K25" t="n">
-        <v>115.979397924862</v>
+        <v>114.834424386505</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.480736098757973</v>
+        <v>-5.433681454559837</v>
       </c>
       <c r="M25" t="n">
-        <v>109.3825265634239</v>
+        <v>112.3564516629817</v>
       </c>
       <c r="N25" t="n">
-        <v>124.5264243347839</v>
+        <v>122.6096091495137</v>
       </c>
       <c r="O25" t="n">
-        <v>-15.14389777136001</v>
+        <v>-10.25315748653201</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5339391766523188</v>
+        <v>0.5318731874415529</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1282104099406951</v>
+        <v>0.1222468582163301</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2515705422196578</v>
+        <v>0.2299398210704469</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5264644665868539</v>
+        <v>0.5384280135748686</v>
       </c>
       <c r="T25" t="n">
-        <v>0.260940105896622</v>
+        <v>0.2871971453232432</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4314268565480275</v>
+        <v>0.3487639761678349</v>
       </c>
       <c r="V25" t="n">
-        <v>103.8161538461538</v>
+        <v>104.460985915493</v>
       </c>
       <c r="W25" t="n">
-        <v>115.045814479638</v>
+        <v>114.4262634631317</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.822963800904978</v>
+        <v>-5.195526097763048</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5718683959737866</v>
+        <v>0.5675214962834676</v>
       </c>
       <c r="Z25" t="n">
-        <v>113.75</v>
+        <v>117.18</v>
       </c>
       <c r="AA25" t="n">
-        <v>-13.08</v>
+        <v>-11.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.575252351995317</v>
+        <v>-0.6658146557452705</v>
       </c>
       <c r="AC25" t="n">
-        <v>114.5419381230804</v>
+        <v>113.1126313914285</v>
       </c>
       <c r="AD25" t="n">
-        <v>110.9666857710851</v>
+        <v>113.7784460471737</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -3178,10 +3178,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.034626841282074</v>
+        <v>-1.008398822393146</v>
       </c>
     </row>
     <row r="26">
@@ -3199,76 +3199,76 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>1403.51</v>
+        <v>1399.801</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.218</v>
+        <v>-2.795</v>
       </c>
       <c r="I26" t="n">
-        <v>1491.964571428571</v>
+        <v>1492.736042253521</v>
       </c>
       <c r="J26" t="n">
-        <v>111.0678886401194</v>
+        <v>111.0839498044373</v>
       </c>
       <c r="K26" t="n">
-        <v>116.9956069095971</v>
+        <v>116.9523974470938</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.927718269477656</v>
+        <v>-5.868447642656478</v>
       </c>
       <c r="M26" t="n">
-        <v>109.774396009472</v>
+        <v>108.2269626499474</v>
       </c>
       <c r="N26" t="n">
-        <v>122.8723029718096</v>
+        <v>122.6997282031435</v>
       </c>
       <c r="O26" t="n">
-        <v>-13.09790696233766</v>
+        <v>-14.47276555319603</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5645837366453093</v>
+        <v>0.5633657303245708</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1318351758531856</v>
+        <v>0.1305384784768613</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2055144067277479</v>
+        <v>0.2051492747697975</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5708883709141763</v>
+        <v>0.5620435092172112</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2261254891707314</v>
+        <v>0.2287017546510412</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4475670779492554</v>
+        <v>0.4479979951776746</v>
       </c>
       <c r="V26" t="n">
-        <v>99.60270408163265</v>
+        <v>99.65181818181819</v>
       </c>
       <c r="W26" t="n">
-        <v>110.4505102040816</v>
+        <v>110.5070422535211</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.220408163265306</v>
+        <v>-6.196542893725993</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5881735539442448</v>
+        <v>0.5872400503846898</v>
       </c>
       <c r="Z26" t="n">
-        <v>107.61</v>
+        <v>106.38</v>
       </c>
       <c r="AA26" t="n">
-        <v>-13.47</v>
+        <v>-14.62</v>
       </c>
       <c r="AB26" t="n">
         <v>1.809266556998161</v>
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.073146226809086</v>
+        <v>-1.071272083700429</v>
       </c>
     </row>
     <row r="27">
@@ -3307,76 +3307,76 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>1316.343</v>
+        <v>1313.813</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1313</v>
+        <v>-0.3628</v>
       </c>
       <c r="I27" t="n">
-        <v>1512.551464788732</v>
+        <v>1512.485013888889</v>
       </c>
       <c r="J27" t="n">
-        <v>112.2209217338965</v>
+        <v>111.8228396286655</v>
       </c>
       <c r="K27" t="n">
-        <v>119.8415084105512</v>
+        <v>119.7472978978662</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.620586676654706</v>
+        <v>-7.924458269200658</v>
       </c>
       <c r="M27" t="n">
-        <v>113.0381375781874</v>
+        <v>112.4324163677347</v>
       </c>
       <c r="N27" t="n">
-        <v>117.9676921248646</v>
+        <v>119.1860134813122</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.929554546677228</v>
+        <v>-6.753597113577465</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5378720433179547</v>
+        <v>0.5368610793724036</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1293953656363305</v>
+        <v>0.1290389784749056</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2633691288495825</v>
+        <v>0.2620859576812637</v>
       </c>
       <c r="S27" t="n">
-        <v>0.530780576839971</v>
+        <v>0.5328649370079155</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2904874987349882</v>
+        <v>0.2868486658469708</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4140395740534769</v>
+        <v>0.4107691561399344</v>
       </c>
       <c r="V27" t="n">
-        <v>104.6956412157153</v>
+        <v>104.7843243243244</v>
       </c>
       <c r="W27" t="n">
-        <v>117.5648628613788</v>
+        <v>117.2432432432432</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.730541141586361</v>
+        <v>-8.04054054054054</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5794881760967839</v>
+        <v>0.5771779405704833</v>
       </c>
       <c r="Z27" t="n">
-        <v>115.21</v>
+        <v>115.76</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.19</v>
+        <v>-7.97</v>
       </c>
       <c r="AB27" t="n">
         <v>-9.725925288085115</v>
@@ -3394,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.331019063224665</v>
+        <v>-1.331003872700855</v>
       </c>
     </row>
     <row r="28">
@@ -3415,76 +3415,76 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>1331.971</v>
+        <v>1336.278</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.3847</v>
+        <v>-1.8419</v>
       </c>
       <c r="I28" t="n">
-        <v>1500.204014084507</v>
+        <v>1500.614597222222</v>
       </c>
       <c r="J28" t="n">
-        <v>109.3177504523412</v>
+        <v>109.0999836776447</v>
       </c>
       <c r="K28" t="n">
-        <v>117.0591362187589</v>
+        <v>117.2588395297681</v>
       </c>
       <c r="L28" t="n">
-        <v>-7.741385766417746</v>
+        <v>-8.158855852123363</v>
       </c>
       <c r="M28" t="n">
-        <v>113.0816395630703</v>
+        <v>114.4240416195474</v>
       </c>
       <c r="N28" t="n">
-        <v>124.387114394479</v>
+        <v>124.5209008468359</v>
       </c>
       <c r="O28" t="n">
-        <v>-11.30547483140876</v>
+        <v>-10.09685922728855</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5304380743721757</v>
+        <v>0.5318534897029034</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1194841303567039</v>
+        <v>0.1215149275710593</v>
       </c>
       <c r="R28" t="n">
-        <v>0.215976367054085</v>
+        <v>0.2142279869298917</v>
       </c>
       <c r="S28" t="n">
-        <v>0.551072809195433</v>
+        <v>0.5657971022024827</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2606419707502618</v>
+        <v>0.2602516704807791</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4189951094660375</v>
+        <v>0.4198652868949841</v>
       </c>
       <c r="V28" t="n">
-        <v>102.8888050885961</v>
+        <v>103.1365441176471</v>
       </c>
       <c r="W28" t="n">
-        <v>111.943661971831</v>
+        <v>112.1789215686275</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.672421626533394</v>
+        <v>-8.819852941176471</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5668256379272927</v>
+        <v>0.5677477915688206</v>
       </c>
       <c r="Z28" t="n">
-        <v>113.15</v>
+        <v>115.24</v>
       </c>
       <c r="AA28" t="n">
-        <v>-12.67</v>
+        <v>-11.32</v>
       </c>
       <c r="AB28" t="n">
         <v>2.960186837728194</v>
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.330100640491755</v>
+        <v>-1.330078829246132</v>
       </c>
     </row>
     <row r="29">
@@ -3523,76 +3523,76 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>1316.573</v>
+        <v>1314.351</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.5413</v>
       </c>
       <c r="I29" t="n">
-        <v>1518.873111111111</v>
+        <v>1519.759602739726</v>
       </c>
       <c r="J29" t="n">
-        <v>108.7617677597191</v>
+        <v>109.5216829492278</v>
       </c>
       <c r="K29" t="n">
-        <v>118.8202886814532</v>
+        <v>118.9372716231152</v>
       </c>
       <c r="L29" t="n">
-        <v>-10.05852092173399</v>
+        <v>-9.415588673887417</v>
       </c>
       <c r="M29" t="n">
-        <v>112.3464928754736</v>
+        <v>114.3660207040932</v>
       </c>
       <c r="N29" t="n">
-        <v>118.4530684480063</v>
+        <v>119.9284409433158</v>
       </c>
       <c r="O29" t="n">
-        <v>-6.106575572532758</v>
+        <v>-5.562420239222653</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5217670695408997</v>
+        <v>0.5251488121289328</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1205089616314498</v>
+        <v>0.1196178814832662</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2500016075736892</v>
+        <v>0.2508571371152646</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5412116450978269</v>
+        <v>0.5512421146282964</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2552028121386206</v>
+        <v>0.2554051110201577</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3356406721756467</v>
+        <v>0.3373898973253706</v>
       </c>
       <c r="V29" t="n">
-        <v>101.8768279569893</v>
+        <v>101.6685359589041</v>
       </c>
       <c r="W29" t="n">
-        <v>110.3629032258065</v>
+        <v>110.9486301369864</v>
       </c>
       <c r="X29" t="n">
-        <v>-11.05645161290323</v>
+        <v>-10.22388698630137</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.557180685359539</v>
+        <v>0.560632505128294</v>
       </c>
       <c r="Z29" t="n">
-        <v>113.13</v>
+        <v>114.66</v>
       </c>
       <c r="AA29" t="n">
-        <v>-7.91</v>
+        <v>-6.88</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.1619477822758719</v>
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.061649090479343</v>
+        <v>-1.059692066864171</v>
       </c>
     </row>
     <row r="30">
@@ -3631,76 +3631,76 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>1296.493</v>
+        <v>1293.985</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9141</v>
+        <v>-1.7457</v>
       </c>
       <c r="I30" t="n">
-        <v>1504.468056338028</v>
+        <v>1503.820680555556</v>
       </c>
       <c r="J30" t="n">
-        <v>106.8848706214898</v>
+        <v>106.9127555718554</v>
       </c>
       <c r="K30" t="n">
-        <v>117.2625778846557</v>
+        <v>116.8852230015424</v>
       </c>
       <c r="L30" t="n">
-        <v>-10.37770726316592</v>
+        <v>-9.972467429686885</v>
       </c>
       <c r="M30" t="n">
-        <v>103.0652602656953</v>
+        <v>102.8092604836777</v>
       </c>
       <c r="N30" t="n">
-        <v>115.9792700578619</v>
+        <v>114.3158035288785</v>
       </c>
       <c r="O30" t="n">
-        <v>-12.91400979216664</v>
+        <v>-11.50654304520073</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5210204899767583</v>
+        <v>0.5227223592092914</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1387589496599859</v>
+        <v>0.1389781430316037</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2426871920775596</v>
+        <v>0.2395297460190133</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5083434322783354</v>
+        <v>0.5128529352023121</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2791849443989571</v>
+        <v>0.2777703390707948</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4584897756394792</v>
+        <v>0.4575665039212987</v>
       </c>
       <c r="V30" t="n">
-        <v>99.23895006402049</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>106.2125480153649</v>
+        <v>106.2681992337165</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.701024327784891</v>
+        <v>-9.249042145593869</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5608273076065462</v>
+        <v>0.5619783850989732</v>
       </c>
       <c r="Z30" t="n">
-        <v>103.32</v>
+        <v>103.03</v>
       </c>
       <c r="AA30" t="n">
-        <v>-13.58</v>
+        <v>-12.09</v>
       </c>
       <c r="AB30" t="n">
         <v>-6.499587896466165</v>
@@ -3712,16 +3712,16 @@
         <v>113.7332995772778</v>
       </c>
       <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.212228073427188</v>
+        <v>-2.218565338594626</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46103</v>
+        <v>46106</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G31" t="n">
-        <v>1258.034</v>
+        <v>1257.058</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.4089</v>
+        <v>-1.2368</v>
       </c>
       <c r="I31" t="n">
-        <v>1506.514742857143</v>
+        <v>1508.677492957746</v>
       </c>
       <c r="J31" t="n">
-        <v>108.7156493882564</v>
+        <v>108.9771388755179</v>
       </c>
       <c r="K31" t="n">
-        <v>120.3263132523816</v>
+        <v>119.4399000442245</v>
       </c>
       <c r="L31" t="n">
-        <v>-11.61066386412505</v>
+        <v>-10.46276116870669</v>
       </c>
       <c r="M31" t="n">
-        <v>109.2135337121945</v>
+        <v>110.6134314516703</v>
       </c>
       <c r="N31" t="n">
-        <v>125.9834272700444</v>
+        <v>122.9234911245336</v>
       </c>
       <c r="O31" t="n">
-        <v>-16.76989355784985</v>
+        <v>-12.31005967286328</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5352003237744293</v>
+        <v>0.5365368233680265</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1331899746560526</v>
+        <v>0.1336215182965959</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2403316270341149</v>
+        <v>0.2430990848903866</v>
       </c>
       <c r="S31" t="n">
-        <v>0.555526486707846</v>
+        <v>0.5664287021970412</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2376609757877343</v>
+        <v>0.2397897120353979</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4095682727592747</v>
+        <v>0.4056266946610693</v>
       </c>
       <c r="V31" t="n">
-        <v>103.6082949308756</v>
+        <v>103.7952401589021</v>
       </c>
       <c r="W31" t="n">
-        <v>112.5161290322581</v>
+        <v>113.032502708559</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.98156682027649</v>
+        <v>-10.71830985915493</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5669621890492769</v>
+        <v>0.5681919652381541</v>
       </c>
       <c r="Z31" t="n">
-        <v>113.81</v>
+        <v>116.17</v>
       </c>
       <c r="AA31" t="n">
-        <v>-16.52</v>
+        <v>-12.37</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3820,16 +3820,16 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1</v>
-      </c>
       <c r="AG31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.469359959398348</v>
+        <v>-1.470342040126938</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -607,76 +607,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>1756.874</v>
+        <v>1750.84</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2415</v>
+        <v>2.3486</v>
       </c>
       <c r="I2" t="n">
-        <v>1493.682464788732</v>
+        <v>1495.885819444444</v>
       </c>
       <c r="J2" t="n">
-        <v>116.7726225147858</v>
+        <v>116.900264380679</v>
       </c>
       <c r="K2" t="n">
-        <v>105.8193320275637</v>
+        <v>105.5645188322798</v>
       </c>
       <c r="L2" t="n">
-        <v>10.95329048722205</v>
+        <v>11.33574554839926</v>
       </c>
       <c r="M2" t="n">
-        <v>116.1281386355679</v>
+        <v>117.234843162215</v>
       </c>
       <c r="N2" t="n">
-        <v>105.424126099685</v>
+        <v>105.5218082271332</v>
       </c>
       <c r="O2" t="n">
-        <v>10.70401253588286</v>
+        <v>11.71303493508181</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5612808692774636</v>
+        <v>0.5606766371469609</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1066908381652615</v>
+        <v>0.1062160838060996</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2159234099063693</v>
+        <v>0.2196046609005238</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5537199092673066</v>
+        <v>0.5580488921655966</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2667331386116227</v>
+        <v>0.2670730388258403</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4258528382251876</v>
+        <v>0.4259068858316259</v>
       </c>
       <c r="V2" t="n">
-        <v>101.7688575899844</v>
+        <v>102.0385396825397</v>
       </c>
       <c r="W2" t="n">
-        <v>118.5989827856025</v>
+        <v>119.0865079365079</v>
       </c>
       <c r="X2" t="n">
-        <v>10.85485133020344</v>
+        <v>11.3484126984127</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.599994776910475</v>
+        <v>0.5992316339870989</v>
       </c>
       <c r="Z2" t="n">
-        <v>115.39</v>
+        <v>116.96</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.989999999999998</v>
+        <v>10.17</v>
       </c>
       <c r="AB2" t="n">
         <v>11.54061896828745</v>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.455253782575244</v>
+        <v>1.396692468264619</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9680838065225761</v>
+        <v>0.9534985895770764</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1004190269046388</v>
+        <v>-0.06850425160578996</v>
       </c>
     </row>
     <row r="5">
@@ -931,76 +931,76 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>1652.324</v>
+        <v>1658.359</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.4282</v>
       </c>
       <c r="I5" t="n">
-        <v>1484.803605633803</v>
+        <v>1488.582361111111</v>
       </c>
       <c r="J5" t="n">
-        <v>117.2478973082106</v>
+        <v>117.210917549777</v>
       </c>
       <c r="K5" t="n">
-        <v>110.3650030182045</v>
+        <v>110.314422414086</v>
       </c>
       <c r="L5" t="n">
-        <v>6.882894290006084</v>
+        <v>6.896495135690944</v>
       </c>
       <c r="M5" t="n">
-        <v>113.0671486090455</v>
+        <v>115.0401665696386</v>
       </c>
       <c r="N5" t="n">
-        <v>111.3724579958304</v>
+        <v>109.7188902052104</v>
       </c>
       <c r="O5" t="n">
-        <v>1.694690613215108</v>
+        <v>5.32127636442826</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5486463484273284</v>
+        <v>0.5483413468690369</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1044215648656459</v>
+        <v>0.1051496796996714</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2898507213136685</v>
+        <v>0.2929068749466081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5218839621574175</v>
+        <v>0.5317636308556516</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2123075857171958</v>
+        <v>0.2119763777192656</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4682678535189928</v>
+        <v>0.4667004705209388</v>
       </c>
       <c r="V5" t="n">
-        <v>97.25119304059652</v>
+        <v>97.12081081081082</v>
       </c>
       <c r="W5" t="n">
-        <v>114.2700911350456</v>
+        <v>114.054054054054</v>
       </c>
       <c r="X5" t="n">
-        <v>7.252278376139188</v>
+        <v>7.202702702702703</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5795621378020794</v>
+        <v>0.5792070665825365</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.54</v>
+        <v>112.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.34</v>
+        <v>6.55</v>
       </c>
       <c r="AB5" t="n">
         <v>9.220352523846751</v>
@@ -1012,7 +1012,7 @@
         <v>108.5881212004577</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9966856050937983</v>
+        <v>0.9808527620454571</v>
       </c>
     </row>
     <row r="6">
@@ -1129,237 +1129,237 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6501945525797281</v>
+        <v>0.6494428255448071</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>1593.941</v>
+        <v>1637.716</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6025</v>
+        <v>-0.4165</v>
       </c>
       <c r="I7" t="n">
-        <v>1506.298506849315</v>
+        <v>1490.265150684932</v>
       </c>
       <c r="J7" t="n">
-        <v>120.0217941041301</v>
+        <v>117.1208875317718</v>
       </c>
       <c r="K7" t="n">
-        <v>115.5284268665138</v>
+        <v>112.6775919801654</v>
       </c>
       <c r="L7" t="n">
-        <v>4.49336723761634</v>
+        <v>4.443295551606407</v>
       </c>
       <c r="M7" t="n">
-        <v>121.7922458677627</v>
+        <v>121.7419792720121</v>
       </c>
       <c r="N7" t="n">
-        <v>116.8255697660083</v>
+        <v>117.1237878936892</v>
       </c>
       <c r="O7" t="n">
-        <v>4.9666761017544</v>
+        <v>4.618191378322839</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5775798132358746</v>
+        <v>0.5618847955998393</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1093900356585961</v>
+        <v>0.1158560807095368</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2305477551151635</v>
+        <v>0.2628076828509504</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5910041138839821</v>
+        <v>0.5801718064608603</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3048379750978497</v>
+        <v>0.2678327365163862</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4059178653494889</v>
+        <v>0.4440679594885688</v>
       </c>
       <c r="V7" t="n">
-        <v>101.3255375674554</v>
+        <v>102.416915851272</v>
       </c>
       <c r="W7" t="n">
-        <v>121.5035284350352</v>
+        <v>119.8438356164383</v>
       </c>
       <c r="X7" t="n">
-        <v>4.449564134495642</v>
+        <v>4.485714285714286</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6171076494744393</v>
+        <v>0.5953958019383466</v>
       </c>
       <c r="Z7" t="n">
-        <v>125.35</v>
+        <v>121.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.722616812266775</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC7" t="n">
-        <v>116.5392386763017</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD7" t="n">
-        <v>113.8166218640349</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.606138612354973</v>
+        <v>1.645653156320357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612750</v>
+        <v>1610612743</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>1579.316</v>
+        <v>1594.888</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4482</v>
+        <v>2.2206</v>
       </c>
       <c r="I8" t="n">
-        <v>1498.790527777778</v>
+        <v>1504.444513513514</v>
       </c>
       <c r="J8" t="n">
-        <v>114.9947400564755</v>
+        <v>119.9034705024823</v>
       </c>
       <c r="K8" t="n">
-        <v>110.7471958471358</v>
+        <v>115.5299617820473</v>
       </c>
       <c r="L8" t="n">
-        <v>4.247544209339688</v>
+        <v>4.37350872043504</v>
       </c>
       <c r="M8" t="n">
-        <v>111.196728777161</v>
+        <v>123.9577726902272</v>
       </c>
       <c r="N8" t="n">
-        <v>112.1659150925616</v>
+        <v>115.1631605208729</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9691863154006422</v>
+        <v>8.794612169354288</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5597987380413881</v>
+        <v>0.5759469052135504</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1249943522007503</v>
+        <v>0.1099738907185844</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2610747023556211</v>
+        <v>0.2340478148113104</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5465412882623248</v>
+        <v>0.5972293103528855</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2887970325747766</v>
+        <v>0.3052834906225837</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4171213995273137</v>
+        <v>0.4080461721307113</v>
       </c>
       <c r="V8" t="n">
-        <v>103.1068013468014</v>
+        <v>101.3713513513513</v>
       </c>
       <c r="W8" t="n">
-        <v>118.1346801346801</v>
+        <v>121.4949324324324</v>
       </c>
       <c r="X8" t="n">
-        <v>3.804713804713805</v>
+        <v>4.44527027027027</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5928568149437025</v>
+        <v>0.6157894090930578</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.6</v>
+        <v>128.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.4299999999999999</v>
+        <v>8.520000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.250350764022217</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC8" t="n">
-        <v>114.1383305986051</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD8" t="n">
-        <v>109.8879798345829</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2359474132550116</v>
+        <v>1.65884988653151</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1369,91 +1369,91 @@
         <v>46106</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>1647.27</v>
+        <v>1579.316</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6692</v>
+        <v>-2.4482</v>
       </c>
       <c r="I9" t="n">
-        <v>1489.691555555556</v>
+        <v>1498.790527777778</v>
       </c>
       <c r="J9" t="n">
-        <v>116.5250500726224</v>
+        <v>114.9947400564755</v>
       </c>
       <c r="K9" t="n">
-        <v>112.6994946632939</v>
+        <v>110.7471958471358</v>
       </c>
       <c r="L9" t="n">
-        <v>3.82555540932849</v>
+        <v>4.247544209339688</v>
       </c>
       <c r="M9" t="n">
-        <v>120.1151737145579</v>
+        <v>111.196728777161</v>
       </c>
       <c r="N9" t="n">
-        <v>117.2619092348234</v>
+        <v>112.1659150925616</v>
       </c>
       <c r="O9" t="n">
-        <v>2.853264479734493</v>
+        <v>-0.9691863154006422</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5590389603124643</v>
+        <v>0.5597987380413881</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1172615642326015</v>
+        <v>0.1249943522007503</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2644418904790862</v>
+        <v>0.2610747023556211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5704942636979263</v>
+        <v>0.5465412882623248</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2667157468069255</v>
+        <v>0.2887970325747766</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4448604255118168</v>
+        <v>0.4171213995273137</v>
       </c>
       <c r="V9" t="n">
-        <v>102.0978378378378</v>
+        <v>103.1068013468014</v>
       </c>
       <c r="W9" t="n">
-        <v>118.7702702702702</v>
+        <v>118.1346801346801</v>
       </c>
       <c r="X9" t="n">
-        <v>3.716216216216216</v>
+        <v>3.804713804713805</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5926889621431041</v>
+        <v>0.5928568149437025</v>
       </c>
       <c r="Z9" t="n">
-        <v>117.49</v>
+        <v>113.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>-0.4299999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.967224035556209</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC9" t="n">
-        <v>120.0962116764131</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD9" t="n">
-        <v>110.1289876408569</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.691733665586856</v>
+        <v>-0.1340578309374893</v>
       </c>
     </row>
     <row r="10">
@@ -1471,76 +1471,76 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>1575.02</v>
+        <v>1571.955</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6455</v>
+        <v>-2.115</v>
       </c>
       <c r="I10" t="n">
-        <v>1497.89823943662</v>
+        <v>1499.029041666667</v>
       </c>
       <c r="J10" t="n">
-        <v>114.5081402177387</v>
+        <v>114.9323361639937</v>
       </c>
       <c r="K10" t="n">
-        <v>110.9840662922424</v>
+        <v>111.2556119534676</v>
       </c>
       <c r="L10" t="n">
-        <v>3.524073925496332</v>
+        <v>3.676724210526132</v>
       </c>
       <c r="M10" t="n">
-        <v>110.2315068362509</v>
+        <v>112.0302305875271</v>
       </c>
       <c r="N10" t="n">
-        <v>115.3463986822449</v>
+        <v>116.5634740813627</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.114891845994104</v>
+        <v>-4.533243493835618</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5397833453443341</v>
+        <v>0.5410913763796836</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1301250193768773</v>
+        <v>0.1292976350608657</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3456255813831912</v>
+        <v>0.3486366200960201</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5391079959108015</v>
+        <v>0.5367883864031614</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2642288216034025</v>
+        <v>0.2645569099514823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3456852676299191</v>
+        <v>0.3464841714782828</v>
       </c>
       <c r="V10" t="n">
-        <v>99.55902688860435</v>
+        <v>99.32436403508771</v>
       </c>
       <c r="W10" t="n">
-        <v>113.9684165599659</v>
+        <v>114.1991959064327</v>
       </c>
       <c r="X10" t="n">
-        <v>3.736235595390525</v>
+        <v>3.995614035087719</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.573471010969931</v>
+        <v>0.5742658756874466</v>
       </c>
       <c r="Z10" t="n">
-        <v>110.79</v>
+        <v>112.07</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.71</v>
+        <v>-3.32</v>
       </c>
       <c r="AB10" t="n">
         <v>3.413694058608522</v>
@@ -1561,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1743618164237429</v>
+        <v>0.1943255441053384</v>
       </c>
     </row>
     <row r="11">
@@ -1669,103 +1669,103 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1941612024610394</v>
+        <v>0.2132560386697264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>1531.564</v>
+        <v>1561.924</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4609</v>
+        <v>4.0758</v>
       </c>
       <c r="I12" t="n">
-        <v>1504.285833333333</v>
+        <v>1496.091753424658</v>
       </c>
       <c r="J12" t="n">
-        <v>113.7311431173802</v>
+        <v>116.6976450061723</v>
       </c>
       <c r="K12" t="n">
-        <v>110.9652149369016</v>
+        <v>114.1356646171615</v>
       </c>
       <c r="L12" t="n">
-        <v>2.76592818047858</v>
+        <v>2.561980389010774</v>
       </c>
       <c r="M12" t="n">
-        <v>117.5980674011579</v>
+        <v>120.9895837814511</v>
       </c>
       <c r="N12" t="n">
-        <v>115.6839366586612</v>
+        <v>110.7663997945813</v>
       </c>
       <c r="O12" t="n">
-        <v>1.914130742496657</v>
+        <v>10.2231839868698</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5383662577126558</v>
+        <v>0.5728718935793922</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1130664434951674</v>
+        <v>0.1250048049620333</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2504140221540508</v>
+        <v>0.2384006964565819</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5450276515356729</v>
+        <v>0.5794717358649966</v>
       </c>
       <c r="T12" t="n">
-        <v>0.271398840497824</v>
+        <v>0.3256080969081872</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4052222903025458</v>
+        <v>0.398792188873006</v>
       </c>
       <c r="V12" t="n">
-        <v>105.6261904761905</v>
+        <v>100.3109648600358</v>
       </c>
       <c r="W12" t="n">
-        <v>120.1753968253969</v>
+        <v>116.6298391899941</v>
       </c>
       <c r="X12" t="n">
-        <v>3.116666666666667</v>
+        <v>1.857057772483622</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5766628789699688</v>
+        <v>0.6091767095408253</v>
       </c>
       <c r="Z12" t="n">
-        <v>121.71</v>
+        <v>120.41</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.094669144490311</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC12" t="n">
-        <v>111.6804548463295</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD12" t="n">
-        <v>112.7751239908198</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3603530881851182</v>
+        <v>1.601220497313665</v>
       </c>
     </row>
     <row r="13">
@@ -1795,76 +1795,76 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>1550.449</v>
+        <v>1555.704</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8964</v>
+        <v>-1.2948</v>
       </c>
       <c r="I13" t="n">
-        <v>1499.719291666667</v>
+        <v>1499.864205479452</v>
       </c>
       <c r="J13" t="n">
-        <v>116.0594839796474</v>
+        <v>115.757475555234</v>
       </c>
       <c r="K13" t="n">
-        <v>113.4927422178393</v>
+        <v>113.5243794173386</v>
       </c>
       <c r="L13" t="n">
-        <v>2.566741761808119</v>
+        <v>2.233096137895396</v>
       </c>
       <c r="M13" t="n">
-        <v>122.6048180628484</v>
+        <v>121.4178935735819</v>
       </c>
       <c r="N13" t="n">
-        <v>114.110263470885</v>
+        <v>113.4128181862122</v>
       </c>
       <c r="O13" t="n">
-        <v>8.494554591963418</v>
+        <v>8.005075387369581</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5614500059833608</v>
+        <v>0.5587874319807177</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1254986889428335</v>
+        <v>0.1247320876483693</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2347284689840954</v>
+        <v>0.2371794664509569</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5901492367491442</v>
+        <v>0.5863357204889815</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3032474363324933</v>
+        <v>0.302649882366875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4054571589269671</v>
+        <v>0.403575967340675</v>
       </c>
       <c r="V13" t="n">
-        <v>98.67018970189702</v>
+        <v>98.85970835174547</v>
       </c>
       <c r="W13" t="n">
-        <v>113.8780487804878</v>
+        <v>113.8276623950508</v>
       </c>
       <c r="X13" t="n">
-        <v>1.585365853658537</v>
+        <v>1.318161732213875</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6053765220982654</v>
+        <v>0.6024951053323064</v>
       </c>
       <c r="Z13" t="n">
-        <v>121.7</v>
+        <v>120.84</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.27</v>
+        <v>6.85</v>
       </c>
       <c r="AB13" t="n">
         <v>4.815266446541752</v>
@@ -1882,106 +1882,106 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.057272164254637</v>
+        <v>1.059042204605437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612747</v>
+        <v>1610612748</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>1560.408</v>
+        <v>1541.118</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9923</v>
+        <v>-2.3788</v>
       </c>
       <c r="I14" t="n">
-        <v>1498.311388888889</v>
+        <v>1506.244520547945</v>
       </c>
       <c r="J14" t="n">
-        <v>116.6602495758146</v>
+        <v>113.6744770063884</v>
       </c>
       <c r="K14" t="n">
-        <v>114.6082226687074</v>
+        <v>111.6215649076278</v>
       </c>
       <c r="L14" t="n">
-        <v>2.05202690710708</v>
+        <v>2.052912098760554</v>
       </c>
       <c r="M14" t="n">
-        <v>121.4787552661077</v>
+        <v>116.869811919753</v>
       </c>
       <c r="N14" t="n">
-        <v>112.6611401571135</v>
+        <v>118.1426582706718</v>
       </c>
       <c r="O14" t="n">
-        <v>8.817615108994094</v>
+        <v>-1.272846350918792</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5721434326640716</v>
+        <v>0.5365638327515762</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1248167872560072</v>
+        <v>0.1128644300413538</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2392673504996769</v>
+        <v>0.2513092669920794</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5800995330512867</v>
+        <v>0.5390060805141018</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3200507259875529</v>
+        <v>0.2753466778627371</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3984966982904639</v>
+        <v>0.4056929191681111</v>
       </c>
       <c r="V14" t="n">
-        <v>100.3966913580247</v>
+        <v>105.8955572010367</v>
       </c>
       <c r="W14" t="n">
-        <v>116.8197530864198</v>
+        <v>120.3894853757867</v>
       </c>
       <c r="X14" t="n">
-        <v>1.567901234567901</v>
+        <v>2.258052573121066</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6085856308650595</v>
+        <v>0.5758687776277032</v>
       </c>
       <c r="Z14" t="n">
-        <v>121.7</v>
+        <v>121.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.36</v>
+        <v>-2.46</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.827913300592181</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC14" t="n">
-        <v>114.1496737878887</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD14" t="n">
-        <v>112.3217604872965</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -1990,106 +1990,106 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.394873520626598</v>
+        <v>0.3722216951168086</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>1511.376</v>
+        <v>1505.042</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6406</v>
+        <v>0.7107</v>
       </c>
       <c r="I15" t="n">
-        <v>1480.827708333333</v>
+        <v>1496.795430555555</v>
       </c>
       <c r="J15" t="n">
-        <v>113.7766280849965</v>
+        <v>113.0784774599792</v>
       </c>
       <c r="K15" t="n">
-        <v>112.2400374758675</v>
+        <v>111.5605635885357</v>
       </c>
       <c r="L15" t="n">
-        <v>1.53659060912899</v>
+        <v>1.517913871443526</v>
       </c>
       <c r="M15" t="n">
-        <v>120.4109026661776</v>
+        <v>115.8694895112704</v>
       </c>
       <c r="N15" t="n">
-        <v>108.7814087274484</v>
+        <v>114.700895172135</v>
       </c>
       <c r="O15" t="n">
-        <v>11.62949393872914</v>
+        <v>1.168594339135413</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5536188819862715</v>
+        <v>0.542778232132711</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.117861930427064</v>
+        <v>0.1160961101089527</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2419422373926377</v>
+        <v>0.2550216234867304</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5797035167134733</v>
+        <v>0.5662527341443399</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2363897912998568</v>
+        <v>0.2593964848600521</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4292289238933412</v>
+        <v>0.3691890880194976</v>
       </c>
       <c r="V15" t="n">
-        <v>104.1380317460317</v>
+        <v>100.7830147058824</v>
       </c>
       <c r="W15" t="n">
-        <v>118.5857142857143</v>
+        <v>114.0661764705883</v>
       </c>
       <c r="X15" t="n">
-        <v>1.836507936507936</v>
+        <v>1.865196078431373</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5842230457083195</v>
+        <v>0.5768109034513951</v>
       </c>
       <c r="Z15" t="n">
-        <v>124.24</v>
+        <v>116.48</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.07</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.981113782848854</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC15" t="n">
-        <v>112.8029837792552</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD15" t="n">
-        <v>113.7840975621041</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2101,103 +2101,103 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.9095322765413298</v>
+        <v>0.2056760553801436</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612756</v>
+        <v>1610612737</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>1507.624</v>
+        <v>1517.636</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2525</v>
+        <v>2.7214</v>
       </c>
       <c r="I16" t="n">
-        <v>1516.454152777778</v>
+        <v>1483.556287671233</v>
       </c>
       <c r="J16" t="n">
-        <v>113.2866827538334</v>
+        <v>113.7139460188449</v>
       </c>
       <c r="K16" t="n">
-        <v>112.1392926130768</v>
+        <v>112.3045211289271</v>
       </c>
       <c r="L16" t="n">
-        <v>1.147390140756679</v>
+        <v>1.409424889917866</v>
       </c>
       <c r="M16" t="n">
-        <v>118.7196042868246</v>
+        <v>118.5112879467137</v>
       </c>
       <c r="N16" t="n">
-        <v>115.5101813717958</v>
+        <v>108.9190604057888</v>
       </c>
       <c r="O16" t="n">
-        <v>3.209422915028772</v>
+        <v>9.592227540924936</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5386739885194024</v>
+        <v>0.5513675640902436</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1182585643998592</v>
+        <v>0.1151892768060538</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2845045285103836</v>
+        <v>0.2387912329679008</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5549428707731872</v>
+        <v>0.5630899663458</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2310536443479878</v>
+        <v>0.2385949493518496</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4569015087700092</v>
+        <v>0.4297333167391637</v>
       </c>
       <c r="V16" t="n">
-        <v>99.40384469696968</v>
+        <v>103.6870319634703</v>
       </c>
       <c r="W16" t="n">
-        <v>112.4807449494949</v>
+        <v>117.955098934551</v>
       </c>
       <c r="X16" t="n">
-        <v>1.176136363636364</v>
+        <v>1.603500761035008</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5706535010178025</v>
+        <v>0.582610014607143</v>
       </c>
       <c r="Z16" t="n">
-        <v>114.63</v>
+        <v>121.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.95</v>
+        <v>9.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.375203171419814</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC16" t="n">
-        <v>114.7034977739938</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD16" t="n">
-        <v>117.0787009454136</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2209,103 +2209,103 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.09333083023374253</v>
+        <v>0.8974958594980356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>1523.417</v>
+        <v>1507.624</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9164</v>
+        <v>-0.2525</v>
       </c>
       <c r="I17" t="n">
-        <v>1492.514652173913</v>
+        <v>1516.454152777778</v>
       </c>
       <c r="J17" t="n">
-        <v>113.4568142054788</v>
+        <v>113.2866827538334</v>
       </c>
       <c r="K17" t="n">
-        <v>112.8190945895778</v>
+        <v>112.1392926130768</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6377196159009948</v>
+        <v>1.147390140756679</v>
       </c>
       <c r="M17" t="n">
-        <v>117.545021261121</v>
+        <v>118.7196042868246</v>
       </c>
       <c r="N17" t="n">
-        <v>119.2147304854601</v>
+        <v>115.5101813717958</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.669709224339038</v>
+        <v>3.209422915028772</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5350509465278205</v>
+        <v>0.5386739885194024</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1151056882291826</v>
+        <v>0.1182585643998592</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2453037725407861</v>
+        <v>0.2845045285103836</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5540849780805727</v>
+        <v>0.5549428707731872</v>
       </c>
       <c r="T17" t="n">
-        <v>0.315402177160877</v>
+        <v>0.2310536443479878</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3882862478687213</v>
+        <v>0.4569015087700092</v>
       </c>
       <c r="V17" t="n">
-        <v>101.9763812033377</v>
+        <v>99.40384469696968</v>
       </c>
       <c r="W17" t="n">
-        <v>115.8142292490119</v>
+        <v>112.4807449494949</v>
       </c>
       <c r="X17" t="n">
-        <v>1.31576635924462</v>
+        <v>1.176136363636364</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5804581042604025</v>
+        <v>0.5706535010178025</v>
       </c>
       <c r="Z17" t="n">
-        <v>120.73</v>
+        <v>114.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>2.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC17" t="n">
-        <v>107.6152962364644</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD17" t="n">
-        <v>108.1384073962044</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -2317,103 +2317,103 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.4507056235110719</v>
+        <v>-0.04236815355659389</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>1510.298</v>
+        <v>1523.417</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1304</v>
+        <v>-1.9164</v>
       </c>
       <c r="I18" t="n">
-        <v>1496.039746478873</v>
+        <v>1492.514652173913</v>
       </c>
       <c r="J18" t="n">
-        <v>112.6678395395337</v>
+        <v>113.4568142054788</v>
       </c>
       <c r="K18" t="n">
-        <v>112.0712437861321</v>
+        <v>112.8190945895778</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5965957534014882</v>
+        <v>0.6377196159009948</v>
       </c>
       <c r="M18" t="n">
-        <v>115.2326549049742</v>
+        <v>117.545021261121</v>
       </c>
       <c r="N18" t="n">
-        <v>116.2513101342109</v>
+        <v>119.2147304854601</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.018655229236692</v>
+        <v>-1.669709224339038</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5407380408991779</v>
+        <v>0.5350509465278205</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1158598294236353</v>
+        <v>0.1151056882291826</v>
       </c>
       <c r="R18" t="n">
-        <v>0.25355135622668</v>
+        <v>0.2453037725407861</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5632883362301022</v>
+        <v>0.5540849780805727</v>
       </c>
       <c r="T18" t="n">
-        <v>0.258948205539726</v>
+        <v>0.315402177160877</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3701017890782413</v>
+        <v>0.3882862478687213</v>
       </c>
       <c r="V18" t="n">
-        <v>100.6615877080666</v>
+        <v>101.9763812033377</v>
       </c>
       <c r="W18" t="n">
-        <v>113.5851472471191</v>
+        <v>115.8142292490119</v>
       </c>
       <c r="X18" t="n">
-        <v>1.086214255228339</v>
+        <v>1.31576635924462</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5745874533393589</v>
+        <v>0.5804581042604025</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.15</v>
+        <v>120.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.4699999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.536933640611859</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC18" t="n">
-        <v>108.3888858603967</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD18" t="n">
-        <v>112.9258195010085</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.268634898800129</v>
+        <v>-0.4035434178065982</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3826633605069894</v>
+        <v>-0.3384582629938973</v>
       </c>
     </row>
     <row r="20">
@@ -2551,76 +2551,76 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>1479.562</v>
+        <v>1480.385</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6566</v>
+        <v>-1.9923</v>
       </c>
       <c r="I20" t="n">
-        <v>1508.360041666667</v>
+        <v>1505.423397260274</v>
       </c>
       <c r="J20" t="n">
-        <v>112.4016856116114</v>
+        <v>112.9272243241923</v>
       </c>
       <c r="K20" t="n">
-        <v>112.3499792560339</v>
+        <v>112.6736155412076</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05170635557735945</v>
+        <v>0.2536087829846333</v>
       </c>
       <c r="M20" t="n">
-        <v>109.6855564088347</v>
+        <v>112.00648753696</v>
       </c>
       <c r="N20" t="n">
-        <v>115.7327696649611</v>
+        <v>116.8555593943861</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.047213256126416</v>
+        <v>-4.849071857425976</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5512942038959984</v>
+        <v>0.5527456657835074</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1348382300776007</v>
+        <v>0.1326078050536529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.25910302554522</v>
+        <v>0.2577790755092829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5366643384778743</v>
+        <v>0.5496723598682487</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2439478398473092</v>
+        <v>0.242959173474206</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5000390599561023</v>
+        <v>0.5020489910994771</v>
       </c>
       <c r="V20" t="n">
-        <v>102.118253968254</v>
+        <v>102.1573047019622</v>
       </c>
       <c r="W20" t="n">
-        <v>114.8825396825397</v>
+        <v>115.4057756386523</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2611111111111112</v>
+        <v>0.3483894853757867</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5854180507076207</v>
+        <v>0.5865799680524209</v>
       </c>
       <c r="Z20" t="n">
-        <v>112.87</v>
+        <v>116.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.64</v>
+        <v>-4.539999999999999</v>
       </c>
       <c r="AB20" t="n">
         <v>2.402868486532558</v>
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.3901946944541106</v>
+        <v>-0.1879001004883992</v>
       </c>
     </row>
     <row r="21">
@@ -2659,76 +2659,76 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>1460.365</v>
+        <v>1464.524</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0113</v>
+        <v>1.319</v>
       </c>
       <c r="I21" t="n">
-        <v>1509.740164383562</v>
+        <v>1508.2545</v>
       </c>
       <c r="J21" t="n">
-        <v>111.5535802956328</v>
+        <v>110.6928115814477</v>
       </c>
       <c r="K21" t="n">
-        <v>112.8552661388475</v>
+        <v>112.5839096652461</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.301685843214741</v>
+        <v>-1.891098083798451</v>
       </c>
       <c r="M21" t="n">
-        <v>113.9656626732359</v>
+        <v>112.4840355392312</v>
       </c>
       <c r="N21" t="n">
-        <v>105.384268953207</v>
+        <v>104.5944809462976</v>
       </c>
       <c r="O21" t="n">
-        <v>8.581393720028856</v>
+        <v>7.889554592933586</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5351566194002902</v>
+        <v>0.5311314223553073</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.14146778552269</v>
+        <v>0.1427629640290994</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3119467028213384</v>
+        <v>0.3107058577485636</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5527888895563711</v>
+        <v>0.5483660303982195</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2872839572269039</v>
+        <v>0.2892164197846558</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4695664165631555</v>
+        <v>0.4664916923112503</v>
       </c>
       <c r="V21" t="n">
-        <v>103.5102258422807</v>
+        <v>103.5651801801802</v>
       </c>
       <c r="W21" t="n">
-        <v>115.7386153276565</v>
+        <v>114.9144144144144</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7615697889670491</v>
+        <v>-1.363738738738739</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5720669835831984</v>
+        <v>0.5684266943899089</v>
       </c>
       <c r="Z21" t="n">
-        <v>116.77</v>
+        <v>115.86</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.949999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="AB21" t="n">
         <v>-3.840928550668963</v>
@@ -2749,211 +2749,211 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.09089318639930394</v>
+        <v>-0.3350589512210745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>1385.239</v>
+        <v>1381.942</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0027</v>
+        <v>2.2995</v>
       </c>
       <c r="I22" t="n">
-        <v>1493.792492957747</v>
+        <v>1508.055432432432</v>
       </c>
       <c r="J22" t="n">
-        <v>111.9903979357038</v>
+        <v>112.1449809261782</v>
       </c>
       <c r="K22" t="n">
-        <v>115.8540815857431</v>
+        <v>116.1627917910209</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.863683650039318</v>
+        <v>-4.017810864842693</v>
       </c>
       <c r="M22" t="n">
-        <v>111.8073657100563</v>
+        <v>115.3883803591507</v>
       </c>
       <c r="N22" t="n">
-        <v>116.8541814037627</v>
+        <v>114.2484261927667</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.046815693706469</v>
+        <v>1.139954166384094</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5506914637643898</v>
+        <v>0.5274461080296675</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1259387511251726</v>
+        <v>0.1169953406743485</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2287348820757405</v>
+        <v>0.2696736446660632</v>
       </c>
       <c r="S22" t="n">
-        <v>0.548582211747871</v>
+        <v>0.5440000808017124</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2443769693842713</v>
+        <v>0.2827323387604225</v>
       </c>
       <c r="U22" t="n">
-        <v>0.446817279743916</v>
+        <v>0.3590735779800531</v>
       </c>
       <c r="V22" t="n">
-        <v>104.413255086072</v>
+        <v>102.7059295659296</v>
       </c>
       <c r="W22" t="n">
-        <v>116.6107198748044</v>
+        <v>115.0941850941851</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.677230046948357</v>
+        <v>-4.207207207207206</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5832337617466857</v>
+        <v>0.5675831110895945</v>
       </c>
       <c r="Z22" t="n">
-        <v>119.36</v>
+        <v>115.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.9433805425336231</v>
+        <v>-9.447870926461551</v>
       </c>
       <c r="AC22" t="n">
-        <v>112.5644270515903</v>
+        <v>108.3910194524218</v>
       </c>
       <c r="AD22" t="n">
-        <v>113.5078075941239</v>
+        <v>117.8388903788833</v>
       </c>
       <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.274885794639634</v>
+        <v>0.03365146501574459</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612740</v>
+        <v>1610612741</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>1383.419</v>
+        <v>1382.431</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5076</v>
+        <v>-0.4371</v>
       </c>
       <c r="I23" t="n">
-        <v>1505.785589041096</v>
+        <v>1493.417138888889</v>
       </c>
       <c r="J23" t="n">
-        <v>112.2958640990509</v>
+        <v>111.6418790940612</v>
       </c>
       <c r="K23" t="n">
-        <v>116.1987057338638</v>
+        <v>115.6910715927458</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.902841634812923</v>
+        <v>-4.049192498684509</v>
       </c>
       <c r="M23" t="n">
-        <v>117.2285993147765</v>
+        <v>111.9028653490087</v>
       </c>
       <c r="N23" t="n">
-        <v>114.1274500933177</v>
+        <v>117.741719892843</v>
       </c>
       <c r="O23" t="n">
-        <v>3.101149221458858</v>
+        <v>-5.838854543834226</v>
       </c>
       <c r="P23" t="n">
-        <v>0.529425236519333</v>
+        <v>0.5488803871956238</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1172635260041805</v>
+        <v>0.1255161420502698</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2687259888794437</v>
+        <v>0.2277478563889072</v>
       </c>
       <c r="S23" t="n">
-        <v>0.553916623310057</v>
+        <v>0.5449087423601159</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2828116351150145</v>
+        <v>0.2425187355317611</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3597480948558597</v>
+        <v>0.4472988650711273</v>
       </c>
       <c r="V23" t="n">
-        <v>102.7634383561644</v>
+        <v>104.4028888888889</v>
       </c>
       <c r="W23" t="n">
-        <v>115.2924657534247</v>
+        <v>116.2246031746031</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.131164383561644</v>
+        <v>-4.845238095238095</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5687211557574223</v>
+        <v>0.5812018359599354</v>
       </c>
       <c r="Z23" t="n">
-        <v>118.26</v>
+        <v>119.57</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.839999999999999</v>
+        <v>-6.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>-9.447870926461551</v>
+        <v>-0.9433805425336231</v>
       </c>
       <c r="AC23" t="n">
-        <v>108.3910194524218</v>
+        <v>112.5644270515903</v>
       </c>
       <c r="AD23" t="n">
-        <v>117.8388903788833</v>
+        <v>113.5078075941239</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.003835387551012206</v>
+        <v>-0.2856044123176633</v>
       </c>
     </row>
     <row r="24">
@@ -2983,76 +2983,76 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>1387.267</v>
+        <v>1384.612</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0318</v>
+        <v>-1.9168</v>
       </c>
       <c r="I24" t="n">
-        <v>1492.156739130435</v>
+        <v>1495.537657142857</v>
       </c>
       <c r="J24" t="n">
-        <v>110.1850361530908</v>
+        <v>110.6526478669424</v>
       </c>
       <c r="K24" t="n">
-        <v>115.6136673111742</v>
+        <v>115.5740353629901</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.428631158083402</v>
+        <v>-4.921387496047651</v>
       </c>
       <c r="M24" t="n">
-        <v>108.1227798172251</v>
+        <v>107.9081849502933</v>
       </c>
       <c r="N24" t="n">
-        <v>124.3346594522542</v>
+        <v>124.3312116376382</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.21187963502906</v>
+        <v>-16.42302668734481</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5328556870653992</v>
+        <v>0.5334395940242856</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1263135833008181</v>
+        <v>0.1260460171490826</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2464948354270139</v>
+        <v>0.2518239203004887</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5226552280287723</v>
+        <v>0.5171462702664064</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2585946150139702</v>
+        <v>0.2578202452673223</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4351180897508055</v>
+        <v>0.4308624276867906</v>
       </c>
       <c r="V24" t="n">
-        <v>103.6906688963211</v>
+        <v>103.5755348837209</v>
       </c>
       <c r="W24" t="n">
-        <v>114.5830546265329</v>
+        <v>114.8604651162791</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.779821627647714</v>
+        <v>-4.404651162790698</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5698821067033008</v>
+        <v>0.5707435224243221</v>
       </c>
       <c r="Z24" t="n">
-        <v>112.22</v>
+        <v>111.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>-14.47</v>
+        <v>-14.95</v>
       </c>
       <c r="AB24" t="n">
         <v>3.575252351995317</v>
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.6885220239430159</v>
+        <v>-0.6310050627876439</v>
       </c>
     </row>
     <row r="25">
@@ -3091,76 +3091,76 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>1369.103</v>
+        <v>1368.156</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0388</v>
+        <v>-0.9866</v>
       </c>
       <c r="I25" t="n">
-        <v>1504.098732394366</v>
+        <v>1505.346541666667</v>
       </c>
       <c r="J25" t="n">
-        <v>109.4007429319452</v>
+        <v>108.7575417537635</v>
       </c>
       <c r="K25" t="n">
-        <v>114.834424386505</v>
+        <v>113.8564584325441</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.433681454559837</v>
+        <v>-5.098916678780511</v>
       </c>
       <c r="M25" t="n">
-        <v>112.3564516629817</v>
+        <v>111.7044445975594</v>
       </c>
       <c r="N25" t="n">
-        <v>122.6096091495137</v>
+        <v>119.4073442750946</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.25315748653201</v>
+        <v>-7.702899677535243</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5318731874415529</v>
+        <v>0.5302917364839623</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1222468582163301</v>
+        <v>0.1244402321725155</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2299398210704469</v>
+        <v>0.2288054958013864</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5384280135748686</v>
+        <v>0.5380780482675814</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2871971453232432</v>
+        <v>0.2884597729835739</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3487639761678349</v>
+        <v>0.3471582529969384</v>
       </c>
       <c r="V25" t="n">
-        <v>104.460985915493</v>
+        <v>104.422972972973</v>
       </c>
       <c r="W25" t="n">
-        <v>114.4262634631317</v>
+        <v>113.7162162162162</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.195526097763048</v>
+        <v>-4.837837837837838</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5675214962834676</v>
+        <v>0.5659782028322644</v>
       </c>
       <c r="Z25" t="n">
-        <v>117.18</v>
+        <v>116.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>-11.77</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AB25" t="n">
         <v>-0.6658146557452705</v>
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.9357308553541782</v>
+        <v>-0.9121617738900951</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.024093335741741</v>
+        <v>-0.9519746727516605</v>
       </c>
     </row>
     <row r="27">
@@ -3307,76 +3307,76 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>1313.813</v>
+        <v>1310.366</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3628</v>
+        <v>-0.5698</v>
       </c>
       <c r="I27" t="n">
-        <v>1512.485013888889</v>
+        <v>1508.98601369863</v>
       </c>
       <c r="J27" t="n">
-        <v>111.8228396286655</v>
+        <v>112.2907379787998</v>
       </c>
       <c r="K27" t="n">
-        <v>119.7472978978662</v>
+        <v>119.8611191829545</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.924458269200658</v>
+        <v>-7.570381204154772</v>
       </c>
       <c r="M27" t="n">
-        <v>112.4324163677347</v>
+        <v>112.1026735628848</v>
       </c>
       <c r="N27" t="n">
-        <v>119.1860134813122</v>
+        <v>119.8612157260471</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.753597113577465</v>
+        <v>-7.758542163162284</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5368610793724036</v>
+        <v>0.5390833228243055</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1290389784749056</v>
+        <v>0.1281425351784173</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2620859576812637</v>
+        <v>0.2613504445840236</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5328649370079155</v>
+        <v>0.5350239520727516</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2868486658469708</v>
+        <v>0.2849157283425882</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4107691561399344</v>
+        <v>0.4105503824494048</v>
       </c>
       <c r="V27" t="n">
-        <v>104.7843243243244</v>
+        <v>104.7554722422495</v>
       </c>
       <c r="W27" t="n">
-        <v>117.2432432432432</v>
+        <v>117.6492429704399</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.04054054054054</v>
+        <v>-7.787310742609949</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5771779405704833</v>
+        <v>0.5792533823930115</v>
       </c>
       <c r="Z27" t="n">
-        <v>115.76</v>
+        <v>116.58</v>
       </c>
       <c r="AA27" t="n">
-        <v>-7.97</v>
+        <v>-9.24</v>
       </c>
       <c r="AB27" t="n">
         <v>-9.725925288085115</v>
@@ -3394,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.303671223879549</v>
+        <v>-1.267419674780598</v>
       </c>
     </row>
     <row r="28">
@@ -3415,76 +3415,76 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>1336.278</v>
+        <v>1334.762</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.8419</v>
+        <v>-1.3404</v>
       </c>
       <c r="I28" t="n">
-        <v>1500.614597222222</v>
+        <v>1501.433684931507</v>
       </c>
       <c r="J28" t="n">
-        <v>109.0999836776447</v>
+        <v>108.9414065061395</v>
       </c>
       <c r="K28" t="n">
-        <v>117.2588395297681</v>
+        <v>116.9592428870239</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.158855852123363</v>
+        <v>-8.017836380884376</v>
       </c>
       <c r="M28" t="n">
-        <v>114.4240416195474</v>
+        <v>113.9720100132994</v>
       </c>
       <c r="N28" t="n">
-        <v>124.5209008468359</v>
+        <v>122.9634590983539</v>
       </c>
       <c r="O28" t="n">
-        <v>-10.09685922728855</v>
+        <v>-8.991449085054599</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5318534897029034</v>
+        <v>0.5315300979455618</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1215149275710593</v>
+        <v>0.1225037289322189</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2142279869298917</v>
+        <v>0.2164939170842621</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5657971022024827</v>
+        <v>0.5719877966037397</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2602516704807791</v>
+        <v>0.2576289386000791</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4198652868949841</v>
+        <v>0.419163014453595</v>
       </c>
       <c r="V28" t="n">
-        <v>103.1365441176471</v>
+        <v>103.038794520548</v>
       </c>
       <c r="W28" t="n">
-        <v>112.1789215686275</v>
+        <v>111.9221135029354</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.819852941176471</v>
+        <v>-8.625048923679062</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5677477915688206</v>
+        <v>0.5670668705856138</v>
       </c>
       <c r="Z28" t="n">
-        <v>115.24</v>
+        <v>114.71</v>
       </c>
       <c r="AA28" t="n">
-        <v>-11.32</v>
+        <v>-10.36</v>
       </c>
       <c r="AB28" t="n">
         <v>2.960186837728194</v>
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.331610154853832</v>
+        <v>-1.246101727693882</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.291958161684083</v>
+        <v>-1.561096374474905</v>
       </c>
     </row>
     <row r="30">
@@ -3631,76 +3631,76 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
-        <v>1293.985</v>
+        <v>1293.161</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.7457</v>
+        <v>-1.9172</v>
       </c>
       <c r="I30" t="n">
-        <v>1503.820680555556</v>
+        <v>1503.488369863014</v>
       </c>
       <c r="J30" t="n">
-        <v>106.9127555718554</v>
+        <v>106.6955098014094</v>
       </c>
       <c r="K30" t="n">
-        <v>116.8852230015424</v>
+        <v>117.1995442841559</v>
       </c>
       <c r="L30" t="n">
-        <v>-9.972467429686885</v>
+        <v>-10.50403448274647</v>
       </c>
       <c r="M30" t="n">
-        <v>102.8092604836777</v>
+        <v>101.5411790819853</v>
       </c>
       <c r="N30" t="n">
-        <v>114.3158035288785</v>
+        <v>115.9104954328633</v>
       </c>
       <c r="O30" t="n">
-        <v>-11.50654304520073</v>
+        <v>-14.3693163508779</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5227223592092914</v>
+        <v>0.5207768437008072</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1389781430316037</v>
+        <v>0.1381274414029926</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2395297460190133</v>
+        <v>0.2415353255029537</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5128529352023121</v>
+        <v>0.5091723796467565</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2777703390707948</v>
+        <v>0.2753334950170813</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4575665039212987</v>
+        <v>0.4574277322053578</v>
       </c>
       <c r="V30" t="n">
-        <v>99.23999999999999</v>
+        <v>99.19973239885314</v>
       </c>
       <c r="W30" t="n">
-        <v>106.2681992337165</v>
+        <v>106.1048104491876</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.249042145593869</v>
+        <v>-9.560688117234788</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5619783850989732</v>
+        <v>0.5595961460666637</v>
       </c>
       <c r="Z30" t="n">
-        <v>103.03</v>
+        <v>102.24</v>
       </c>
       <c r="AA30" t="n">
-        <v>-12.09</v>
+        <v>-13.94</v>
       </c>
       <c r="AB30" t="n">
         <v>-6.499587896466165</v>
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.132631132423297</v>
+        <v>-2.034044114399213</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.058</v>
+        <v>1260.505</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2368</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>1508.677492957746</v>
+        <v>1505.971041666667</v>
       </c>
       <c r="J31" t="n">
-        <v>108.9771388755179</v>
+        <v>109.0952966771024</v>
       </c>
       <c r="K31" t="n">
-        <v>119.4399000442245</v>
+        <v>119.9046698410049</v>
       </c>
       <c r="L31" t="n">
-        <v>-10.46276116870669</v>
+        <v>-10.80937316390264</v>
       </c>
       <c r="M31" t="n">
-        <v>110.6134314516703</v>
+        <v>110.7523453050666</v>
       </c>
       <c r="N31" t="n">
-        <v>122.9234911245336</v>
+        <v>123.1213169680927</v>
       </c>
       <c r="O31" t="n">
-        <v>-12.31005967286328</v>
+        <v>-12.36897166302604</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5365368233680265</v>
+        <v>0.5376406795018001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1336215182965959</v>
+        <v>0.1326161591191427</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2430990848903866</v>
+        <v>0.2394455899516614</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5664287021970412</v>
+        <v>0.5697131585022143</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2397897120353979</v>
+        <v>0.2362439240472753</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4056266946610693</v>
+        <v>0.4073054159682846</v>
       </c>
       <c r="V31" t="n">
-        <v>103.7952401589021</v>
+        <v>103.7179791666667</v>
       </c>
       <c r="W31" t="n">
-        <v>113.032502708559</v>
+        <v>113.121875</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.71830985915493</v>
+        <v>-10.971875</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5681919652381541</v>
+        <v>0.569034840958254</v>
       </c>
       <c r="Z31" t="n">
-        <v>116.17</v>
+        <v>117.36</v>
       </c>
       <c r="AA31" t="n">
-        <v>-12.37</v>
+        <v>-12.2</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3820,7 +3820,7 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.475752388282609</v>
+        <v>-1.462580266283221</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.396692468264619</v>
+        <v>1.402342048796811</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9534985895770764</v>
+        <v>0.9613787528032571</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.06850425160578996</v>
+        <v>-0.05548037597658636</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9808527620454571</v>
+        <v>0.9885952524682656</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6494428255448071</v>
+        <v>0.6588532931318379</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.645653156320357</v>
+        <v>1.650049724505211</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65884988653151</v>
+        <v>1.66318003593343</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1340578309374893</v>
+        <v>-0.1207040259328637</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1943255441053384</v>
+        <v>0.2060266045469457</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2132560386697264</v>
+        <v>0.224861822448919</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.601220497313665</v>
+        <v>1.605840693858463</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.059042204605437</v>
+        <v>1.066391169698105</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.3722216951168086</v>
+        <v>0.3830274090862391</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.2056760553801436</v>
+        <v>0.217319989008329</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.8974958594980356</v>
+        <v>0.7881730209015466</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.04236815355659389</v>
+        <v>-0.02947582019545941</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.4035434178065982</v>
+        <v>-0.388833299199155</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3384582629938973</v>
+        <v>-0.3240757161940581</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1879001004883992</v>
+        <v>-0.1742753088108057</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.3350589512210745</v>
+        <v>-0.3206935130646001</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.03365146501574459</v>
+        <v>0.04616119371164053</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2856044123176633</v>
+        <v>-0.3139915333677319</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.6310050627876439</v>
+        <v>-0.6151501359298177</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.9121617738900951</v>
+        <v>-0.8948917929797605</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.9519746727516605</v>
+        <v>-1.154888664734465</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.267419674780598</v>
+        <v>-1.248361690552222</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.246101727693882</v>
+        <v>-1.227151036111298</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.561096374474905</v>
+        <v>-1.540560323433185</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.034044114399213</v>
+        <v>-2.011127730292063</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.462580266283221</v>
+        <v>-1.442540044124928</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.402342048796811</v>
+        <v>1.318249984659178</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>1728.821</v>
+        <v>1731.476</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8856</v>
+        <v>1.8711</v>
       </c>
       <c r="I3" t="n">
-        <v>1512.470591549296</v>
+        <v>1510.731652777778</v>
       </c>
       <c r="J3" t="n">
-        <v>117.3877812581318</v>
+        <v>117.5792874089684</v>
       </c>
       <c r="K3" t="n">
-        <v>108.9043843197315</v>
+        <v>108.7720490057709</v>
       </c>
       <c r="L3" t="n">
-        <v>8.483396938400279</v>
+        <v>8.807238403197507</v>
       </c>
       <c r="M3" t="n">
-        <v>124.0575328453496</v>
+        <v>124.9133382900033</v>
       </c>
       <c r="N3" t="n">
-        <v>110.014448718639</v>
+        <v>108.2880836103874</v>
       </c>
       <c r="O3" t="n">
-        <v>14.04308412671063</v>
+        <v>16.62525467961587</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5603876192810846</v>
+        <v>0.561650349722584</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1124661740932666</v>
+        <v>0.1119384336426832</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2578826853122713</v>
+        <v>0.2567219510165967</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5825975534783464</v>
+        <v>0.5878199071152477</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2805154394961951</v>
+        <v>0.2794218653484273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4259273397239809</v>
+        <v>0.4234726356287385</v>
       </c>
       <c r="V3" t="n">
-        <v>102.0246265471618</v>
+        <v>101.9468137254901</v>
       </c>
       <c r="W3" t="n">
-        <v>119.4489970123773</v>
+        <v>119.6127450980392</v>
       </c>
       <c r="X3" t="n">
-        <v>8.173708920187794</v>
+        <v>8.598039215686276</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5961811490629734</v>
+        <v>0.5972986693477695</v>
       </c>
       <c r="Z3" t="n">
-        <v>125.16</v>
+        <v>126.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.21</v>
+        <v>15.8</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -796,7 +796,7 @@
         <v>114.9918244005745</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9613787528032571</v>
+        <v>0.8924013092237099</v>
       </c>
     </row>
     <row r="4">
@@ -823,76 +823,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>1673.754</v>
+        <v>1675.231</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2338</v>
+        <v>-0.1345</v>
       </c>
       <c r="I4" t="n">
-        <v>1491.511126760563</v>
+        <v>1490.009847222222</v>
       </c>
       <c r="J4" t="n">
-        <v>114.9760603792054</v>
+        <v>114.7328777483964</v>
       </c>
       <c r="K4" t="n">
-        <v>107.7466008376071</v>
+        <v>107.1815778754609</v>
       </c>
       <c r="L4" t="n">
-        <v>7.229459541598239</v>
+        <v>7.551299872935456</v>
       </c>
       <c r="M4" t="n">
-        <v>120.8864718420659</v>
+        <v>120.6711111385838</v>
       </c>
       <c r="N4" t="n">
-        <v>109.3482686233348</v>
+        <v>106.2938922956714</v>
       </c>
       <c r="O4" t="n">
-        <v>11.53820321873111</v>
+        <v>14.3772188429124</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5458134423745101</v>
+        <v>0.545572739274102</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1224513214693638</v>
+        <v>0.1236188832626498</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3033694647116994</v>
+        <v>0.3037423859387597</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5717910382819438</v>
+        <v>0.5782982118830915</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2946597194465311</v>
+        <v>0.2924062974359234</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3476755456258619</v>
+        <v>0.3470148397348503</v>
       </c>
       <c r="V4" t="n">
-        <v>102.2082299200609</v>
+        <v>102.1006372549019</v>
       </c>
       <c r="W4" t="n">
-        <v>117.7217358203274</v>
+        <v>117.3174019607843</v>
       </c>
       <c r="X4" t="n">
-        <v>7.953939855348307</v>
+        <v>8.19607843137255</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5824674183157785</v>
+        <v>0.5819967496316072</v>
       </c>
       <c r="Z4" t="n">
-        <v>122.43</v>
+        <v>122.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.55</v>
+        <v>14.53</v>
       </c>
       <c r="AB4" t="n">
         <v>1.549391602834736</v>
@@ -904,16 +904,16 @@
         <v>110.9722985057385</v>
       </c>
       <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.05548037597658636</v>
+        <v>0.06143486571132148</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9885952524682656</v>
+        <v>0.8962673621316659</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6588532931318379</v>
+        <v>0.5950864322312313</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.650049724505211</v>
+        <v>1.559256439741149</v>
       </c>
     </row>
     <row r="8">
@@ -1345,223 +1345,223 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.66318003593343</v>
+        <v>1.572158489801168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>1579.316</v>
+        <v>1571.955</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4482</v>
+        <v>-2.115</v>
       </c>
       <c r="I9" t="n">
-        <v>1498.790527777778</v>
+        <v>1499.029041666667</v>
       </c>
       <c r="J9" t="n">
-        <v>114.9947400564755</v>
+        <v>114.9323361639937</v>
       </c>
       <c r="K9" t="n">
-        <v>110.7471958471358</v>
+        <v>111.2556119534676</v>
       </c>
       <c r="L9" t="n">
-        <v>4.247544209339688</v>
+        <v>3.676724210526132</v>
       </c>
       <c r="M9" t="n">
-        <v>111.196728777161</v>
+        <v>112.0302305875271</v>
       </c>
       <c r="N9" t="n">
-        <v>112.1659150925616</v>
+        <v>116.5634740813627</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9691863154006422</v>
+        <v>-4.533243493835618</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5597987380413881</v>
+        <v>0.5410913763796836</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1249943522007503</v>
+        <v>0.1292976350608657</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2610747023556211</v>
+        <v>0.3486366200960201</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5465412882623248</v>
+        <v>0.5367883864031614</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2887970325747766</v>
+        <v>0.2645569099514823</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4171213995273137</v>
+        <v>0.3464841714782828</v>
       </c>
       <c r="V9" t="n">
-        <v>103.1068013468014</v>
+        <v>99.32436403508771</v>
       </c>
       <c r="W9" t="n">
-        <v>118.1346801346801</v>
+        <v>114.1991959064327</v>
       </c>
       <c r="X9" t="n">
-        <v>3.804713804713805</v>
+        <v>3.995614035087719</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5928568149437025</v>
+        <v>0.5742658756874466</v>
       </c>
       <c r="Z9" t="n">
-        <v>113.6</v>
+        <v>112.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.4299999999999999</v>
+        <v>-3.32</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.250350764022217</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC9" t="n">
-        <v>114.1383305986051</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD9" t="n">
-        <v>109.8879798345829</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1207040259328637</v>
+        <v>0.1549752620601617</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>1571.955</v>
+        <v>1582.381</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.115</v>
+        <v>-0.3322</v>
       </c>
       <c r="I10" t="n">
-        <v>1499.029041666667</v>
+        <v>1499.834767123288</v>
       </c>
       <c r="J10" t="n">
-        <v>114.9323361639937</v>
+        <v>114.4282222729561</v>
       </c>
       <c r="K10" t="n">
-        <v>111.2556119534676</v>
+        <v>110.9083716287702</v>
       </c>
       <c r="L10" t="n">
-        <v>3.676724210526132</v>
+        <v>3.519850644185845</v>
       </c>
       <c r="M10" t="n">
-        <v>112.0302305875271</v>
+        <v>108.2073708580311</v>
       </c>
       <c r="N10" t="n">
-        <v>116.5634740813627</v>
+        <v>112.0407963514088</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.533243493835618</v>
+        <v>-3.833425493377661</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5410913763796836</v>
+        <v>0.5556122724308996</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1292976350608657</v>
+        <v>0.1250658662264155</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3486366200960201</v>
+        <v>0.2596696231719286</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5367883864031614</v>
+        <v>0.5249427043843291</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2645569099514823</v>
+        <v>0.2949825387157494</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3464841714782828</v>
+        <v>0.4209706593521603</v>
       </c>
       <c r="V10" t="n">
-        <v>99.32436403508771</v>
+        <v>102.8994520547946</v>
       </c>
       <c r="W10" t="n">
-        <v>114.1991959064327</v>
+        <v>117.3541498791297</v>
       </c>
       <c r="X10" t="n">
-        <v>3.995614035087719</v>
+        <v>3.075745366639806</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5742658756874466</v>
+        <v>0.5899963583557084</v>
       </c>
       <c r="Z10" t="n">
-        <v>112.07</v>
+        <v>110.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.32</v>
+        <v>-3.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.413694058608522</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC10" t="n">
-        <v>112.3850185369902</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD10" t="n">
-        <v>108.9713244783817</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2060266045469457</v>
+        <v>0.2696744462917988</v>
       </c>
     </row>
     <row r="11">
@@ -1579,76 +1579,76 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>1585.81</v>
+        <v>1590.882</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3874</v>
+        <v>2.6352</v>
       </c>
       <c r="I11" t="n">
-        <v>1493.130958333333</v>
+        <v>1495.442657534247</v>
       </c>
       <c r="J11" t="n">
-        <v>115.9229240571725</v>
+        <v>115.8085488022522</v>
       </c>
       <c r="K11" t="n">
-        <v>112.4097813148812</v>
+        <v>112.6625142964027</v>
       </c>
       <c r="L11" t="n">
-        <v>3.513142742291282</v>
+        <v>3.14603450584958</v>
       </c>
       <c r="M11" t="n">
-        <v>118.9625739102969</v>
+        <v>117.7042768679311</v>
       </c>
       <c r="N11" t="n">
-        <v>108.8794278261441</v>
+        <v>111.4027382732558</v>
       </c>
       <c r="O11" t="n">
-        <v>10.0831460841528</v>
+        <v>6.301538594675312</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5560978430042903</v>
+        <v>0.5524535248134598</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1306211069524975</v>
+        <v>0.1285986555778894</v>
       </c>
       <c r="R11" t="n">
-        <v>0.305417531360279</v>
+        <v>0.3063239802530656</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5727424814377063</v>
+        <v>0.5617471810919845</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2503261617229583</v>
+        <v>0.2525413550482655</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4825001993335964</v>
+        <v>0.484369618853381</v>
       </c>
       <c r="V11" t="n">
-        <v>99.83223809523807</v>
+        <v>99.89104261796042</v>
       </c>
       <c r="W11" t="n">
-        <v>116.3071428571429</v>
+        <v>116.277397260274</v>
       </c>
       <c r="X11" t="n">
-        <v>4.807142857142857</v>
+        <v>4.470319634703197</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.592632282845572</v>
+        <v>0.5896003764595595</v>
       </c>
       <c r="Z11" t="n">
-        <v>117.87</v>
+        <v>117.51</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AB11" t="n">
         <v>-10.13717477219789</v>
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.224861822448919</v>
+        <v>0.2200596426123817</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.605840693858463</v>
+        <v>1.516279163675467</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.066391169698105</v>
+        <v>0.9917271020472143</v>
       </c>
     </row>
     <row r="14">
@@ -1993,115 +1993,115 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.3830274090862391</v>
+        <v>0.1582153884703806</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>1505.042</v>
+        <v>1504.204</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7107</v>
+        <v>-1.0757</v>
       </c>
       <c r="I15" t="n">
-        <v>1496.795430555555</v>
+        <v>1517.468767123288</v>
       </c>
       <c r="J15" t="n">
-        <v>113.0784774599792</v>
+        <v>113.7260737570083</v>
       </c>
       <c r="K15" t="n">
-        <v>111.5605635885357</v>
+        <v>111.7420676851524</v>
       </c>
       <c r="L15" t="n">
-        <v>1.517913871443526</v>
+        <v>1.984006071855917</v>
       </c>
       <c r="M15" t="n">
-        <v>115.8694895112704</v>
+        <v>119.5347307103522</v>
       </c>
       <c r="N15" t="n">
-        <v>114.700895172135</v>
+        <v>114.0245628123576</v>
       </c>
       <c r="O15" t="n">
-        <v>1.168594339135413</v>
+        <v>5.51016789799468</v>
       </c>
       <c r="P15" t="n">
-        <v>0.542778232132711</v>
+        <v>0.5402559721952398</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1160961101089527</v>
+        <v>0.1182637479616529</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2550216234867304</v>
+        <v>0.2893646183530116</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5662527341443399</v>
+        <v>0.5577788690445787</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2593964848600521</v>
+        <v>0.2283680449583401</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3691890880194976</v>
+        <v>0.4581499540849762</v>
       </c>
       <c r="V15" t="n">
-        <v>100.7830147058824</v>
+        <v>99.58012720156557</v>
       </c>
       <c r="W15" t="n">
-        <v>114.0661764705883</v>
+        <v>113.1555772994129</v>
       </c>
       <c r="X15" t="n">
-        <v>1.865196078431373</v>
+        <v>2.055283757338551</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5768109034513951</v>
+        <v>0.5712835721441518</v>
       </c>
       <c r="Z15" t="n">
-        <v>116.48</v>
+        <v>116.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>5.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.536933640611859</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC15" t="n">
-        <v>108.3888858603967</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD15" t="n">
-        <v>112.9258195010085</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.217319989008329</v>
+        <v>-0.07242096860923961</v>
       </c>
     </row>
     <row r="16">
@@ -2119,76 +2119,76 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>1517.636</v>
+        <v>1515.872</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7214</v>
+        <v>2.601</v>
       </c>
       <c r="I16" t="n">
-        <v>1483.556287671233</v>
+        <v>1485.918486486486</v>
       </c>
       <c r="J16" t="n">
-        <v>113.7139460188449</v>
+        <v>114.0423870586319</v>
       </c>
       <c r="K16" t="n">
-        <v>112.3045211289271</v>
+        <v>112.3267853106687</v>
       </c>
       <c r="L16" t="n">
-        <v>1.409424889917866</v>
+        <v>1.715601747963108</v>
       </c>
       <c r="M16" t="n">
-        <v>118.5112879467137</v>
+        <v>118.9394660785629</v>
       </c>
       <c r="N16" t="n">
-        <v>108.9190604057888</v>
+        <v>109.1683779977121</v>
       </c>
       <c r="O16" t="n">
-        <v>9.592227540924936</v>
+        <v>9.771088080850765</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5513675640902436</v>
+        <v>0.5536219381182681</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1151892768060538</v>
+        <v>0.1163042263345683</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2387912329679008</v>
+        <v>0.2418419141030064</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5630899663458</v>
+        <v>0.5609427023576505</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2385949493518496</v>
+        <v>0.2382952768134829</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4297333167391637</v>
+        <v>0.4298126046579471</v>
       </c>
       <c r="V16" t="n">
-        <v>103.6870319634703</v>
+        <v>103.7007158509861</v>
       </c>
       <c r="W16" t="n">
-        <v>117.955098934551</v>
+        <v>118.3192111029949</v>
       </c>
       <c r="X16" t="n">
-        <v>1.603500761035008</v>
+        <v>1.953250547845143</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.582610014607143</v>
+        <v>0.5845622037081731</v>
       </c>
       <c r="Z16" t="n">
-        <v>121.35</v>
+        <v>121.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.74</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
         <v>-0.981113782848854</v>
@@ -2200,112 +2200,112 @@
         <v>113.7840975621041</v>
       </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.7881730209015466</v>
+        <v>0.8559925378542008</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>1507.624</v>
+        <v>1505.042</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2525</v>
+        <v>0.7107</v>
       </c>
       <c r="I17" t="n">
-        <v>1516.454152777778</v>
+        <v>1496.795430555555</v>
       </c>
       <c r="J17" t="n">
-        <v>113.2866827538334</v>
+        <v>113.0784774599792</v>
       </c>
       <c r="K17" t="n">
-        <v>112.1392926130768</v>
+        <v>111.5605635885357</v>
       </c>
       <c r="L17" t="n">
-        <v>1.147390140756679</v>
+        <v>1.517913871443526</v>
       </c>
       <c r="M17" t="n">
-        <v>118.7196042868246</v>
+        <v>115.8694895112704</v>
       </c>
       <c r="N17" t="n">
-        <v>115.5101813717958</v>
+        <v>114.700895172135</v>
       </c>
       <c r="O17" t="n">
-        <v>3.209422915028772</v>
+        <v>1.168594339135413</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5386739885194024</v>
+        <v>0.542778232132711</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1182585643998592</v>
+        <v>0.1160961101089527</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2845045285103836</v>
+        <v>0.2550216234867304</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5549428707731872</v>
+        <v>0.5662527341443399</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2310536443479878</v>
+        <v>0.2593964848600521</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4569015087700092</v>
+        <v>0.3691890880194976</v>
       </c>
       <c r="V17" t="n">
-        <v>99.40384469696968</v>
+        <v>100.7830147058824</v>
       </c>
       <c r="W17" t="n">
-        <v>112.4807449494949</v>
+        <v>114.0661764705883</v>
       </c>
       <c r="X17" t="n">
-        <v>1.176136363636364</v>
+        <v>1.865196078431373</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5706535010178025</v>
+        <v>0.5768109034513951</v>
       </c>
       <c r="Z17" t="n">
-        <v>114.63</v>
+        <v>116.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.375203171419814</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC17" t="n">
-        <v>114.7034977739938</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD17" t="n">
-        <v>117.0787009454136</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.02947582019545941</v>
+        <v>0.1657769892121725</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.388833299199155</v>
+        <v>-0.4239407288943591</v>
       </c>
     </row>
     <row r="19">
@@ -2443,76 +2443,76 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>1466.767</v>
+        <v>1469.575</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0474</v>
+        <v>0.1933</v>
       </c>
       <c r="I19" t="n">
-        <v>1498.779</v>
+        <v>1497.223657534247</v>
       </c>
       <c r="J19" t="n">
-        <v>113.4572304016832</v>
+        <v>113.4308448980004</v>
       </c>
       <c r="K19" t="n">
-        <v>113.1555451692424</v>
+        <v>113.1733010220948</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3016852324407445</v>
+        <v>0.2575438759055876</v>
       </c>
       <c r="M19" t="n">
-        <v>113.6079435006834</v>
+        <v>114.285926442809</v>
       </c>
       <c r="N19" t="n">
-        <v>115.4468774267562</v>
+        <v>114.9526667337413</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.838933926072703</v>
+        <v>-0.6667402909323203</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5321602185382215</v>
+        <v>0.5322507943117178</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.114130259174332</v>
+        <v>0.1138856581463011</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2612642510733914</v>
+        <v>0.2596154503377267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5413927720632195</v>
+        <v>0.5389088110303376</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2812339030142152</v>
+        <v>0.2835401824238258</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3949267448455321</v>
+        <v>0.3947943751215166</v>
       </c>
       <c r="V19" t="n">
-        <v>103.0025925925926</v>
+        <v>102.6970112079701</v>
       </c>
       <c r="W19" t="n">
-        <v>116.6452991452991</v>
+        <v>116.2067247820672</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1232193732193733</v>
+        <v>-0.2374429223744292</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5744636725259946</v>
+        <v>0.5746603057191856</v>
       </c>
       <c r="Z19" t="n">
-        <v>118.48</v>
+        <v>118.27</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.51</v>
+        <v>-0.5</v>
       </c>
       <c r="AB19" t="n">
         <v>-6.382503892565079</v>
@@ -2524,7 +2524,7 @@
         <v>116.2614936572104</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3240757161940581</v>
+        <v>0.4046827248421163</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1742753088108057</v>
+        <v>-0.2324765213360193</v>
       </c>
     </row>
     <row r="21">
@@ -2749,103 +2749,103 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.3206935130646001</v>
+        <v>-0.0480800098264676</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1610612740</v>
+        <v>1610612741</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>1381.942</v>
+        <v>1381.482</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2995</v>
+        <v>-0.4564</v>
       </c>
       <c r="I22" t="n">
-        <v>1508.055432432432</v>
+        <v>1496.943479452055</v>
       </c>
       <c r="J22" t="n">
-        <v>112.1449809261782</v>
+        <v>111.6885269438393</v>
       </c>
       <c r="K22" t="n">
-        <v>116.1627917910209</v>
+        <v>115.3428658126772</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.017810864842693</v>
+        <v>-3.654338868837813</v>
       </c>
       <c r="M22" t="n">
-        <v>115.3883803591507</v>
+        <v>112.3032771831725</v>
       </c>
       <c r="N22" t="n">
-        <v>114.2484261927667</v>
+        <v>118.1624481805777</v>
       </c>
       <c r="O22" t="n">
-        <v>1.139954166384094</v>
+        <v>-5.859170997405267</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5274461080296675</v>
+        <v>0.5500114312960163</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1169953406743485</v>
+        <v>0.1275107330361474</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2696736446660632</v>
+        <v>0.2294790941793377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5440000808017124</v>
+        <v>0.5494875563020285</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2827323387604225</v>
+        <v>0.2505574560148133</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3590735779800531</v>
+        <v>0.4456053865141036</v>
       </c>
       <c r="V22" t="n">
-        <v>102.7059295659296</v>
+        <v>104.6541429100334</v>
       </c>
       <c r="W22" t="n">
-        <v>115.0941850941851</v>
+        <v>116.482784154017</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.207207207207206</v>
+        <v>-4.545353572750835</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5675831110895945</v>
+        <v>0.5829072430684848</v>
       </c>
       <c r="Z22" t="n">
-        <v>115.81</v>
+        <v>121.39</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>-6.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>-9.447870926461551</v>
+        <v>-0.9433805425336231</v>
       </c>
       <c r="AC22" t="n">
-        <v>108.3910194524218</v>
+        <v>112.5644270515903</v>
       </c>
       <c r="AD22" t="n">
-        <v>117.8388903788833</v>
+        <v>113.5078075941239</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2857,21 +2857,21 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.04616119371164053</v>
+        <v>0.05594255157270823</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2881,91 +2881,91 @@
         <v>46108</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>1382.431</v>
+        <v>1381.942</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4371</v>
+        <v>2.2995</v>
       </c>
       <c r="I23" t="n">
-        <v>1493.417138888889</v>
+        <v>1508.055432432432</v>
       </c>
       <c r="J23" t="n">
-        <v>111.6418790940612</v>
+        <v>112.1449809261782</v>
       </c>
       <c r="K23" t="n">
-        <v>115.6910715927458</v>
+        <v>116.1627917910209</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.049192498684509</v>
+        <v>-4.017810864842693</v>
       </c>
       <c r="M23" t="n">
-        <v>111.9028653490087</v>
+        <v>115.3883803591507</v>
       </c>
       <c r="N23" t="n">
-        <v>117.741719892843</v>
+        <v>114.2484261927667</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.838854543834226</v>
+        <v>1.139954166384094</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5488803871956238</v>
+        <v>0.5274461080296675</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1255161420502698</v>
+        <v>0.1169953406743485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2277478563889072</v>
+        <v>0.2696736446660632</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5449087423601159</v>
+        <v>0.5440000808017124</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2425187355317611</v>
+        <v>0.2827323387604225</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4472988650711273</v>
+        <v>0.3590735779800531</v>
       </c>
       <c r="V23" t="n">
-        <v>104.4028888888889</v>
+        <v>102.7059295659296</v>
       </c>
       <c r="W23" t="n">
-        <v>116.2246031746031</v>
+        <v>115.0941850941851</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.845238095238095</v>
+        <v>-4.207207207207206</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5812018359599354</v>
+        <v>0.5675831110895945</v>
       </c>
       <c r="Z23" t="n">
-        <v>119.57</v>
+        <v>115.81</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.9433805425336231</v>
+        <v>-9.447870926461551</v>
       </c>
       <c r="AC23" t="n">
-        <v>112.5644270515903</v>
+        <v>108.3910194524218</v>
       </c>
       <c r="AD23" t="n">
-        <v>113.5078075941239</v>
+        <v>117.8388903788833</v>
       </c>
       <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1</v>
       </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.3139915333677319</v>
+        <v>0.0176128102464128</v>
       </c>
     </row>
     <row r="24">
@@ -2983,76 +2983,76 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>1384.612</v>
+        <v>1382.574</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9168</v>
+        <v>-1.8884</v>
       </c>
       <c r="I24" t="n">
-        <v>1495.537657142857</v>
+        <v>1496.613957746479</v>
       </c>
       <c r="J24" t="n">
-        <v>110.6526478669424</v>
+        <v>110.5082319094104</v>
       </c>
       <c r="K24" t="n">
-        <v>115.5740353629901</v>
+        <v>115.3610514702156</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.921387496047651</v>
+        <v>-4.852819560805172</v>
       </c>
       <c r="M24" t="n">
-        <v>107.9081849502933</v>
+        <v>107.3702020857575</v>
       </c>
       <c r="N24" t="n">
-        <v>124.3312116376382</v>
+        <v>122.916232423345</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.42302668734481</v>
+        <v>-15.54603033758751</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5334395940242856</v>
+        <v>0.5334166269017803</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1260460171490826</v>
+        <v>0.1258961809168631</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2518239203004887</v>
+        <v>0.2501302627425632</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5171462702664064</v>
+        <v>0.5183945678850819</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2578202452673223</v>
+        <v>0.2561223111375087</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4308624276867906</v>
+        <v>0.4293641667531403</v>
       </c>
       <c r="V24" t="n">
-        <v>103.5755348837209</v>
+        <v>103.9257298335467</v>
       </c>
       <c r="W24" t="n">
-        <v>114.8604651162791</v>
+        <v>115.1446862996159</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.404651162790698</v>
+        <v>-4.230473751600512</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5707435224243221</v>
+        <v>0.5703615908919931</v>
       </c>
       <c r="Z24" t="n">
-        <v>111.34</v>
+        <v>112.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>-14.95</v>
+        <v>-13.76</v>
       </c>
       <c r="AB24" t="n">
         <v>3.575252351995317</v>
@@ -3064,16 +3064,16 @@
         <v>110.9666857710851</v>
       </c>
       <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.6151501359298177</v>
+        <v>-1.147425639684343</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8948917929797605</v>
+        <v>-0.8989278633415372</v>
       </c>
     </row>
     <row r="26">
@@ -3199,76 +3199,76 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>1399.801</v>
+        <v>1395.642</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.795</v>
+        <v>-2.0688</v>
       </c>
       <c r="I26" t="n">
-        <v>1492.736042253521</v>
+        <v>1492.286444444444</v>
       </c>
       <c r="J26" t="n">
-        <v>111.0839498044373</v>
+        <v>110.8694414786139</v>
       </c>
       <c r="K26" t="n">
-        <v>116.9523974470938</v>
+        <v>117.060409327615</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.868447642656478</v>
+        <v>-6.190967849001092</v>
       </c>
       <c r="M26" t="n">
-        <v>108.2269626499474</v>
+        <v>106.8382962042546</v>
       </c>
       <c r="N26" t="n">
-        <v>122.6997282031435</v>
+        <v>125.2761142486587</v>
       </c>
       <c r="O26" t="n">
-        <v>-14.47276555319603</v>
+        <v>-18.43781804440419</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5633657303245708</v>
+        <v>0.5630501233332103</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1305384784768613</v>
+        <v>0.1312647622832813</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2051492747697975</v>
+        <v>0.205071837990632</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5620435092172112</v>
+        <v>0.5575832452976177</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2287017546510412</v>
+        <v>0.2251872788982814</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4479979951776746</v>
+        <v>0.4492826341808012</v>
       </c>
       <c r="V26" t="n">
-        <v>99.65181818181819</v>
+        <v>99.63772839506174</v>
       </c>
       <c r="W26" t="n">
-        <v>110.5070422535211</v>
+        <v>110.2641975308642</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.196542893725993</v>
+        <v>-6.550617283950617</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5872400503846898</v>
+        <v>0.5866829768336588</v>
       </c>
       <c r="Z26" t="n">
-        <v>106.38</v>
+        <v>104.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>-14.62</v>
+        <v>-18.77</v>
       </c>
       <c r="AB26" t="n">
         <v>1.809266556998161</v>
@@ -3280,7 +3280,7 @@
         <v>112.4407240264407</v>
       </c>
       <c r="AE26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3289,21 +3289,21 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.154888664734465</v>
+        <v>-1.21696063186939</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612762</v>
+        <v>1610612754</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3313,79 +3313,79 @@
         <v>46108</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>1310.366</v>
+        <v>1334.762</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5698</v>
+        <v>-1.3404</v>
       </c>
       <c r="I27" t="n">
-        <v>1508.98601369863</v>
+        <v>1501.433684931507</v>
       </c>
       <c r="J27" t="n">
-        <v>112.2907379787998</v>
+        <v>108.9414065061395</v>
       </c>
       <c r="K27" t="n">
-        <v>119.8611191829545</v>
+        <v>116.9592428870239</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.570381204154772</v>
+        <v>-8.017836380884376</v>
       </c>
       <c r="M27" t="n">
-        <v>112.1026735628848</v>
+        <v>113.9720100132994</v>
       </c>
       <c r="N27" t="n">
-        <v>119.8612157260471</v>
+        <v>122.9634590983539</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.758542163162284</v>
+        <v>-8.991449085054599</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5390833228243055</v>
+        <v>0.5315300979455618</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1281425351784173</v>
+        <v>0.1225037289322189</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2613504445840236</v>
+        <v>0.2164939170842621</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5350239520727516</v>
+        <v>0.5719877966037397</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2849157283425882</v>
+        <v>0.2576289386000791</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4105503824494048</v>
+        <v>0.419163014453595</v>
       </c>
       <c r="V27" t="n">
-        <v>104.7554722422495</v>
+        <v>103.038794520548</v>
       </c>
       <c r="W27" t="n">
-        <v>117.6492429704399</v>
+        <v>111.9221135029354</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.787310742609949</v>
+        <v>-8.625048923679062</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5792533823930115</v>
+        <v>0.5670668705856138</v>
       </c>
       <c r="Z27" t="n">
-        <v>116.58</v>
+        <v>114.71</v>
       </c>
       <c r="AA27" t="n">
-        <v>-9.24</v>
+        <v>-10.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>-9.725925288085115</v>
+        <v>2.960186837728194</v>
       </c>
       <c r="AC27" t="n">
-        <v>108.7199864623461</v>
+        <v>114.8929919496836</v>
       </c>
       <c r="AD27" t="n">
-        <v>118.4459117504312</v>
+        <v>111.9328051119554</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -3397,115 +3397,115 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.248361690552222</v>
+        <v>-1.238941799022681</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F28" t="n">
         <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>1334.762</v>
+        <v>1309.746</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.3404</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1501.433684931507</v>
+        <v>1510.146851351351</v>
       </c>
       <c r="J28" t="n">
-        <v>108.9414065061395</v>
+        <v>111.9508944993898</v>
       </c>
       <c r="K28" t="n">
-        <v>116.9592428870239</v>
+        <v>120.0449034796656</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.017836380884376</v>
+        <v>-8.094008980275769</v>
       </c>
       <c r="M28" t="n">
-        <v>113.9720100132994</v>
+        <v>112.5694386500763</v>
       </c>
       <c r="N28" t="n">
-        <v>122.9634590983539</v>
+        <v>121.4295861468688</v>
       </c>
       <c r="O28" t="n">
-        <v>-8.991449085054599</v>
+        <v>-8.860147496792447</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5315300979455618</v>
+        <v>0.5377424847058799</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1225037289322189</v>
+        <v>0.1284890314310867</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2164939170842621</v>
+        <v>0.2608945517585634</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5719877966037397</v>
+        <v>0.5441452335372824</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2576289386000791</v>
+        <v>0.2837604962548124</v>
       </c>
       <c r="U28" t="n">
-        <v>0.419163014453595</v>
+        <v>0.4067702277337957</v>
       </c>
       <c r="V28" t="n">
-        <v>103.038794520548</v>
+        <v>104.7094671814672</v>
       </c>
       <c r="W28" t="n">
-        <v>111.9221135029354</v>
+        <v>117.2571428571429</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.625048923679062</v>
+        <v>-8.301930501930503</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5670668705856138</v>
+        <v>0.5776469115932003</v>
       </c>
       <c r="Z28" t="n">
-        <v>114.71</v>
+        <v>117.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>-10.36</v>
+        <v>-10.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.960186837728194</v>
+        <v>-9.725925288085115</v>
       </c>
       <c r="AC28" t="n">
-        <v>114.8929919496836</v>
+        <v>108.7199864623461</v>
       </c>
       <c r="AD28" t="n">
-        <v>111.9328051119554</v>
+        <v>118.4459117504312</v>
       </c>
       <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.227151036111298</v>
+        <v>-1.229156938563336</v>
       </c>
     </row>
     <row r="29">
@@ -3523,76 +3523,76 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G29" t="n">
-        <v>1314.351</v>
+        <v>1313.534</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5413</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>1519.759602739726</v>
+        <v>1519.809027027027</v>
       </c>
       <c r="J29" t="n">
-        <v>109.5216829492278</v>
+        <v>109.4281799030073</v>
       </c>
       <c r="K29" t="n">
-        <v>118.9372716231152</v>
+        <v>118.878965700675</v>
       </c>
       <c r="L29" t="n">
-        <v>-9.415588673887417</v>
+        <v>-9.450785797667715</v>
       </c>
       <c r="M29" t="n">
-        <v>114.3660207040932</v>
+        <v>114.2670244637234</v>
       </c>
       <c r="N29" t="n">
-        <v>119.9284409433158</v>
+        <v>119.893539689222</v>
       </c>
       <c r="O29" t="n">
-        <v>-5.562420239222653</v>
+        <v>-5.626515225498592</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5251488121289328</v>
+        <v>0.524540984249476</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1196178814832662</v>
+        <v>0.1205089780689227</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2508571371152646</v>
+        <v>0.2540644475573293</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5512421146282964</v>
+        <v>0.5510808243057159</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2554051110201577</v>
+        <v>0.2538995225608229</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3373898973253706</v>
+        <v>0.3368814227934586</v>
       </c>
       <c r="V29" t="n">
-        <v>101.6685359589041</v>
+        <v>101.7198417930125</v>
       </c>
       <c r="W29" t="n">
-        <v>110.9486301369864</v>
+        <v>110.8905735003296</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.22388698630137</v>
+        <v>-10.3295978905735</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.560632505128294</v>
+        <v>0.5599371178912355</v>
       </c>
       <c r="Z29" t="n">
-        <v>114.66</v>
+        <v>113.72</v>
       </c>
       <c r="AA29" t="n">
-        <v>-6.88</v>
+        <v>-6.94</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.1619477822758719</v>
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.540560323433185</v>
+        <v>-1.510084503121899</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.011127730292063</v>
+        <v>-2.00168274072081</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.442540044124928</v>
+        <v>-1.685695157394356</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.318249984659178</v>
+        <v>1.46379076817337</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.8924013092237099</v>
+        <v>1.004001044092361</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.06143486571132148</v>
+        <v>0.106804800867139</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8962673621316659</v>
+        <v>0.7207608197075324</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5950864322312313</v>
+        <v>0.6829895366178786</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.559256439741149</v>
+        <v>1.578972505468806</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.572158489801168</v>
+        <v>1.737936323285583</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1549752620601617</v>
+        <v>0.2078005665195296</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2696744462917988</v>
+        <v>0.3316415206243005</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2200596426123817</v>
+        <v>0.3369427540269588</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.516279163675467</v>
+        <v>1.677603295561837</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.9917271020472143</v>
+        <v>0.5722897213022632</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1582153884703806</v>
+        <v>0.2112989379225138</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.07242096860923961</v>
+        <v>-0.03771962923927924</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.8559925378542008</v>
+        <v>0.5485632803832007</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1657769892121725</v>
+        <v>0.219463214387913</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.4239407288943591</v>
+        <v>-0.4172562649356132</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.4046827248421163</v>
+        <v>0.4774102472261266</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2324765213360193</v>
+        <v>-0.2105319512469154</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.0480800098264676</v>
+        <v>-0.0114386440720636</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.05594255157270823</v>
+        <v>-0.5051550383261743</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0176128102464128</v>
+        <v>-0.005277217672691084</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.147425639684343</v>
+        <v>-1.04227355452378</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8989278633415372</v>
+        <v>-0.9301008881252235</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.21696063186939</v>
+        <v>-1.273481547324432</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.238941799022681</v>
+        <v>-1.226505686390654</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.229156938563336</v>
+        <v>-1.397173135336179</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.510084503121899</v>
+        <v>-1.547311837775633</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-2.00168274072081</v>
+        <v>-1.794331578452543</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.685695157394356</v>
+        <v>-1.47971236274613</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.46379076817337</v>
+        <v>1.497491084558155</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.004001044092361</v>
+        <v>1.050393376610797</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.106804800867139</v>
+        <v>0.177910495630647</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.7207608197075324</v>
+        <v>0.3003716069254416</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6829895366178786</v>
+        <v>1.001804915426879</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.578972505468806</v>
+        <v>1.12309548916628</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.737936323285583</v>
+        <v>1.764104697636828</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.2078005665195296</v>
+        <v>0.2761841800297318</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3316415206243005</v>
+        <v>0.3065025076973801</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3369427540269588</v>
+        <v>0.4017176616233741</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.677603295561837</v>
+        <v>1.705420434131273</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.5722897213022632</v>
+        <v>0.605524366572649</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.2112989379225138</v>
+        <v>0.2795777154672761</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.03771962923927924</v>
+        <v>0.03743090579493385</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.5485632803832007</v>
+        <v>0.6075258963062041</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.219463214387913</v>
+        <v>-0.07773062798800867</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.4172562649356132</v>
+        <v>-0.3316800258638012</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.4774102472261266</v>
+        <v>0.53837235106892</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2105319512469154</v>
+        <v>-0.1306309898434237</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.0114386440720636</v>
+        <v>0.0629615288489149</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.5051550383261743</v>
+        <v>-0.4171042313504106</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.005277217672691084</v>
+        <v>-0.27596812460072</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.04227355452378</v>
+        <v>-0.9394223620756135</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.9301008881252235</v>
+        <v>-0.8303488021411535</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.273481547324432</v>
+        <v>-1.738145041157377</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.226505686390654</v>
+        <v>-0.6341182737992591</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.397173135336179</v>
+        <v>-1.284522104721547</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.547311837775633</v>
+        <v>-1.742427653737866</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.794331578452543</v>
+        <v>-1.969485449824274</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.47971236274613</v>
+        <v>-1.364805526392233</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -607,76 +607,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>1750.84</v>
+        <v>1751.789</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3486</v>
+        <v>1.8212</v>
       </c>
       <c r="I2" t="n">
-        <v>1495.885819444444</v>
+        <v>1494.331643835616</v>
       </c>
       <c r="J2" t="n">
-        <v>116.900264380679</v>
+        <v>116.9236604844726</v>
       </c>
       <c r="K2" t="n">
-        <v>105.5645188322798</v>
+        <v>105.6674176696925</v>
       </c>
       <c r="L2" t="n">
-        <v>11.33574554839926</v>
+        <v>11.25624281478007</v>
       </c>
       <c r="M2" t="n">
-        <v>117.234843162215</v>
+        <v>118.3443029623195</v>
       </c>
       <c r="N2" t="n">
-        <v>105.5218082271332</v>
+        <v>106.180148252947</v>
       </c>
       <c r="O2" t="n">
-        <v>11.71303493508181</v>
+        <v>12.16415470937252</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5606766371469609</v>
+        <v>0.5603044545257453</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1062160838060996</v>
+        <v>0.1072115022136621</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2196046609005238</v>
+        <v>0.2212515301163551</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5580488921655966</v>
+        <v>0.5554877456399852</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2670730388258403</v>
+        <v>0.2731351382098174</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4259068858316259</v>
+        <v>0.4241542036692744</v>
       </c>
       <c r="V2" t="n">
-        <v>102.0385396825397</v>
+        <v>101.6736301369863</v>
       </c>
       <c r="W2" t="n">
-        <v>119.0865079365079</v>
+        <v>118.6845509893455</v>
       </c>
       <c r="X2" t="n">
-        <v>11.3484126984127</v>
+        <v>11.23972602739726</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5992316339870989</v>
+        <v>0.5998096733057342</v>
       </c>
       <c r="Z2" t="n">
-        <v>116.96</v>
+        <v>117.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.17</v>
+        <v>10.82</v>
       </c>
       <c r="AB2" t="n">
         <v>11.54061896828745</v>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.497491084558155</v>
+        <v>1.028066606257016</v>
       </c>
     </row>
     <row r="3">
@@ -721,7 +721,7 @@
         <v>46109</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
         <v>1731.476</v>
@@ -733,13 +733,13 @@
         <v>1510.731652777778</v>
       </c>
       <c r="J3" t="n">
-        <v>117.5792874089684</v>
+        <v>117.5881719099868</v>
       </c>
       <c r="K3" t="n">
-        <v>108.7720490057709</v>
+        <v>108.7606052633075</v>
       </c>
       <c r="L3" t="n">
-        <v>8.807238403197507</v>
+        <v>8.827566646679363</v>
       </c>
       <c r="M3" t="n">
         <v>124.9133382900033</v>
@@ -751,34 +751,34 @@
         <v>16.62525467961587</v>
       </c>
       <c r="P3" t="n">
-        <v>0.561650349722584</v>
+        <v>0.5617123911674172</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1119384336426832</v>
+        <v>0.111928483695515</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2567219510165967</v>
+        <v>0.2567095738744724</v>
       </c>
       <c r="S3" t="n">
         <v>0.5878199071152477</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2794218653484273</v>
+        <v>0.2793716332417011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4234726356287385</v>
+        <v>0.4234448907172028</v>
       </c>
       <c r="V3" t="n">
-        <v>101.9468137254901</v>
+        <v>101.9443097643097</v>
       </c>
       <c r="W3" t="n">
-        <v>119.6127450980392</v>
+        <v>119.6195286195286</v>
       </c>
       <c r="X3" t="n">
-        <v>8.598039215686276</v>
+        <v>8.619528619528619</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5972986693477695</v>
+        <v>0.5973464063397171</v>
       </c>
       <c r="Z3" t="n">
         <v>126.19</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.050393376610797</v>
+        <v>1.132986260676032</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.177910495630647</v>
+        <v>-0.5487767941119038</v>
       </c>
     </row>
     <row r="5">
@@ -931,76 +931,76 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>1658.359</v>
+        <v>1660.123</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4282</v>
+        <v>0.3613</v>
       </c>
       <c r="I5" t="n">
-        <v>1488.582361111111</v>
+        <v>1488.980356164384</v>
       </c>
       <c r="J5" t="n">
-        <v>117.210917549777</v>
+        <v>117.4960933759783</v>
       </c>
       <c r="K5" t="n">
-        <v>110.314422414086</v>
+        <v>110.2106546073493</v>
       </c>
       <c r="L5" t="n">
-        <v>6.896495135690944</v>
+        <v>7.285438768629046</v>
       </c>
       <c r="M5" t="n">
-        <v>115.0401665696386</v>
+        <v>115.7381248363943</v>
       </c>
       <c r="N5" t="n">
-        <v>109.7188902052104</v>
+        <v>110.3489221931051</v>
       </c>
       <c r="O5" t="n">
-        <v>5.32127636442826</v>
+        <v>5.389202643289144</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5483413468690369</v>
+        <v>0.5494459199122412</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1051496796996714</v>
+        <v>0.1031261859981875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2929068749466081</v>
+        <v>0.2904140245416875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5317636308556516</v>
+        <v>0.5352442198784093</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2119763777192656</v>
+        <v>0.2125352809958431</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4667004705209388</v>
+        <v>0.4655305832735115</v>
       </c>
       <c r="V5" t="n">
-        <v>97.12081081081082</v>
+        <v>97.01012133072408</v>
       </c>
       <c r="W5" t="n">
-        <v>114.054054054054</v>
+        <v>114.1197651663405</v>
       </c>
       <c r="X5" t="n">
-        <v>7.202702702702703</v>
+        <v>7.428180039138942</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5792070665825365</v>
+        <v>0.579978699181117</v>
       </c>
       <c r="Z5" t="n">
-        <v>112.24</v>
+        <v>111.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.55</v>
+        <v>6.180000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>9.220352523846751</v>
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3003716069254416</v>
+        <v>0.8443260495032402</v>
       </c>
     </row>
     <row r="6">
@@ -1039,76 +1039,76 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46107</v>
+        <v>46110</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>1661.885</v>
+        <v>1656.813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0692</v>
+        <v>0.6916</v>
       </c>
       <c r="I6" t="n">
-        <v>1484.587111111111</v>
+        <v>1485.973726027397</v>
       </c>
       <c r="J6" t="n">
-        <v>117.4055805175939</v>
+        <v>117.1977984790908</v>
       </c>
       <c r="K6" t="n">
-        <v>110.7868648411097</v>
+        <v>110.8022814185654</v>
       </c>
       <c r="L6" t="n">
-        <v>6.618715676484227</v>
+        <v>6.395517060525354</v>
       </c>
       <c r="M6" t="n">
-        <v>121.3766576228191</v>
+        <v>118.3080391000842</v>
       </c>
       <c r="N6" t="n">
-        <v>111.9795146550886</v>
+        <v>113.7266536287964</v>
       </c>
       <c r="O6" t="n">
-        <v>9.39714296773052</v>
+        <v>4.581385471287755</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5553539830452668</v>
+        <v>0.5541063526436519</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1148876370982657</v>
+        <v>0.1167410326083382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2880838594247036</v>
+        <v>0.2931776654280925</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5701781612952713</v>
+        <v>0.5577500483299311</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2367413216275416</v>
+        <v>0.2383205045765506</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4289810295681382</v>
+        <v>0.4303959091814751</v>
       </c>
       <c r="V6" t="n">
-        <v>99.50724999999998</v>
+        <v>99.45131849315068</v>
       </c>
       <c r="W6" t="n">
-        <v>116.5601851851852</v>
+        <v>116.3095034246576</v>
       </c>
       <c r="X6" t="n">
-        <v>6.118055555555555</v>
+        <v>5.919948630136987</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5881959753234444</v>
+        <v>0.5870619828401078</v>
       </c>
       <c r="Z6" t="n">
-        <v>118.03</v>
+        <v>114.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.890000000000001</v>
+        <v>4.39</v>
       </c>
       <c r="AB6" t="n">
         <v>2.775420617465777</v>
@@ -1120,7 +1120,7 @@
         <v>112.335295999638</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1129,103 +1129,103 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.001804915426879</v>
+        <v>0.7826694671736264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>1637.716</v>
+        <v>1595.508</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4165</v>
+        <v>1.3553</v>
       </c>
       <c r="I7" t="n">
-        <v>1490.265150684932</v>
+        <v>1501.8568</v>
       </c>
       <c r="J7" t="n">
-        <v>117.1208875317718</v>
+        <v>119.8584384956113</v>
       </c>
       <c r="K7" t="n">
-        <v>112.6775919801654</v>
+        <v>115.1037310005922</v>
       </c>
       <c r="L7" t="n">
-        <v>4.443295551606407</v>
+        <v>4.754707495019058</v>
       </c>
       <c r="M7" t="n">
-        <v>121.7419792720121</v>
+        <v>123.6130227773458</v>
       </c>
       <c r="N7" t="n">
-        <v>117.1237878936892</v>
+        <v>112.697727550607</v>
       </c>
       <c r="O7" t="n">
-        <v>4.618191378322839</v>
+        <v>10.91529522673882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5618847955998393</v>
+        <v>0.5767760996365826</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1158560807095368</v>
+        <v>0.109873372326596</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2628076828509504</v>
+        <v>0.2314344380250866</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5801718064608603</v>
+        <v>0.6043246941612436</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2678327365163862</v>
+        <v>0.3010600293726614</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4440679594885688</v>
+        <v>0.4082371567757013</v>
       </c>
       <c r="V7" t="n">
-        <v>102.416915851272</v>
+        <v>101.1446511627907</v>
       </c>
       <c r="W7" t="n">
-        <v>119.8438356164383</v>
+        <v>121.2093023255813</v>
       </c>
       <c r="X7" t="n">
-        <v>4.485714285714286</v>
+        <v>4.858604651162791</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5953958019383466</v>
+        <v>0.6162103193762901</v>
       </c>
       <c r="Z7" t="n">
-        <v>121.19</v>
+        <v>127.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.35</v>
+        <v>11.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.967224035556209</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC7" t="n">
-        <v>120.0962116764131</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD7" t="n">
-        <v>110.1289876408569</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1234,106 +1234,106 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12309548916628</v>
+        <v>1.888626284526246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>1594.888</v>
+        <v>1573.994</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2206</v>
+        <v>-1.7339</v>
       </c>
       <c r="I8" t="n">
-        <v>1504.444513513514</v>
+        <v>1497.461684931507</v>
       </c>
       <c r="J8" t="n">
-        <v>119.9034705024823</v>
+        <v>115.4732767025396</v>
       </c>
       <c r="K8" t="n">
-        <v>115.5299617820473</v>
+        <v>110.9438758825305</v>
       </c>
       <c r="L8" t="n">
-        <v>4.37350872043504</v>
+        <v>4.529400820009132</v>
       </c>
       <c r="M8" t="n">
-        <v>123.9577726902272</v>
+        <v>114.1711478489707</v>
       </c>
       <c r="N8" t="n">
-        <v>115.1631605208729</v>
+        <v>112.6584127834637</v>
       </c>
       <c r="O8" t="n">
-        <v>8.794612169354288</v>
+        <v>1.512735065507021</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5759469052135504</v>
+        <v>0.5414669011587684</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1099738907185844</v>
+        <v>0.1271019501579171</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2340478148113104</v>
+        <v>0.349966902743361</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5972293103528855</v>
+        <v>0.5390639306586834</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3052834906225837</v>
+        <v>0.2624693584063961</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4080461721307113</v>
+        <v>0.3485133151534441</v>
       </c>
       <c r="V8" t="n">
-        <v>101.3713513513513</v>
+        <v>99.35631748589849</v>
       </c>
       <c r="W8" t="n">
-        <v>121.4949324324324</v>
+        <v>114.7211925866237</v>
       </c>
       <c r="X8" t="n">
-        <v>4.44527027027027</v>
+        <v>4.74375503626108</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6157894090930578</v>
+        <v>0.5746826108918848</v>
       </c>
       <c r="Z8" t="n">
-        <v>128.16</v>
+        <v>113.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.520000000000001</v>
+        <v>2.029999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.722616812266775</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC8" t="n">
-        <v>116.5392386763017</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD8" t="n">
-        <v>113.8166218640349</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1342,24 +1342,24 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.764104697636828</v>
+        <v>0.3132942668198304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1369,79 +1369,79 @@
         <v>46108</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>1571.955</v>
+        <v>1637.716</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.115</v>
+        <v>-0.4165</v>
       </c>
       <c r="I9" t="n">
-        <v>1499.029041666667</v>
+        <v>1490.265150684932</v>
       </c>
       <c r="J9" t="n">
-        <v>114.9323361639937</v>
+        <v>117.1208875317718</v>
       </c>
       <c r="K9" t="n">
-        <v>111.2556119534676</v>
+        <v>112.6775919801654</v>
       </c>
       <c r="L9" t="n">
-        <v>3.676724210526132</v>
+        <v>4.443295551606407</v>
       </c>
       <c r="M9" t="n">
-        <v>112.0302305875271</v>
+        <v>121.7419792720121</v>
       </c>
       <c r="N9" t="n">
-        <v>116.5634740813627</v>
+        <v>117.1237878936892</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.533243493835618</v>
+        <v>4.618191378322839</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5410913763796836</v>
+        <v>0.5618847955998393</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1292976350608657</v>
+        <v>0.1158560807095368</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3486366200960201</v>
+        <v>0.2628076828509504</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5367883864031614</v>
+        <v>0.5801718064608603</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2645569099514823</v>
+        <v>0.2678327365163862</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3464841714782828</v>
+        <v>0.4440679594885688</v>
       </c>
       <c r="V9" t="n">
-        <v>99.32436403508771</v>
+        <v>102.416915851272</v>
       </c>
       <c r="W9" t="n">
-        <v>114.1991959064327</v>
+        <v>119.8438356164383</v>
       </c>
       <c r="X9" t="n">
-        <v>3.995614035087719</v>
+        <v>4.485714285714286</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5742658756874466</v>
+        <v>0.5953958019383466</v>
       </c>
       <c r="Z9" t="n">
-        <v>112.07</v>
+        <v>121.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.32</v>
+        <v>4.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.413694058608522</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC9" t="n">
-        <v>112.3850185369902</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD9" t="n">
-        <v>108.9713244783817</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1450,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.2761841800297318</v>
+        <v>1.209959435189236</v>
       </c>
     </row>
     <row r="10">
@@ -1477,7 +1477,7 @@
         <v>46109</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
         <v>1582.381</v>
@@ -1489,13 +1489,13 @@
         <v>1499.834767123288</v>
       </c>
       <c r="J10" t="n">
-        <v>114.4282222729561</v>
+        <v>114.3754224965118</v>
       </c>
       <c r="K10" t="n">
-        <v>110.9083716287702</v>
+        <v>110.9079435992749</v>
       </c>
       <c r="L10" t="n">
-        <v>3.519850644185845</v>
+        <v>3.467478897236908</v>
       </c>
       <c r="M10" t="n">
         <v>108.2073708580311</v>
@@ -1507,34 +1507,34 @@
         <v>-3.833425493377661</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5556122724308996</v>
+        <v>0.5552618481181406</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1250658662264155</v>
+        <v>0.1250625715671174</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2596696231719286</v>
+        <v>0.2596254830453977</v>
       </c>
       <c r="S10" t="n">
         <v>0.5249427043843291</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2949825387157494</v>
+        <v>0.2951591537827984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4209706593521603</v>
+        <v>0.4211314769536547</v>
       </c>
       <c r="V10" t="n">
-        <v>102.8994520547946</v>
+        <v>102.8930136986302</v>
       </c>
       <c r="W10" t="n">
-        <v>117.3541498791297</v>
+        <v>117.2966609589041</v>
       </c>
       <c r="X10" t="n">
-        <v>3.075745366639806</v>
+        <v>3.028253424657534</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5899963583557084</v>
+        <v>0.5897067782655263</v>
       </c>
       <c r="Z10" t="n">
         <v>110.85</v>
@@ -1561,103 +1561,103 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3065025076973801</v>
+        <v>0.3453937181903723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>1590.882</v>
+        <v>1557.165</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6352</v>
+        <v>-1.2445</v>
       </c>
       <c r="I11" t="n">
-        <v>1495.442657534247</v>
+        <v>1497.633094594595</v>
       </c>
       <c r="J11" t="n">
-        <v>115.8085488022522</v>
+        <v>116.2449984779174</v>
       </c>
       <c r="K11" t="n">
-        <v>112.6625142964027</v>
+        <v>113.5402952146427</v>
       </c>
       <c r="L11" t="n">
-        <v>3.14603450584958</v>
+        <v>2.704703263274769</v>
       </c>
       <c r="M11" t="n">
-        <v>117.7042768679311</v>
+        <v>122.2639351473496</v>
       </c>
       <c r="N11" t="n">
-        <v>111.4027382732558</v>
+        <v>113.0364485781071</v>
       </c>
       <c r="O11" t="n">
-        <v>6.301538594675312</v>
+        <v>9.227486569242526</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5524535248134598</v>
+        <v>0.5632271125158083</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1285986555778894</v>
+        <v>0.1261370559508971</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3063239802530656</v>
+        <v>0.2356273039812238</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5617471810919845</v>
+        <v>0.5979483400602705</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2525413550482655</v>
+        <v>0.304845913388296</v>
       </c>
       <c r="U11" t="n">
-        <v>0.484369618853381</v>
+        <v>0.4040940941967319</v>
       </c>
       <c r="V11" t="n">
-        <v>99.89104261796042</v>
+        <v>98.80972178060414</v>
       </c>
       <c r="W11" t="n">
-        <v>116.277397260274</v>
+        <v>114.2118441971383</v>
       </c>
       <c r="X11" t="n">
-        <v>4.470319634703197</v>
+        <v>1.697138314785373</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5896003764595595</v>
+        <v>0.6070779040559841</v>
       </c>
       <c r="Z11" t="n">
-        <v>117.51</v>
+        <v>121.06</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.960000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>-10.13717477219789</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC11" t="n">
-        <v>104.7204689341547</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD11" t="n">
-        <v>114.8576437063525</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1669,103 +1669,103 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4017176616233741</v>
+        <v>0.6619823415113724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1561.924</v>
+        <v>1506.79</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0758</v>
+        <v>0.7286</v>
       </c>
       <c r="I12" t="n">
-        <v>1496.091753424658</v>
+        <v>1495.222095890411</v>
       </c>
       <c r="J12" t="n">
-        <v>116.6976450061723</v>
+        <v>113.4806201819405</v>
       </c>
       <c r="K12" t="n">
-        <v>114.1356646171615</v>
+        <v>110.8121139286902</v>
       </c>
       <c r="L12" t="n">
-        <v>2.561980389010774</v>
+        <v>2.668506253250338</v>
       </c>
       <c r="M12" t="n">
-        <v>120.9895837814511</v>
+        <v>117.2308493376413</v>
       </c>
       <c r="N12" t="n">
-        <v>110.7663997945813</v>
+        <v>113.6359976902031</v>
       </c>
       <c r="O12" t="n">
-        <v>10.2231839868698</v>
+        <v>3.594851647438205</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5728718935793922</v>
+        <v>0.5451525426361739</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1250048049620333</v>
+        <v>0.1153459035030485</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2384006964565819</v>
+        <v>0.2526799779822146</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5794717358649966</v>
+        <v>0.574704985225027</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3256080969081872</v>
+        <v>0.2597286308871877</v>
       </c>
       <c r="U12" t="n">
-        <v>0.398792188873006</v>
+        <v>0.3685756589552447</v>
       </c>
       <c r="V12" t="n">
-        <v>100.3109648600358</v>
+        <v>100.9594977168949</v>
       </c>
       <c r="W12" t="n">
-        <v>116.6298391899941</v>
+        <v>114.6811263318113</v>
       </c>
       <c r="X12" t="n">
-        <v>1.857057772483622</v>
+        <v>3.082572298325723</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6091767095408253</v>
+        <v>0.5792077900500039</v>
       </c>
       <c r="Z12" t="n">
-        <v>120.41</v>
+        <v>118.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>5.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.827913300592181</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC12" t="n">
-        <v>114.1496737878887</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD12" t="n">
-        <v>112.3217604872965</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -1774,132 +1774,132 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.705420434131273</v>
+        <v>0.3447388734279041</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>1555.704</v>
+        <v>1586.136</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2948</v>
+        <v>2.924</v>
       </c>
       <c r="I13" t="n">
-        <v>1499.864205479452</v>
+        <v>1495.093094594595</v>
       </c>
       <c r="J13" t="n">
-        <v>115.757475555234</v>
+        <v>115.5562531244554</v>
       </c>
       <c r="K13" t="n">
-        <v>113.5243794173386</v>
+        <v>112.94315819016</v>
       </c>
       <c r="L13" t="n">
-        <v>2.233096137895396</v>
+        <v>2.613094934295391</v>
       </c>
       <c r="M13" t="n">
-        <v>121.4178935735819</v>
+        <v>116.9555428221011</v>
       </c>
       <c r="N13" t="n">
-        <v>113.4128181862122</v>
+        <v>111.710624465496</v>
       </c>
       <c r="O13" t="n">
-        <v>8.005075387369581</v>
+        <v>5.244918356605079</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5587874319807177</v>
+        <v>0.5523941966402368</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1247320876483693</v>
+        <v>0.128750466774083</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2371794664509569</v>
+        <v>0.3034645174819195</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5863357204889815</v>
+        <v>0.5603704240638722</v>
       </c>
       <c r="T13" t="n">
-        <v>0.302649882366875</v>
+        <v>0.2507148379026036</v>
       </c>
       <c r="U13" t="n">
-        <v>0.403575967340675</v>
+        <v>0.4840705248689424</v>
       </c>
       <c r="V13" t="n">
-        <v>98.85970835174547</v>
+        <v>99.67280308880309</v>
       </c>
       <c r="W13" t="n">
-        <v>113.8276623950508</v>
+        <v>115.8162162162162</v>
       </c>
       <c r="X13" t="n">
-        <v>1.318161732213875</v>
+        <v>4.034749034749035</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6024951053323064</v>
+        <v>0.5892582805895568</v>
       </c>
       <c r="Z13" t="n">
-        <v>120.84</v>
+        <v>115.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.85</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.815266446541752</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC13" t="n">
-        <v>113.8106821492749</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD13" t="n">
-        <v>108.9954157027332</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.605524366572649</v>
+        <v>0.4462025172999437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1909,79 +1909,79 @@
         <v>46108</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>1541.118</v>
+        <v>1561.924</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.3788</v>
+        <v>4.0758</v>
       </c>
       <c r="I14" t="n">
-        <v>1506.244520547945</v>
+        <v>1496.091753424658</v>
       </c>
       <c r="J14" t="n">
-        <v>113.6744770063884</v>
+        <v>116.6976450061723</v>
       </c>
       <c r="K14" t="n">
-        <v>111.6215649076278</v>
+        <v>114.1356646171615</v>
       </c>
       <c r="L14" t="n">
-        <v>2.052912098760554</v>
+        <v>2.561980389010774</v>
       </c>
       <c r="M14" t="n">
-        <v>116.869811919753</v>
+        <v>120.9895837814511</v>
       </c>
       <c r="N14" t="n">
-        <v>118.1426582706718</v>
+        <v>110.7663997945813</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.272846350918792</v>
+        <v>10.2231839868698</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5365638327515762</v>
+        <v>0.5728718935793922</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1128644300413538</v>
+        <v>0.1250048049620333</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2513092669920794</v>
+        <v>0.2384006964565819</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5390060805141018</v>
+        <v>0.5794717358649966</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2753466778627371</v>
+        <v>0.3256080969081872</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4056929191681111</v>
+        <v>0.398792188873006</v>
       </c>
       <c r="V14" t="n">
-        <v>105.8955572010367</v>
+        <v>100.3109648600358</v>
       </c>
       <c r="W14" t="n">
-        <v>120.3894853757867</v>
+        <v>116.6298391899941</v>
       </c>
       <c r="X14" t="n">
-        <v>2.258052573121066</v>
+        <v>1.857057772483622</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5758687776277032</v>
+        <v>0.6091767095408253</v>
       </c>
       <c r="Z14" t="n">
-        <v>121.97</v>
+        <v>120.41</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2.46</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.094669144490311</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC14" t="n">
-        <v>111.6804548463295</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD14" t="n">
-        <v>112.7751239908198</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.2795777154672761</v>
+        <v>1.826494471608916</v>
       </c>
     </row>
     <row r="15">
@@ -2017,7 +2017,7 @@
         <v>46109</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>1504.204</v>
@@ -2029,13 +2029,13 @@
         <v>1517.468767123288</v>
       </c>
       <c r="J15" t="n">
-        <v>113.7260737570083</v>
+        <v>113.6894727017141</v>
       </c>
       <c r="K15" t="n">
-        <v>111.7420676851524</v>
+        <v>111.7575872193213</v>
       </c>
       <c r="L15" t="n">
-        <v>1.984006071855917</v>
+        <v>1.931885482392746</v>
       </c>
       <c r="M15" t="n">
         <v>119.5347307103522</v>
@@ -2047,34 +2047,34 @@
         <v>5.51016789799468</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5402559721952398</v>
+        <v>0.5401535652889792</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1182637479616529</v>
+        <v>0.1183191744178145</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2893646183530116</v>
+        <v>0.2890819478950038</v>
       </c>
       <c r="S15" t="n">
         <v>0.5577788690445787</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2283680449583401</v>
+        <v>0.2284333411757111</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4581499540849762</v>
+        <v>0.4580228789478641</v>
       </c>
       <c r="V15" t="n">
-        <v>99.58012720156557</v>
+        <v>99.56970776255709</v>
       </c>
       <c r="W15" t="n">
-        <v>113.1555772994129</v>
+        <v>113.1041095890411</v>
       </c>
       <c r="X15" t="n">
-        <v>2.055283757338551</v>
+        <v>1.998630136986301</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5712835721441518</v>
+        <v>0.5712332507838508</v>
       </c>
       <c r="Z15" t="n">
         <v>116.18</v>
@@ -2101,430 +2101,430 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.03743090579493385</v>
+        <v>0.03972186941841134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612737</v>
+        <v>1610612748</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>1515.872</v>
+        <v>1536.983</v>
       </c>
       <c r="H16" t="n">
-        <v>2.601</v>
+        <v>-2.9846</v>
       </c>
       <c r="I16" t="n">
-        <v>1485.918486486486</v>
+        <v>1508.021162162162</v>
       </c>
       <c r="J16" t="n">
-        <v>114.0423870586319</v>
+        <v>113.6306665551732</v>
       </c>
       <c r="K16" t="n">
-        <v>112.3267853106687</v>
+        <v>111.7891211115908</v>
       </c>
       <c r="L16" t="n">
-        <v>1.715601747963108</v>
+        <v>1.841545443582428</v>
       </c>
       <c r="M16" t="n">
-        <v>118.9394660785629</v>
+        <v>115.8736283700667</v>
       </c>
       <c r="N16" t="n">
-        <v>109.1683779977121</v>
+        <v>119.2840964864683</v>
       </c>
       <c r="O16" t="n">
-        <v>9.771088080850765</v>
+        <v>-3.410468116401621</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5536219381182681</v>
+        <v>0.5365868750358272</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1163042263345683</v>
+        <v>0.1115060662447834</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2418419141030064</v>
+        <v>0.2504201599983731</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5609427023576505</v>
+        <v>0.5367135105411195</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2382952768134829</v>
+        <v>0.2708280425983094</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4298126046579471</v>
+        <v>0.4034576356833746</v>
       </c>
       <c r="V16" t="n">
-        <v>103.7007158509861</v>
+        <v>105.7943243243244</v>
       </c>
       <c r="W16" t="n">
-        <v>118.3192111029949</v>
+        <v>120.2203453453454</v>
       </c>
       <c r="X16" t="n">
-        <v>1.953250547845143</v>
+        <v>2.037162162162162</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5845622037081731</v>
+        <v>0.5749539790763334</v>
       </c>
       <c r="Z16" t="n">
-        <v>121.38</v>
+        <v>120.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>-4.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.981113782848854</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC16" t="n">
-        <v>112.8029837792552</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD16" t="n">
-        <v>113.7840975621041</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.6075258963062041</v>
+        <v>0.3168871637284518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>1505.042</v>
+        <v>1515.872</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7107</v>
+        <v>2.601</v>
       </c>
       <c r="I17" t="n">
-        <v>1496.795430555555</v>
+        <v>1485.918486486486</v>
       </c>
       <c r="J17" t="n">
-        <v>113.0784774599792</v>
+        <v>114.0272831681167</v>
       </c>
       <c r="K17" t="n">
-        <v>111.5605635885357</v>
+        <v>112.3220705995947</v>
       </c>
       <c r="L17" t="n">
-        <v>1.517913871443526</v>
+        <v>1.70521256852204</v>
       </c>
       <c r="M17" t="n">
-        <v>115.8694895112704</v>
+        <v>118.9394660785629</v>
       </c>
       <c r="N17" t="n">
-        <v>114.700895172135</v>
+        <v>109.1683779977121</v>
       </c>
       <c r="O17" t="n">
-        <v>1.168594339135413</v>
+        <v>9.771088080850765</v>
       </c>
       <c r="P17" t="n">
-        <v>0.542778232132711</v>
+        <v>0.5535622747566453</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1160961101089527</v>
+        <v>0.1163040841905131</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2550216234867304</v>
+        <v>0.2417115844459832</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5662527341443399</v>
+        <v>0.5609427023576505</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2593964848600521</v>
+        <v>0.2382826048271262</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3691890880194976</v>
+        <v>0.4297686423322414</v>
       </c>
       <c r="V17" t="n">
-        <v>100.7830147058824</v>
+        <v>103.7085516285516</v>
       </c>
       <c r="W17" t="n">
-        <v>114.0661764705883</v>
+        <v>118.3125433125433</v>
       </c>
       <c r="X17" t="n">
-        <v>1.865196078431373</v>
+        <v>1.941787941787942</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5768109034513951</v>
+        <v>0.5845071262333967</v>
       </c>
       <c r="Z17" t="n">
-        <v>116.48</v>
+        <v>121.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>-4.536933640611859</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC17" t="n">
-        <v>108.3888858603967</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD17" t="n">
-        <v>112.9258195010085</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.07773062798800867</v>
+        <v>0.6641014559642947</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>1523.417</v>
+        <v>1469.575</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9164</v>
+        <v>0.1933</v>
       </c>
       <c r="I18" t="n">
-        <v>1492.514652173913</v>
+        <v>1497.223657534247</v>
       </c>
       <c r="J18" t="n">
-        <v>113.4568142054788</v>
+        <v>113.4308448980004</v>
       </c>
       <c r="K18" t="n">
-        <v>112.8190945895778</v>
+        <v>113.1733010220948</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6377196159009948</v>
+        <v>0.2575438759055876</v>
       </c>
       <c r="M18" t="n">
-        <v>117.545021261121</v>
+        <v>114.285926442809</v>
       </c>
       <c r="N18" t="n">
-        <v>119.2147304854601</v>
+        <v>114.9526667337413</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.669709224339038</v>
+        <v>-0.6667402909323203</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5350509465278205</v>
+        <v>0.5322507943117178</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1151056882291826</v>
+        <v>0.1138856581463011</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2453037725407861</v>
+        <v>0.2596154503377267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5540849780805727</v>
+        <v>0.5389088110303376</v>
       </c>
       <c r="T18" t="n">
-        <v>0.315402177160877</v>
+        <v>0.2835401824238258</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3882862478687213</v>
+        <v>0.3947943751215166</v>
       </c>
       <c r="V18" t="n">
-        <v>101.9763812033377</v>
+        <v>102.6970112079701</v>
       </c>
       <c r="W18" t="n">
-        <v>115.8142292490119</v>
+        <v>116.2067247820672</v>
       </c>
       <c r="X18" t="n">
-        <v>1.31576635924462</v>
+        <v>-0.2374429223744292</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5804581042604025</v>
+        <v>0.5746603057191856</v>
       </c>
       <c r="Z18" t="n">
-        <v>120.73</v>
+        <v>118.27</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC18" t="n">
-        <v>107.6152962364644</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD18" t="n">
-        <v>108.1384073962044</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.3316800258638012</v>
+        <v>0.567987890700778</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>1469.575</v>
+        <v>1481.014</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1933</v>
+        <v>-1.3473</v>
       </c>
       <c r="I19" t="n">
-        <v>1497.223657534247</v>
+        <v>1502.113689189189</v>
       </c>
       <c r="J19" t="n">
-        <v>113.4308448980004</v>
+        <v>112.4044524312674</v>
       </c>
       <c r="K19" t="n">
-        <v>113.1733010220948</v>
+        <v>112.7861785332087</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2575438759055876</v>
+        <v>-0.3817261019414203</v>
       </c>
       <c r="M19" t="n">
-        <v>114.285926442809</v>
+        <v>110.2168956740512</v>
       </c>
       <c r="N19" t="n">
-        <v>114.9526667337413</v>
+        <v>116.9725404071555</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6667402909323203</v>
+        <v>-6.755644733104332</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5322507943117178</v>
+        <v>0.5504793651048593</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1138856581463011</v>
+        <v>0.1328372431307155</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2596154503377267</v>
+        <v>0.2570915493288971</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5389088110303376</v>
+        <v>0.5476170154961076</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2835401824238258</v>
+        <v>0.2384067173177889</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3947943751215166</v>
+        <v>0.5019426603519649</v>
       </c>
       <c r="V19" t="n">
-        <v>102.6970112079701</v>
+        <v>101.9257894736842</v>
       </c>
       <c r="W19" t="n">
-        <v>116.2067247820672</v>
+        <v>114.6052631578947</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2374429223744292</v>
+        <v>-0.3289473684210526</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5746603057191856</v>
+        <v>0.5840270860744731</v>
       </c>
       <c r="Z19" t="n">
-        <v>118.27</v>
+        <v>113.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.5</v>
+        <v>-6.619999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>-6.382503892565079</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC19" t="n">
-        <v>109.8789897646453</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD19" t="n">
-        <v>116.2614936572104</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2533,103 +2533,103 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.53837235106892</v>
+        <v>-0.09806936194486636</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>1480.385</v>
+        <v>1461.235</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9923</v>
+        <v>1.549</v>
       </c>
       <c r="I20" t="n">
-        <v>1505.423397260274</v>
+        <v>1506.38652</v>
       </c>
       <c r="J20" t="n">
-        <v>112.9272243241923</v>
+        <v>111.2216623861247</v>
       </c>
       <c r="K20" t="n">
-        <v>112.6736155412076</v>
+        <v>112.1168712348716</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2536087829846333</v>
+        <v>-0.8952088487468716</v>
       </c>
       <c r="M20" t="n">
-        <v>112.00648753696</v>
+        <v>112.1685038482119</v>
       </c>
       <c r="N20" t="n">
-        <v>116.8555593943861</v>
+        <v>102.5585218996881</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.849071857425976</v>
+        <v>9.60998194852375</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5527456657835074</v>
+        <v>0.533728531648594</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1326078050536529</v>
+        <v>0.1413464855055116</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2577790755092829</v>
+        <v>0.3094815730887919</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5496723598682487</v>
+        <v>0.549333250051234</v>
       </c>
       <c r="T20" t="n">
-        <v>0.242959173474206</v>
+        <v>0.2895384070123483</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5020489910994771</v>
+        <v>0.4664863724660987</v>
       </c>
       <c r="V20" t="n">
-        <v>102.1573047019622</v>
+        <v>103.5428842105263</v>
       </c>
       <c r="W20" t="n">
-        <v>115.4057756386523</v>
+        <v>115.4442105263158</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3483894853757867</v>
+        <v>-0.3252631578947368</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5865799680524209</v>
+        <v>0.5706694607236947</v>
       </c>
       <c r="Z20" t="n">
-        <v>116.15</v>
+        <v>115.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.539999999999999</v>
+        <v>10.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.402868486532558</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC20" t="n">
-        <v>112.5227430890375</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD20" t="n">
-        <v>110.1198746025049</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -2641,115 +2641,115 @@
         <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1306309898434237</v>
+        <v>-0.2562829430804895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>1464.524</v>
+        <v>1524.235</v>
       </c>
       <c r="H21" t="n">
-        <v>1.319</v>
+        <v>-2.6666</v>
       </c>
       <c r="I21" t="n">
-        <v>1508.2545</v>
+        <v>1489.969457142857</v>
       </c>
       <c r="J21" t="n">
-        <v>110.6928115814477</v>
+        <v>112.1867878734385</v>
       </c>
       <c r="K21" t="n">
-        <v>112.5839096652461</v>
+        <v>113.1839346520263</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.891098083798451</v>
+        <v>-0.9971467785878004</v>
       </c>
       <c r="M21" t="n">
-        <v>112.4840355392312</v>
+        <v>112.6204706932376</v>
       </c>
       <c r="N21" t="n">
-        <v>104.5944809462976</v>
+        <v>122.5455492412534</v>
       </c>
       <c r="O21" t="n">
-        <v>7.889554592933586</v>
+        <v>-9.925078548015824</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5311314223553073</v>
+        <v>0.5304614213388</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1427629640290994</v>
+        <v>0.1185123358169038</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3107058577485636</v>
+        <v>0.2443306741994797</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5483660303982195</v>
+        <v>0.5325938772236181</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2892164197846558</v>
+        <v>0.3109914586971597</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4664916923112503</v>
+        <v>0.3909380133278451</v>
       </c>
       <c r="V21" t="n">
-        <v>103.5651801801802</v>
+        <v>102.2711688311689</v>
       </c>
       <c r="W21" t="n">
-        <v>114.9144144144144</v>
+        <v>114.8580086580086</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.363738738738739</v>
+        <v>-0.3428571428571434</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5684266943899089</v>
+        <v>0.575752054793909</v>
       </c>
       <c r="Z21" t="n">
-        <v>115.86</v>
+        <v>116.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.57</v>
+        <v>-7.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.840928550668963</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC21" t="n">
-        <v>109.2995408403883</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD21" t="n">
-        <v>113.1404693910572</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.0629615288489149</v>
+        <v>-0.3302803963629716</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.4171042313504106</v>
+        <v>-0.4207230540168955</v>
       </c>
     </row>
     <row r="23">
@@ -2875,76 +2875,76 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>1381.942</v>
+        <v>1380.194</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2995</v>
+        <v>1.6597</v>
       </c>
       <c r="I23" t="n">
-        <v>1508.055432432432</v>
+        <v>1508.015253333333</v>
       </c>
       <c r="J23" t="n">
-        <v>112.1449809261782</v>
+        <v>111.9767068327859</v>
       </c>
       <c r="K23" t="n">
-        <v>116.1627917910209</v>
+        <v>116.7282581229986</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.017810864842693</v>
+        <v>-4.751551290212712</v>
       </c>
       <c r="M23" t="n">
-        <v>115.3883803591507</v>
+        <v>113.784720892972</v>
       </c>
       <c r="N23" t="n">
-        <v>114.2484261927667</v>
+        <v>115.9210420958728</v>
       </c>
       <c r="O23" t="n">
-        <v>1.139954166384094</v>
+        <v>-2.136321202900874</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5274461080296675</v>
+        <v>0.5273226041640725</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1169953406743485</v>
+        <v>0.1163695129258574</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2696736446660632</v>
+        <v>0.2662434068103681</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5440000808017124</v>
+        <v>0.5421438336073836</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2827323387604225</v>
+        <v>0.2842289577821487</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3590735779800531</v>
+        <v>0.3594156293884965</v>
       </c>
       <c r="V23" t="n">
-        <v>102.7059295659296</v>
+        <v>102.6263294117647</v>
       </c>
       <c r="W23" t="n">
-        <v>115.0941850941851</v>
+        <v>114.8635294117647</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.207207207207206</v>
+        <v>-4.875294117647059</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5675831110895945</v>
+        <v>0.5671303949984788</v>
       </c>
       <c r="Z23" t="n">
-        <v>115.81</v>
+        <v>114.51</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>-1.04</v>
       </c>
       <c r="AB23" t="n">
         <v>-9.447870926461551</v>
@@ -2956,16 +2956,16 @@
         <v>117.8388903788833</v>
       </c>
       <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
       </c>
       <c r="AG23" t="n">
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.27596812460072</v>
+        <v>-0.2712955643181959</v>
       </c>
     </row>
     <row r="24">
@@ -2989,7 +2989,7 @@
         <v>46109</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
         <v>1382.574</v>
@@ -3001,13 +3001,13 @@
         <v>1496.613957746479</v>
       </c>
       <c r="J24" t="n">
-        <v>110.5082319094104</v>
+        <v>110.5055249362239</v>
       </c>
       <c r="K24" t="n">
-        <v>115.3610514702156</v>
+        <v>115.3575291679639</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.852819560805172</v>
+        <v>-4.852004231739963</v>
       </c>
       <c r="M24" t="n">
         <v>107.3702020857575</v>
@@ -3019,34 +3019,34 @@
         <v>-15.54603033758751</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5334166269017803</v>
+        <v>0.5334111903734295</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1258961809168631</v>
+        <v>0.1258870247217159</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2501302627425632</v>
+        <v>0.2500970280116494</v>
       </c>
       <c r="S24" t="n">
         <v>0.5183945678850819</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2561223111375087</v>
+        <v>0.2560697184893396</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4293641667531403</v>
+        <v>0.429324023984164</v>
       </c>
       <c r="V24" t="n">
-        <v>103.9257298335467</v>
+        <v>103.9323681624631</v>
       </c>
       <c r="W24" t="n">
-        <v>115.1446862996159</v>
+        <v>115.1500163773338</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.230473751600512</v>
+        <v>-4.227644939403866</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5703615908919931</v>
+        <v>0.5703483866190858</v>
       </c>
       <c r="Z24" t="n">
         <v>112.4</v>
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9394223620756135</v>
+        <v>-0.9737260303339774</v>
       </c>
     </row>
     <row r="25">
@@ -3097,7 +3097,7 @@
         <v>46108</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
         <v>1368.156</v>
@@ -3109,13 +3109,13 @@
         <v>1505.346541666667</v>
       </c>
       <c r="J25" t="n">
-        <v>108.7575417537635</v>
+        <v>108.7476742754251</v>
       </c>
       <c r="K25" t="n">
-        <v>113.8564584325441</v>
+        <v>113.8379254495863</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.098916678780511</v>
+        <v>-5.090251174161131</v>
       </c>
       <c r="M25" t="n">
         <v>111.7044445975594</v>
@@ -3127,34 +3127,34 @@
         <v>-7.702899677535243</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5302917364839623</v>
+        <v>0.5302588372436102</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1244402321725155</v>
+        <v>0.1244621746614578</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2288054958013864</v>
+        <v>0.2287606857794077</v>
       </c>
       <c r="S25" t="n">
         <v>0.5380780482675814</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2884597729835739</v>
+        <v>0.2885229756050143</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3471582529969384</v>
+        <v>0.3471190076599779</v>
       </c>
       <c r="V25" t="n">
-        <v>104.422972972973</v>
+        <v>104.4225385802469</v>
       </c>
       <c r="W25" t="n">
-        <v>113.7162162162162</v>
+        <v>113.7056327160494</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.837837837837838</v>
+        <v>-4.828703703703704</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5659782028322644</v>
+        <v>0.5659510480172956</v>
       </c>
       <c r="Z25" t="n">
         <v>116.83</v>
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8303488021411535</v>
+        <v>-0.8582446795382304</v>
       </c>
     </row>
     <row r="26">
@@ -3199,76 +3199,76 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>1395.642</v>
+        <v>1392.576</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.0688</v>
+        <v>-1.9533</v>
       </c>
       <c r="I26" t="n">
-        <v>1492.286444444444</v>
+        <v>1495.56301369863</v>
       </c>
       <c r="J26" t="n">
-        <v>110.8694414786139</v>
+        <v>111.0014556837374</v>
       </c>
       <c r="K26" t="n">
-        <v>117.060409327615</v>
+        <v>117.2487831258569</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.190967849001092</v>
+        <v>-6.247327442119441</v>
       </c>
       <c r="M26" t="n">
-        <v>106.8382962042546</v>
+        <v>108.5295033782342</v>
       </c>
       <c r="N26" t="n">
-        <v>125.2761142486587</v>
+        <v>125.2671883999827</v>
       </c>
       <c r="O26" t="n">
-        <v>-18.43781804440419</v>
+        <v>-16.73768502174848</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5630501233332103</v>
+        <v>0.5654017522911772</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1312647622832813</v>
+        <v>0.1327099764755128</v>
       </c>
       <c r="R26" t="n">
-        <v>0.205071837990632</v>
+        <v>0.2028133467877343</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5575832452976177</v>
+        <v>0.5718101821538651</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2251872788982814</v>
+        <v>0.2258276597635588</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4492826341808012</v>
+        <v>0.4513818030705053</v>
       </c>
       <c r="V26" t="n">
-        <v>99.63772839506174</v>
+        <v>99.64861145703611</v>
       </c>
       <c r="W26" t="n">
-        <v>110.2641975308642</v>
+        <v>110.4564134495641</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.550617283950617</v>
+        <v>-6.503113325031133</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5866829768336588</v>
+        <v>0.5891929792821271</v>
       </c>
       <c r="Z26" t="n">
-        <v>104.72</v>
+        <v>106.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>-18.77</v>
+        <v>-16.34</v>
       </c>
       <c r="AB26" t="n">
         <v>1.809266556998161</v>
@@ -3280,16 +3280,16 @@
         <v>112.4407240264407</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.738145041157377</v>
+        <v>-1.325354312902254</v>
       </c>
     </row>
     <row r="27">
@@ -3307,76 +3307,76 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>1334.762</v>
+        <v>1333.301</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3404</v>
+        <v>-0.994</v>
       </c>
       <c r="I27" t="n">
-        <v>1501.433684931507</v>
+        <v>1502.167067567568</v>
       </c>
       <c r="J27" t="n">
-        <v>108.9414065061395</v>
+        <v>109.4082721137208</v>
       </c>
       <c r="K27" t="n">
-        <v>116.9592428870239</v>
+        <v>116.9669386163866</v>
       </c>
       <c r="L27" t="n">
-        <v>-8.017836380884376</v>
+        <v>-7.558666502665764</v>
       </c>
       <c r="M27" t="n">
-        <v>113.9720100132994</v>
+        <v>116.0042747534943</v>
       </c>
       <c r="N27" t="n">
-        <v>122.9634590983539</v>
+        <v>121.8606261889702</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.991449085054599</v>
+        <v>-5.856351435475844</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5315300979455618</v>
+        <v>0.5342633260882516</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1225037289322189</v>
+        <v>0.1211612138054672</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2164939170842621</v>
+        <v>0.2127180396534026</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5719877966037397</v>
+        <v>0.5880433477755221</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2576289386000791</v>
+        <v>0.2560087037621718</v>
       </c>
       <c r="U27" t="n">
-        <v>0.419163014453595</v>
+        <v>0.419362922121174</v>
       </c>
       <c r="V27" t="n">
-        <v>103.038794520548</v>
+        <v>103.0802837837838</v>
       </c>
       <c r="W27" t="n">
-        <v>111.9221135029354</v>
+        <v>112.4827702702703</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.625048923679062</v>
+        <v>-8.099662162162163</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5670668705856138</v>
+        <v>0.5696062997045964</v>
       </c>
       <c r="Z27" t="n">
-        <v>114.71</v>
+        <v>117.09</v>
       </c>
       <c r="AA27" t="n">
-        <v>-10.36</v>
+        <v>-6.85</v>
       </c>
       <c r="AB27" t="n">
         <v>2.960186837728194</v>
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.6341182737992591</v>
+        <v>-1.163399342344155</v>
       </c>
     </row>
     <row r="28">
@@ -3421,7 +3421,7 @@
         <v>46109</v>
       </c>
       <c r="F28" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G28" t="n">
         <v>1309.746</v>
@@ -3433,13 +3433,13 @@
         <v>1510.146851351351</v>
       </c>
       <c r="J28" t="n">
-        <v>111.9508944993898</v>
+        <v>111.9393183172995</v>
       </c>
       <c r="K28" t="n">
-        <v>120.0449034796656</v>
+        <v>120.06006319031</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.094008980275769</v>
+        <v>-8.120744873010466</v>
       </c>
       <c r="M28" t="n">
         <v>112.5694386500763</v>
@@ -3451,34 +3451,34 @@
         <v>-8.860147496792447</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5377424847058799</v>
+        <v>0.5377139582276784</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1284890314310867</v>
+        <v>0.128478213953888</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2608945517585634</v>
+        <v>0.260821655944377</v>
       </c>
       <c r="S28" t="n">
         <v>0.5441452335372824</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2837604962548124</v>
+        <v>0.2836228157608296</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4067702277337957</v>
+        <v>0.4064907799125234</v>
       </c>
       <c r="V28" t="n">
-        <v>104.7094671814672</v>
+        <v>104.707846027846</v>
       </c>
       <c r="W28" t="n">
-        <v>117.2571428571429</v>
+        <v>117.2424242424242</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.301930501930503</v>
+        <v>-8.331695331695331</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5776469115932003</v>
+        <v>0.5775852326738963</v>
       </c>
       <c r="Z28" t="n">
         <v>117.28</v>
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.284522104721547</v>
+        <v>-1.339099494480226</v>
       </c>
     </row>
     <row r="29">
@@ -3523,76 +3523,76 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
-        <v>1313.534</v>
+        <v>1312.653</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.4716</v>
       </c>
       <c r="I29" t="n">
-        <v>1519.809027027027</v>
+        <v>1519.756533333333</v>
       </c>
       <c r="J29" t="n">
-        <v>109.4281799030073</v>
+        <v>109.1593090233404</v>
       </c>
       <c r="K29" t="n">
-        <v>118.878965700675</v>
+        <v>118.8379255399209</v>
       </c>
       <c r="L29" t="n">
-        <v>-9.450785797667715</v>
+        <v>-9.678616516580554</v>
       </c>
       <c r="M29" t="n">
-        <v>114.2670244637234</v>
+        <v>112.4250289223267</v>
       </c>
       <c r="N29" t="n">
-        <v>119.893539689222</v>
+        <v>121.1076641610534</v>
       </c>
       <c r="O29" t="n">
-        <v>-5.626515225498592</v>
+        <v>-8.682635238726643</v>
       </c>
       <c r="P29" t="n">
-        <v>0.524540984249476</v>
+        <v>0.5234094071119985</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1205089780689227</v>
+        <v>0.120760413153027</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2540644475573293</v>
+        <v>0.2538523429764113</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5510808243057159</v>
+        <v>0.5494064771474977</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2538995225608229</v>
+        <v>0.2562029693431301</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3368814227934586</v>
+        <v>0.337851023300382</v>
       </c>
       <c r="V29" t="n">
-        <v>101.7198417930125</v>
+        <v>101.6559301587301</v>
       </c>
       <c r="W29" t="n">
-        <v>110.8905735003296</v>
+        <v>110.584126984127</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.3295978905735</v>
+        <v>-10.49206349206349</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.5599371178912355</v>
+        <v>0.558874235035893</v>
       </c>
       <c r="Z29" t="n">
-        <v>113.72</v>
+        <v>111.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>-6.94</v>
+        <v>-9.979999999999999</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.1619477822758719</v>
@@ -3604,16 +3604,16 @@
         <v>114.7058177516698</v>
       </c>
       <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1</v>
       </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.742427653737866</v>
+        <v>-1.493679486412309</v>
       </c>
     </row>
     <row r="30">
@@ -3631,76 +3631,76 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F30" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G30" t="n">
-        <v>1293.161</v>
+        <v>1292.136</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.9172</v>
+        <v>-1.7089</v>
       </c>
       <c r="I30" t="n">
-        <v>1503.488369863014</v>
+        <v>1504.278040540541</v>
       </c>
       <c r="J30" t="n">
-        <v>106.6955098014094</v>
+        <v>107.098714182423</v>
       </c>
       <c r="K30" t="n">
-        <v>117.1995442841559</v>
+        <v>116.8059463442823</v>
       </c>
       <c r="L30" t="n">
-        <v>-10.50403448274647</v>
+        <v>-9.707232161859281</v>
       </c>
       <c r="M30" t="n">
-        <v>101.5411790819853</v>
+        <v>101.4996411341091</v>
       </c>
       <c r="N30" t="n">
-        <v>115.9104954328633</v>
+        <v>114.8456990541268</v>
       </c>
       <c r="O30" t="n">
-        <v>-14.3693163508779</v>
+        <v>-13.34605792001766</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5207768437008072</v>
+        <v>0.5228788571849389</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1381274414029926</v>
+        <v>0.1382980014451012</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2415353255029537</v>
+        <v>0.2425397378513306</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5091723796467565</v>
+        <v>0.5051319384702859</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2753334950170813</v>
+        <v>0.275625022426591</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4574277322053578</v>
+        <v>0.4584689476235541</v>
       </c>
       <c r="V30" t="n">
-        <v>99.19973239885314</v>
+        <v>99.15240893066978</v>
       </c>
       <c r="W30" t="n">
-        <v>106.1048104491876</v>
+        <v>106.3892479435958</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.560688117234788</v>
+        <v>-8.91069330199765</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5595961460666637</v>
+        <v>0.5616258067653828</v>
       </c>
       <c r="Z30" t="n">
-        <v>102.24</v>
+        <v>101.51</v>
       </c>
       <c r="AA30" t="n">
-        <v>-13.94</v>
+        <v>-13.06</v>
       </c>
       <c r="AB30" t="n">
         <v>-6.499587896466165</v>
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.969485449824274</v>
+        <v>-1.74802864321345</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>1260.505</v>
+        <v>1259.877</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.6629</v>
       </c>
       <c r="I31" t="n">
-        <v>1505.971041666667</v>
+        <v>1505.620547945206</v>
       </c>
       <c r="J31" t="n">
-        <v>109.0952966771024</v>
+        <v>108.4065914419434</v>
       </c>
       <c r="K31" t="n">
-        <v>119.9046698410049</v>
+        <v>119.788958771733</v>
       </c>
       <c r="L31" t="n">
-        <v>-10.80937316390264</v>
+        <v>-11.38236732978958</v>
       </c>
       <c r="M31" t="n">
-        <v>110.7523453050666</v>
+        <v>108.19083768269</v>
       </c>
       <c r="N31" t="n">
-        <v>123.1213169680927</v>
+        <v>122.0124736856867</v>
       </c>
       <c r="O31" t="n">
-        <v>-12.36897166302604</v>
+        <v>-13.82163600299673</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5376406795018001</v>
+        <v>0.5332562266103287</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1326161591191427</v>
+        <v>0.1330304639804435</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2394455899516614</v>
+        <v>0.2395338816723344</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5697131585022143</v>
+        <v>0.5556852771276904</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2362439240472753</v>
+        <v>0.23813071282829</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4073054159682846</v>
+        <v>0.4031452535117044</v>
       </c>
       <c r="V31" t="n">
-        <v>103.7179791666667</v>
+        <v>103.6997794854661</v>
       </c>
       <c r="W31" t="n">
-        <v>113.121875</v>
+        <v>112.3635148680254</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.971875</v>
+        <v>-11.62545940527898</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.569034840958254</v>
+        <v>0.5655237529046609</v>
       </c>
       <c r="Z31" t="n">
-        <v>117.36</v>
+        <v>114.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>-12.2</v>
+        <v>-13.85</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.364805526392233</v>
+        <v>-1.586478568935741</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -607,76 +607,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>1751.789</v>
+        <v>1754.887</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8212</v>
+        <v>1.4047</v>
       </c>
       <c r="I2" t="n">
-        <v>1494.331643835616</v>
+        <v>1496.527337837838</v>
       </c>
       <c r="J2" t="n">
-        <v>116.9236604844726</v>
+        <v>116.6136556484661</v>
       </c>
       <c r="K2" t="n">
-        <v>105.6674176696925</v>
+        <v>105.5200522436053</v>
       </c>
       <c r="L2" t="n">
-        <v>11.25624281478007</v>
+        <v>11.09360340486083</v>
       </c>
       <c r="M2" t="n">
-        <v>118.3443029623195</v>
+        <v>118.0988633185223</v>
       </c>
       <c r="N2" t="n">
-        <v>106.180148252947</v>
+        <v>105.7753252132156</v>
       </c>
       <c r="O2" t="n">
-        <v>12.16415470937252</v>
+        <v>12.32353810530669</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5603044545257453</v>
+        <v>0.5598477134663284</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1072115022136621</v>
+        <v>0.1082406721706002</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2212515301163551</v>
+        <v>0.2182158490783956</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5554877456399852</v>
+        <v>0.556510062828969</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2731351382098174</v>
+        <v>0.2732903189468668</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4241542036692744</v>
+        <v>0.4247527880134307</v>
       </c>
       <c r="V2" t="n">
-        <v>101.6736301369863</v>
+        <v>101.9579922779923</v>
       </c>
       <c r="W2" t="n">
-        <v>118.6845509893455</v>
+        <v>118.6602316602317</v>
       </c>
       <c r="X2" t="n">
-        <v>11.23972602739726</v>
+        <v>11.03629343629343</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5998096733057342</v>
+        <v>0.5997252508221246</v>
       </c>
       <c r="Z2" t="n">
-        <v>117.48</v>
+        <v>118.41</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.82</v>
+        <v>10.48</v>
       </c>
       <c r="AB2" t="n">
         <v>11.54061896828745</v>
@@ -688,16 +688,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.028066606257016</v>
+        <v>1.054647813739654</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>1731.476</v>
+        <v>1734.542</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8711</v>
+        <v>2.3067</v>
       </c>
       <c r="I3" t="n">
-        <v>1510.731652777778</v>
+        <v>1509.155082191781</v>
       </c>
       <c r="J3" t="n">
-        <v>117.5881719099868</v>
+        <v>117.6751750385884</v>
       </c>
       <c r="K3" t="n">
-        <v>108.7606052633075</v>
+        <v>108.9566992132959</v>
       </c>
       <c r="L3" t="n">
-        <v>8.827566646679363</v>
+        <v>8.718475825292476</v>
       </c>
       <c r="M3" t="n">
-        <v>124.9133382900033</v>
+        <v>123.4064825459442</v>
       </c>
       <c r="N3" t="n">
-        <v>108.2880836103874</v>
+        <v>107.8794850827237</v>
       </c>
       <c r="O3" t="n">
-        <v>16.62525467961587</v>
+        <v>15.52699746322049</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5617123911674172</v>
+        <v>0.5611559395719231</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.111928483695515</v>
+        <v>0.1116258364864828</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2567095738744724</v>
+        <v>0.2597479565148158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5878199071152477</v>
+        <v>0.576963378344393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2793716332417011</v>
+        <v>0.2795098994218806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4234448907172028</v>
+        <v>0.4221250686525996</v>
       </c>
       <c r="V3" t="n">
-        <v>101.9443097643097</v>
+        <v>102.0280389329488</v>
       </c>
       <c r="W3" t="n">
-        <v>119.6195286195286</v>
+        <v>119.7433309300649</v>
       </c>
       <c r="X3" t="n">
-        <v>8.619528619528619</v>
+        <v>8.397620764239367</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5973464063397171</v>
+        <v>0.5966895789339024</v>
       </c>
       <c r="Z3" t="n">
-        <v>126.19</v>
+        <v>124.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.8</v>
+        <v>14.73</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -796,7 +796,7 @@
         <v>114.9918244005745</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.132986260676032</v>
+        <v>1.05794599333186</v>
       </c>
     </row>
     <row r="4">
@@ -823,76 +823,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>1675.231</v>
+        <v>1679.675</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1345</v>
+        <v>0.3824</v>
       </c>
       <c r="I4" t="n">
-        <v>1490.009847222222</v>
+        <v>1494.837527027027</v>
       </c>
       <c r="J4" t="n">
-        <v>114.7328777483964</v>
+        <v>115.0499064043499</v>
       </c>
       <c r="K4" t="n">
-        <v>107.1815778754609</v>
+        <v>107.4550411192851</v>
       </c>
       <c r="L4" t="n">
-        <v>7.551299872935456</v>
+        <v>7.594865285064778</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6711111385838</v>
+        <v>118.1453411518176</v>
       </c>
       <c r="N4" t="n">
-        <v>106.2938922956714</v>
+        <v>106.6396216175497</v>
       </c>
       <c r="O4" t="n">
-        <v>14.3772188429124</v>
+        <v>11.50571953426796</v>
       </c>
       <c r="P4" t="n">
-        <v>0.545572739274102</v>
+        <v>0.5488759747473901</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1236188832626498</v>
+        <v>0.1245083001906635</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3037423859387597</v>
+        <v>0.3034672410517253</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5782982118830915</v>
+        <v>0.5762722377660962</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2924062974359234</v>
+        <v>0.2950725942446417</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3470148397348503</v>
+        <v>0.3478787002128193</v>
       </c>
       <c r="V4" t="n">
-        <v>102.1006372549019</v>
+        <v>101.6533075933076</v>
       </c>
       <c r="W4" t="n">
-        <v>117.3174019607843</v>
+        <v>117.0096525096526</v>
       </c>
       <c r="X4" t="n">
-        <v>8.19607843137255</v>
+        <v>8.077220077220078</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5819967496316072</v>
+        <v>0.5849306574504874</v>
       </c>
       <c r="Z4" t="n">
-        <v>122.14</v>
+        <v>117.04</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.53</v>
+        <v>10.45</v>
       </c>
       <c r="AB4" t="n">
         <v>1.549391602834736</v>
@@ -904,16 +904,16 @@
         <v>110.9722985057385</v>
       </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.5487767941119038</v>
+        <v>-0.2435200837404501</v>
       </c>
     </row>
     <row r="5">
@@ -931,76 +931,76 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>1660.123</v>
+        <v>1665.825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3613</v>
+        <v>1.1853</v>
       </c>
       <c r="I5" t="n">
-        <v>1488.980356164384</v>
+        <v>1490.29327027027</v>
       </c>
       <c r="J5" t="n">
-        <v>117.4960933759783</v>
+        <v>116.9162980958358</v>
       </c>
       <c r="K5" t="n">
-        <v>110.2106546073493</v>
+        <v>110.2850404118825</v>
       </c>
       <c r="L5" t="n">
-        <v>7.285438768629046</v>
+        <v>6.631257683953395</v>
       </c>
       <c r="M5" t="n">
-        <v>115.7381248363943</v>
+        <v>114.0503244848795</v>
       </c>
       <c r="N5" t="n">
-        <v>110.3489221931051</v>
+        <v>110.8482182518995</v>
       </c>
       <c r="O5" t="n">
-        <v>5.389202643289144</v>
+        <v>3.202106232980003</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5494459199122412</v>
+        <v>0.547409285206768</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1031261859981875</v>
+        <v>0.1047176941552145</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2904140245416875</v>
+        <v>0.2894756767696865</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5352442198784093</v>
+        <v>0.531073798697889</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2125352809958431</v>
+        <v>0.2141354934040395</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4655305832735115</v>
+        <v>0.4655994455248036</v>
       </c>
       <c r="V5" t="n">
-        <v>97.01012133072408</v>
+        <v>97.20340956340956</v>
       </c>
       <c r="W5" t="n">
-        <v>114.1197651663405</v>
+        <v>113.8108108108108</v>
       </c>
       <c r="X5" t="n">
-        <v>7.428180039138942</v>
+        <v>6.866943866943868</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.579978699181117</v>
+        <v>0.5781378650785803</v>
       </c>
       <c r="Z5" t="n">
-        <v>111.75</v>
+        <v>111</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.180000000000001</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="AB5" t="n">
         <v>9.220352523846751</v>
@@ -1012,16 +1012,16 @@
         <v>108.5881212004577</v>
       </c>
       <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8443260495032402</v>
+        <v>1.154744255921994</v>
       </c>
     </row>
     <row r="6">
@@ -1039,76 +1039,76 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>1656.813</v>
+        <v>1653.715</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6916</v>
+        <v>0.5508</v>
       </c>
       <c r="I6" t="n">
-        <v>1485.973726027397</v>
+        <v>1489.565824324324</v>
       </c>
       <c r="J6" t="n">
-        <v>117.1977984790908</v>
+        <v>116.9928602595211</v>
       </c>
       <c r="K6" t="n">
-        <v>110.8022814185654</v>
+        <v>111.3143552011961</v>
       </c>
       <c r="L6" t="n">
-        <v>6.395517060525354</v>
+        <v>5.67850505832501</v>
       </c>
       <c r="M6" t="n">
-        <v>118.3080391000842</v>
+        <v>118.9050852839192</v>
       </c>
       <c r="N6" t="n">
-        <v>113.7266536287964</v>
+        <v>115.490129606859</v>
       </c>
       <c r="O6" t="n">
-        <v>4.581385471287755</v>
+        <v>3.414955677060157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5541063526436519</v>
+        <v>0.5531418193831777</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1167410326083382</v>
+        <v>0.1161127571774494</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2931776654280925</v>
+        <v>0.2909811475820107</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5577500483299311</v>
+        <v>0.5603445175844828</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2383205045765506</v>
+        <v>0.2368330158372437</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4303959091814751</v>
+        <v>0.4293995914850238</v>
       </c>
       <c r="V6" t="n">
-        <v>99.45131849315068</v>
+        <v>98.91096979332275</v>
       </c>
       <c r="W6" t="n">
-        <v>116.3095034246576</v>
+        <v>115.5902225755167</v>
       </c>
       <c r="X6" t="n">
-        <v>5.919948630136987</v>
+        <v>5.487678855325915</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5870619828401078</v>
+        <v>0.5861065869212786</v>
       </c>
       <c r="Z6" t="n">
-        <v>114.22</v>
+        <v>112.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.39</v>
+        <v>3.77</v>
       </c>
       <c r="AB6" t="n">
         <v>2.775420617465777</v>
@@ -1120,7 +1120,7 @@
         <v>112.335295999638</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1129,103 +1129,103 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.7826694671736264</v>
+        <v>1.018649873552174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>1595.508</v>
+        <v>1578.449</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3553</v>
+        <v>-0.5871</v>
       </c>
       <c r="I7" t="n">
-        <v>1501.8568</v>
+        <v>1495.876986486486</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8584384956113</v>
+        <v>115.7075921372753</v>
       </c>
       <c r="K7" t="n">
-        <v>115.1037310005922</v>
+        <v>110.8974706490588</v>
       </c>
       <c r="L7" t="n">
-        <v>4.754707495019058</v>
+        <v>4.810121488216581</v>
       </c>
       <c r="M7" t="n">
-        <v>123.6130227773458</v>
+        <v>115.5599209331499</v>
       </c>
       <c r="N7" t="n">
-        <v>112.697727550607</v>
+        <v>112.8664682587248</v>
       </c>
       <c r="O7" t="n">
-        <v>10.91529522673882</v>
+        <v>2.693452674425058</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5767760996365826</v>
+        <v>0.5447533095779298</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.109873372326596</v>
+        <v>0.1266528565862367</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2314344380250866</v>
+        <v>0.3438517791625675</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6043246941612436</v>
+        <v>0.548269707561173</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3010600293726614</v>
+        <v>0.2620519417962008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4082371567757013</v>
+        <v>0.3505428808571338</v>
       </c>
       <c r="V7" t="n">
-        <v>101.1446511627907</v>
+        <v>98.65701858108109</v>
       </c>
       <c r="W7" t="n">
-        <v>121.2093023255813</v>
+        <v>113.9864864864865</v>
       </c>
       <c r="X7" t="n">
-        <v>4.858604651162791</v>
+        <v>4.756756756756757</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6162103193762901</v>
+        <v>0.5774111730857776</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.07</v>
+        <v>112.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.03</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.722616812266775</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC7" t="n">
-        <v>116.5392386763017</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD7" t="n">
-        <v>113.8166218640349</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1234,24 +1234,24 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.888626284526246</v>
+        <v>0.7094142512935475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1261,79 +1261,79 @@
         <v>46110</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>1573.994</v>
+        <v>1595.508</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7339</v>
+        <v>1.3553</v>
       </c>
       <c r="I8" t="n">
-        <v>1497.461684931507</v>
+        <v>1501.8568</v>
       </c>
       <c r="J8" t="n">
-        <v>115.4732767025396</v>
+        <v>119.8587919475473</v>
       </c>
       <c r="K8" t="n">
-        <v>110.9438758825305</v>
+        <v>115.0958848187337</v>
       </c>
       <c r="L8" t="n">
-        <v>4.529400820009132</v>
+        <v>4.762907128813691</v>
       </c>
       <c r="M8" t="n">
-        <v>114.1711478489707</v>
+        <v>123.6130227773458</v>
       </c>
       <c r="N8" t="n">
-        <v>112.6584127834637</v>
+        <v>112.697727550607</v>
       </c>
       <c r="O8" t="n">
-        <v>1.512735065507021</v>
+        <v>10.91529522673882</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5414669011587684</v>
+        <v>0.5767951977185795</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1271019501579171</v>
+        <v>0.1098720540359938</v>
       </c>
       <c r="R8" t="n">
-        <v>0.349966902743361</v>
+        <v>0.2313927488520803</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5390639306586834</v>
+        <v>0.6043246941612436</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2624693584063961</v>
+        <v>0.3009684618297749</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3485133151534441</v>
+        <v>0.4082694011760947</v>
       </c>
       <c r="V8" t="n">
-        <v>99.35631748589849</v>
+        <v>101.1406349206349</v>
       </c>
       <c r="W8" t="n">
-        <v>114.7211925866237</v>
+        <v>121.2063492063492</v>
       </c>
       <c r="X8" t="n">
-        <v>4.74375503626108</v>
+        <v>4.868888888888889</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5746826108918848</v>
+        <v>0.6162212021528615</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.48</v>
+        <v>127.07</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.029999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.413694058608522</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC8" t="n">
-        <v>112.3850185369902</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD8" t="n">
-        <v>108.9713244783817</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1342,106 +1342,106 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3132942668198304</v>
+        <v>1.671732794537588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>1637.716</v>
+        <v>1575.058</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4165</v>
+        <v>0.3107</v>
       </c>
       <c r="I9" t="n">
-        <v>1490.265150684932</v>
+        <v>1502.204986486486</v>
       </c>
       <c r="J9" t="n">
-        <v>117.1208875317718</v>
+        <v>114.9522244771508</v>
       </c>
       <c r="K9" t="n">
-        <v>112.6775919801654</v>
+        <v>110.415465443249</v>
       </c>
       <c r="L9" t="n">
-        <v>4.443295551606407</v>
+        <v>4.536759033901898</v>
       </c>
       <c r="M9" t="n">
-        <v>121.7419792720121</v>
+        <v>110.973587900957</v>
       </c>
       <c r="N9" t="n">
-        <v>117.1237878936892</v>
+        <v>109.555917378623</v>
       </c>
       <c r="O9" t="n">
-        <v>4.618191378322839</v>
+        <v>1.41767052233401</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5618847955998393</v>
+        <v>0.5597016598288915</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1158560807095368</v>
+        <v>0.1242750360897376</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2628076828509504</v>
+        <v>0.2571044444016876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5801718064608603</v>
+        <v>0.544689202983769</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2678327365163862</v>
+        <v>0.2895374975883943</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4440679594885688</v>
+        <v>0.417331824472558</v>
       </c>
       <c r="V9" t="n">
-        <v>102.416915851272</v>
+        <v>103.0054808296668</v>
       </c>
       <c r="W9" t="n">
-        <v>119.8438356164383</v>
+        <v>117.9943431803897</v>
       </c>
       <c r="X9" t="n">
-        <v>4.485714285714286</v>
+        <v>4.103079824010056</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5953958019383466</v>
+        <v>0.5929581246296418</v>
       </c>
       <c r="Z9" t="n">
-        <v>121.19</v>
+        <v>114.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.35</v>
+        <v>2.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.967224035556209</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC9" t="n">
-        <v>120.0962116764131</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD9" t="n">
-        <v>110.1289876408569</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1450,106 +1450,106 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.209959435189236</v>
+        <v>0.7854853950029779</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612750</v>
+        <v>1610612739</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1582.381</v>
+        <v>1641.851</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3322</v>
+        <v>-0.4295</v>
       </c>
       <c r="I10" t="n">
-        <v>1499.834767123288</v>
+        <v>1490.952351351351</v>
       </c>
       <c r="J10" t="n">
-        <v>114.3754224965118</v>
+        <v>116.9726637626015</v>
       </c>
       <c r="K10" t="n">
-        <v>110.9079435992749</v>
+        <v>112.600316646653</v>
       </c>
       <c r="L10" t="n">
-        <v>3.467478897236908</v>
+        <v>4.372347115948564</v>
       </c>
       <c r="M10" t="n">
-        <v>108.2073708580311</v>
+        <v>122.8320412332206</v>
       </c>
       <c r="N10" t="n">
-        <v>112.0407963514088</v>
+        <v>116.6956804899088</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.833425493377661</v>
+        <v>6.13636074331168</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5552618481181406</v>
+        <v>0.560608721564555</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1250625715671174</v>
+        <v>0.1159089974077238</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2596254830453977</v>
+        <v>0.2645611477954666</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5249427043843291</v>
+        <v>0.5859569232727092</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2951591537827984</v>
+        <v>0.268029570467252</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4211314769536547</v>
+        <v>0.4417072432302836</v>
       </c>
       <c r="V10" t="n">
-        <v>102.8930136986302</v>
+        <v>102.2525634725635</v>
       </c>
       <c r="W10" t="n">
-        <v>117.2966609589041</v>
+        <v>119.4709254709255</v>
       </c>
       <c r="X10" t="n">
-        <v>3.028253424657534</v>
+        <v>4.374283374283374</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5897067782655263</v>
+        <v>0.594325440124746</v>
       </c>
       <c r="Z10" t="n">
-        <v>110.85</v>
+        <v>123.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.37</v>
+        <v>6.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.250350764022217</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC10" t="n">
-        <v>114.1383305986051</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD10" t="n">
-        <v>109.8879798345829</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -1558,106 +1558,106 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3453937181903723</v>
+        <v>1.463427058115498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F11" t="n">
         <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>1557.165</v>
+        <v>1580.433</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2445</v>
+        <v>2.2264</v>
       </c>
       <c r="I11" t="n">
-        <v>1497.633094594595</v>
+        <v>1497.293493333333</v>
       </c>
       <c r="J11" t="n">
-        <v>116.2449984779174</v>
+        <v>115.8694853761621</v>
       </c>
       <c r="K11" t="n">
-        <v>113.5402952146427</v>
+        <v>112.0997831654642</v>
       </c>
       <c r="L11" t="n">
-        <v>2.704703263274769</v>
+        <v>3.769702210697881</v>
       </c>
       <c r="M11" t="n">
-        <v>122.2639351473496</v>
+        <v>118.4491199903235</v>
       </c>
       <c r="N11" t="n">
-        <v>113.0364485781071</v>
+        <v>108.0429191492245</v>
       </c>
       <c r="O11" t="n">
-        <v>9.227486569242526</v>
+        <v>10.40620084109897</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5632271125158083</v>
+        <v>0.5527424035352789</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1261370559508971</v>
+        <v>0.1282559349327903</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2356273039812238</v>
+        <v>0.305507837493888</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5979483400602705</v>
+        <v>0.5638218079694002</v>
       </c>
       <c r="T11" t="n">
-        <v>0.304845913388296</v>
+        <v>0.2521244191640875</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4040940941967319</v>
+        <v>0.4825000667489923</v>
       </c>
       <c r="V11" t="n">
-        <v>98.80972178060414</v>
+        <v>99.6653411764706</v>
       </c>
       <c r="W11" t="n">
-        <v>114.2118441971383</v>
+        <v>116.1070588235294</v>
       </c>
       <c r="X11" t="n">
-        <v>1.697138314785373</v>
+        <v>5.117647058823529</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.6070779040559841</v>
+        <v>0.5902065337376826</v>
       </c>
       <c r="Z11" t="n">
-        <v>121.06</v>
+        <v>117.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.52</v>
+        <v>12.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.815266446541752</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC11" t="n">
-        <v>113.8106821492749</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD11" t="n">
-        <v>108.9954157027332</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1666,132 +1666,132 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.6619823415113724</v>
+        <v>0.5896988706654002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>1506.79</v>
+        <v>1562.95</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7286</v>
+        <v>3.4054</v>
       </c>
       <c r="I12" t="n">
-        <v>1495.222095890411</v>
+        <v>1493.349445945946</v>
       </c>
       <c r="J12" t="n">
-        <v>113.4806201819405</v>
+        <v>116.7716169045549</v>
       </c>
       <c r="K12" t="n">
-        <v>110.8121139286902</v>
+        <v>113.8579626635471</v>
       </c>
       <c r="L12" t="n">
-        <v>2.668506253250338</v>
+        <v>2.913654241007723</v>
       </c>
       <c r="M12" t="n">
-        <v>117.2308493376413</v>
+        <v>121.486935110467</v>
       </c>
       <c r="N12" t="n">
-        <v>113.6359976902031</v>
+        <v>110.7308856635711</v>
       </c>
       <c r="O12" t="n">
-        <v>3.594851647438205</v>
+        <v>10.75604944689594</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5451525426361739</v>
+        <v>0.5732021274980995</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1153459035030485</v>
+        <v>0.125332779499649</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2526799779822146</v>
+        <v>0.2389884340124057</v>
       </c>
       <c r="S12" t="n">
-        <v>0.574704985225027</v>
+        <v>0.5861618102069696</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2597286308871877</v>
+        <v>0.3253973693490874</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3685756589552447</v>
+        <v>0.3966976517946511</v>
       </c>
       <c r="V12" t="n">
-        <v>100.9594977168949</v>
+        <v>100.3452113652113</v>
       </c>
       <c r="W12" t="n">
-        <v>114.6811263318113</v>
+        <v>116.7214137214137</v>
       </c>
       <c r="X12" t="n">
-        <v>3.082572298325723</v>
+        <v>2.172557172557173</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5792077900500039</v>
+        <v>0.6097055293758746</v>
       </c>
       <c r="Z12" t="n">
-        <v>118.21</v>
+        <v>121.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.11</v>
+        <v>8.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.536933640611859</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC12" t="n">
-        <v>108.3888858603967</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD12" t="n">
-        <v>112.9258195010085</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3447388734279041</v>
+        <v>1.384298349405215</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1801,622 +1801,622 @@
         <v>46110</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>1586.136</v>
+        <v>1557.165</v>
       </c>
       <c r="H13" t="n">
-        <v>2.924</v>
+        <v>-1.2445</v>
       </c>
       <c r="I13" t="n">
-        <v>1495.093094594595</v>
+        <v>1497.633094594595</v>
       </c>
       <c r="J13" t="n">
-        <v>115.5562531244554</v>
+        <v>116.2232391202087</v>
       </c>
       <c r="K13" t="n">
-        <v>112.94315819016</v>
+        <v>113.5442006401876</v>
       </c>
       <c r="L13" t="n">
-        <v>2.613094934295391</v>
+        <v>2.679038480021139</v>
       </c>
       <c r="M13" t="n">
-        <v>116.9555428221011</v>
+        <v>122.2639351473496</v>
       </c>
       <c r="N13" t="n">
-        <v>111.710624465496</v>
+        <v>113.0364485781071</v>
       </c>
       <c r="O13" t="n">
-        <v>5.244918356605079</v>
+        <v>9.227486569242526</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5523941966402368</v>
+        <v>0.5630493279092167</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.128750466774083</v>
+        <v>0.1260936537482905</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3034645174819195</v>
+        <v>0.2356311658846714</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5603704240638722</v>
+        <v>0.5979483400602705</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2507148379026036</v>
+        <v>0.3047469395663296</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4840705248689424</v>
+        <v>0.4041184775377864</v>
       </c>
       <c r="V13" t="n">
-        <v>99.67280308880309</v>
+        <v>98.80778528528529</v>
       </c>
       <c r="W13" t="n">
-        <v>115.8162162162162</v>
+        <v>114.1903153153153</v>
       </c>
       <c r="X13" t="n">
-        <v>4.034749034749035</v>
+        <v>1.676426426426426</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5892582805895568</v>
+        <v>0.6069030739213469</v>
       </c>
       <c r="Z13" t="n">
-        <v>115.47</v>
+        <v>121.06</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.220000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.13717477219789</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC13" t="n">
-        <v>104.7204689341547</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD13" t="n">
-        <v>114.8576437063525</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.4462025172999437</v>
+        <v>0.4333003593217314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612747</v>
+        <v>1610612748</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>1561.924</v>
+        <v>1531.531</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0758</v>
+        <v>-3.1116</v>
       </c>
       <c r="I14" t="n">
-        <v>1496.091753424658</v>
+        <v>1505.69156</v>
       </c>
       <c r="J14" t="n">
-        <v>116.6976450061723</v>
+        <v>113.7409191744289</v>
       </c>
       <c r="K14" t="n">
-        <v>114.1356646171615</v>
+        <v>111.3794604939758</v>
       </c>
       <c r="L14" t="n">
-        <v>2.561980389010774</v>
+        <v>2.361458680452965</v>
       </c>
       <c r="M14" t="n">
-        <v>120.9895837814511</v>
+        <v>115.8719111038512</v>
       </c>
       <c r="N14" t="n">
-        <v>110.7663997945813</v>
+        <v>118.4071104219959</v>
       </c>
       <c r="O14" t="n">
-        <v>10.2231839868698</v>
+        <v>-2.535199318144721</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5728718935793922</v>
+        <v>0.5363101165105528</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1250048049620333</v>
+        <v>0.1118098196120276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2384006964565819</v>
+        <v>0.2529481789512728</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5794717358649966</v>
+        <v>0.5361416630337882</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3256080969081872</v>
+        <v>0.2731182182832637</v>
       </c>
       <c r="U14" t="n">
-        <v>0.398792188873006</v>
+        <v>0.4045384214955133</v>
       </c>
       <c r="V14" t="n">
-        <v>100.3109648600358</v>
+        <v>105.7295609756098</v>
       </c>
       <c r="W14" t="n">
-        <v>116.6298391899941</v>
+        <v>120.2227642276422</v>
       </c>
       <c r="X14" t="n">
-        <v>1.857057772483622</v>
+        <v>2.507317073170732</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6091767095408253</v>
+        <v>0.574987932045124</v>
       </c>
       <c r="Z14" t="n">
-        <v>120.41</v>
+        <v>120.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>-4.489999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.827913300592181</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC14" t="n">
-        <v>114.1496737878887</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD14" t="n">
-        <v>112.3217604872965</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.826494471608916</v>
+        <v>-0.07654764934946894</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612756</v>
+        <v>1610612737</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>1504.204</v>
+        <v>1516.752</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0757</v>
+        <v>2.4002</v>
       </c>
       <c r="I15" t="n">
-        <v>1517.468767123288</v>
+        <v>1483.620026666666</v>
       </c>
       <c r="J15" t="n">
-        <v>113.6894727017141</v>
+        <v>113.8274900391103</v>
       </c>
       <c r="K15" t="n">
-        <v>111.7575872193213</v>
+        <v>111.9794820808451</v>
       </c>
       <c r="L15" t="n">
-        <v>1.931885482392746</v>
+        <v>1.848007958265218</v>
       </c>
       <c r="M15" t="n">
-        <v>119.5347307103522</v>
+        <v>117.5443697775149</v>
       </c>
       <c r="N15" t="n">
-        <v>114.0245628123576</v>
+        <v>107.7478076007739</v>
       </c>
       <c r="O15" t="n">
-        <v>5.51016789799468</v>
+        <v>9.796562176741007</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5401535652889792</v>
+        <v>0.5529268379355065</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1183191744178145</v>
+        <v>0.1158941589141836</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2890819478950038</v>
+        <v>0.2392961828508606</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5577788690445787</v>
+        <v>0.5568263189467541</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2284333411757111</v>
+        <v>0.2362437545286008</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4580228789478641</v>
+        <v>0.4289594164025617</v>
       </c>
       <c r="V15" t="n">
-        <v>99.56970776255709</v>
+        <v>103.7074119658119</v>
       </c>
       <c r="W15" t="n">
-        <v>113.1041095890411</v>
+        <v>118.0929914529914</v>
       </c>
       <c r="X15" t="n">
-        <v>1.998630136986301</v>
+        <v>2.049230769230769</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5712332507838508</v>
+        <v>0.5836060710830497</v>
       </c>
       <c r="Z15" t="n">
-        <v>116.18</v>
+        <v>120.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.29</v>
+        <v>9.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.375203171419814</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC15" t="n">
-        <v>114.7034977739938</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD15" t="n">
-        <v>117.0787009454136</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.03972186941841134</v>
+        <v>0.7323739481909893</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612748</v>
+        <v>1610612756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>1536.983</v>
+        <v>1510.467</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.9846</v>
+        <v>-0.9538</v>
       </c>
       <c r="I16" t="n">
-        <v>1508.021162162162</v>
+        <v>1512.922053333333</v>
       </c>
       <c r="J16" t="n">
-        <v>113.6306665551732</v>
+        <v>113.2152099640899</v>
       </c>
       <c r="K16" t="n">
-        <v>111.7891211115908</v>
+        <v>111.5522987927236</v>
       </c>
       <c r="L16" t="n">
-        <v>1.841545443582428</v>
+        <v>1.662911171366294</v>
       </c>
       <c r="M16" t="n">
-        <v>115.8736283700667</v>
+        <v>116.078878571102</v>
       </c>
       <c r="N16" t="n">
-        <v>119.2840964864683</v>
+        <v>112.6056784529052</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.410468116401621</v>
+        <v>3.473200118196776</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5365868750358272</v>
+        <v>0.5383510419265531</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1115060662447834</v>
+        <v>0.119353115065673</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2504201599983731</v>
+        <v>0.2871305178145186</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5367135105411195</v>
+        <v>0.5413192871582424</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2708280425983094</v>
+        <v>0.231068915104776</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4034576356833746</v>
+        <v>0.4579950885299742</v>
       </c>
       <c r="V16" t="n">
-        <v>105.7943243243244</v>
+        <v>99.82764227642275</v>
       </c>
       <c r="W16" t="n">
-        <v>120.2203453453454</v>
+        <v>112.8731707317073</v>
       </c>
       <c r="X16" t="n">
-        <v>2.037162162162162</v>
+        <v>1.710569105691057</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5749539790763334</v>
+        <v>0.5701305819990877</v>
       </c>
       <c r="Z16" t="n">
-        <v>120.97</v>
+        <v>116.13</v>
       </c>
       <c r="AA16" t="n">
-        <v>-4.67</v>
+        <v>4.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.094669144490311</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC16" t="n">
-        <v>111.6804548463295</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD16" t="n">
-        <v>112.7751239908198</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3168871637284518</v>
+        <v>0.08047548469645489</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>1515.872</v>
+        <v>1515.772</v>
       </c>
       <c r="H17" t="n">
-        <v>2.601</v>
+        <v>0.9318</v>
       </c>
       <c r="I17" t="n">
-        <v>1485.918486486486</v>
+        <v>1495.614162162162</v>
       </c>
       <c r="J17" t="n">
-        <v>114.0272831681167</v>
+        <v>112.9917312467636</v>
       </c>
       <c r="K17" t="n">
-        <v>112.3220705995947</v>
+        <v>111.8874680377456</v>
       </c>
       <c r="L17" t="n">
-        <v>1.70521256852204</v>
+        <v>1.104263209017855</v>
       </c>
       <c r="M17" t="n">
-        <v>118.9394660785629</v>
+        <v>117.1774719255155</v>
       </c>
       <c r="N17" t="n">
-        <v>109.1683779977121</v>
+        <v>115.4856358995865</v>
       </c>
       <c r="O17" t="n">
-        <v>9.771088080850765</v>
+        <v>1.691836025928978</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5535622747566453</v>
+        <v>0.5424223638757518</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1163040841905131</v>
+        <v>0.1164992817984343</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2417115844459832</v>
+        <v>0.2566098128748526</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5609427023576505</v>
+        <v>0.5738457380891842</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2382826048271262</v>
+        <v>0.263268479510689</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4297686423322414</v>
+        <v>0.3685386386392667</v>
       </c>
       <c r="V17" t="n">
-        <v>103.7085516285516</v>
+        <v>100.2155007949125</v>
       </c>
       <c r="W17" t="n">
-        <v>118.3125433125433</v>
+        <v>113.4324324324324</v>
       </c>
       <c r="X17" t="n">
-        <v>1.941787941787942</v>
+        <v>1.736486486486487</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5845071262333967</v>
+        <v>0.5765112689620505</v>
       </c>
       <c r="Z17" t="n">
-        <v>121.38</v>
+        <v>116.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.981113782848854</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC17" t="n">
-        <v>112.8029837792552</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD17" t="n">
-        <v>113.7840975621041</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1</v>
-      </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.6641014559642947</v>
+        <v>0.1448612802524424</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>1469.575</v>
+        <v>1515.253</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1933</v>
+        <v>-3.3347</v>
       </c>
       <c r="I18" t="n">
-        <v>1497.223657534247</v>
+        <v>1490.206366197183</v>
       </c>
       <c r="J18" t="n">
-        <v>113.4308448980004</v>
+        <v>112.4151295176243</v>
       </c>
       <c r="K18" t="n">
-        <v>113.1733010220948</v>
+        <v>112.5048569557328</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2575438759055876</v>
+        <v>-0.08972743810860399</v>
       </c>
       <c r="M18" t="n">
-        <v>114.285926442809</v>
+        <v>110.387435824646</v>
       </c>
       <c r="N18" t="n">
-        <v>114.9526667337413</v>
+        <v>119.8495590449733</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6667402909323203</v>
+        <v>-9.462123220327285</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5322507943117178</v>
+        <v>0.5313770659618372</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1138856581463011</v>
+        <v>0.119096756762158</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2596154503377267</v>
+        <v>0.2447455167990914</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5389088110303376</v>
+        <v>0.525956343852752</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2835401824238258</v>
+        <v>0.3180583424352549</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3947943751215166</v>
+        <v>0.3890970049711139</v>
       </c>
       <c r="V18" t="n">
-        <v>102.6970112079701</v>
+        <v>102.4760641627543</v>
       </c>
       <c r="W18" t="n">
-        <v>116.2067247820672</v>
+        <v>115.314945226917</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2374429223744292</v>
+        <v>0.6177621283255086</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5746603057191856</v>
+        <v>0.5777524740222608</v>
       </c>
       <c r="Z18" t="n">
-        <v>118.27</v>
+        <v>115.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.5</v>
+        <v>-7.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>-6.382503892565079</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC18" t="n">
-        <v>109.8789897646453</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD18" t="n">
-        <v>116.2614936572104</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2425,103 +2425,103 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.567987890700778</v>
+        <v>-0.2596253792261301</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F19" t="n">
         <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>1481.014</v>
+        <v>1474.321</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3473</v>
+        <v>0.4704</v>
       </c>
       <c r="I19" t="n">
-        <v>1502.113689189189</v>
+        <v>1498.489310810811</v>
       </c>
       <c r="J19" t="n">
-        <v>112.4044524312674</v>
+        <v>113.0507643207421</v>
       </c>
       <c r="K19" t="n">
-        <v>112.7861785332087</v>
+        <v>113.2514554240724</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3817261019414203</v>
+        <v>-0.2006911033302979</v>
       </c>
       <c r="M19" t="n">
-        <v>110.2168956740512</v>
+        <v>114.0343818366226</v>
       </c>
       <c r="N19" t="n">
-        <v>116.9725404071555</v>
+        <v>114.7058555748773</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.755644733104332</v>
+        <v>-0.6714737382547205</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5504793651048593</v>
+        <v>0.5299584005606888</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1328372431307155</v>
+        <v>0.1134356184693611</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2570915493288971</v>
+        <v>0.2588711535791979</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5476170154961076</v>
+        <v>0.5338541721015952</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2384067173177889</v>
+        <v>0.2801048380450918</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5019426603519649</v>
+        <v>0.3944872462997808</v>
       </c>
       <c r="V19" t="n">
-        <v>101.9257894736842</v>
+        <v>102.7823684210526</v>
       </c>
       <c r="W19" t="n">
-        <v>114.6052631578947</v>
+        <v>115.9868421052632</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3289473684210526</v>
+        <v>-0.5657894736842105</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5840270860744731</v>
+        <v>0.5724719551909406</v>
       </c>
       <c r="Z19" t="n">
-        <v>113.7</v>
+        <v>118.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>-6.619999999999999</v>
+        <v>-0.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.402868486532558</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC19" t="n">
-        <v>112.5227430890375</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD19" t="n">
-        <v>110.1198746025049</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -2533,21 +2533,21 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.09806936194486636</v>
+        <v>0.4903444140992576</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2557,79 +2557,79 @@
         <v>46110</v>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>1461.235</v>
+        <v>1481.014</v>
       </c>
       <c r="H20" t="n">
-        <v>1.549</v>
+        <v>-1.3473</v>
       </c>
       <c r="I20" t="n">
-        <v>1506.38652</v>
+        <v>1502.113689189189</v>
       </c>
       <c r="J20" t="n">
-        <v>111.2216623861247</v>
+        <v>112.4264854956626</v>
       </c>
       <c r="K20" t="n">
-        <v>112.1168712348716</v>
+        <v>112.7709595170368</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8952088487468716</v>
+        <v>-0.3444740213742258</v>
       </c>
       <c r="M20" t="n">
-        <v>112.1685038482119</v>
+        <v>110.2168956740512</v>
       </c>
       <c r="N20" t="n">
-        <v>102.5585218996881</v>
+        <v>116.9725404071555</v>
       </c>
       <c r="O20" t="n">
-        <v>9.60998194852375</v>
+        <v>-6.755644733104332</v>
       </c>
       <c r="P20" t="n">
-        <v>0.533728531648594</v>
+        <v>0.5505672792816279</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1413464855055116</v>
+        <v>0.1328449955632938</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3094815730887919</v>
+        <v>0.257186056692933</v>
       </c>
       <c r="S20" t="n">
-        <v>0.549333250051234</v>
+        <v>0.5476170154961076</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2895384070123483</v>
+        <v>0.2386160975356581</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4664863724660987</v>
+        <v>0.5019345889557217</v>
       </c>
       <c r="V20" t="n">
-        <v>103.5428842105263</v>
+        <v>101.9413447593936</v>
       </c>
       <c r="W20" t="n">
-        <v>115.4442105263158</v>
+        <v>114.6479894528675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3252631578947368</v>
+        <v>-0.2841133816743572</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5706694607236947</v>
+        <v>0.5841351721022416</v>
       </c>
       <c r="Z20" t="n">
-        <v>115.44</v>
+        <v>113.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.34</v>
+        <v>-6.619999999999999</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.840928550668963</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC20" t="n">
-        <v>109.2995408403883</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD20" t="n">
-        <v>113.1404693910572</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -2638,24 +2638,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.2562829430804895</v>
+        <v>-0.7030458990769218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2665,91 +2665,91 @@
         <v>46110</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>1524.235</v>
+        <v>1461.235</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6666</v>
+        <v>1.549</v>
       </c>
       <c r="I21" t="n">
-        <v>1489.969457142857</v>
+        <v>1506.38652</v>
       </c>
       <c r="J21" t="n">
-        <v>112.1867878734385</v>
+        <v>111.2338292538253</v>
       </c>
       <c r="K21" t="n">
-        <v>113.1839346520263</v>
+        <v>112.0772110009368</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9971467785878004</v>
+        <v>-0.8433817471115478</v>
       </c>
       <c r="M21" t="n">
-        <v>112.6204706932376</v>
+        <v>112.1685038482119</v>
       </c>
       <c r="N21" t="n">
-        <v>122.5455492412534</v>
+        <v>102.5585218996881</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.925078548015824</v>
+        <v>9.60998194852375</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5304614213388</v>
+        <v>0.5338001034461746</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1185123358169038</v>
+        <v>0.1413185191573287</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2443306741994797</v>
+        <v>0.3094197279083685</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5325938772236181</v>
+        <v>0.549333250051234</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3109914586971597</v>
+        <v>0.2896623628925938</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3909380133278451</v>
+        <v>0.4664144779896672</v>
       </c>
       <c r="V21" t="n">
-        <v>102.2711688311689</v>
+        <v>103.5418888888889</v>
       </c>
       <c r="W21" t="n">
-        <v>114.8580086580086</v>
+        <v>115.4555555555555</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3428571428571434</v>
+        <v>-0.2722222222222224</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.575752054793909</v>
+        <v>0.5707352849467603</v>
       </c>
       <c r="Z21" t="n">
-        <v>116.52</v>
+        <v>115.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>-7.45</v>
+        <v>10.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC21" t="n">
-        <v>107.6152962364644</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD21" t="n">
-        <v>108.1384073962044</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.3302803963629716</v>
+        <v>-0.3913271559838703</v>
       </c>
     </row>
     <row r="22">
@@ -2767,76 +2767,76 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>1381.482</v>
+        <v>1379.867</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4564</v>
+        <v>-0.8242</v>
       </c>
       <c r="I22" t="n">
-        <v>1496.943479452055</v>
+        <v>1495.397945945946</v>
       </c>
       <c r="J22" t="n">
-        <v>111.6885269438393</v>
+        <v>111.6145029009255</v>
       </c>
       <c r="K22" t="n">
-        <v>115.3428658126772</v>
+        <v>115.8641627858758</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.654338868837813</v>
+        <v>-4.249659884950336</v>
       </c>
       <c r="M22" t="n">
-        <v>112.3032771831725</v>
+        <v>112.524283740846</v>
       </c>
       <c r="N22" t="n">
-        <v>118.1624481805777</v>
+        <v>119.0215976853151</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.859170997405267</v>
+        <v>-6.497313944469074</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5500114312960163</v>
+        <v>0.5492724481555097</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1275107330361474</v>
+        <v>0.1254502510971707</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2294790941793377</v>
+        <v>0.2263545954995142</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5494875563020285</v>
+        <v>0.5504964637989375</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2505574560148133</v>
+        <v>0.2460559638084806</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4456053865141036</v>
+        <v>0.4471020313296633</v>
       </c>
       <c r="V22" t="n">
-        <v>104.6541429100334</v>
+        <v>104.4573243243243</v>
       </c>
       <c r="W22" t="n">
-        <v>116.482784154017</v>
+        <v>116.2990990990991</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.545353572750835</v>
+        <v>-4.941441441441442</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5829072430684848</v>
+        <v>0.5816386049501766</v>
       </c>
       <c r="Z22" t="n">
-        <v>121.39</v>
+        <v>121.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.67</v>
+        <v>-6.72</v>
       </c>
       <c r="AB22" t="n">
         <v>-0.9433805425336231</v>
@@ -2848,16 +2848,16 @@
         <v>113.5078075941239</v>
       </c>
       <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1</v>
-      </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.4207230540168955</v>
+        <v>-0.4104168172554537</v>
       </c>
     </row>
     <row r="23">
@@ -2881,7 +2881,7 @@
         <v>46110</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
         <v>1380.194</v>
@@ -2893,13 +2893,13 @@
         <v>1508.015253333333</v>
       </c>
       <c r="J23" t="n">
-        <v>111.9767068327859</v>
+        <v>111.985626370175</v>
       </c>
       <c r="K23" t="n">
-        <v>116.7282581229986</v>
+        <v>116.71122574781</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.751551290212712</v>
+        <v>-4.725599377634998</v>
       </c>
       <c r="M23" t="n">
         <v>113.784720892972</v>
@@ -2911,34 +2911,34 @@
         <v>-2.136321202900874</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5273226041640725</v>
+        <v>0.5273613612763056</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1163695129258574</v>
+        <v>0.1163903358334531</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2662434068103681</v>
+        <v>0.2663200004285781</v>
       </c>
       <c r="S23" t="n">
         <v>0.5421438336073836</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2842289577821487</v>
+        <v>0.2841931548059005</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3594156293884965</v>
+        <v>0.3594348556456938</v>
       </c>
       <c r="V23" t="n">
-        <v>102.6263294117647</v>
+        <v>102.6292266666667</v>
       </c>
       <c r="W23" t="n">
-        <v>114.8635294117647</v>
+        <v>114.8746666666666</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.875294117647059</v>
+        <v>-4.851809523809524</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5671303949984788</v>
+        <v>0.5671723136071763</v>
       </c>
       <c r="Z23" t="n">
         <v>114.51</v>
@@ -2965,211 +2965,211 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2712955643181959</v>
+        <v>-0.4402893876814114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>1382.574</v>
+        <v>1389.808</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8884</v>
+        <v>-2.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>1496.613957746479</v>
+        <v>1496.395472972973</v>
       </c>
       <c r="J24" t="n">
-        <v>110.5055249362239</v>
+        <v>111.2684022912795</v>
       </c>
       <c r="K24" t="n">
-        <v>115.3575291679639</v>
+        <v>116.4796851011481</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.852004231739963</v>
+        <v>-5.211282809868516</v>
       </c>
       <c r="M24" t="n">
-        <v>107.3702020857575</v>
+        <v>109.2355695170871</v>
       </c>
       <c r="N24" t="n">
-        <v>122.916232423345</v>
+        <v>121.0077932952984</v>
       </c>
       <c r="O24" t="n">
-        <v>-15.54603033758751</v>
+        <v>-11.77222377821126</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5334111903734295</v>
+        <v>0.5654139548645576</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1258870247217159</v>
+        <v>0.1318193190835407</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2500970280116494</v>
+        <v>0.2048077253296345</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5183945678850819</v>
+        <v>0.5701947244408464</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2560697184893396</v>
+        <v>0.2268512971722048</v>
       </c>
       <c r="U24" t="n">
-        <v>0.429324023984164</v>
+        <v>0.4541403908818142</v>
       </c>
       <c r="V24" t="n">
-        <v>103.9323681624631</v>
+        <v>99.54065919578115</v>
       </c>
       <c r="W24" t="n">
-        <v>115.1500163773338</v>
+        <v>110.5438365194463</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.227644939403866</v>
+        <v>-5.592617007251153</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5703483866190858</v>
+        <v>0.5893963364390316</v>
       </c>
       <c r="Z24" t="n">
-        <v>112.4</v>
+        <v>106.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>-13.76</v>
+        <v>-12.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.575252351995317</v>
+        <v>1.809266556998161</v>
       </c>
       <c r="AC24" t="n">
-        <v>114.5419381230804</v>
+        <v>114.2499905834389</v>
       </c>
       <c r="AD24" t="n">
-        <v>110.9666857710851</v>
+        <v>112.4407240264407</v>
       </c>
       <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1</v>
-      </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9737260303339774</v>
+        <v>-0.9920046818490768</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="F25" t="n">
         <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>1368.156</v>
+        <v>1384.188</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9866</v>
+        <v>-1.6948</v>
       </c>
       <c r="I25" t="n">
-        <v>1505.346541666667</v>
+        <v>1495.014902777778</v>
       </c>
       <c r="J25" t="n">
-        <v>108.7476742754251</v>
+        <v>110.4050796922825</v>
       </c>
       <c r="K25" t="n">
-        <v>113.8379254495863</v>
+        <v>115.7632853352394</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.090251174161131</v>
+        <v>-5.358205642957026</v>
       </c>
       <c r="M25" t="n">
-        <v>111.7044445975594</v>
+        <v>106.0100295254461</v>
       </c>
       <c r="N25" t="n">
-        <v>119.4073442750946</v>
+        <v>122.6045926253662</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.702899677535243</v>
+        <v>-16.59456309992011</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5302588372436102</v>
+        <v>0.5347989950220621</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1244621746614578</v>
+        <v>0.1283240210595969</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2287606857794077</v>
+        <v>0.2487730257572817</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5380780482675814</v>
+        <v>0.5187382426128976</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2885229756050143</v>
+        <v>0.2572702462424255</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3471190076599779</v>
+        <v>0.4292011251938953</v>
       </c>
       <c r="V25" t="n">
-        <v>104.4225385802469</v>
+        <v>103.7409799382716</v>
       </c>
       <c r="W25" t="n">
-        <v>113.7056327160494</v>
+        <v>114.7762345679013</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.828703703703704</v>
+        <v>-4.881172839506173</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5659510480172956</v>
+        <v>0.5721354304306145</v>
       </c>
       <c r="Z25" t="n">
-        <v>116.83</v>
+        <v>110.04</v>
       </c>
       <c r="AA25" t="n">
-        <v>-9.199999999999999</v>
+        <v>-15.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.6658146557452705</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC25" t="n">
-        <v>113.1126313914285</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD25" t="n">
-        <v>113.7784460471737</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -3178,106 +3178,106 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.8582446795382304</v>
+        <v>-1.272452310562987</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>1392.576</v>
+        <v>1367.445</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9533</v>
+        <v>-1.236</v>
       </c>
       <c r="I26" t="n">
-        <v>1495.56301369863</v>
+        <v>1505.736932432432</v>
       </c>
       <c r="J26" t="n">
-        <v>111.0014556837374</v>
+        <v>108.1434911067367</v>
       </c>
       <c r="K26" t="n">
-        <v>117.2487831258569</v>
+        <v>114.4567808048534</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.247327442119441</v>
+        <v>-6.313289698116715</v>
       </c>
       <c r="M26" t="n">
-        <v>108.5295033782342</v>
+        <v>109.452233134867</v>
       </c>
       <c r="N26" t="n">
-        <v>125.2671883999827</v>
+        <v>119.5412037673145</v>
       </c>
       <c r="O26" t="n">
-        <v>-16.73768502174848</v>
+        <v>-10.0889706324475</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5654017522911772</v>
+        <v>0.5250881248043711</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1327099764755128</v>
+        <v>0.1239270820247598</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2028133467877343</v>
+        <v>0.2300202165299197</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5718101821538651</v>
+        <v>0.5194393351601714</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2258276597635588</v>
+        <v>0.2891105229330774</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4513818030705053</v>
+        <v>0.3487197505468425</v>
       </c>
       <c r="V26" t="n">
-        <v>99.64861145703611</v>
+        <v>104.18</v>
       </c>
       <c r="W26" t="n">
-        <v>110.4564134495641</v>
+        <v>112.8741312741312</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.503113325031133</v>
+        <v>-5.985328185328186</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5891929792821271</v>
+        <v>0.5616617807446239</v>
       </c>
       <c r="Z26" t="n">
-        <v>106.88</v>
+        <v>114.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>-16.34</v>
+        <v>-10.99</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.809266556998161</v>
+        <v>-0.6658146557452705</v>
       </c>
       <c r="AC26" t="n">
-        <v>114.2499905834389</v>
+        <v>113.1126313914285</v>
       </c>
       <c r="AD26" t="n">
-        <v>112.4407240264407</v>
+        <v>113.7784460471737</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.325354312902254</v>
+        <v>-0.8826179422952067</v>
       </c>
     </row>
     <row r="27">
@@ -3313,7 +3313,7 @@
         <v>46110</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
         <v>1333.301</v>
@@ -3325,13 +3325,13 @@
         <v>1502.167067567568</v>
       </c>
       <c r="J27" t="n">
-        <v>109.4082721137208</v>
+        <v>109.3859430195654</v>
       </c>
       <c r="K27" t="n">
-        <v>116.9669386163866</v>
+        <v>116.9711120655437</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.558666502665764</v>
+        <v>-7.585169045978272</v>
       </c>
       <c r="M27" t="n">
         <v>116.0042747534943</v>
@@ -3343,34 +3343,34 @@
         <v>-5.856351435475844</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5342633260882516</v>
+        <v>0.5340928136128059</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1211612138054672</v>
+        <v>0.1211856141443302</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2127180396534026</v>
+        <v>0.212873111392034</v>
       </c>
       <c r="S27" t="n">
         <v>0.5880433477755221</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2560087037621718</v>
+        <v>0.2561487579208239</v>
       </c>
       <c r="U27" t="n">
-        <v>0.419362922121174</v>
+        <v>0.4193573664174413</v>
       </c>
       <c r="V27" t="n">
-        <v>103.0802837837838</v>
+        <v>103.0781595881596</v>
       </c>
       <c r="W27" t="n">
-        <v>112.4827702702703</v>
+        <v>112.4552767052767</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.099662162162163</v>
+        <v>-8.130308880308881</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5696062997045964</v>
+        <v>0.5694583842231599</v>
       </c>
       <c r="Z27" t="n">
         <v>117.09</v>
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1.163399342344155</v>
+        <v>-0.8565486750296631</v>
       </c>
     </row>
     <row r="28">
@@ -3415,76 +3415,76 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>1309.746</v>
+        <v>1307.985</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.9192</v>
       </c>
       <c r="I28" t="n">
-        <v>1510.146851351351</v>
+        <v>1510.067613333333</v>
       </c>
       <c r="J28" t="n">
-        <v>111.9393183172995</v>
+        <v>112.0542475400604</v>
       </c>
       <c r="K28" t="n">
-        <v>120.06006319031</v>
+        <v>119.9067105543185</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.120744873010466</v>
+        <v>-7.852463014258137</v>
       </c>
       <c r="M28" t="n">
-        <v>112.5694386500763</v>
+        <v>111.9894237089151</v>
       </c>
       <c r="N28" t="n">
-        <v>121.4295861468688</v>
+        <v>121.4919277036386</v>
       </c>
       <c r="O28" t="n">
-        <v>-8.860147496792447</v>
+        <v>-9.502503994723583</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5377139582276784</v>
+        <v>0.5387142966048171</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.128478213953888</v>
+        <v>0.128748458530245</v>
       </c>
       <c r="R28" t="n">
-        <v>0.260821655944377</v>
+        <v>0.2604464396585496</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5441452335372824</v>
+        <v>0.5452983241606455</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2836228157608296</v>
+        <v>0.2832750446804164</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4064907799125234</v>
+        <v>0.4068857240311238</v>
       </c>
       <c r="V28" t="n">
-        <v>104.707846027846</v>
+        <v>104.6242117647058</v>
       </c>
       <c r="W28" t="n">
-        <v>117.2424242424242</v>
+        <v>117.2576470588236</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.331695331695331</v>
+        <v>-8.068235294117647</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5775852326738963</v>
+        <v>0.5783510978438789</v>
       </c>
       <c r="Z28" t="n">
-        <v>117.28</v>
+        <v>116.78</v>
       </c>
       <c r="AA28" t="n">
-        <v>-10.42</v>
+        <v>-11.34</v>
       </c>
       <c r="AB28" t="n">
         <v>-9.725925288085115</v>
@@ -3496,16 +3496,16 @@
         <v>118.4459117504312</v>
       </c>
       <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="n">
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.339099494480226</v>
+        <v>-1.621555960980303</v>
       </c>
     </row>
     <row r="29">
@@ -3529,7 +3529,7 @@
         <v>46110</v>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
         <v>1312.653</v>
@@ -3541,13 +3541,13 @@
         <v>1519.756533333333</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1593090233404</v>
+        <v>109.1440390404885</v>
       </c>
       <c r="K29" t="n">
-        <v>118.8379255399209</v>
+        <v>118.8397956810164</v>
       </c>
       <c r="L29" t="n">
-        <v>-9.678616516580554</v>
+        <v>-9.695756640527938</v>
       </c>
       <c r="M29" t="n">
         <v>112.4250289223267</v>
@@ -3559,34 +3559,34 @@
         <v>-8.682635238726643</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5234094071119985</v>
+        <v>0.5233431516354192</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.120760413153027</v>
+        <v>0.1207896874930093</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2538523429764113</v>
+        <v>0.2539389239464369</v>
       </c>
       <c r="S29" t="n">
         <v>0.5494064771474977</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2562029693431301</v>
+        <v>0.2562806730547172</v>
       </c>
       <c r="U29" t="n">
-        <v>0.337851023300382</v>
+        <v>0.3379318888869711</v>
       </c>
       <c r="V29" t="n">
-        <v>101.6559301587301</v>
+        <v>101.6479452991453</v>
       </c>
       <c r="W29" t="n">
-        <v>110.584126984127</v>
+        <v>110.5623931623932</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.49206349206349</v>
+        <v>-10.5042735042735</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.558874235035893</v>
+        <v>0.558803275179501</v>
       </c>
       <c r="Z29" t="n">
         <v>111.15</v>
@@ -3613,7 +3613,7 @@
         <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.493679486412309</v>
+        <v>-1.743820197725972</v>
       </c>
     </row>
     <row r="30">
@@ -3631,76 +3631,76 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G30" t="n">
-        <v>1292.136</v>
+        <v>1294.032</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.7089</v>
+        <v>-1.4447</v>
       </c>
       <c r="I30" t="n">
-        <v>1504.278040540541</v>
+        <v>1501.72304</v>
       </c>
       <c r="J30" t="n">
-        <v>107.098714182423</v>
+        <v>106.6396659292955</v>
       </c>
       <c r="K30" t="n">
-        <v>116.8059463442823</v>
+        <v>117.0537081099374</v>
       </c>
       <c r="L30" t="n">
-        <v>-9.707232161859281</v>
+        <v>-10.41404218064183</v>
       </c>
       <c r="M30" t="n">
-        <v>101.4996411341091</v>
+        <v>99.88338055761382</v>
       </c>
       <c r="N30" t="n">
-        <v>114.8456990541268</v>
+        <v>113.3443506278637</v>
       </c>
       <c r="O30" t="n">
-        <v>-13.34605792001766</v>
+        <v>-13.46097007024982</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5228788571849389</v>
+        <v>0.5202040066964976</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1382980014451012</v>
+        <v>0.1383763370598489</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2425397378513306</v>
+        <v>0.2396344701445607</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5051319384702859</v>
+        <v>0.4960370991051177</v>
       </c>
       <c r="T30" t="n">
-        <v>0.275625022426591</v>
+        <v>0.2781054659202154</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4584689476235541</v>
+        <v>0.4587452752110392</v>
       </c>
       <c r="V30" t="n">
-        <v>99.15240893066978</v>
+        <v>99.07138787878786</v>
       </c>
       <c r="W30" t="n">
-        <v>106.3892479435958</v>
+        <v>105.8451515151516</v>
       </c>
       <c r="X30" t="n">
-        <v>-8.91069330199765</v>
+        <v>-9.630303030303029</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5616258067653828</v>
+        <v>0.5598989442375895</v>
       </c>
       <c r="Z30" t="n">
-        <v>101.51</v>
+        <v>99.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>-13.06</v>
+        <v>-12.91</v>
       </c>
       <c r="AB30" t="n">
         <v>-6.499587896466165</v>
@@ -3718,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.74802864321345</v>
+        <v>-1.527916746817435</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>1259.877</v>
+        <v>1258.158</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6629</v>
+        <v>-0.5584</v>
       </c>
       <c r="I31" t="n">
-        <v>1505.620547945206</v>
+        <v>1505.020743243243</v>
       </c>
       <c r="J31" t="n">
-        <v>108.4065914419434</v>
+        <v>108.3839503310121</v>
       </c>
       <c r="K31" t="n">
-        <v>119.788958771733</v>
+        <v>119.8255649266585</v>
       </c>
       <c r="L31" t="n">
-        <v>-11.38236732978958</v>
+        <v>-11.44161459564642</v>
       </c>
       <c r="M31" t="n">
-        <v>108.19083768269</v>
+        <v>107.4275001861903</v>
       </c>
       <c r="N31" t="n">
-        <v>122.0124736856867</v>
+        <v>121.388243173222</v>
       </c>
       <c r="O31" t="n">
-        <v>-13.82163600299673</v>
+        <v>-13.96074298703179</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5332562266103287</v>
+        <v>0.5334401619956255</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1330304639804435</v>
+        <v>0.1318143240784889</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2395338816723344</v>
+        <v>0.2370592000614369</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5556852771276904</v>
+        <v>0.5454680986563969</v>
       </c>
       <c r="T31" t="n">
-        <v>0.23813071282829</v>
+        <v>0.2363967466545321</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4031452535117044</v>
+        <v>0.4041425680322631</v>
       </c>
       <c r="V31" t="n">
-        <v>103.6997794854661</v>
+        <v>103.6577541827542</v>
       </c>
       <c r="W31" t="n">
-        <v>112.3635148680254</v>
+        <v>112.3581081081081</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.62545940527898</v>
+        <v>-11.54665379665379</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5655237529046609</v>
+        <v>0.5652795629526614</v>
       </c>
       <c r="Z31" t="n">
-        <v>114.28</v>
+        <v>111.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>-13.85</v>
+        <v>-13.51</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3820,16 +3820,16 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.586478568935741</v>
+        <v>-1.349711254552437</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.054647813739654</v>
+        <v>1.144467156633482</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.05794599333186</v>
+        <v>0.9408463785982776</v>
       </c>
     </row>
     <row r="4">
@@ -841,58 +841,58 @@
         <v>1494.837527027027</v>
       </c>
       <c r="J4" t="n">
-        <v>115.0499064043499</v>
+        <v>115.0037914900197</v>
       </c>
       <c r="K4" t="n">
-        <v>107.4550411192851</v>
+        <v>107.6723814989632</v>
       </c>
       <c r="L4" t="n">
-        <v>7.594865285064778</v>
+        <v>7.331409991056543</v>
       </c>
       <c r="M4" t="n">
-        <v>118.1453411518176</v>
+        <v>117.9516585116308</v>
       </c>
       <c r="N4" t="n">
-        <v>106.6396216175497</v>
+        <v>107.5524512121974</v>
       </c>
       <c r="O4" t="n">
-        <v>11.50571953426796</v>
+        <v>10.39920729943336</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5488759747473901</v>
+        <v>0.54790031287187</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1245083001906635</v>
+        <v>0.1240687795425427</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3034672410517253</v>
+        <v>0.3026169009156709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5762722377660962</v>
+        <v>0.5721744578889115</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2950725942446417</v>
+        <v>0.2958261313704036</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3478787002128193</v>
+        <v>0.347991168440545</v>
       </c>
       <c r="V4" t="n">
-        <v>101.6533075933076</v>
+        <v>102.1433075933076</v>
       </c>
       <c r="W4" t="n">
-        <v>117.0096525096526</v>
+        <v>117.5810810810811</v>
       </c>
       <c r="X4" t="n">
-        <v>8.077220077220078</v>
+        <v>7.886743886743888</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5849306574504874</v>
+        <v>0.5843526842735363</v>
       </c>
       <c r="Z4" t="n">
-        <v>117.04</v>
+        <v>119.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.45</v>
+        <v>9.65</v>
       </c>
       <c r="AB4" t="n">
         <v>1.549391602834736</v>
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2435200837404501</v>
+        <v>-0.2243526728704913</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.154744255921994</v>
+        <v>1.126556939133272</v>
       </c>
     </row>
     <row r="6">
@@ -1057,58 +1057,58 @@
         <v>1489.565824324324</v>
       </c>
       <c r="J6" t="n">
-        <v>116.9928602595211</v>
+        <v>116.9487175068908</v>
       </c>
       <c r="K6" t="n">
-        <v>111.3143552011961</v>
+        <v>111.1358166697704</v>
       </c>
       <c r="L6" t="n">
-        <v>5.67850505832501</v>
+        <v>5.812900837120325</v>
       </c>
       <c r="M6" t="n">
-        <v>118.9050852839192</v>
+        <v>118.7549999249761</v>
       </c>
       <c r="N6" t="n">
-        <v>115.490129606859</v>
+        <v>114.8830986000118</v>
       </c>
       <c r="O6" t="n">
-        <v>3.414955677060157</v>
+        <v>3.871901324964229</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5531418193831777</v>
+        <v>0.5524156631377466</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1161127571774494</v>
+        <v>0.1155458011279033</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2909811475820107</v>
+        <v>0.2914395127462582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5603445175844828</v>
+        <v>0.5578755863500172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2368330158372437</v>
+        <v>0.2373983455316732</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4293995914850238</v>
+        <v>0.4295652915678739</v>
       </c>
       <c r="V6" t="n">
-        <v>98.91096979332275</v>
+        <v>99.26685214626391</v>
       </c>
       <c r="W6" t="n">
-        <v>115.5902225755167</v>
+        <v>115.9431637519873</v>
       </c>
       <c r="X6" t="n">
-        <v>5.487678855325915</v>
+        <v>5.546502384737679</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5861065869212786</v>
+        <v>0.5853170016078657</v>
       </c>
       <c r="Z6" t="n">
-        <v>112.69</v>
+        <v>113.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="AB6" t="n">
         <v>2.775420617465777</v>
@@ -1129,103 +1129,103 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.018649873552174</v>
+        <v>1.078725517542721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46112</v>
+        <v>46110</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>1578.449</v>
+        <v>1595.508</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5871</v>
+        <v>1.3553</v>
       </c>
       <c r="I7" t="n">
-        <v>1495.876986486486</v>
+        <v>1501.8568</v>
       </c>
       <c r="J7" t="n">
-        <v>115.7075921372753</v>
+        <v>119.8587919475473</v>
       </c>
       <c r="K7" t="n">
-        <v>110.8974706490588</v>
+        <v>115.0958848187337</v>
       </c>
       <c r="L7" t="n">
-        <v>4.810121488216581</v>
+        <v>4.762907128813691</v>
       </c>
       <c r="M7" t="n">
-        <v>115.5599209331499</v>
+        <v>123.6130227773458</v>
       </c>
       <c r="N7" t="n">
-        <v>112.8664682587248</v>
+        <v>112.697727550607</v>
       </c>
       <c r="O7" t="n">
-        <v>2.693452674425058</v>
+        <v>10.91529522673882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5447533095779298</v>
+        <v>0.5767951977185795</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1266528565862367</v>
+        <v>0.1098720540359938</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3438517791625675</v>
+        <v>0.2313927488520803</v>
       </c>
       <c r="S7" t="n">
-        <v>0.548269707561173</v>
+        <v>0.6043246941612436</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2620519417962008</v>
+        <v>0.3009684618297749</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3505428808571338</v>
+        <v>0.4082694011760947</v>
       </c>
       <c r="V7" t="n">
-        <v>98.65701858108109</v>
+        <v>101.1406349206349</v>
       </c>
       <c r="W7" t="n">
-        <v>113.9864864864865</v>
+        <v>121.2063492063492</v>
       </c>
       <c r="X7" t="n">
-        <v>4.756756756756757</v>
+        <v>4.868888888888889</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5774111730857776</v>
+        <v>0.6162212021528615</v>
       </c>
       <c r="Z7" t="n">
-        <v>112.07</v>
+        <v>127.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>11.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.413694058608522</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC7" t="n">
-        <v>112.3850185369902</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD7" t="n">
-        <v>108.9713244783817</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1234,106 +1234,106 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.7094142512935475</v>
+        <v>1.608438258285271</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>1595.508</v>
+        <v>1578.449</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3553</v>
+        <v>-0.5871</v>
       </c>
       <c r="I8" t="n">
-        <v>1501.8568</v>
+        <v>1495.876986486486</v>
       </c>
       <c r="J8" t="n">
-        <v>119.8587919475473</v>
+        <v>115.5178949476356</v>
       </c>
       <c r="K8" t="n">
-        <v>115.0958848187337</v>
+        <v>110.8505689743891</v>
       </c>
       <c r="L8" t="n">
-        <v>4.762907128813691</v>
+        <v>4.667325973246558</v>
       </c>
       <c r="M8" t="n">
-        <v>123.6130227773458</v>
+        <v>114.9528899263027</v>
       </c>
       <c r="N8" t="n">
-        <v>112.697727550607</v>
+        <v>112.7163828997817</v>
       </c>
       <c r="O8" t="n">
-        <v>10.91529522673882</v>
+        <v>2.236507026520986</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5767951977185795</v>
+        <v>0.5442046055645519</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1098720540359938</v>
+        <v>0.127042078805649</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2313927488520803</v>
+        <v>0.3429589220197104</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6043246941612436</v>
+        <v>0.5465138547183636</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3009684618297749</v>
+        <v>0.2616687199455877</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4082694011760947</v>
+        <v>0.3505254616821059</v>
       </c>
       <c r="V8" t="n">
-        <v>101.1406349206349</v>
+        <v>99.03514358108109</v>
       </c>
       <c r="W8" t="n">
-        <v>121.2063492063492</v>
+        <v>114.2989864864865</v>
       </c>
       <c r="X8" t="n">
-        <v>4.868888888888889</v>
+        <v>4.694256756756757</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6162212021528615</v>
+        <v>0.5769313179786882</v>
       </c>
       <c r="Z8" t="n">
-        <v>127.07</v>
+        <v>113.07</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.722616812266775</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC8" t="n">
-        <v>116.5392386763017</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD8" t="n">
-        <v>113.8166218640349</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.671732794537588</v>
+        <v>0.469839084743044</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.7854853950029779</v>
+        <v>0.8461642528187161</v>
       </c>
     </row>
     <row r="10">
@@ -1471,76 +1471,76 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>1641.851</v>
+        <v>1642.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4295</v>
+        <v>-0.1251</v>
       </c>
       <c r="I10" t="n">
-        <v>1490.952351351351</v>
+        <v>1488.512786666667</v>
       </c>
       <c r="J10" t="n">
-        <v>116.9726637626015</v>
+        <v>116.8743270139733</v>
       </c>
       <c r="K10" t="n">
-        <v>112.600316646653</v>
+        <v>113.0743600371265</v>
       </c>
       <c r="L10" t="n">
-        <v>4.372347115948564</v>
+        <v>3.799966976846822</v>
       </c>
       <c r="M10" t="n">
-        <v>122.8320412332206</v>
+        <v>122.228227073958</v>
       </c>
       <c r="N10" t="n">
-        <v>116.6956804899088</v>
+        <v>119.2668111604354</v>
       </c>
       <c r="O10" t="n">
-        <v>6.13636074331168</v>
+        <v>2.961415913522665</v>
       </c>
       <c r="P10" t="n">
-        <v>0.560608721564555</v>
+        <v>0.5608988194153629</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1159089974077238</v>
+        <v>0.1165195053313867</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2645611477954666</v>
+        <v>0.2646375296408656</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5859569232727092</v>
+        <v>0.5880122051555773</v>
       </c>
       <c r="T10" t="n">
-        <v>0.268029570467252</v>
+        <v>0.266273032258899</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4417072432302836</v>
+        <v>0.4433383359183564</v>
       </c>
       <c r="V10" t="n">
-        <v>102.2525634725635</v>
+        <v>102.1497886178861</v>
       </c>
       <c r="W10" t="n">
-        <v>119.4709254709255</v>
+        <v>119.269918699187</v>
       </c>
       <c r="X10" t="n">
-        <v>4.374283374283374</v>
+        <v>3.847154471544715</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.594325440124746</v>
+        <v>0.5942052802403387</v>
       </c>
       <c r="Z10" t="n">
-        <v>123.08</v>
+        <v>122.81</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.03</v>
+        <v>3.28</v>
       </c>
       <c r="AB10" t="n">
         <v>9.967224035556209</v>
@@ -1552,16 +1552,16 @@
         <v>110.1289876408569</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.463427058115498</v>
+        <v>1.509883395809169</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.5896988706654002</v>
+        <v>0.3846455861595832</v>
       </c>
     </row>
     <row r="12">
@@ -1687,76 +1687,76 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>1562.95</v>
+        <v>1563.777</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4054</v>
+        <v>2.8829</v>
       </c>
       <c r="I12" t="n">
-        <v>1493.349445945946</v>
+        <v>1490.21356</v>
       </c>
       <c r="J12" t="n">
-        <v>116.7716169045549</v>
+        <v>117.1445149676861</v>
       </c>
       <c r="K12" t="n">
-        <v>113.8579626635471</v>
+        <v>114.0931817722708</v>
       </c>
       <c r="L12" t="n">
-        <v>2.913654241007723</v>
+        <v>3.051333195415258</v>
       </c>
       <c r="M12" t="n">
-        <v>121.486935110467</v>
+        <v>122.2459294720319</v>
       </c>
       <c r="N12" t="n">
-        <v>110.7308856635711</v>
+        <v>111.2401223350463</v>
       </c>
       <c r="O12" t="n">
-        <v>10.75604944689594</v>
+        <v>11.0058071369856</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5732021274980995</v>
+        <v>0.5742086184011108</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.125332779499649</v>
+        <v>0.1243224405097613</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2389884340124057</v>
+        <v>0.2392508407950233</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5861618102069696</v>
+        <v>0.5933263770082704</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3253973693490874</v>
+        <v>0.3240728329422835</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3966976517946511</v>
+        <v>0.3971746377419328</v>
       </c>
       <c r="V12" t="n">
-        <v>100.3452113652113</v>
+        <v>100.2461561904762</v>
       </c>
       <c r="W12" t="n">
-        <v>116.7214137214137</v>
+        <v>116.9748571428571</v>
       </c>
       <c r="X12" t="n">
-        <v>2.172557172557173</v>
+        <v>2.304</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6097055293758746</v>
+        <v>0.6110680973903058</v>
       </c>
       <c r="Z12" t="n">
-        <v>121.35</v>
+        <v>122.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="AB12" t="n">
         <v>1.827913300592181</v>
@@ -1768,232 +1768,232 @@
         <v>112.3217604872965</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.384298349405215</v>
+        <v>1.631216456215913</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>1557.165</v>
+        <v>1531.531</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2445</v>
+        <v>-3.1116</v>
       </c>
       <c r="I13" t="n">
-        <v>1497.633094594595</v>
+        <v>1505.69156</v>
       </c>
       <c r="J13" t="n">
-        <v>116.2232391202087</v>
+        <v>113.7409191744289</v>
       </c>
       <c r="K13" t="n">
-        <v>113.5442006401876</v>
+        <v>111.3794604939758</v>
       </c>
       <c r="L13" t="n">
-        <v>2.679038480021139</v>
+        <v>2.361458680452965</v>
       </c>
       <c r="M13" t="n">
-        <v>122.2639351473496</v>
+        <v>115.8719111038512</v>
       </c>
       <c r="N13" t="n">
-        <v>113.0364485781071</v>
+        <v>118.4071104219959</v>
       </c>
       <c r="O13" t="n">
-        <v>9.227486569242526</v>
+        <v>-2.535199318144721</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5630493279092167</v>
+        <v>0.5363101165105528</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1260936537482905</v>
+        <v>0.1118098196120276</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2356311658846714</v>
+        <v>0.2529481789512728</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5979483400602705</v>
+        <v>0.5361416630337882</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3047469395663296</v>
+        <v>0.2731182182832637</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4041184775377864</v>
+        <v>0.4045384214955133</v>
       </c>
       <c r="V13" t="n">
-        <v>98.80778528528529</v>
+        <v>105.7295609756098</v>
       </c>
       <c r="W13" t="n">
-        <v>114.1903153153153</v>
+        <v>120.2227642276422</v>
       </c>
       <c r="X13" t="n">
-        <v>1.676426426426426</v>
+        <v>2.507317073170732</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6069030739213469</v>
+        <v>0.574987932045124</v>
       </c>
       <c r="Z13" t="n">
-        <v>121.06</v>
+        <v>120.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.52</v>
+        <v>-4.489999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.815266446541752</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC13" t="n">
-        <v>113.8106821492749</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD13" t="n">
-        <v>108.9954157027332</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.4333003593217314</v>
+        <v>0.02842587194406881</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612748</v>
+        <v>1610612746</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>1531.531</v>
+        <v>1559.934</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.1116</v>
+        <v>-0.369</v>
       </c>
       <c r="I14" t="n">
-        <v>1505.69156</v>
+        <v>1496.232333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>113.7409191744289</v>
+        <v>115.9483952380811</v>
       </c>
       <c r="K14" t="n">
-        <v>111.3794604939758</v>
+        <v>113.7503670545904</v>
       </c>
       <c r="L14" t="n">
-        <v>2.361458680452965</v>
+        <v>2.198028183490708</v>
       </c>
       <c r="M14" t="n">
-        <v>115.8719111038512</v>
+        <v>118.6065612920006</v>
       </c>
       <c r="N14" t="n">
-        <v>118.4071104219959</v>
+        <v>112.8318133006466</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.535199318144721</v>
+        <v>5.774747991354014</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5363101165105528</v>
+        <v>0.5615911794000334</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1118098196120276</v>
+        <v>0.1260816157267504</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2529481789512728</v>
+        <v>0.235003752760578</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5361416630337882</v>
+        <v>0.5803389757403798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2731182182832637</v>
+        <v>0.3038393680319152</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4045384214955133</v>
+        <v>0.4040814687946172</v>
       </c>
       <c r="V14" t="n">
-        <v>105.7295609756098</v>
+        <v>98.6519649122807</v>
       </c>
       <c r="W14" t="n">
-        <v>120.2227642276422</v>
+        <v>113.7368421052632</v>
       </c>
       <c r="X14" t="n">
-        <v>2.507317073170732</v>
+        <v>1.190877192982456</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.574987932045124</v>
+        <v>0.6053168140463405</v>
       </c>
       <c r="Z14" t="n">
-        <v>120.8</v>
+        <v>116.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>-4.489999999999999</v>
+        <v>4.130000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.094669144490311</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC14" t="n">
-        <v>111.6804548463295</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD14" t="n">
-        <v>112.7751239908198</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1</v>
-      </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.07654764934946894</v>
+        <v>0.3645699799132338</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.7323739481909893</v>
+        <v>0.5943140525477608</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.08047548469645489</v>
+        <v>0.08023621246628569</v>
       </c>
     </row>
     <row r="17">
@@ -2245,58 +2245,58 @@
         <v>1495.614162162162</v>
       </c>
       <c r="J17" t="n">
-        <v>112.9917312467636</v>
+        <v>113.260210539307</v>
       </c>
       <c r="K17" t="n">
-        <v>111.8874680377456</v>
+        <v>111.8305025553377</v>
       </c>
       <c r="L17" t="n">
-        <v>1.104263209017855</v>
+        <v>1.429707983969206</v>
       </c>
       <c r="M17" t="n">
-        <v>117.1774719255155</v>
+        <v>118.0903015201633</v>
       </c>
       <c r="N17" t="n">
-        <v>115.4856358995865</v>
+        <v>115.2919532593997</v>
       </c>
       <c r="O17" t="n">
-        <v>1.691836025928978</v>
+        <v>2.79834826076357</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5424223638757518</v>
+        <v>0.5435790063080056</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1164992817984343</v>
+        <v>0.1156496788769415</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2566098128748526</v>
+        <v>0.2559576673159639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5738457380891842</v>
+        <v>0.5777783223588471</v>
       </c>
       <c r="T17" t="n">
-        <v>0.263268479510689</v>
+        <v>0.2626998779788668</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3685386386392667</v>
+        <v>0.3681741504778421</v>
       </c>
       <c r="V17" t="n">
-        <v>100.2155007949125</v>
+        <v>100.8207949125596</v>
       </c>
       <c r="W17" t="n">
-        <v>113.4324324324324</v>
+        <v>114.3736089030206</v>
       </c>
       <c r="X17" t="n">
-        <v>1.736486486486487</v>
+        <v>1.971780604133546</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5765112689620505</v>
+        <v>0.5774946886625965</v>
       </c>
       <c r="Z17" t="n">
-        <v>116.31</v>
+        <v>119.51</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AB17" t="n">
         <v>-4.536933640611859</v>
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1448612802524424</v>
+        <v>0.3354089720088078</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.2596253792261301</v>
+        <v>-0.3534539730612285</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.4903444140992576</v>
+        <v>0.5118069354933249</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.7030458990769218</v>
+        <v>-0.3409077073260275</v>
       </c>
     </row>
     <row r="21">
@@ -2659,76 +2659,76 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>1461.235</v>
+        <v>1462.955</v>
       </c>
       <c r="H21" t="n">
-        <v>1.549</v>
+        <v>1.5089</v>
       </c>
       <c r="I21" t="n">
-        <v>1506.38652</v>
+        <v>1503.14297368421</v>
       </c>
       <c r="J21" t="n">
-        <v>111.2338292538253</v>
+        <v>111.3551059071822</v>
       </c>
       <c r="K21" t="n">
-        <v>112.0772110009368</v>
+        <v>112.4852297991604</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8433817471115478</v>
+        <v>-1.130123891978222</v>
       </c>
       <c r="M21" t="n">
-        <v>112.1685038482119</v>
+        <v>113.796125832089</v>
       </c>
       <c r="N21" t="n">
-        <v>102.5585218996881</v>
+        <v>103.6274762135796</v>
       </c>
       <c r="O21" t="n">
-        <v>9.60998194852375</v>
+        <v>10.16864961850941</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5338001034461746</v>
+        <v>0.53308121378109</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1413185191573287</v>
+        <v>0.1411220582402496</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3094197279083685</v>
+        <v>0.3138209316122616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.549333250051234</v>
+        <v>0.5501894938354689</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2896623628925938</v>
+        <v>0.2859735985147895</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4664144779896672</v>
+        <v>0.4678732084769952</v>
       </c>
       <c r="V21" t="n">
-        <v>103.5418888888889</v>
+        <v>103.2807112375533</v>
       </c>
       <c r="W21" t="n">
-        <v>115.4555555555555</v>
+        <v>115.3058321479374</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2722222222222224</v>
+        <v>-0.5106685633001422</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5707352849467603</v>
+        <v>0.5702431553636502</v>
       </c>
       <c r="Z21" t="n">
-        <v>115.44</v>
+        <v>116.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.34</v>
+        <v>11.17</v>
       </c>
       <c r="AB21" t="n">
         <v>-3.840928550668963</v>
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.3913271559838703</v>
+        <v>-0.5373897719310309</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.4104168172554537</v>
+        <v>-0.4268619459623897</v>
       </c>
     </row>
     <row r="23">
@@ -2965,103 +2965,103 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.4402893876814114</v>
+        <v>-0.4541394036544683</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>1389.808</v>
+        <v>1384.188</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0852</v>
+        <v>-1.6948</v>
       </c>
       <c r="I24" t="n">
-        <v>1496.395472972973</v>
+        <v>1495.014902777778</v>
       </c>
       <c r="J24" t="n">
-        <v>111.2684022912795</v>
+        <v>110.4050796922825</v>
       </c>
       <c r="K24" t="n">
-        <v>116.4796851011481</v>
+        <v>115.7632853352394</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.211282809868516</v>
+        <v>-5.358205642957026</v>
       </c>
       <c r="M24" t="n">
-        <v>109.2355695170871</v>
+        <v>106.0100295254461</v>
       </c>
       <c r="N24" t="n">
-        <v>121.0077932952984</v>
+        <v>122.6045926253662</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.77222377821126</v>
+        <v>-16.59456309992011</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5654139548645576</v>
+        <v>0.5347989950220621</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1318193190835407</v>
+        <v>0.1283240210595969</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2048077253296345</v>
+        <v>0.2487730257572817</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5701947244408464</v>
+        <v>0.5187382426128976</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2268512971722048</v>
+        <v>0.2572702462424255</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4541403908818142</v>
+        <v>0.4292011251938953</v>
       </c>
       <c r="V24" t="n">
-        <v>99.54065919578115</v>
+        <v>103.7409799382716</v>
       </c>
       <c r="W24" t="n">
-        <v>110.5438365194463</v>
+        <v>114.7762345679013</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.592617007251153</v>
+        <v>-4.881172839506173</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5893963364390316</v>
+        <v>0.5721354304306145</v>
       </c>
       <c r="Z24" t="n">
-        <v>106.99</v>
+        <v>110.04</v>
       </c>
       <c r="AA24" t="n">
-        <v>-12.05</v>
+        <v>-15.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.809266556998161</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC24" t="n">
-        <v>114.2499905834389</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD24" t="n">
-        <v>112.4407240264407</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -3070,106 +3070,106 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9920046818490768</v>
+        <v>-1.112783538102896</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>1384.188</v>
+        <v>1389.808</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6948</v>
+        <v>-2.0852</v>
       </c>
       <c r="I25" t="n">
-        <v>1495.014902777778</v>
+        <v>1496.395472972973</v>
       </c>
       <c r="J25" t="n">
-        <v>110.4050796922825</v>
+        <v>111.0843447152485</v>
       </c>
       <c r="K25" t="n">
-        <v>115.7632853352394</v>
+        <v>116.508571287028</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.358205642957026</v>
+        <v>-5.424226571779472</v>
       </c>
       <c r="M25" t="n">
-        <v>106.0100295254461</v>
+        <v>108.4809334553597</v>
       </c>
       <c r="N25" t="n">
-        <v>122.6045926253662</v>
+        <v>121.126226657406</v>
       </c>
       <c r="O25" t="n">
-        <v>-16.59456309992011</v>
+        <v>-12.64529320204618</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5347989950220621</v>
+        <v>0.564359975607904</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1283240210595969</v>
+        <v>0.1320448378704686</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2487730257572817</v>
+        <v>0.2048077253296345</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5187382426128976</v>
+        <v>0.5658734094885665</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2572702462424255</v>
+        <v>0.2274979102130966</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4292011251938953</v>
+        <v>0.4535843036666473</v>
       </c>
       <c r="V25" t="n">
-        <v>103.7409799382716</v>
+        <v>99.84651285431772</v>
       </c>
       <c r="W25" t="n">
-        <v>114.7762345679013</v>
+        <v>110.7389584706658</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.881172839506173</v>
+        <v>-5.690177982860909</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5721354304306145</v>
+        <v>0.5885266172640808</v>
       </c>
       <c r="Z25" t="n">
-        <v>110.04</v>
+        <v>107.79</v>
       </c>
       <c r="AA25" t="n">
-        <v>-15.47</v>
+        <v>-12.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.575252351995317</v>
+        <v>1.809266556998161</v>
       </c>
       <c r="AC25" t="n">
-        <v>114.5419381230804</v>
+        <v>114.2499905834389</v>
       </c>
       <c r="AD25" t="n">
-        <v>110.9666857710851</v>
+        <v>112.4407240264407</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -3178,10 +3178,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.272452310562987</v>
+        <v>-1.180414315198027</v>
       </c>
     </row>
     <row r="26">
@@ -3217,58 +3217,58 @@
         <v>1505.736932432432</v>
       </c>
       <c r="J26" t="n">
-        <v>108.1434911067367</v>
+        <v>108.1773292101959</v>
       </c>
       <c r="K26" t="n">
-        <v>114.4567808048534</v>
+        <v>114.2411705015027</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.313289698116715</v>
+        <v>-6.063841291306736</v>
       </c>
       <c r="M26" t="n">
-        <v>109.452233134867</v>
+        <v>109.5706664969746</v>
       </c>
       <c r="N26" t="n">
-        <v>119.5412037673145</v>
+        <v>118.7865677055872</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.0889706324475</v>
+        <v>-9.21590120861258</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5250881248043711</v>
+        <v>0.5254347634598332</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1239270820247598</v>
+        <v>0.1238032917883228</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2300202165299197</v>
+        <v>0.2296992867007931</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5194393351601714</v>
+        <v>0.520652570454289</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2891105229330774</v>
+        <v>0.2887043604680914</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3487197505468425</v>
+        <v>0.3483415992863383</v>
       </c>
       <c r="V26" t="n">
-        <v>104.18</v>
+        <v>104.5382857142857</v>
       </c>
       <c r="W26" t="n">
-        <v>112.8741312741312</v>
+        <v>113.2169884169884</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.985328185328186</v>
+        <v>-5.871042471042471</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5616617807446239</v>
+        <v>0.5618309712619205</v>
       </c>
       <c r="Z26" t="n">
-        <v>114.63</v>
+        <v>115.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>-10.99</v>
+        <v>-10.59</v>
       </c>
       <c r="AB26" t="n">
         <v>-0.6658146557452705</v>
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.8826179422952067</v>
+        <v>-1.065296720537024</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.8565486750296631</v>
+        <v>-0.883340938084121</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.621555960980303</v>
+        <v>-1.449735815167216</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.743820197725972</v>
+        <v>-1.557076542454088</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.527916746817435</v>
+        <v>-1.798011424195572</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.349711254552437</v>
+        <v>-1.271780281768349</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -613,7 +613,7 @@
         <v>46111</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
         <v>1754.887</v>
@@ -625,13 +625,13 @@
         <v>1496.527337837838</v>
       </c>
       <c r="J2" t="n">
-        <v>116.6136556484661</v>
+        <v>116.6530283556399</v>
       </c>
       <c r="K2" t="n">
-        <v>105.5200522436053</v>
+        <v>105.5363273232863</v>
       </c>
       <c r="L2" t="n">
-        <v>11.09360340486083</v>
+        <v>11.11670103235359</v>
       </c>
       <c r="M2" t="n">
         <v>118.0988633185223</v>
@@ -643,34 +643,34 @@
         <v>12.32353810530669</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5598477134663284</v>
+        <v>0.5599724631762372</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1082406721706002</v>
+        <v>0.1080537136291331</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2182158490783956</v>
+        <v>0.2184571131540753</v>
       </c>
       <c r="S2" t="n">
         <v>0.556510062828969</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2732903189468668</v>
+        <v>0.2727661952333165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4247527880134307</v>
+        <v>0.4247743075324854</v>
       </c>
       <c r="V2" t="n">
-        <v>101.9579922779923</v>
+        <v>101.9358602504944</v>
       </c>
       <c r="W2" t="n">
-        <v>118.6602316602317</v>
+        <v>118.6802900461437</v>
       </c>
       <c r="X2" t="n">
-        <v>11.03629343629343</v>
+        <v>11.06657877389584</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5997252508221246</v>
+        <v>0.5997262411615215</v>
       </c>
       <c r="Z2" t="n">
         <v>118.41</v>
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.144467156633482</v>
+        <v>1.128497146887424</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>1734.542</v>
+        <v>1735.369</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3067</v>
+        <v>2.8785</v>
       </c>
       <c r="I3" t="n">
-        <v>1509.155082191781</v>
+        <v>1507.407945945946</v>
       </c>
       <c r="J3" t="n">
-        <v>117.6751750385884</v>
+        <v>117.4393759570561</v>
       </c>
       <c r="K3" t="n">
-        <v>108.9566992132959</v>
+        <v>108.8008610571052</v>
       </c>
       <c r="L3" t="n">
-        <v>8.718475825292476</v>
+        <v>8.638514899951035</v>
       </c>
       <c r="M3" t="n">
-        <v>123.4064825459442</v>
+        <v>122.0053173201866</v>
       </c>
       <c r="N3" t="n">
-        <v>107.8794850827237</v>
+        <v>106.6072036100713</v>
       </c>
       <c r="O3" t="n">
-        <v>15.52699746322049</v>
+        <v>15.39811371011537</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5611559395719231</v>
+        <v>0.5605054799289906</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1116258364864828</v>
+        <v>0.1124123883310109</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2597479565148158</v>
+        <v>0.2577406721649955</v>
       </c>
       <c r="S3" t="n">
-        <v>0.576963378344393</v>
+        <v>0.5687480949707696</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2795098994218806</v>
+        <v>0.2831579697772845</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4221250686525996</v>
+        <v>0.4238251658030815</v>
       </c>
       <c r="V3" t="n">
-        <v>102.0280389329488</v>
+        <v>101.5825</v>
       </c>
       <c r="W3" t="n">
-        <v>119.7433309300649</v>
+        <v>119.1599099099099</v>
       </c>
       <c r="X3" t="n">
-        <v>8.397620764239367</v>
+        <v>8.579954954954955</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5966895789339024</v>
+        <v>0.5966858113914896</v>
       </c>
       <c r="Z3" t="n">
-        <v>124.77</v>
+        <v>122.53</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.73</v>
+        <v>15.57</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9408463785982776</v>
+        <v>0.9288160867109657</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +829,7 @@
         <v>46112</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
         <v>1679.675</v>
@@ -841,13 +841,13 @@
         <v>1494.837527027027</v>
       </c>
       <c r="J4" t="n">
-        <v>115.0037914900197</v>
+        <v>115.1392762201249</v>
       </c>
       <c r="K4" t="n">
-        <v>107.6723814989632</v>
+        <v>107.7282548734106</v>
       </c>
       <c r="L4" t="n">
-        <v>7.331409991056543</v>
+        <v>7.411021346714317</v>
       </c>
       <c r="M4" t="n">
         <v>117.9516585116308</v>
@@ -859,34 +859,34 @@
         <v>10.39920729943336</v>
       </c>
       <c r="P4" t="n">
-        <v>0.54790031287187</v>
+        <v>0.5491455415103479</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1240687795425427</v>
+        <v>0.1244900504816549</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3026169009156709</v>
+        <v>0.3021615225442529</v>
       </c>
       <c r="S4" t="n">
         <v>0.5721744578889115</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2958261313704036</v>
+        <v>0.2968225597733392</v>
       </c>
       <c r="U4" t="n">
-        <v>0.347991168440545</v>
+        <v>0.3477062357669112</v>
       </c>
       <c r="V4" t="n">
-        <v>102.1433075933076</v>
+        <v>102.1197384481255</v>
       </c>
       <c r="W4" t="n">
-        <v>117.5810810810811</v>
+        <v>117.662598081953</v>
       </c>
       <c r="X4" t="n">
-        <v>7.886743886743888</v>
+        <v>7.913687881429817</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5843526842735363</v>
+        <v>0.5856708343387226</v>
       </c>
       <c r="Z4" t="n">
         <v>119.44</v>
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2243526728704913</v>
+        <v>-0.2138294435156924</v>
       </c>
     </row>
     <row r="5">
@@ -931,76 +931,76 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>1665.825</v>
+        <v>1660.943</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1853</v>
+        <v>1.3374</v>
       </c>
       <c r="I5" t="n">
-        <v>1490.29327027027</v>
+        <v>1490.646053333333</v>
       </c>
       <c r="J5" t="n">
-        <v>116.9162980958358</v>
+        <v>117.9432994945024</v>
       </c>
       <c r="K5" t="n">
-        <v>110.2850404118825</v>
+        <v>110.7303915184354</v>
       </c>
       <c r="L5" t="n">
-        <v>6.631257683953395</v>
+        <v>7.212907976067041</v>
       </c>
       <c r="M5" t="n">
-        <v>114.0503244848795</v>
+        <v>117.1335655402602</v>
       </c>
       <c r="N5" t="n">
-        <v>110.8482182518995</v>
+        <v>110.887503750448</v>
       </c>
       <c r="O5" t="n">
-        <v>3.202106232980003</v>
+        <v>6.246061789812174</v>
       </c>
       <c r="P5" t="n">
-        <v>0.547409285206768</v>
+        <v>0.5522146110438987</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1047176941552145</v>
+        <v>0.1031479733089335</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2894756767696865</v>
+        <v>0.290819625906369</v>
       </c>
       <c r="S5" t="n">
-        <v>0.531073798697889</v>
+        <v>0.5433248038752407</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2141354934040395</v>
+        <v>0.2128439213511577</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4655994455248036</v>
+        <v>0.4657637091997578</v>
       </c>
       <c r="V5" t="n">
-        <v>97.20340956340956</v>
+        <v>97.27819428571429</v>
       </c>
       <c r="W5" t="n">
-        <v>113.8108108108108</v>
+        <v>114.904</v>
       </c>
       <c r="X5" t="n">
-        <v>6.866943866943868</v>
+        <v>7.392</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5781378650785803</v>
+        <v>0.5822628956384461</v>
       </c>
       <c r="Z5" t="n">
-        <v>111</v>
+        <v>114.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.039999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="AB5" t="n">
         <v>9.220352523846751</v>
@@ -1012,16 +1012,16 @@
         <v>108.5881212004577</v>
       </c>
       <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1</v>
-      </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.126556939133272</v>
+        <v>1.107669226533732</v>
       </c>
     </row>
     <row r="6">
@@ -1039,76 +1039,76 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>1653.715</v>
+        <v>1647.336</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5508</v>
+        <v>-0.3741</v>
       </c>
       <c r="I6" t="n">
-        <v>1489.565824324324</v>
+        <v>1490.750933333333</v>
       </c>
       <c r="J6" t="n">
-        <v>116.9487175068908</v>
+        <v>117.6349842737596</v>
       </c>
       <c r="K6" t="n">
-        <v>111.1358166697704</v>
+        <v>111.2198305782562</v>
       </c>
       <c r="L6" t="n">
-        <v>5.812900837120325</v>
+        <v>6.415153695503457</v>
       </c>
       <c r="M6" t="n">
-        <v>118.7549999249761</v>
+        <v>120.7779352140565</v>
       </c>
       <c r="N6" t="n">
-        <v>114.8830986000118</v>
+        <v>115.1380970877481</v>
       </c>
       <c r="O6" t="n">
-        <v>3.871901324964229</v>
+        <v>5.639838126308488</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5524156631377466</v>
+        <v>0.5554936792720591</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1155458011279033</v>
+        <v>0.1169365570451051</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2914395127462582</v>
+        <v>0.2995517512045568</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5578755863500172</v>
+        <v>0.562695735099172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2373983455316732</v>
+        <v>0.2392035349468124</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4295652915678739</v>
+        <v>0.4284171924531922</v>
       </c>
       <c r="V6" t="n">
-        <v>99.26685214626391</v>
+        <v>99.34934736842106</v>
       </c>
       <c r="W6" t="n">
-        <v>115.9431637519873</v>
+        <v>116.6670175438597</v>
       </c>
       <c r="X6" t="n">
-        <v>5.546502384737679</v>
+        <v>6.053684210526316</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5853170016078657</v>
+        <v>0.5886513899888971</v>
       </c>
       <c r="Z6" t="n">
-        <v>113.89</v>
+        <v>115.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.97</v>
+        <v>5.96</v>
       </c>
       <c r="AB6" t="n">
         <v>2.775420617465777</v>
@@ -1120,16 +1120,16 @@
         <v>112.335295999638</v>
       </c>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.078725517542721</v>
+        <v>0.9976778471500981</v>
       </c>
     </row>
     <row r="7">
@@ -1147,76 +1147,76 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>1595.508</v>
+        <v>1599.001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3553</v>
+        <v>1.2726</v>
       </c>
       <c r="I7" t="n">
-        <v>1501.8568</v>
+        <v>1501.582552631579</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8587919475473</v>
+        <v>119.9302232467695</v>
       </c>
       <c r="K7" t="n">
-        <v>115.0958848187337</v>
+        <v>115.1280532122343</v>
       </c>
       <c r="L7" t="n">
-        <v>4.762907128813691</v>
+        <v>4.802170034535283</v>
       </c>
       <c r="M7" t="n">
-        <v>123.6130227773458</v>
+        <v>122.8283988323978</v>
       </c>
       <c r="N7" t="n">
-        <v>112.697727550607</v>
+        <v>114.5298021973138</v>
       </c>
       <c r="O7" t="n">
-        <v>10.91529522673882</v>
+        <v>8.298596635084081</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5767951977185795</v>
+        <v>0.5763058782599089</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1098720540359938</v>
+        <v>0.1099122727259536</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2313927488520803</v>
+        <v>0.2331833158135433</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6043246941612436</v>
+        <v>0.5969146242792409</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3009684618297749</v>
+        <v>0.3036550397177876</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4082694011760947</v>
+        <v>0.4081594209280318</v>
       </c>
       <c r="V7" t="n">
-        <v>101.1406349206349</v>
+        <v>101.3301412066752</v>
       </c>
       <c r="W7" t="n">
-        <v>121.2063492063492</v>
+        <v>121.4762516046213</v>
       </c>
       <c r="X7" t="n">
-        <v>4.868888888888889</v>
+        <v>4.874197689345315</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6162212021528615</v>
+        <v>0.6161378401454218</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.07</v>
+        <v>127.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.03</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB7" t="n">
         <v>2.722616812266775</v>
@@ -1228,112 +1228,112 @@
         <v>113.8166218640349</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.608438258285271</v>
+        <v>1.575100798425221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>1578.449</v>
+        <v>1575.058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5871</v>
+        <v>0.3107</v>
       </c>
       <c r="I8" t="n">
-        <v>1495.876986486486</v>
+        <v>1502.204986486486</v>
       </c>
       <c r="J8" t="n">
-        <v>115.5178949476356</v>
+        <v>114.9700538712982</v>
       </c>
       <c r="K8" t="n">
-        <v>110.8505689743891</v>
+        <v>110.2840103679508</v>
       </c>
       <c r="L8" t="n">
-        <v>4.667325973246558</v>
+        <v>4.686043503347449</v>
       </c>
       <c r="M8" t="n">
-        <v>114.9528899263027</v>
+        <v>110.973587900957</v>
       </c>
       <c r="N8" t="n">
-        <v>112.7163828997817</v>
+        <v>109.555917378623</v>
       </c>
       <c r="O8" t="n">
-        <v>2.236507026520986</v>
+        <v>1.41767052233401</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5442046055645519</v>
+        <v>0.5599819014686255</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.127042078805649</v>
+        <v>0.1240581560783763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3429589220197104</v>
+        <v>0.2563243743739458</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5465138547183636</v>
+        <v>0.544689202983769</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2616687199455877</v>
+        <v>0.2885004965531732</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3505254616821059</v>
+        <v>0.4167367709569746</v>
       </c>
       <c r="V8" t="n">
-        <v>99.03514358108109</v>
+        <v>103.0188076311605</v>
       </c>
       <c r="W8" t="n">
-        <v>114.2989864864865</v>
+        <v>118.0321939586646</v>
       </c>
       <c r="X8" t="n">
-        <v>4.694256756756757</v>
+        <v>4.266295707472177</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5769313179786882</v>
+        <v>0.5930791719344871</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.07</v>
+        <v>114.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.413694058608522</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC8" t="n">
-        <v>112.3850185369902</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD8" t="n">
-        <v>108.9713244783817</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1342,118 +1342,118 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.469839084743044</v>
+        <v>0.8359624720346067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>1575.058</v>
+        <v>1584.828</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3107</v>
+        <v>0.1629</v>
       </c>
       <c r="I9" t="n">
-        <v>1502.204986486486</v>
+        <v>1497.981493333333</v>
       </c>
       <c r="J9" t="n">
-        <v>114.9522244771508</v>
+        <v>115.6583684984793</v>
       </c>
       <c r="K9" t="n">
-        <v>110.415465443249</v>
+        <v>111.1578191183936</v>
       </c>
       <c r="L9" t="n">
-        <v>4.536759033901898</v>
+        <v>4.500549380085617</v>
       </c>
       <c r="M9" t="n">
-        <v>110.973587900957</v>
+        <v>118.4645138426517</v>
       </c>
       <c r="N9" t="n">
-        <v>109.555917378623</v>
+        <v>111.5640511951537</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41767052233401</v>
+        <v>6.900462647497992</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5597016598288915</v>
+        <v>0.5433369960177337</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1242750360897376</v>
+        <v>0.1262942730836234</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2571044444016876</v>
+        <v>0.3446208856598313</v>
       </c>
       <c r="S9" t="n">
-        <v>0.544689202983769</v>
+        <v>0.5568142229719847</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2895374975883943</v>
+        <v>0.2624683941816954</v>
       </c>
       <c r="U9" t="n">
-        <v>0.417331824472558</v>
+        <v>0.3520606583910677</v>
       </c>
       <c r="V9" t="n">
-        <v>103.0054808296668</v>
+        <v>99.086</v>
       </c>
       <c r="W9" t="n">
-        <v>117.9943431803897</v>
+        <v>114.476</v>
       </c>
       <c r="X9" t="n">
-        <v>4.103079824010056</v>
+        <v>4.505000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5929581246296418</v>
+        <v>0.5765287526009019</v>
       </c>
       <c r="Z9" t="n">
-        <v>114.1</v>
+        <v>115.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.28</v>
+        <v>5.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.250350764022217</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC9" t="n">
-        <v>114.1383305986051</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD9" t="n">
-        <v>109.8879798345829</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.8461642528187161</v>
+        <v>0.516135001415806</v>
       </c>
     </row>
     <row r="10">
@@ -1477,7 +1477,7 @@
         <v>46112</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
         <v>1642.78</v>
@@ -1489,13 +1489,13 @@
         <v>1488.512786666667</v>
       </c>
       <c r="J10" t="n">
-        <v>116.8743270139733</v>
+        <v>116.8640831944832</v>
       </c>
       <c r="K10" t="n">
-        <v>113.0743600371265</v>
+        <v>113.1701660322143</v>
       </c>
       <c r="L10" t="n">
-        <v>3.799966976846822</v>
+        <v>3.693917162268839</v>
       </c>
       <c r="M10" t="n">
         <v>122.228227073958</v>
@@ -1507,34 +1507,34 @@
         <v>2.961415913522665</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5608988194153629</v>
+        <v>0.5609403391835851</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1165195053313867</v>
+        <v>0.1165786864781034</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2646375296408656</v>
+        <v>0.2646908658853611</v>
       </c>
       <c r="S10" t="n">
         <v>0.5880122051555773</v>
       </c>
       <c r="T10" t="n">
-        <v>0.266273032258899</v>
+        <v>0.2660265796165251</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4433383359183564</v>
+        <v>0.4433637496558964</v>
       </c>
       <c r="V10" t="n">
-        <v>102.1497886178861</v>
+        <v>102.1253411764706</v>
       </c>
       <c r="W10" t="n">
-        <v>119.269918699187</v>
+        <v>119.2376470588236</v>
       </c>
       <c r="X10" t="n">
-        <v>3.847154471544715</v>
+        <v>3.755294117647058</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5942052802403387</v>
+        <v>0.5941964598826075</v>
       </c>
       <c r="Z10" t="n">
         <v>122.81</v>
@@ -1561,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.509883395809169</v>
+        <v>1.504127520882633</v>
       </c>
     </row>
     <row r="11">
@@ -1585,7 +1585,7 @@
         <v>46112</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
         <v>1580.433</v>
@@ -1597,52 +1597,52 @@
         <v>1497.293493333333</v>
       </c>
       <c r="J11" t="n">
-        <v>115.8694853761621</v>
+        <v>115.849206742656</v>
       </c>
       <c r="K11" t="n">
-        <v>112.0997831654642</v>
+        <v>112.2297629365615</v>
       </c>
       <c r="L11" t="n">
-        <v>3.769702210697881</v>
+        <v>3.619443806094497</v>
       </c>
       <c r="M11" t="n">
-        <v>118.4491199903235</v>
+        <v>118.5722088734538</v>
       </c>
       <c r="N11" t="n">
         <v>108.0429191492245</v>
       </c>
       <c r="O11" t="n">
-        <v>10.40620084109897</v>
+        <v>10.52928972422932</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5527424035352789</v>
+        <v>0.5528217641175907</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1282559349327903</v>
+        <v>0.1283233919657186</v>
       </c>
       <c r="R11" t="n">
-        <v>0.305507837493888</v>
+        <v>0.3052757185150465</v>
       </c>
       <c r="S11" t="n">
         <v>0.5638218079694002</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2521244191640875</v>
+        <v>0.2519009610075865</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4825000667489923</v>
+        <v>0.4827171335862863</v>
       </c>
       <c r="V11" t="n">
-        <v>99.6653411764706</v>
+        <v>99.68879999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>116.1070588235294</v>
+        <v>116.1013953488372</v>
       </c>
       <c r="X11" t="n">
-        <v>5.117647058823529</v>
+        <v>4.953488372093023</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5902065337376826</v>
+        <v>0.590163834529823</v>
       </c>
       <c r="Z11" t="n">
         <v>117.27</v>
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3846455861595832</v>
+        <v>0.3854014318134431</v>
       </c>
     </row>
     <row r="12">
@@ -1693,7 +1693,7 @@
         <v>46112</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
         <v>1563.777</v>
@@ -1705,13 +1705,13 @@
         <v>1490.21356</v>
       </c>
       <c r="J12" t="n">
-        <v>117.1445149676861</v>
+        <v>117.0649331276973</v>
       </c>
       <c r="K12" t="n">
-        <v>114.0931817722708</v>
+        <v>114.0888539065797</v>
       </c>
       <c r="L12" t="n">
-        <v>3.051333195415258</v>
+        <v>2.976079221117644</v>
       </c>
       <c r="M12" t="n">
         <v>122.2459294720319</v>
@@ -1723,34 +1723,34 @@
         <v>11.0058071369856</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5742086184011108</v>
+        <v>0.5739554128782122</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1243224405097613</v>
+        <v>0.1244787944645825</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2392508407950233</v>
+        <v>0.239192021866405</v>
       </c>
       <c r="S12" t="n">
         <v>0.5933263770082704</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3240728329422835</v>
+        <v>0.3241320385285712</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3971746377419328</v>
+        <v>0.3973042172868758</v>
       </c>
       <c r="V12" t="n">
-        <v>100.2461561904762</v>
+        <v>100.2617302325582</v>
       </c>
       <c r="W12" t="n">
-        <v>116.9748571428571</v>
+        <v>116.92</v>
       </c>
       <c r="X12" t="n">
-        <v>2.304</v>
+        <v>2.24</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6110680973903058</v>
+        <v>0.6107325762662917</v>
       </c>
       <c r="Z12" t="n">
         <v>122.05</v>
@@ -1777,115 +1777,115 @@
         <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.631216456215913</v>
+        <v>1.605827477504895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>1531.531</v>
+        <v>1521.635</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.1116</v>
+        <v>2.2789</v>
       </c>
       <c r="I13" t="n">
-        <v>1505.69156</v>
+        <v>1486.017460526316</v>
       </c>
       <c r="J13" t="n">
-        <v>113.7409191744289</v>
+        <v>113.9707468270876</v>
       </c>
       <c r="K13" t="n">
-        <v>111.3794604939758</v>
+        <v>111.5643938317927</v>
       </c>
       <c r="L13" t="n">
-        <v>2.361458680452965</v>
+        <v>2.406352995294905</v>
       </c>
       <c r="M13" t="n">
-        <v>115.8719111038512</v>
+        <v>118.3840893776426</v>
       </c>
       <c r="N13" t="n">
-        <v>118.4071104219959</v>
+        <v>106.7715599768774</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.535199318144721</v>
+        <v>11.61252940076515</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5363101165105528</v>
+        <v>0.5539635872810795</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1118098196120276</v>
+        <v>0.1167066689761772</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2529481789512728</v>
+        <v>0.2407859497037374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5361416630337882</v>
+        <v>0.5691156447894506</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2731182182832637</v>
+        <v>0.2385889869815702</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4045384214955133</v>
+        <v>0.4284885902688828</v>
       </c>
       <c r="V13" t="n">
-        <v>105.7295609756098</v>
+        <v>103.9297960526316</v>
       </c>
       <c r="W13" t="n">
-        <v>120.2227642276422</v>
+        <v>118.4667763157894</v>
       </c>
       <c r="X13" t="n">
-        <v>2.507317073170732</v>
+        <v>2.623684210526316</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.574987932045124</v>
+        <v>0.5848545178709627</v>
       </c>
       <c r="Z13" t="n">
-        <v>120.8</v>
+        <v>122.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>-4.489999999999999</v>
+        <v>11.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.094669144490311</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC13" t="n">
-        <v>111.6804548463295</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD13" t="n">
-        <v>112.7751239908198</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.02842587194406881</v>
+        <v>0.6312724420106667</v>
       </c>
     </row>
     <row r="14">
@@ -1909,7 +1909,7 @@
         <v>46112</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>1559.934</v>
@@ -1921,13 +1921,13 @@
         <v>1496.232333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>115.9483952380811</v>
+        <v>115.9438123958599</v>
       </c>
       <c r="K14" t="n">
-        <v>113.7503670545904</v>
+        <v>113.7599027464007</v>
       </c>
       <c r="L14" t="n">
-        <v>2.198028183490708</v>
+        <v>2.183909649459133</v>
       </c>
       <c r="M14" t="n">
         <v>118.6065612920006</v>
@@ -1939,34 +1939,34 @@
         <v>5.774747991354014</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5615911794000334</v>
+        <v>0.561597483145205</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1260816157267504</v>
+        <v>0.1261022622517228</v>
       </c>
       <c r="R14" t="n">
-        <v>0.235003752760578</v>
+        <v>0.234966999852213</v>
       </c>
       <c r="S14" t="n">
         <v>0.5803389757403798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3038393680319152</v>
+        <v>0.3038375545347913</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4040814687946172</v>
+        <v>0.4040674378236122</v>
       </c>
       <c r="V14" t="n">
-        <v>98.6519649122807</v>
+        <v>98.64425925925926</v>
       </c>
       <c r="W14" t="n">
-        <v>113.7368421052632</v>
+        <v>113.7222222222222</v>
       </c>
       <c r="X14" t="n">
-        <v>1.190877192982456</v>
+        <v>1.174074074074074</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6053168140463405</v>
+        <v>0.6053145495194063</v>
       </c>
       <c r="Z14" t="n">
         <v>116.42</v>
@@ -1993,103 +1993,103 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.3645699799132338</v>
+        <v>0.3636844859740119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612737</v>
+        <v>1610612748</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>1516.752</v>
+        <v>1533.636</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4002</v>
+        <v>-2.7113</v>
       </c>
       <c r="I15" t="n">
-        <v>1483.620026666666</v>
+        <v>1505.278789473684</v>
       </c>
       <c r="J15" t="n">
-        <v>113.8274900391103</v>
+        <v>113.984454965129</v>
       </c>
       <c r="K15" t="n">
-        <v>111.9794820808451</v>
+        <v>112.2586812931816</v>
       </c>
       <c r="L15" t="n">
-        <v>1.848007958265218</v>
+        <v>1.725773671947434</v>
       </c>
       <c r="M15" t="n">
-        <v>117.5443697775149</v>
+        <v>115.7806766419599</v>
       </c>
       <c r="N15" t="n">
-        <v>107.7478076007739</v>
+        <v>122.3318716431754</v>
       </c>
       <c r="O15" t="n">
-        <v>9.796562176741007</v>
+        <v>-6.551195001215493</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5529268379355065</v>
+        <v>0.537712963923746</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1158941589141836</v>
+        <v>0.1112415592742477</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2392961828508606</v>
+        <v>0.2519334999041863</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5568263189467541</v>
+        <v>0.5383739776913999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2362437545286008</v>
+        <v>0.2719616798845572</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4289594164025617</v>
+        <v>0.4063485241097721</v>
       </c>
       <c r="V15" t="n">
-        <v>103.7074119658119</v>
+        <v>105.665911872705</v>
       </c>
       <c r="W15" t="n">
-        <v>118.0929914529914</v>
+        <v>120.4406364749082</v>
       </c>
       <c r="X15" t="n">
-        <v>2.049230769230769</v>
+        <v>1.946144430844553</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5836060710830497</v>
+        <v>0.5760248946858337</v>
       </c>
       <c r="Z15" t="n">
-        <v>120.19</v>
+        <v>119.01</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.82</v>
+        <v>-8.280000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.981113782848854</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC15" t="n">
-        <v>112.8029837792552</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD15" t="n">
-        <v>113.7840975621041</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.5943140525477608</v>
+        <v>0.05280924997521638</v>
       </c>
     </row>
     <row r="16">
@@ -2125,7 +2125,7 @@
         <v>46112</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
         <v>1510.467</v>
@@ -2137,13 +2137,13 @@
         <v>1512.922053333333</v>
       </c>
       <c r="J16" t="n">
-        <v>113.2152099640899</v>
+        <v>113.1407795736791</v>
       </c>
       <c r="K16" t="n">
-        <v>111.5522987927236</v>
+        <v>111.5017629140347</v>
       </c>
       <c r="L16" t="n">
-        <v>1.662911171366294</v>
+        <v>1.639016659644434</v>
       </c>
       <c r="M16" t="n">
         <v>116.078878571102</v>
@@ -2155,34 +2155,34 @@
         <v>3.473200118196776</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5383510419265531</v>
+        <v>0.5380366682481879</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.119353115065673</v>
+        <v>0.119573004826412</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2871305178145186</v>
+        <v>0.2868321744630224</v>
       </c>
       <c r="S16" t="n">
         <v>0.5413192871582424</v>
       </c>
       <c r="T16" t="n">
-        <v>0.231068915104776</v>
+        <v>0.2319267154748918</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4579950885299742</v>
+        <v>0.4583282688898132</v>
       </c>
       <c r="V16" t="n">
-        <v>99.82764227642275</v>
+        <v>99.89399999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>112.8731707317073</v>
+        <v>112.8635294117647</v>
       </c>
       <c r="X16" t="n">
-        <v>1.710569105691057</v>
+        <v>1.681176470588235</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5701305819990877</v>
+        <v>0.5699587726688814</v>
       </c>
       <c r="Z16" t="n">
         <v>116.13</v>
@@ -2209,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.08023621246628569</v>
+        <v>0.1019760617912528</v>
       </c>
     </row>
     <row r="17">
@@ -2227,76 +2227,76 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>1515.772</v>
+        <v>1513.967</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9318</v>
+        <v>0.5175</v>
       </c>
       <c r="I17" t="n">
-        <v>1495.614162162162</v>
+        <v>1498.068306666667</v>
       </c>
       <c r="J17" t="n">
-        <v>113.260210539307</v>
+        <v>113.3795012307266</v>
       </c>
       <c r="K17" t="n">
-        <v>111.8305025553377</v>
+        <v>111.8525989203726</v>
       </c>
       <c r="L17" t="n">
-        <v>1.429707983969206</v>
+        <v>1.526902310354019</v>
       </c>
       <c r="M17" t="n">
-        <v>118.0903015201633</v>
+        <v>119.0008012020616</v>
       </c>
       <c r="N17" t="n">
-        <v>115.2919532593997</v>
+        <v>115.837254644371</v>
       </c>
       <c r="O17" t="n">
-        <v>2.79834826076357</v>
+        <v>3.163546557690581</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5435790063080056</v>
+        <v>0.5451942484259756</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1156496788769415</v>
+        <v>0.115499508690161</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2559576673159639</v>
+        <v>0.2517852498832425</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5777783223588471</v>
+        <v>0.5887321211300018</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2626998779788668</v>
+        <v>0.2652380958826372</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3681741504778421</v>
+        <v>0.3670760629041485</v>
       </c>
       <c r="V17" t="n">
-        <v>100.8207949125596</v>
+        <v>100.7690256410256</v>
       </c>
       <c r="W17" t="n">
-        <v>114.3736089030206</v>
+        <v>114.3634188034189</v>
       </c>
       <c r="X17" t="n">
-        <v>1.971780604133546</v>
+        <v>1.925470085470086</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5774946886625965</v>
+        <v>0.5790750032406927</v>
       </c>
       <c r="Z17" t="n">
-        <v>119.51</v>
+        <v>119.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="AB17" t="n">
         <v>-4.536933640611859</v>
@@ -2308,112 +2308,112 @@
         <v>112.9258195010085</v>
       </c>
       <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3354089720088078</v>
+        <v>0.307394356422662</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>1515.253</v>
+        <v>1472.215</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3347</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1490.206366197183</v>
+        <v>1498.929866666667</v>
       </c>
       <c r="J18" t="n">
-        <v>112.4151295176243</v>
+        <v>113.9844315618287</v>
       </c>
       <c r="K18" t="n">
-        <v>112.5048569557328</v>
+        <v>113.4156275902304</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.08972743810860399</v>
+        <v>0.5688039715983007</v>
       </c>
       <c r="M18" t="n">
-        <v>110.387435824646</v>
+        <v>115.4172867081167</v>
       </c>
       <c r="N18" t="n">
-        <v>119.8495590449733</v>
+        <v>114.8869612042637</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.462123220327285</v>
+        <v>0.530325503852987</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5313770659618372</v>
+        <v>0.5351457441619317</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.119096756762158</v>
+        <v>0.1131602468595699</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2447455167990914</v>
+        <v>0.26060149308536</v>
       </c>
       <c r="S18" t="n">
-        <v>0.525956343852752</v>
+        <v>0.5464156884276465</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3180583424352549</v>
+        <v>0.2780537193113485</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3890970049711139</v>
+        <v>0.3933920893953691</v>
       </c>
       <c r="V18" t="n">
-        <v>102.4760641627543</v>
+        <v>102.8899298245614</v>
       </c>
       <c r="W18" t="n">
-        <v>115.314945226917</v>
+        <v>117.0515789473684</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6177621283255086</v>
+        <v>0.1505263157894736</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5777524740222608</v>
+        <v>0.5770440496152104</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.63</v>
+        <v>120.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>-7.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC18" t="n">
-        <v>107.6152962364644</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD18" t="n">
-        <v>108.1384073962044</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -2425,106 +2425,106 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.3534539730612285</v>
+        <v>0.4966292790296482</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>1474.321</v>
+        <v>1477.52</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4704</v>
+        <v>-1.0752</v>
       </c>
       <c r="I19" t="n">
-        <v>1498.489310810811</v>
+        <v>1503.358946666667</v>
       </c>
       <c r="J19" t="n">
-        <v>113.0507643207421</v>
+        <v>112.2816408728654</v>
       </c>
       <c r="K19" t="n">
-        <v>113.2514554240724</v>
+        <v>112.7064985066904</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2006911033302979</v>
+        <v>-0.4248576338250612</v>
       </c>
       <c r="M19" t="n">
-        <v>114.0343818366226</v>
+        <v>109.6266905431995</v>
       </c>
       <c r="N19" t="n">
-        <v>114.7058555748773</v>
+        <v>116.6624372135305</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6714737382547205</v>
+        <v>-7.035746670330974</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5299584005606888</v>
+        <v>0.5504657775710466</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1134356184693611</v>
+        <v>0.1324747031929864</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2588711535791979</v>
+        <v>0.2519977137835492</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5338541721015952</v>
+        <v>0.5492561348734037</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2801048380450918</v>
+        <v>0.2402159177901141</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3944872462997808</v>
+        <v>0.4994888756778889</v>
       </c>
       <c r="V19" t="n">
-        <v>102.7823684210526</v>
+        <v>101.5903619047619</v>
       </c>
       <c r="W19" t="n">
-        <v>115.9868421052632</v>
+        <v>114.0392380952381</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5657894736842105</v>
+        <v>-0.5401904761904762</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5724719551909406</v>
+        <v>0.5843520306626269</v>
       </c>
       <c r="Z19" t="n">
-        <v>118.9</v>
+        <v>110.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.28</v>
+        <v>-7.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>-6.382503892565079</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC19" t="n">
-        <v>109.8789897646453</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD19" t="n">
-        <v>116.2614936572104</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2533,115 +2533,115 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.5118069354933249</v>
+        <v>-0.3281407323510546</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>1481.014</v>
+        <v>1517.594</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3473</v>
+        <v>-3.5061</v>
       </c>
       <c r="I20" t="n">
-        <v>1502.113689189189</v>
+        <v>1490.487763888889</v>
       </c>
       <c r="J20" t="n">
-        <v>112.4264854956626</v>
+        <v>111.9487583735943</v>
       </c>
       <c r="K20" t="n">
-        <v>112.7709595170368</v>
+        <v>112.852901991738</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3444740213742258</v>
+        <v>-0.9041436181436305</v>
       </c>
       <c r="M20" t="n">
-        <v>110.2168956740512</v>
+        <v>107.8715998687121</v>
       </c>
       <c r="N20" t="n">
-        <v>116.9725404071555</v>
+        <v>120.5781407699248</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.755644733104332</v>
+        <v>-12.7065409012127</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5505672792816279</v>
+        <v>0.5290344421716072</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1328449955632938</v>
+        <v>0.1189425539863543</v>
       </c>
       <c r="R20" t="n">
-        <v>0.257186056692933</v>
+        <v>0.2428295425858887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5476170154961076</v>
+        <v>0.5150248708953298</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2386160975356581</v>
+        <v>0.3161902200269517</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5019345889557217</v>
+        <v>0.3887147877557122</v>
       </c>
       <c r="V20" t="n">
-        <v>101.9413447593936</v>
+        <v>102.5710810810811</v>
       </c>
       <c r="W20" t="n">
-        <v>114.6479894528675</v>
+        <v>114.9324324324324</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2841133816743572</v>
+        <v>-0.2297297297297297</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5841351721022416</v>
+        <v>0.5753604355976911</v>
       </c>
       <c r="Z20" t="n">
-        <v>113.7</v>
+        <v>112.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>-6.619999999999999</v>
+        <v>-10.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.402868486532558</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC20" t="n">
-        <v>112.5227430890375</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD20" t="n">
-        <v>110.1198746025049</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.3409077073260275</v>
+        <v>-0.1389626567450439</v>
       </c>
     </row>
     <row r="21">
@@ -2665,7 +2665,7 @@
         <v>46112</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>1462.955</v>
@@ -2677,13 +2677,13 @@
         <v>1503.14297368421</v>
       </c>
       <c r="J21" t="n">
-        <v>111.3551059071822</v>
+        <v>111.3212065587594</v>
       </c>
       <c r="K21" t="n">
-        <v>112.4852297991604</v>
+        <v>112.4836368048986</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.130123891978222</v>
+        <v>-1.162430246139138</v>
       </c>
       <c r="M21" t="n">
         <v>113.796125832089</v>
@@ -2695,34 +2695,34 @@
         <v>10.16864961850941</v>
       </c>
       <c r="P21" t="n">
-        <v>0.53308121378109</v>
+        <v>0.5330816563423848</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1411220582402496</v>
+        <v>0.1411884942028879</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3138209316122616</v>
+        <v>0.3132931057657975</v>
       </c>
       <c r="S21" t="n">
         <v>0.5501894938354689</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2859735985147895</v>
+        <v>0.2863153481299546</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4678732084769952</v>
+        <v>0.4677699825621559</v>
       </c>
       <c r="V21" t="n">
-        <v>103.2807112375533</v>
+        <v>103.3185434516523</v>
       </c>
       <c r="W21" t="n">
-        <v>115.3058321479374</v>
+        <v>115.3108935128519</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5106685633001422</v>
+        <v>-0.5514075887392901</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5702431553636502</v>
+        <v>0.5702199768546904</v>
       </c>
       <c r="Z21" t="n">
         <v>116.52</v>
@@ -2749,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.5373897719310309</v>
+        <v>-0.5208196091730017</v>
       </c>
     </row>
     <row r="22">
@@ -2767,76 +2767,76 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>1379.867</v>
+        <v>1379.04</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8242</v>
+        <v>-0.8052</v>
       </c>
       <c r="I22" t="n">
-        <v>1495.397945945946</v>
+        <v>1498.586533333333</v>
       </c>
       <c r="J22" t="n">
-        <v>111.6145029009255</v>
+        <v>111.6466488854735</v>
       </c>
       <c r="K22" t="n">
-        <v>115.8641627858758</v>
+        <v>115.9903649027076</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.249659884950336</v>
+        <v>-4.343716017234031</v>
       </c>
       <c r="M22" t="n">
-        <v>112.524283740846</v>
+        <v>111.997286104648</v>
       </c>
       <c r="N22" t="n">
-        <v>119.0215976853151</v>
+        <v>121.0023674622528</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.497313944469074</v>
+        <v>-9.005081357604777</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5492724481555097</v>
+        <v>0.5496681499284022</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1254502510971707</v>
+        <v>0.1268731669476357</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2263545954995142</v>
+        <v>0.2296270604637786</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5504964637989375</v>
+        <v>0.5541231651861768</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2460559638084806</v>
+        <v>0.2469650628214027</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4471020313296633</v>
+        <v>0.4455523571143614</v>
       </c>
       <c r="V22" t="n">
-        <v>104.4573243243243</v>
+        <v>104.6596727272727</v>
       </c>
       <c r="W22" t="n">
-        <v>116.2990990990991</v>
+        <v>116.5660606060606</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.941441441441442</v>
+        <v>-5.057575757575758</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5816386049501766</v>
+        <v>0.5821111599703364</v>
       </c>
       <c r="Z22" t="n">
-        <v>121.65</v>
+        <v>121.41</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.72</v>
+        <v>-9.01</v>
       </c>
       <c r="AB22" t="n">
         <v>-0.9433805425336231</v>
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.4268619459623897</v>
+        <v>-0.3882638080349268</v>
       </c>
     </row>
     <row r="23">
@@ -2881,7 +2881,7 @@
         <v>46110</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
         <v>1380.194</v>
@@ -2893,13 +2893,13 @@
         <v>1508.015253333333</v>
       </c>
       <c r="J23" t="n">
-        <v>111.985626370175</v>
+        <v>112.0095682863248</v>
       </c>
       <c r="K23" t="n">
-        <v>116.71122574781</v>
+        <v>116.6655072670407</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.725599377634998</v>
+        <v>-4.65593898071587</v>
       </c>
       <c r="M23" t="n">
         <v>113.784720892972</v>
@@ -2911,34 +2911,34 @@
         <v>-2.136321202900874</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5273613612763056</v>
+        <v>0.5274653935249312</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1163903358334531</v>
+        <v>0.1164462289012098</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2663200004285781</v>
+        <v>0.2665255938248261</v>
       </c>
       <c r="S23" t="n">
         <v>0.5421438336073836</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2841931548059005</v>
+        <v>0.2840970520801815</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3594348556456938</v>
+        <v>0.3594864629676445</v>
       </c>
       <c r="V23" t="n">
-        <v>102.6292266666667</v>
+        <v>102.6370035087719</v>
       </c>
       <c r="W23" t="n">
-        <v>114.8746666666666</v>
+        <v>114.9045614035087</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.851809523809524</v>
+        <v>-4.788771929824562</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5671723136071763</v>
+        <v>0.5672848319778909</v>
       </c>
       <c r="Z23" t="n">
         <v>114.51</v>
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.4541394036544683</v>
+        <v>-0.4242476545941131</v>
       </c>
     </row>
     <row r="24">
@@ -2983,76 +2983,76 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>1384.188</v>
+        <v>1379.688</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6948</v>
+        <v>-1.7918</v>
       </c>
       <c r="I24" t="n">
-        <v>1495.014902777778</v>
+        <v>1495.164917808219</v>
       </c>
       <c r="J24" t="n">
-        <v>110.4050796922825</v>
+        <v>110.8475367280819</v>
       </c>
       <c r="K24" t="n">
-        <v>115.7632853352394</v>
+        <v>116.1182130038252</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.358205642957026</v>
+        <v>-5.270676275743345</v>
       </c>
       <c r="M24" t="n">
-        <v>106.0100295254461</v>
+        <v>107.6057654648695</v>
       </c>
       <c r="N24" t="n">
-        <v>122.6045926253662</v>
+        <v>124.1558169866645</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.59456309992011</v>
+        <v>-16.55005152179498</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5347989950220621</v>
+        <v>0.5364854383330634</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1283240210595969</v>
+        <v>0.1271719235378404</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2487730257572817</v>
+        <v>0.24756723582568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5187382426128976</v>
+        <v>0.5306987152229944</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2572702462424255</v>
+        <v>0.2609564692037231</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4292011251938953</v>
+        <v>0.4308478934060112</v>
       </c>
       <c r="V24" t="n">
-        <v>103.7409799382716</v>
+        <v>103.5728462709285</v>
       </c>
       <c r="W24" t="n">
-        <v>114.7762345679013</v>
+        <v>115.031202435312</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.881172839506173</v>
+        <v>-4.753805175038051</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5721354304306145</v>
+        <v>0.5740063892441803</v>
       </c>
       <c r="Z24" t="n">
-        <v>110.04</v>
+        <v>110.81</v>
       </c>
       <c r="AA24" t="n">
-        <v>-15.47</v>
+        <v>-15.59</v>
       </c>
       <c r="AB24" t="n">
         <v>3.575252351995317</v>
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.112783538102896</v>
+        <v>-1.336120759393987</v>
       </c>
     </row>
     <row r="25">
@@ -3091,76 +3091,76 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>1389.808</v>
+        <v>1392.794</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.0852</v>
+        <v>-1.9178</v>
       </c>
       <c r="I25" t="n">
-        <v>1496.395472972973</v>
+        <v>1494.676133333333</v>
       </c>
       <c r="J25" t="n">
-        <v>111.0843447152485</v>
+        <v>111.2462406419491</v>
       </c>
       <c r="K25" t="n">
-        <v>116.508571287028</v>
+        <v>117.1873068154184</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.424226571779472</v>
+        <v>-5.941066173469398</v>
       </c>
       <c r="M25" t="n">
-        <v>108.4809334553597</v>
+        <v>109.8699173762595</v>
       </c>
       <c r="N25" t="n">
-        <v>121.126226657406</v>
+        <v>123.1000876756754</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.64529320204618</v>
+        <v>-13.23017029941586</v>
       </c>
       <c r="P25" t="n">
-        <v>0.564359975607904</v>
+        <v>0.5645626067479678</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1320448378704686</v>
+        <v>0.1321159774411719</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2048077253296345</v>
+        <v>0.2082057821899348</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5658734094885665</v>
+        <v>0.5677341548638143</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2274979102130966</v>
+        <v>0.2254461079656181</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4535843036666473</v>
+        <v>0.4519929170250186</v>
       </c>
       <c r="V25" t="n">
-        <v>99.84651285431772</v>
+        <v>99.57681616161616</v>
       </c>
       <c r="W25" t="n">
-        <v>110.7389584706658</v>
+        <v>110.6727272727273</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.690177982860909</v>
+        <v>-6.025858585858586</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5885266172640808</v>
+        <v>0.5884534757256186</v>
       </c>
       <c r="Z25" t="n">
-        <v>107.79</v>
+        <v>108.41</v>
       </c>
       <c r="AA25" t="n">
-        <v>-12.45</v>
+        <v>-12.66</v>
       </c>
       <c r="AB25" t="n">
         <v>1.809266556998161</v>
@@ -3172,16 +3172,16 @@
         <v>112.4407240264407</v>
       </c>
       <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1</v>
       </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.180414315198027</v>
+        <v>-1.133310788772001</v>
       </c>
     </row>
     <row r="26">
@@ -3205,7 +3205,7 @@
         <v>46112</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
         <v>1367.445</v>
@@ -3217,13 +3217,13 @@
         <v>1505.736932432432</v>
       </c>
       <c r="J26" t="n">
-        <v>108.1773292101959</v>
+        <v>108.1628123718708</v>
       </c>
       <c r="K26" t="n">
-        <v>114.2411705015027</v>
+        <v>114.241379265655</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.063841291306736</v>
+        <v>-6.078566893784112</v>
       </c>
       <c r="M26" t="n">
         <v>109.5706664969746</v>
@@ -3235,34 +3235,34 @@
         <v>-9.21590120861258</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5254347634598332</v>
+        <v>0.52533166245338</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1238032917883228</v>
+        <v>0.1237952040717519</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2296992867007931</v>
+        <v>0.2296991213980427</v>
       </c>
       <c r="S26" t="n">
         <v>0.520652570454289</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2887043604680914</v>
+        <v>0.288706923016706</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3483415992863383</v>
+        <v>0.3483646601866096</v>
       </c>
       <c r="V26" t="n">
-        <v>104.5382857142857</v>
+        <v>104.5411764705882</v>
       </c>
       <c r="W26" t="n">
-        <v>113.2169884169884</v>
+        <v>113.2046899841017</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.871042471042471</v>
+        <v>-5.886724960254372</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5618309712619205</v>
+        <v>0.5617402691419118</v>
       </c>
       <c r="Z26" t="n">
         <v>115.83</v>
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1.065296720537024</v>
+        <v>-0.831042387901073</v>
       </c>
     </row>
     <row r="27">
@@ -3307,76 +3307,76 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
       <c r="F27" t="n">
         <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>1333.301</v>
+        <v>1338.754</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.994</v>
+        <v>-0.346</v>
       </c>
       <c r="I27" t="n">
-        <v>1502.167067567568</v>
+        <v>1502.63128</v>
       </c>
       <c r="J27" t="n">
-        <v>109.3859430195654</v>
+        <v>109.7168549128822</v>
       </c>
       <c r="K27" t="n">
-        <v>116.9711120655437</v>
+        <v>116.8433985310214</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.585169045978272</v>
+        <v>-7.12654361813933</v>
       </c>
       <c r="M27" t="n">
-        <v>116.0042747534943</v>
+        <v>118.9171734093284</v>
       </c>
       <c r="N27" t="n">
-        <v>121.8606261889702</v>
+        <v>122.0742567182238</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.856351435475844</v>
+        <v>-3.157083308895318</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5340928136128059</v>
+        <v>0.5357845505631168</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1211856141443302</v>
+        <v>0.1211021796219608</v>
       </c>
       <c r="R27" t="n">
-        <v>0.212873111392034</v>
+        <v>0.2143633248927037</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5880433477755221</v>
+        <v>0.6049063678783739</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2561487579208239</v>
+        <v>0.2535873769257557</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4193573664174413</v>
+        <v>0.4205294228691061</v>
       </c>
       <c r="V27" t="n">
-        <v>103.0781595881596</v>
+        <v>103.2823365079365</v>
       </c>
       <c r="W27" t="n">
-        <v>112.4552767052767</v>
+        <v>112.9939682539682</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.130308880308881</v>
+        <v>-7.747619047619049</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5694583842231599</v>
+        <v>0.5708527815450193</v>
       </c>
       <c r="Z27" t="n">
-        <v>117.09</v>
+        <v>120.43</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.85</v>
+        <v>-4.67</v>
       </c>
       <c r="AB27" t="n">
         <v>2.960186837728194</v>
@@ -3388,7 +3388,7 @@
         <v>111.9328051119554</v>
       </c>
       <c r="AE27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.883340938084121</v>
+        <v>-0.9533364359244573</v>
       </c>
     </row>
     <row r="28">
@@ -3415,76 +3415,76 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>1307.985</v>
+        <v>1307.055</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9192</v>
+        <v>-1.0144</v>
       </c>
       <c r="I28" t="n">
-        <v>1510.067613333333</v>
+        <v>1511.801605263158</v>
       </c>
       <c r="J28" t="n">
-        <v>112.0542475400604</v>
+        <v>112.010452041258</v>
       </c>
       <c r="K28" t="n">
-        <v>119.9067105543185</v>
+        <v>119.9901278243179</v>
       </c>
       <c r="L28" t="n">
-        <v>-7.852463014258137</v>
+        <v>-7.979675783060011</v>
       </c>
       <c r="M28" t="n">
-        <v>111.9894237089151</v>
+        <v>110.9783569526622</v>
       </c>
       <c r="N28" t="n">
-        <v>121.4919277036386</v>
+        <v>120.126243683934</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.502503994723583</v>
+        <v>-9.1478867312718</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5387142966048171</v>
+        <v>0.5380082744551464</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.128748458530245</v>
+        <v>0.1279663446181419</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2604464396585496</v>
+        <v>0.2601605462032421</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5452983241606455</v>
+        <v>0.5395462824183588</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2832750446804164</v>
+        <v>0.2836730110498208</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4068857240311238</v>
+        <v>0.4077012239107814</v>
       </c>
       <c r="V28" t="n">
-        <v>104.6242117647058</v>
+        <v>104.7084615384615</v>
       </c>
       <c r="W28" t="n">
-        <v>117.2576470588236</v>
+        <v>117.3205128205129</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.068235294117647</v>
+        <v>-8.179487179487179</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5783510978438789</v>
+        <v>0.5775856118857268</v>
       </c>
       <c r="Z28" t="n">
-        <v>116.78</v>
+        <v>116.82</v>
       </c>
       <c r="AA28" t="n">
-        <v>-11.34</v>
+        <v>-11.02</v>
       </c>
       <c r="AB28" t="n">
         <v>-9.725925288085115</v>
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.449735815167216</v>
+        <v>-1.405933653530657</v>
       </c>
     </row>
     <row r="29">
@@ -3523,76 +3523,76 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>1312.653</v>
+        <v>1310.757</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4716</v>
+        <v>-0.8026</v>
       </c>
       <c r="I29" t="n">
-        <v>1519.756533333333</v>
+        <v>1516.76152631579</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1440390404885</v>
+        <v>109.6506485001995</v>
       </c>
       <c r="K29" t="n">
-        <v>118.8397956810164</v>
+        <v>118.8173637638446</v>
       </c>
       <c r="L29" t="n">
-        <v>-9.695756640527938</v>
+        <v>-9.166715263645051</v>
       </c>
       <c r="M29" t="n">
-        <v>112.4250289223267</v>
+        <v>114.2082428854661</v>
       </c>
       <c r="N29" t="n">
-        <v>121.1076641610534</v>
+        <v>122.8110160291269</v>
       </c>
       <c r="O29" t="n">
-        <v>-8.682635238726643</v>
+        <v>-8.602773143660794</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5233431516354192</v>
+        <v>0.5237406401578811</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1207896874930093</v>
+        <v>0.1203218403332457</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2539389239464369</v>
+        <v>0.2575512976501724</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5494064771474977</v>
+        <v>0.5521994378100236</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2562806730547172</v>
+        <v>0.2573159643465087</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3379318888869711</v>
+        <v>0.3379416451810295</v>
       </c>
       <c r="V29" t="n">
-        <v>101.6479452991453</v>
+        <v>101.6028324099723</v>
       </c>
       <c r="W29" t="n">
-        <v>110.5623931623932</v>
+        <v>111.0339335180056</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.5042735042735</v>
+        <v>-9.936288088642662</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.558803275179501</v>
+        <v>0.5600176911920542</v>
       </c>
       <c r="Z29" t="n">
-        <v>111.15</v>
+        <v>112.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>-9.979999999999999</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.1619477822758719</v>
@@ -3604,16 +3604,16 @@
         <v>114.7058177516698</v>
       </c>
       <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1</v>
-      </c>
       <c r="AG29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.557076542454088</v>
+        <v>-1.554830066682773</v>
       </c>
     </row>
     <row r="30">
@@ -3637,7 +3637,7 @@
         <v>46112</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G30" t="n">
         <v>1294.032</v>
@@ -3649,13 +3649,13 @@
         <v>1501.72304</v>
       </c>
       <c r="J30" t="n">
-        <v>106.6396659292955</v>
+        <v>106.5735229248656</v>
       </c>
       <c r="K30" t="n">
-        <v>117.0537081099374</v>
+        <v>117.0749205821124</v>
       </c>
       <c r="L30" t="n">
-        <v>-10.41404218064183</v>
+        <v>-10.50139765724669</v>
       </c>
       <c r="M30" t="n">
         <v>99.88338055761382</v>
@@ -3667,34 +3667,34 @@
         <v>-13.46097007024982</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5202040066964976</v>
+        <v>0.5198137615037446</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1383763370598489</v>
+        <v>0.1383904577161692</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2396344701445607</v>
+        <v>0.2391442090549466</v>
       </c>
       <c r="S30" t="n">
         <v>0.4960370991051177</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2781054659202154</v>
+        <v>0.2785091760612896</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4587452752110392</v>
+        <v>0.4588363798352281</v>
       </c>
       <c r="V30" t="n">
-        <v>99.07138787878786</v>
+        <v>99.05321081081081</v>
       </c>
       <c r="W30" t="n">
-        <v>105.8451515151516</v>
+        <v>105.7578378378379</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.630303030303029</v>
+        <v>-9.724324324324323</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5598989442375895</v>
+        <v>0.559664431501391</v>
       </c>
       <c r="Z30" t="n">
         <v>99.95</v>
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.798011424195572</v>
+        <v>-1.70070001358613</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>1258.158</v>
+        <v>1257.331</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5584</v>
+        <v>-0.4749</v>
       </c>
       <c r="I31" t="n">
-        <v>1505.020743243243</v>
+        <v>1505.793133333333</v>
       </c>
       <c r="J31" t="n">
-        <v>108.3839503310121</v>
+        <v>108.9368258185659</v>
       </c>
       <c r="K31" t="n">
-        <v>119.8255649266585</v>
+        <v>120.6012009392548</v>
       </c>
       <c r="L31" t="n">
-        <v>-11.44161459564642</v>
+        <v>-11.66437512068896</v>
       </c>
       <c r="M31" t="n">
-        <v>107.4275001861903</v>
+        <v>108.5300715708885</v>
       </c>
       <c r="N31" t="n">
-        <v>121.388243173222</v>
+        <v>124.1405019236009</v>
       </c>
       <c r="O31" t="n">
-        <v>-13.96074298703179</v>
+        <v>-15.61043035271232</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5334401619956255</v>
+        <v>0.5362923003100211</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1318143240784889</v>
+        <v>0.131173573577824</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2370592000614369</v>
+        <v>0.2366362148665032</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5454680986563969</v>
+        <v>0.5539569619436472</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2363967466545321</v>
+        <v>0.2351517579588084</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4041425680322631</v>
+        <v>0.4048352729941456</v>
       </c>
       <c r="V31" t="n">
-        <v>103.6577541827542</v>
+        <v>103.7796129032258</v>
       </c>
       <c r="W31" t="n">
-        <v>112.3581081081081</v>
+        <v>113.0774193548387</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.54665379665379</v>
+        <v>-11.80645161290323</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5652795629526614</v>
+        <v>0.5680913396971063</v>
       </c>
       <c r="Z31" t="n">
-        <v>111.89</v>
+        <v>112.19</v>
       </c>
       <c r="AA31" t="n">
-        <v>-13.51</v>
+        <v>-15.07</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3820,16 +3820,16 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1</v>
-      </c>
       <c r="AG31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.271780281768349</v>
+        <v>-1.609442874357366</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -607,76 +607,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>1754.887</v>
+        <v>1757.767</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4047</v>
+        <v>1.1245</v>
       </c>
       <c r="I2" t="n">
-        <v>1496.527337837838</v>
+        <v>1499.007706666667</v>
       </c>
       <c r="J2" t="n">
-        <v>116.6530283556399</v>
+        <v>117.2413219849427</v>
       </c>
       <c r="K2" t="n">
-        <v>105.5363273232863</v>
+        <v>105.2637053679997</v>
       </c>
       <c r="L2" t="n">
-        <v>11.11670103235359</v>
+        <v>11.97761661694292</v>
       </c>
       <c r="M2" t="n">
-        <v>118.0988633185223</v>
+        <v>118.9420600968889</v>
       </c>
       <c r="N2" t="n">
-        <v>105.7753252132156</v>
+        <v>103.1303261403143</v>
       </c>
       <c r="O2" t="n">
-        <v>12.32353810530669</v>
+        <v>15.81173395657466</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5599724631762372</v>
+        <v>0.5624857078936398</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1080537136291331</v>
+        <v>0.1068741006528377</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2184571131540753</v>
+        <v>0.2216172577137017</v>
       </c>
       <c r="S2" t="n">
-        <v>0.556510062828969</v>
+        <v>0.5597592956164686</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2727661952333165</v>
+        <v>0.2670186883181301</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4247743075324854</v>
+        <v>0.4244352598922859</v>
       </c>
       <c r="V2" t="n">
-        <v>101.9358602504944</v>
+        <v>101.9052929292929</v>
       </c>
       <c r="W2" t="n">
-        <v>118.6802900461437</v>
+        <v>119.3474747474747</v>
       </c>
       <c r="X2" t="n">
-        <v>11.06657877389584</v>
+        <v>12.1119191919192</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5997262411615215</v>
+        <v>0.6011065078311637</v>
       </c>
       <c r="Z2" t="n">
-        <v>118.41</v>
+        <v>119.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.48</v>
+        <v>14.47</v>
       </c>
       <c r="AB2" t="n">
         <v>11.54061896828745</v>
@@ -688,16 +688,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.128497146887424</v>
+        <v>1.160209884304797</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>1735.369</v>
+        <v>1737.898</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8785</v>
+        <v>2.7465</v>
       </c>
       <c r="I3" t="n">
-        <v>1507.407945945946</v>
+        <v>1507.00944</v>
       </c>
       <c r="J3" t="n">
-        <v>117.4393759570561</v>
+        <v>117.6361134440906</v>
       </c>
       <c r="K3" t="n">
-        <v>108.8008610571052</v>
+        <v>108.724823032893</v>
       </c>
       <c r="L3" t="n">
-        <v>8.638514899951035</v>
+        <v>8.911290411197573</v>
       </c>
       <c r="M3" t="n">
-        <v>122.0053173201866</v>
+        <v>122.3297494542914</v>
       </c>
       <c r="N3" t="n">
-        <v>106.6072036100713</v>
+        <v>104.9267753835455</v>
       </c>
       <c r="O3" t="n">
-        <v>15.39811371011537</v>
+        <v>17.40297407074593</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5605054799289906</v>
+        <v>0.5618913705460741</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1124123883310109</v>
+        <v>0.1123980357238551</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2577406721649955</v>
+        <v>0.2589068454834924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5687480949707696</v>
+        <v>0.5742827147222532</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2831579697772845</v>
+        <v>0.2771865720764432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4238251658030815</v>
+        <v>0.4221749789571716</v>
       </c>
       <c r="V3" t="n">
-        <v>101.5825</v>
+        <v>101.9633513513514</v>
       </c>
       <c r="W3" t="n">
-        <v>119.1599099099099</v>
+        <v>119.6735135135135</v>
       </c>
       <c r="X3" t="n">
-        <v>8.579954954954955</v>
+        <v>8.673513513513514</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5966858113914896</v>
+        <v>0.5974052592754979</v>
       </c>
       <c r="Z3" t="n">
-        <v>122.53</v>
+        <v>123.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.57</v>
+        <v>17.38</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -796,16 +796,16 @@
         <v>114.9918244005745</v>
       </c>
       <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9288160867109657</v>
+        <v>0.9629973371312547</v>
       </c>
     </row>
     <row r="4">
@@ -823,76 +823,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>1679.675</v>
+        <v>1681.48</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3824</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1494.837527027027</v>
+        <v>1495.116653333333</v>
       </c>
       <c r="J4" t="n">
-        <v>115.1392762201249</v>
+        <v>114.7173468953014</v>
       </c>
       <c r="K4" t="n">
-        <v>107.7282548734106</v>
+        <v>107.4244639502166</v>
       </c>
       <c r="L4" t="n">
-        <v>7.411021346714317</v>
+        <v>7.292882945084827</v>
       </c>
       <c r="M4" t="n">
-        <v>117.9516585116308</v>
+        <v>116.2858247592205</v>
       </c>
       <c r="N4" t="n">
-        <v>107.5524512121974</v>
+        <v>106.9469613825711</v>
       </c>
       <c r="O4" t="n">
-        <v>10.39920729943336</v>
+        <v>9.338863376649558</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5491455415103479</v>
+        <v>0.5459977134717223</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1244900504816549</v>
+        <v>0.1230712772744636</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3021615225442529</v>
+        <v>0.3000991914852677</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5721744578889115</v>
+        <v>0.5639624130671045</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2968225597733392</v>
+        <v>0.2959223958437266</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3477062357669112</v>
+        <v>0.3458162779405154</v>
       </c>
       <c r="V4" t="n">
-        <v>102.1197384481255</v>
+        <v>102.2258916666666</v>
       </c>
       <c r="W4" t="n">
-        <v>117.662598081953</v>
+        <v>117.34</v>
       </c>
       <c r="X4" t="n">
-        <v>7.913687881429817</v>
+        <v>7.764166666666666</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5856708343387226</v>
+        <v>0.5823861715356856</v>
       </c>
       <c r="Z4" t="n">
-        <v>119.44</v>
+        <v>118.13</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.65</v>
+        <v>8.6</v>
       </c>
       <c r="AB4" t="n">
         <v>1.549391602834736</v>
@@ -904,16 +904,16 @@
         <v>110.9722985057385</v>
       </c>
       <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
       </c>
       <c r="AG4" t="n">
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2138294435156924</v>
+        <v>-0.1627069220023516</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.107669226533732</v>
+        <v>1.120014192829525</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9976778471500981</v>
+        <v>1.00924680319027</v>
       </c>
     </row>
     <row r="7">
@@ -1237,331 +1237,331 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.575100798425221</v>
+        <v>1.474378589934948</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>1575.058</v>
+        <v>1584.828</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3107</v>
+        <v>0.1629</v>
       </c>
       <c r="I8" t="n">
-        <v>1502.204986486486</v>
+        <v>1497.981493333333</v>
       </c>
       <c r="J8" t="n">
-        <v>114.9700538712982</v>
+        <v>115.6583684984793</v>
       </c>
       <c r="K8" t="n">
-        <v>110.2840103679508</v>
+        <v>111.1578191183936</v>
       </c>
       <c r="L8" t="n">
-        <v>4.686043503347449</v>
+        <v>4.500549380085617</v>
       </c>
       <c r="M8" t="n">
-        <v>110.973587900957</v>
+        <v>118.4645138426517</v>
       </c>
       <c r="N8" t="n">
-        <v>109.555917378623</v>
+        <v>111.5640511951537</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41767052233401</v>
+        <v>6.900462647497992</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5599819014686255</v>
+        <v>0.5433369960177337</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1240581560783763</v>
+        <v>0.1262942730836234</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2563243743739458</v>
+        <v>0.3446208856598313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.544689202983769</v>
+        <v>0.5568142229719847</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2885004965531732</v>
+        <v>0.2624683941816954</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4167367709569746</v>
+        <v>0.3520606583910677</v>
       </c>
       <c r="V8" t="n">
-        <v>103.0188076311605</v>
+        <v>99.086</v>
       </c>
       <c r="W8" t="n">
-        <v>118.0321939586646</v>
+        <v>114.476</v>
       </c>
       <c r="X8" t="n">
-        <v>4.266295707472177</v>
+        <v>4.505000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5930791719344871</v>
+        <v>0.5765287526009019</v>
       </c>
       <c r="Z8" t="n">
-        <v>114.1</v>
+        <v>115.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.28</v>
+        <v>5.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.250350764022217</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC8" t="n">
-        <v>114.1383305986051</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD8" t="n">
-        <v>109.8879798345829</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.8359624720346067</v>
+        <v>0.5434409497093642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>1584.828</v>
+        <v>1637.361</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1629</v>
+        <v>-0.494</v>
       </c>
       <c r="I9" t="n">
-        <v>1497.981493333333</v>
+        <v>1489.503105263158</v>
       </c>
       <c r="J9" t="n">
-        <v>115.6583684984793</v>
+        <v>116.9821759846004</v>
       </c>
       <c r="K9" t="n">
-        <v>111.1578191183936</v>
+        <v>112.7205313403235</v>
       </c>
       <c r="L9" t="n">
-        <v>4.500549380085617</v>
+        <v>4.26164464427677</v>
       </c>
       <c r="M9" t="n">
-        <v>118.4645138426517</v>
+        <v>121.7979103309086</v>
       </c>
       <c r="N9" t="n">
-        <v>111.5640511951537</v>
+        <v>117.1440500400287</v>
       </c>
       <c r="O9" t="n">
-        <v>6.900462647497992</v>
+        <v>4.653860290879916</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5433369960177337</v>
+        <v>0.5622045220013564</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1262942730836234</v>
+        <v>0.1170139325863426</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3446208856598313</v>
+        <v>0.2634540678088494</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5568142229719847</v>
+        <v>0.5902082720988117</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2624683941816954</v>
+        <v>0.2682599897013254</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3520606583910677</v>
+        <v>0.4431598579957102</v>
       </c>
       <c r="V9" t="n">
-        <v>99.086</v>
+        <v>102.1592030075188</v>
       </c>
       <c r="W9" t="n">
-        <v>114.476</v>
+        <v>119.3037593984962</v>
       </c>
       <c r="X9" t="n">
-        <v>4.505000000000001</v>
+        <v>4.136842105263158</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5765287526009019</v>
+        <v>0.5952877592132905</v>
       </c>
       <c r="Z9" t="n">
-        <v>115.49</v>
+        <v>122.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.82</v>
+        <v>4.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.413694058608522</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC9" t="n">
-        <v>112.3850185369902</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD9" t="n">
-        <v>108.9713244783817</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.516135001415806</v>
+        <v>1.42313926641163</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>1642.78</v>
+        <v>1579.057</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1251</v>
+        <v>0.8065</v>
       </c>
       <c r="I10" t="n">
-        <v>1488.512786666667</v>
+        <v>1500.461506666667</v>
       </c>
       <c r="J10" t="n">
-        <v>116.8640831944832</v>
+        <v>114.5510091728242</v>
       </c>
       <c r="K10" t="n">
-        <v>113.1701660322143</v>
+        <v>110.6393014336458</v>
       </c>
       <c r="L10" t="n">
-        <v>3.693917162268839</v>
+        <v>3.911707739178512</v>
       </c>
       <c r="M10" t="n">
-        <v>122.228227073958</v>
+        <v>109.9760628138808</v>
       </c>
       <c r="N10" t="n">
-        <v>119.2668111604354</v>
+        <v>108.5662251088618</v>
       </c>
       <c r="O10" t="n">
-        <v>2.961415913522665</v>
+        <v>1.40983770501907</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5609403391835851</v>
+        <v>0.5580554349269832</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1165786864781034</v>
+        <v>0.1246675148687783</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2646908658853611</v>
+        <v>0.2542267892037883</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5880122051555773</v>
+        <v>0.543141722363614</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2660265796165251</v>
+        <v>0.2911943806214223</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4433637496558964</v>
+        <v>0.4202932805961634</v>
       </c>
       <c r="V10" t="n">
-        <v>102.1253411764706</v>
+        <v>103.0096</v>
       </c>
       <c r="W10" t="n">
-        <v>119.2376470588236</v>
+        <v>117.6495238095238</v>
       </c>
       <c r="X10" t="n">
-        <v>3.755294117647058</v>
+        <v>3.587428571428572</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5941964598826075</v>
+        <v>0.5917326719248989</v>
       </c>
       <c r="Z10" t="n">
-        <v>122.81</v>
+        <v>114.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.967224035556209</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC10" t="n">
-        <v>120.0962116764131</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD10" t="n">
-        <v>110.1289876408569</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1</v>
-      </c>
       <c r="AG10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.504127520882633</v>
+        <v>0.8752704342673691</v>
       </c>
     </row>
     <row r="11">
@@ -1579,76 +1579,76 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>1580.433</v>
+        <v>1582.953</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2264</v>
+        <v>1.7598</v>
       </c>
       <c r="I11" t="n">
-        <v>1497.293493333333</v>
+        <v>1494.619</v>
       </c>
       <c r="J11" t="n">
-        <v>115.849206742656</v>
+        <v>116.1936704899855</v>
       </c>
       <c r="K11" t="n">
-        <v>112.2297629365615</v>
+        <v>112.3272523065444</v>
       </c>
       <c r="L11" t="n">
-        <v>3.619443806094497</v>
+        <v>3.866418183441092</v>
       </c>
       <c r="M11" t="n">
-        <v>118.5722088734538</v>
+        <v>120.8701470534281</v>
       </c>
       <c r="N11" t="n">
-        <v>108.0429191492245</v>
+        <v>108.8115959964366</v>
       </c>
       <c r="O11" t="n">
-        <v>10.52928972422932</v>
+        <v>12.05855105699137</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5528217641175907</v>
+        <v>0.5548254208961517</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1283233919657186</v>
+        <v>0.1274390415058646</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3052757185150465</v>
+        <v>0.3057836610503921</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5638218079694002</v>
+        <v>0.5777780135176525</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2519009610075865</v>
+        <v>0.2487142834544319</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4827171335862863</v>
+        <v>0.4844422156465903</v>
       </c>
       <c r="V11" t="n">
-        <v>99.68879999999999</v>
+        <v>99.6992105263158</v>
       </c>
       <c r="W11" t="n">
-        <v>116.1013953488372</v>
+        <v>116.4329769736842</v>
       </c>
       <c r="X11" t="n">
-        <v>4.953488372093023</v>
+        <v>5.162828947368421</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.590163834529823</v>
+        <v>0.5915768055953945</v>
       </c>
       <c r="Z11" t="n">
-        <v>117.27</v>
+        <v>119.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.55</v>
+        <v>14.06</v>
       </c>
       <c r="AB11" t="n">
         <v>-10.13717477219789</v>
@@ -1669,211 +1669,211 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3854014318134431</v>
+        <v>0.2064592478889887</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>1563.777</v>
+        <v>1521.635</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8829</v>
+        <v>2.2789</v>
       </c>
       <c r="I12" t="n">
-        <v>1490.21356</v>
+        <v>1486.017460526316</v>
       </c>
       <c r="J12" t="n">
-        <v>117.0649331276973</v>
+        <v>113.9707468270876</v>
       </c>
       <c r="K12" t="n">
-        <v>114.0888539065797</v>
+        <v>111.5643938317927</v>
       </c>
       <c r="L12" t="n">
-        <v>2.976079221117644</v>
+        <v>2.406352995294905</v>
       </c>
       <c r="M12" t="n">
-        <v>122.2459294720319</v>
+        <v>118.3840893776426</v>
       </c>
       <c r="N12" t="n">
-        <v>111.2401223350463</v>
+        <v>106.7715599768774</v>
       </c>
       <c r="O12" t="n">
-        <v>11.0058071369856</v>
+        <v>11.61252940076515</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5739554128782122</v>
+        <v>0.5539635872810795</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1244787944645825</v>
+        <v>0.1167066689761772</v>
       </c>
       <c r="R12" t="n">
-        <v>0.239192021866405</v>
+        <v>0.2407859497037374</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5933263770082704</v>
+        <v>0.5691156447894506</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3241320385285712</v>
+        <v>0.2385889869815702</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3973042172868758</v>
+        <v>0.4284885902688828</v>
       </c>
       <c r="V12" t="n">
-        <v>100.2617302325582</v>
+        <v>103.9297960526316</v>
       </c>
       <c r="W12" t="n">
-        <v>116.92</v>
+        <v>118.4667763157894</v>
       </c>
       <c r="X12" t="n">
-        <v>2.24</v>
+        <v>2.623684210526316</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6107325762662917</v>
+        <v>0.5848545178709627</v>
       </c>
       <c r="Z12" t="n">
-        <v>122.05</v>
+        <v>122.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.51</v>
+        <v>11.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.827913300592181</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC12" t="n">
-        <v>114.1496737878887</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD12" t="n">
-        <v>112.3217604872965</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.605827477504895</v>
+        <v>0.5943087781602799</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>1521.635</v>
+        <v>1569.196</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2789</v>
+        <v>2.4652</v>
       </c>
       <c r="I13" t="n">
-        <v>1486.017460526316</v>
+        <v>1492.221013157895</v>
       </c>
       <c r="J13" t="n">
-        <v>113.9707468270876</v>
+        <v>116.4194087094877</v>
       </c>
       <c r="K13" t="n">
-        <v>111.5643938317927</v>
+        <v>114.5045932890717</v>
       </c>
       <c r="L13" t="n">
-        <v>2.406352995294905</v>
+        <v>1.914815420415977</v>
       </c>
       <c r="M13" t="n">
-        <v>118.3840893776426</v>
+        <v>118.0663825506114</v>
       </c>
       <c r="N13" t="n">
-        <v>106.7715599768774</v>
+        <v>112.2261586960545</v>
       </c>
       <c r="O13" t="n">
-        <v>11.61252940076515</v>
+        <v>5.840223854556848</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5539635872810795</v>
+        <v>0.5712291588266269</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1167066689761772</v>
+        <v>0.1256972656006453</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2407859497037374</v>
+        <v>0.2376870464441672</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5691156447894506</v>
+        <v>0.5768626394342689</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2385889869815702</v>
+        <v>0.324642865172263</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4284885902688828</v>
+        <v>0.3971457498802721</v>
       </c>
       <c r="V13" t="n">
-        <v>103.9297960526316</v>
+        <v>100.3483313397129</v>
       </c>
       <c r="W13" t="n">
-        <v>118.4667763157894</v>
+        <v>116.3427033492823</v>
       </c>
       <c r="X13" t="n">
-        <v>2.623684210526316</v>
+        <v>1.093002392344498</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5848545178709627</v>
+        <v>0.6082332378082067</v>
       </c>
       <c r="Z13" t="n">
-        <v>122.35</v>
+        <v>117.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.63</v>
+        <v>2.989999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.981113782848854</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC13" t="n">
-        <v>112.8029837792552</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD13" t="n">
-        <v>113.7840975621041</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -1882,106 +1882,106 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.6312724420106667</v>
+        <v>1.649776602112722</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>1559.934</v>
+        <v>1533.636</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.369</v>
+        <v>-2.7113</v>
       </c>
       <c r="I14" t="n">
-        <v>1496.232333333333</v>
+        <v>1505.278789473684</v>
       </c>
       <c r="J14" t="n">
-        <v>115.9438123958599</v>
+        <v>113.984454965129</v>
       </c>
       <c r="K14" t="n">
-        <v>113.7599027464007</v>
+        <v>112.2586812931816</v>
       </c>
       <c r="L14" t="n">
-        <v>2.183909649459133</v>
+        <v>1.725773671947434</v>
       </c>
       <c r="M14" t="n">
-        <v>118.6065612920006</v>
+        <v>115.7806766419599</v>
       </c>
       <c r="N14" t="n">
-        <v>112.8318133006466</v>
+        <v>122.3318716431754</v>
       </c>
       <c r="O14" t="n">
-        <v>5.774747991354014</v>
+        <v>-6.551195001215493</v>
       </c>
       <c r="P14" t="n">
-        <v>0.561597483145205</v>
+        <v>0.537712963923746</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1261022622517228</v>
+        <v>0.1112415592742477</v>
       </c>
       <c r="R14" t="n">
-        <v>0.234966999852213</v>
+        <v>0.2519334999041863</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5803389757403798</v>
+        <v>0.5383739776913999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3038375545347913</v>
+        <v>0.2719616798845572</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4040674378236122</v>
+        <v>0.4063485241097721</v>
       </c>
       <c r="V14" t="n">
-        <v>98.64425925925926</v>
+        <v>105.665911872705</v>
       </c>
       <c r="W14" t="n">
-        <v>113.7222222222222</v>
+        <v>120.4406364749082</v>
       </c>
       <c r="X14" t="n">
-        <v>1.174074074074074</v>
+        <v>1.946144430844553</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6053145495194063</v>
+        <v>0.5760248946858337</v>
       </c>
       <c r="Z14" t="n">
-        <v>116.42</v>
+        <v>119.01</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.130000000000001</v>
+        <v>-8.280000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.815266446541752</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC14" t="n">
-        <v>113.8106821492749</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD14" t="n">
-        <v>108.9954157027332</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -1990,106 +1990,106 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.3636844859740119</v>
+        <v>0.06142548409181948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612748</v>
+        <v>1610612746</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>1533.636</v>
+        <v>1555.38</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.7113</v>
+        <v>0.4326</v>
       </c>
       <c r="I15" t="n">
-        <v>1505.278789473684</v>
+        <v>1495.794473684211</v>
       </c>
       <c r="J15" t="n">
-        <v>113.984454965129</v>
+        <v>115.5308680528053</v>
       </c>
       <c r="K15" t="n">
-        <v>112.2586812931816</v>
+        <v>113.8324266773286</v>
       </c>
       <c r="L15" t="n">
-        <v>1.725773671947434</v>
+        <v>1.698441375476713</v>
       </c>
       <c r="M15" t="n">
-        <v>115.7806766419599</v>
+        <v>116.8446816593703</v>
       </c>
       <c r="N15" t="n">
-        <v>122.3318716431754</v>
+        <v>114.0963488752868</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.551195001215493</v>
+        <v>2.748332784083542</v>
       </c>
       <c r="P15" t="n">
-        <v>0.537712963923746</v>
+        <v>0.5588537995811402</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1112415592742477</v>
+        <v>0.1249793680202745</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2519334999041863</v>
+        <v>0.2346421905870804</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5383739776913999</v>
+        <v>0.5730362557347206</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2719616798845572</v>
+        <v>0.3010272971365625</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4063485241097721</v>
+        <v>0.401287615049342</v>
       </c>
       <c r="V15" t="n">
-        <v>105.665911872705</v>
+        <v>98.74230769230769</v>
       </c>
       <c r="W15" t="n">
-        <v>120.4406364749082</v>
+        <v>113.4871794871795</v>
       </c>
       <c r="X15" t="n">
-        <v>1.946144430844553</v>
+        <v>0.8205128205128207</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5760248946858337</v>
+        <v>0.6023923312009145</v>
       </c>
       <c r="Z15" t="n">
-        <v>119.01</v>
+        <v>114.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>-8.280000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.094669144490311</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC15" t="n">
-        <v>111.6804548463295</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD15" t="n">
-        <v>112.7751239908198</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2098,106 +2098,106 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.05280924997521638</v>
+        <v>0.3775130299558238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>1510.467</v>
+        <v>1513.967</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9538</v>
+        <v>0.5175</v>
       </c>
       <c r="I16" t="n">
-        <v>1512.922053333333</v>
+        <v>1498.068306666667</v>
       </c>
       <c r="J16" t="n">
-        <v>113.1407795736791</v>
+        <v>113.3795012307266</v>
       </c>
       <c r="K16" t="n">
-        <v>111.5017629140347</v>
+        <v>111.8525989203726</v>
       </c>
       <c r="L16" t="n">
-        <v>1.639016659644434</v>
+        <v>1.526902310354019</v>
       </c>
       <c r="M16" t="n">
-        <v>116.078878571102</v>
+        <v>119.0008012020616</v>
       </c>
       <c r="N16" t="n">
-        <v>112.6056784529052</v>
+        <v>115.837254644371</v>
       </c>
       <c r="O16" t="n">
-        <v>3.473200118196776</v>
+        <v>3.163546557690581</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5380366682481879</v>
+        <v>0.5451942484259756</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.119573004826412</v>
+        <v>0.115499508690161</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2868321744630224</v>
+        <v>0.2517852498832425</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5413192871582424</v>
+        <v>0.5887321211300018</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2319267154748918</v>
+        <v>0.2652380958826372</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4583282688898132</v>
+        <v>0.3670760629041485</v>
       </c>
       <c r="V16" t="n">
-        <v>99.89399999999999</v>
+        <v>100.7690256410256</v>
       </c>
       <c r="W16" t="n">
-        <v>112.8635294117647</v>
+        <v>114.3634188034189</v>
       </c>
       <c r="X16" t="n">
-        <v>1.681176470588235</v>
+        <v>1.925470085470086</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5699587726688814</v>
+        <v>0.5790750032406927</v>
       </c>
       <c r="Z16" t="n">
-        <v>116.13</v>
+        <v>119.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.55</v>
+        <v>5.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.375203171419814</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC16" t="n">
-        <v>114.7034977739938</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD16" t="n">
-        <v>117.0787009454136</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2206,118 +2206,118 @@
         <v>1</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1019760617912528</v>
+        <v>0.3327135263285276</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>1513.967</v>
+        <v>1508.125</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5175</v>
+        <v>-0.3898</v>
       </c>
       <c r="I17" t="n">
-        <v>1498.068306666667</v>
+        <v>1512.952723684211</v>
       </c>
       <c r="J17" t="n">
-        <v>113.3795012307266</v>
+        <v>113.2684828587621</v>
       </c>
       <c r="K17" t="n">
-        <v>111.8525989203726</v>
+        <v>112.0833372779551</v>
       </c>
       <c r="L17" t="n">
-        <v>1.526902310354019</v>
+        <v>1.185145580806992</v>
       </c>
       <c r="M17" t="n">
-        <v>119.0008012020616</v>
+        <v>114.6323939940298</v>
       </c>
       <c r="N17" t="n">
-        <v>115.837254644371</v>
+        <v>114.4480454447687</v>
       </c>
       <c r="O17" t="n">
-        <v>3.163546557690581</v>
+        <v>0.1843485492610615</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5451942484259756</v>
+        <v>0.5393078145788982</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.115499508690161</v>
+        <v>0.1186873682728986</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2517852498832425</v>
+        <v>0.2856564534487521</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5887321211300018</v>
+        <v>0.5377984330123883</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2652380958826372</v>
+        <v>0.2262413696256032</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3670760629041485</v>
+        <v>0.456550343791927</v>
       </c>
       <c r="V17" t="n">
-        <v>100.7690256410256</v>
+        <v>99.65044929396662</v>
       </c>
       <c r="W17" t="n">
-        <v>114.3634188034189</v>
+        <v>112.7509627727857</v>
       </c>
       <c r="X17" t="n">
-        <v>1.925470085470086</v>
+        <v>1.245186136071887</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5790750032406927</v>
+        <v>0.5702778619371006</v>
       </c>
       <c r="Z17" t="n">
-        <v>119.86</v>
+        <v>114.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.05</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>-4.536933640611859</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC17" t="n">
-        <v>108.3888858603967</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD17" t="n">
-        <v>112.9258195010085</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1</v>
-      </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.307394356422662</v>
+        <v>0.01836888096608447</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.4966292790296482</v>
+        <v>0.5066414413749813</v>
       </c>
     </row>
     <row r="19">
@@ -2443,76 +2443,76 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>1477.52</v>
+        <v>1474.991</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0752</v>
+        <v>-1.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>1503.358946666667</v>
+        <v>1506.411710526316</v>
       </c>
       <c r="J19" t="n">
-        <v>112.2816408728654</v>
+        <v>112.4327589050653</v>
       </c>
       <c r="K19" t="n">
-        <v>112.7064985066904</v>
+        <v>112.9572150915985</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4248576338250612</v>
+        <v>-0.5244561865333028</v>
       </c>
       <c r="M19" t="n">
-        <v>109.6266905431995</v>
+        <v>109.9734404020988</v>
       </c>
       <c r="N19" t="n">
-        <v>116.6624372135305</v>
+        <v>116.3520023932743</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.035746670330974</v>
+        <v>-6.378561991175575</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5504657775710466</v>
+        <v>0.5498925907421595</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1324747031929864</v>
+        <v>0.1319571408514362</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2519977137835492</v>
+        <v>0.2563491495441706</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5492561348734037</v>
+        <v>0.5544058001170727</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2402159177901141</v>
+        <v>0.2386765745649697</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4994888756778889</v>
+        <v>0.4997351196251281</v>
       </c>
       <c r="V19" t="n">
-        <v>101.5903619047619</v>
+        <v>102.0110453216374</v>
       </c>
       <c r="W19" t="n">
-        <v>114.0392380952381</v>
+        <v>114.7609649122807</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5401904761904762</v>
+        <v>-0.3991228070175439</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5843520306626269</v>
+        <v>0.5837245340717334</v>
       </c>
       <c r="Z19" t="n">
-        <v>110.11</v>
+        <v>112.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>-7.65</v>
+        <v>-6.91</v>
       </c>
       <c r="AB19" t="n">
         <v>2.402868486532558</v>
@@ -2524,232 +2524,232 @@
         <v>110.1198746025049</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3281407323510546</v>
+        <v>-0.3082982535776363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>1517.594</v>
+        <v>1467.509</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.5061</v>
+        <v>1.6738</v>
       </c>
       <c r="I20" t="n">
-        <v>1490.487763888889</v>
+        <v>1503.88051948052</v>
       </c>
       <c r="J20" t="n">
-        <v>111.9487583735943</v>
+        <v>111.4731251846435</v>
       </c>
       <c r="K20" t="n">
-        <v>112.852901991738</v>
+        <v>112.2064478325931</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9041436181436305</v>
+        <v>-0.7333226479496043</v>
       </c>
       <c r="M20" t="n">
-        <v>107.8715998687121</v>
+        <v>113.9996153916357</v>
       </c>
       <c r="N20" t="n">
-        <v>120.5781407699248</v>
+        <v>103.491548713392</v>
       </c>
       <c r="O20" t="n">
-        <v>-12.7065409012127</v>
+        <v>10.50806667824366</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5290344421716072</v>
+        <v>0.5340566350449895</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1189425539863543</v>
+        <v>0.140574133685937</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2428295425858887</v>
+        <v>0.3116283493387423</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5150248708953298</v>
+        <v>0.5462692030856715</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3161902200269517</v>
+        <v>0.2844703452452553</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3887147877557122</v>
+        <v>0.470120992747168</v>
       </c>
       <c r="V20" t="n">
-        <v>102.5710810810811</v>
+        <v>103.3384809130263</v>
       </c>
       <c r="W20" t="n">
-        <v>114.9324324324324</v>
+        <v>115.4057457693821</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2297297297297297</v>
+        <v>-0.2786304604486423</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5753604355976911</v>
+        <v>0.5707724847405173</v>
       </c>
       <c r="Z20" t="n">
-        <v>112.34</v>
+        <v>116.02</v>
       </c>
       <c r="AA20" t="n">
-        <v>-10.46</v>
+        <v>11.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC20" t="n">
-        <v>107.6152962364644</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD20" t="n">
-        <v>108.1384073962044</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1389626567450439</v>
+        <v>-0.5084641148377209</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612757</v>
+        <v>1610612753</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>1462.955</v>
+        <v>1517.594</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5089</v>
+        <v>-3.5061</v>
       </c>
       <c r="I21" t="n">
-        <v>1503.14297368421</v>
+        <v>1490.487763888889</v>
       </c>
       <c r="J21" t="n">
-        <v>111.3212065587594</v>
+        <v>111.9487583735943</v>
       </c>
       <c r="K21" t="n">
-        <v>112.4836368048986</v>
+        <v>112.852901991738</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.162430246139138</v>
+        <v>-0.9041436181436305</v>
       </c>
       <c r="M21" t="n">
-        <v>113.796125832089</v>
+        <v>107.8715998687121</v>
       </c>
       <c r="N21" t="n">
-        <v>103.6274762135796</v>
+        <v>120.5781407699248</v>
       </c>
       <c r="O21" t="n">
-        <v>10.16864961850941</v>
+        <v>-12.7065409012127</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5330816563423848</v>
+        <v>0.5290344421716072</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1411884942028879</v>
+        <v>0.1189425539863543</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3132931057657975</v>
+        <v>0.2428295425858887</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5501894938354689</v>
+        <v>0.5150248708953298</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2863153481299546</v>
+        <v>0.3161902200269517</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4677699825621559</v>
+        <v>0.3887147877557122</v>
       </c>
       <c r="V21" t="n">
-        <v>103.3185434516523</v>
+        <v>102.5710810810811</v>
       </c>
       <c r="W21" t="n">
-        <v>115.3108935128519</v>
+        <v>114.9324324324324</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5514075887392901</v>
+        <v>-0.2297297297297297</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5702199768546904</v>
+        <v>0.5753604355976911</v>
       </c>
       <c r="Z21" t="n">
-        <v>116.52</v>
+        <v>112.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.17</v>
+        <v>-10.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.840928550668963</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC21" t="n">
-        <v>109.2995408403883</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD21" t="n">
-        <v>113.1404693910572</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.5208196091730017</v>
+        <v>-0.1137986114161466</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3882638080349268</v>
+        <v>-0.3646713092680558</v>
       </c>
     </row>
     <row r="23">
@@ -2875,76 +2875,76 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46110</v>
+        <v>46114</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>1380.194</v>
+        <v>1375.739</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6597</v>
+        <v>0.7695</v>
       </c>
       <c r="I23" t="n">
-        <v>1508.015253333333</v>
+        <v>1508.883394736842</v>
       </c>
       <c r="J23" t="n">
-        <v>112.0095682863248</v>
+        <v>111.9147963701947</v>
       </c>
       <c r="K23" t="n">
-        <v>116.6655072670407</v>
+        <v>116.476910660563</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.65593898071587</v>
+        <v>-4.562114290368302</v>
       </c>
       <c r="M23" t="n">
-        <v>113.784720892972</v>
+        <v>111.3630347239127</v>
       </c>
       <c r="N23" t="n">
-        <v>115.9210420958728</v>
+        <v>116.5494897145978</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.136321202900874</v>
+        <v>-5.186454990685206</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5274653935249312</v>
+        <v>0.5274744140557101</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1164462289012098</v>
+        <v>0.1181034499933678</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2665255938248261</v>
+        <v>0.2680315069823698</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5421438336073836</v>
+        <v>0.5368460745769359</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2840970520801815</v>
+        <v>0.2842388138380912</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3594864629676445</v>
+        <v>0.3574637764393076</v>
       </c>
       <c r="V23" t="n">
-        <v>102.6370035087719</v>
+        <v>102.6282503556187</v>
       </c>
       <c r="W23" t="n">
-        <v>114.9045614035087</v>
+        <v>114.8335704125178</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.788771929824562</v>
+        <v>-4.625889046941679</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5672848319778909</v>
+        <v>0.5676001493215278</v>
       </c>
       <c r="Z23" t="n">
-        <v>114.51</v>
+        <v>111.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1.04</v>
+        <v>-3.72</v>
       </c>
       <c r="AB23" t="n">
         <v>-9.447870926461551</v>
@@ -2956,7 +2956,7 @@
         <v>117.8388903788833</v>
       </c>
       <c r="AE23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.4242476545941131</v>
+        <v>-0.2301051334295568</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.336120759393987</v>
+        <v>-1.403485284842642</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.133310788772001</v>
+        <v>-1.535687751673983</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.831042387901073</v>
+        <v>-0.8251487496078399</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.9533364359244573</v>
+        <v>-0.8058120769535597</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.405933653530657</v>
+        <v>-1.189228455659425</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.554830066682773</v>
+        <v>-1.565396979634305</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.70070001358613</v>
+        <v>-1.697217668599295</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.609442874357366</v>
+        <v>-1.60588313715587</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.160209884304797</v>
+        <v>1.19066009539253</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9629973371312547</v>
+        <v>0.9904526820793171</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1627069220023516</v>
+        <v>-0.1523465013746741</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.120014192829525</v>
+        <v>1.149853992880611</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.00924680319027</v>
+        <v>0.6086370494183901</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.474378589934948</v>
+        <v>1.509599761248695</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5434409497093642</v>
+        <v>0.5645249190204263</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.42313926641163</v>
+        <v>1.457582318294139</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.8752704342673691</v>
+        <v>0.9013935600707034</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2064592478889887</v>
+        <v>0.2224258192305278</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.5943087781602799</v>
+        <v>0.6161652253851949</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.649776602112722</v>
+        <v>1.687661364436094</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.06142548409181948</v>
+        <v>0.07518957534509685</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.3775130299558238</v>
+        <v>0.3960772209078623</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3327135263285276</v>
+        <v>0.3505973928366585</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01836888096608447</v>
+        <v>0.03147911543064027</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5066414413749813</v>
+        <v>0.5271665740245498</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3082982535776363</v>
+        <v>-0.3001487802523161</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.5084641148377209</v>
+        <v>-0.5033543566258527</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.1137986114161466</v>
+        <v>-0.1026954700771229</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3646713092680558</v>
+        <v>-0.3573779161369051</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2301051334295568</v>
+        <v>-0.2207682208097144</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.403485284842642</v>
+        <v>-1.299946129675503</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.535687751673983</v>
+        <v>-1.546177392850851</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.8251487496078399</v>
+        <v>-0.8930404375165395</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.8058120769535597</v>
+        <v>-0.8052178394638954</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.189228455659425</v>
+        <v>-1.194456772294427</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.565396979634305</v>
+        <v>-1.576337784604397</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.697217668599295</v>
+        <v>-1.710160300144558</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.60588313715587</v>
+        <v>-1.617438764174682</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19066009539253</v>
+        <v>1.298178201960466</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9904526820793171</v>
+        <v>1.086603249714169</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1523465013746741</v>
+        <v>-0.1210827128836391</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.149853992880611</v>
+        <v>1.255055177455824</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6086370494183901</v>
+        <v>0.6831085793108045</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.509599761248695</v>
+        <v>1.635226882907159</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5645249190204263</v>
+        <v>0.6364918145867599</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.457582318294139</v>
+        <v>1.580255951376932</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9013935600707034</v>
+        <v>0.9924874566261719</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2224258192305278</v>
+        <v>0.2749687345781535</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.6161652253851949</v>
+        <v>0.69106419615995</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.687661364436094</v>
+        <v>0.3154144255297608</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.07518957534509685</v>
+        <v>0.1193725917907262</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.3960772209078623</v>
+        <v>0.4584798564161167</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3505973928366585</v>
+        <v>0.4104177377707845</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.03147911543064027</v>
+        <v>0.07318030392276011</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5271665740245498</v>
+        <v>0.5970123071714287</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3001487802523161</v>
+        <v>-0.2772770294572658</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.5033543566258527</v>
+        <v>-0.1814514423287036</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.1026954700771229</v>
+        <v>-0.06861255505124934</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3573779161369051</v>
+        <v>-0.3377555676467387</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2207682208097144</v>
+        <v>-0.1933893362124705</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.299946129675503</v>
+        <v>-1.333841683880202</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.546177392850851</v>
+        <v>-1.594053665473349</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.8930404375165395</v>
+        <v>-0.9038323702260936</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.8052178394638954</v>
+        <v>-0.8110233094543785</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.194456772294427</v>
+        <v>-1.222362766186594</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.576337784604397</v>
+        <v>-1.625926528417755</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.710160300144558</v>
+        <v>-1.767347327309923</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.617438764174682</v>
+        <v>-1.669361172749605</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.298178201960466</v>
+        <v>1.288045463310073</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.086603249714169</v>
+        <v>1.076133845107003</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1210827128836391</v>
+        <v>-0.1334738324469614</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.255055177455824</v>
+        <v>1.244853819840144</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6831085793108045</v>
+        <v>0.6719971189318088</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.635226882907159</v>
+        <v>1.625630468691419</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.6364918145867599</v>
+        <v>0.6253061758727068</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.580255951376932</v>
+        <v>1.570572065364262</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9924874566261719</v>
+        <v>0.9818682914580743</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2749687345781535</v>
+        <v>0.4649916267618481</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.69106419615995</v>
+        <v>0.6799653950552673</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3154144255297608</v>
+        <v>0.3037178764965158</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1193725917907262</v>
+        <v>0.1073640936783363</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.4584798564161167</v>
+        <v>0.4470109584335238</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.4104177377707845</v>
+        <v>0.3988723615520559</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.07318030392276011</v>
+        <v>0.06109830291872104</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5970123071714287</v>
+        <v>0.5857638471924016</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.2772770294572658</v>
+        <v>-0.2899166912439162</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1814514423287036</v>
+        <v>-0.1939386228663617</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.06861255505124934</v>
+        <v>-0.08092018214204062</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3377555676467387</v>
+        <v>-0.3504914651394954</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.1933893362124705</v>
+        <v>-0.205895512772217</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.333841683880202</v>
+        <v>-1.348162590759892</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.594053665473349</v>
+        <v>-1.608788631365303</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.9038323702260936</v>
+        <v>-0.9174690302444906</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.8110233094543785</v>
+        <v>-0.6603426411337436</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.222362766186594</v>
+        <v>-1.236506283653753</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.625926528417755</v>
+        <v>-1.640712211598237</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.767347327309923</v>
+        <v>-1.782358044541275</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.669361172749605</v>
+        <v>-1.684215970756469</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.288045463310073</v>
+        <v>1.287305484948234</v>
       </c>
     </row>
     <row r="3">
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.076133845107003</v>
+        <v>1.074884942189992</v>
       </c>
     </row>
     <row r="4">
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1334738324469614</v>
+        <v>-0.1376277155366194</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.244853819840144</v>
+        <v>1.244010112913885</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6719971189318088</v>
+        <v>0.6697776458056601</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.625630468691419</v>
+        <v>1.625701230675739</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.6253061758727068</v>
+        <v>0.622974570303663</v>
       </c>
     </row>
     <row r="9">
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.570572065364262</v>
+        <v>1.570510599707363</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9818682914580743</v>
+        <v>0.9803930014492847</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4649916267618481</v>
+        <v>0.4622750115775418</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.6799653950552673</v>
+        <v>0.6777650584512972</v>
       </c>
     </row>
     <row r="13">
@@ -1885,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3037178764965158</v>
+        <v>0.3006139480902592</v>
       </c>
     </row>
     <row r="14">
@@ -1993,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1073640936783363</v>
+        <v>0.1037886042391138</v>
       </c>
     </row>
     <row r="15">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.4470109584335238</v>
+        <v>0.4442511610787055</v>
       </c>
     </row>
     <row r="16">
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3988723615520559</v>
+        <v>0.3959969550852299</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.06109830291872104</v>
+        <v>0.05741170207757666</v>
       </c>
     </row>
     <row r="18">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5857638471924016</v>
+        <v>0.5833372772122284</v>
       </c>
     </row>
     <row r="19">
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.2899166912439162</v>
+        <v>-0.294446285740992</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1939386228663617</v>
+        <v>-0.1982377175155782</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.08092018214204062</v>
+        <v>-0.08494785297712305</v>
       </c>
     </row>
     <row r="22">
@@ -2857,7 +2857,7 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3504914651394954</v>
+        <v>-0.3551665353312072</v>
       </c>
     </row>
     <row r="23">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.205895512772217</v>
+        <v>-0.2102233229535417</v>
       </c>
     </row>
     <row r="24">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.348162590759892</v>
+        <v>-1.35523365668851</v>
       </c>
     </row>
     <row r="25">
@@ -3181,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.608788631365303</v>
+        <v>-1.616485613857187</v>
       </c>
     </row>
     <row r="26">
@@ -3289,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.9174690302444906</v>
+        <v>-0.9235057473697733</v>
       </c>
     </row>
     <row r="27">
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.6603426411337436</v>
+        <v>-0.5507618313038203</v>
       </c>
     </row>
     <row r="28">
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.236506283653753</v>
+        <v>-1.243309197052991</v>
       </c>
     </row>
     <row r="29">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.640712211598237</v>
+        <v>-1.648485861400802</v>
       </c>
     </row>
     <row r="30">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.782358044541275</v>
+        <v>-1.790471869380649</v>
       </c>
     </row>
     <row r="31">
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.684215970756469</v>
+        <v>-1.692094098696974</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.287305484948234</v>
+        <v>1.31291452604812</v>
       </c>
     </row>
     <row r="3">
@@ -715,76 +715,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>1737.898</v>
+        <v>1742.526</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7465</v>
+        <v>2.7768</v>
       </c>
       <c r="I3" t="n">
-        <v>1507.00944</v>
+        <v>1507.645894736842</v>
       </c>
       <c r="J3" t="n">
-        <v>117.6361134440906</v>
+        <v>117.6849754573543</v>
       </c>
       <c r="K3" t="n">
-        <v>108.724823032893</v>
+        <v>109.3042487158585</v>
       </c>
       <c r="L3" t="n">
-        <v>8.911290411197573</v>
+        <v>8.38072674149571</v>
       </c>
       <c r="M3" t="n">
-        <v>122.3297494542914</v>
+        <v>122.5689995533142</v>
       </c>
       <c r="N3" t="n">
-        <v>104.9267753835455</v>
+        <v>107.1379126581208</v>
       </c>
       <c r="O3" t="n">
-        <v>17.40297407074593</v>
+        <v>15.43108689519351</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5618913705460741</v>
+        <v>0.5607443959776774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1123980357238551</v>
+        <v>0.111345276640822</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2589068454834924</v>
+        <v>0.2586134533501876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5742827147222532</v>
+        <v>0.5747747313152169</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2771865720764432</v>
+        <v>0.2785661842752067</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4221749789571716</v>
+        <v>0.4237601600488914</v>
       </c>
       <c r="V3" t="n">
-        <v>101.9633513513514</v>
+        <v>102.2026869806094</v>
       </c>
       <c r="W3" t="n">
-        <v>119.6735135135135</v>
+        <v>120.0737534626039</v>
       </c>
       <c r="X3" t="n">
-        <v>8.673513513513514</v>
+        <v>8.249307479224377</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5974052592754979</v>
+        <v>0.5968987177919708</v>
       </c>
       <c r="Z3" t="n">
-        <v>123.67</v>
+        <v>125.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.38</v>
+        <v>15.82</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.513643863094118</v>
@@ -796,112 +796,112 @@
         <v>114.9918244005745</v>
       </c>
       <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.074884942189992</v>
+        <v>1.135425767027671</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>1681.48</v>
+        <v>1665.917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8564000000000001</v>
+        <v>1.4098</v>
       </c>
       <c r="I4" t="n">
-        <v>1495.116653333333</v>
+        <v>1491.211710526316</v>
       </c>
       <c r="J4" t="n">
-        <v>114.7173468953014</v>
+        <v>118.1110692189767</v>
       </c>
       <c r="K4" t="n">
-        <v>107.4244639502166</v>
+        <v>110.4075801109533</v>
       </c>
       <c r="L4" t="n">
-        <v>7.292882945084827</v>
+        <v>7.703489108023413</v>
       </c>
       <c r="M4" t="n">
-        <v>116.2858247592205</v>
+        <v>120.0399163923804</v>
       </c>
       <c r="N4" t="n">
-        <v>106.9469613825711</v>
+        <v>110.2799586460739</v>
       </c>
       <c r="O4" t="n">
-        <v>9.338863376649558</v>
+        <v>9.759957746306444</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5459977134717223</v>
+        <v>0.5529664693136956</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1230712772744636</v>
+        <v>0.103017238538334</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3000991914852677</v>
+        <v>0.2911945402038768</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5639624130671045</v>
+        <v>0.5591970231378005</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2959223958437266</v>
+        <v>0.2129312584950386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3458162779405154</v>
+        <v>0.4644885152262388</v>
       </c>
       <c r="V4" t="n">
-        <v>102.2258916666666</v>
+        <v>97.13762426900584</v>
       </c>
       <c r="W4" t="n">
-        <v>117.34</v>
+        <v>114.9115497076024</v>
       </c>
       <c r="X4" t="n">
-        <v>7.764166666666666</v>
+        <v>7.911915204678362</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5823861715356856</v>
+        <v>0.5832252038070996</v>
       </c>
       <c r="Z4" t="n">
-        <v>118.13</v>
+        <v>116.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.6</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.549391602834736</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC4" t="n">
-        <v>112.5216901085732</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD4" t="n">
-        <v>110.9722985057385</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -913,103 +913,103 @@
         <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1376277155366194</v>
+        <v>1.342029503725302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46113</v>
+        <v>46116</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>1660.943</v>
+        <v>1683.544</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3374</v>
+        <v>0.9001</v>
       </c>
       <c r="I5" t="n">
-        <v>1490.646053333333</v>
+        <v>1496.221131578947</v>
       </c>
       <c r="J5" t="n">
-        <v>117.9432994945024</v>
+        <v>115.0309937585101</v>
       </c>
       <c r="K5" t="n">
-        <v>110.7303915184354</v>
+        <v>107.3689317915697</v>
       </c>
       <c r="L5" t="n">
-        <v>7.212907976067041</v>
+        <v>7.662061966940354</v>
       </c>
       <c r="M5" t="n">
-        <v>117.1335655402602</v>
+        <v>117.5361602685391</v>
       </c>
       <c r="N5" t="n">
-        <v>110.887503750448</v>
+        <v>104.6279607731459</v>
       </c>
       <c r="O5" t="n">
-        <v>6.246061789812174</v>
+        <v>12.90819949539315</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5522146110438987</v>
+        <v>0.5464672750475887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1031479733089335</v>
+        <v>0.12283425981663</v>
       </c>
       <c r="R5" t="n">
-        <v>0.290819625906369</v>
+        <v>0.3044040214423252</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5433248038752407</v>
+        <v>0.5656548199416427</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2128439213511577</v>
+        <v>0.2947027455367071</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4657637091997578</v>
+        <v>0.3466883279881908</v>
       </c>
       <c r="V5" t="n">
-        <v>97.27819428571429</v>
+        <v>101.9686046511628</v>
       </c>
       <c r="W5" t="n">
-        <v>114.904</v>
+        <v>117.3880048959608</v>
       </c>
       <c r="X5" t="n">
-        <v>7.392</v>
+        <v>8.16891064871481</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5822628956384461</v>
+        <v>0.5828557710124233</v>
       </c>
       <c r="Z5" t="n">
-        <v>114.24</v>
+        <v>118.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.75</v>
+        <v>11.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.220352523846751</v>
+        <v>1.549391602834736</v>
       </c>
       <c r="AC5" t="n">
-        <v>117.8084737243045</v>
+        <v>112.5216901085732</v>
       </c>
       <c r="AD5" t="n">
-        <v>108.5881212004577</v>
+        <v>110.9722985057385</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.244010112913885</v>
+        <v>-0.04852226975727989</v>
       </c>
     </row>
     <row r="6">
@@ -1039,76 +1039,76 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>1647.336</v>
+        <v>1648.941</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3741</v>
+        <v>-0.991</v>
       </c>
       <c r="I6" t="n">
-        <v>1490.750933333333</v>
+        <v>1489.289578947368</v>
       </c>
       <c r="J6" t="n">
-        <v>117.6349842737596</v>
+        <v>117.9706699467943</v>
       </c>
       <c r="K6" t="n">
-        <v>111.2198305782562</v>
+        <v>110.6589943550442</v>
       </c>
       <c r="L6" t="n">
-        <v>6.415153695503457</v>
+        <v>7.31167559175005</v>
       </c>
       <c r="M6" t="n">
-        <v>120.7779352140565</v>
+        <v>120.7898645952503</v>
       </c>
       <c r="N6" t="n">
-        <v>115.1380970877481</v>
+        <v>112.6273827428719</v>
       </c>
       <c r="O6" t="n">
-        <v>5.639838126308488</v>
+        <v>8.16248185237837</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5554936792720591</v>
+        <v>0.5560310730564268</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1169365570451051</v>
+        <v>0.115112667568659</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2995517512045568</v>
+        <v>0.2964438486720482</v>
       </c>
       <c r="S6" t="n">
-        <v>0.562695735099172</v>
+        <v>0.5621486391416562</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2392035349468124</v>
+        <v>0.2405725860638662</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4284171924531922</v>
+        <v>0.4292181614417677</v>
       </c>
       <c r="V6" t="n">
-        <v>99.34934736842106</v>
+        <v>99.37570412517782</v>
       </c>
       <c r="W6" t="n">
-        <v>116.6670175438597</v>
+        <v>117.0142247510669</v>
       </c>
       <c r="X6" t="n">
-        <v>6.053684210526316</v>
+        <v>6.906116642958748</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5886513899888971</v>
+        <v>0.5895093395094154</v>
       </c>
       <c r="Z6" t="n">
-        <v>115.33</v>
+        <v>115.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.96</v>
+        <v>8.32</v>
       </c>
       <c r="AB6" t="n">
         <v>2.775420617465777</v>
@@ -1120,232 +1120,232 @@
         <v>112.335295999638</v>
       </c>
       <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6697776458056601</v>
+        <v>1.133916491181493</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>1599.001</v>
+        <v>1585.829</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2726</v>
+        <v>1.0188</v>
       </c>
       <c r="I7" t="n">
-        <v>1501.582552631579</v>
+        <v>1496.597447368421</v>
       </c>
       <c r="J7" t="n">
-        <v>119.9302232467695</v>
+        <v>115.9157194813752</v>
       </c>
       <c r="K7" t="n">
-        <v>115.1280532122343</v>
+        <v>110.9122626703685</v>
       </c>
       <c r="L7" t="n">
-        <v>4.802170034535283</v>
+        <v>5.003456811006686</v>
       </c>
       <c r="M7" t="n">
-        <v>122.8283988323978</v>
+        <v>120.3886237542536</v>
       </c>
       <c r="N7" t="n">
-        <v>114.5298021973138</v>
+        <v>110.698878641257</v>
       </c>
       <c r="O7" t="n">
-        <v>8.298596635084081</v>
+        <v>9.689745112996638</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5763058782599089</v>
+        <v>0.5452221018608326</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1099122727259536</v>
+        <v>0.1260276341667428</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2331833158135433</v>
+        <v>0.3433319978584573</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5969146242792409</v>
+        <v>0.5696540530569422</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3036550397177876</v>
+        <v>0.2641337604909269</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4081594209280318</v>
+        <v>0.350408669191881</v>
       </c>
       <c r="V7" t="n">
-        <v>101.3301412066752</v>
+        <v>99.25412066752246</v>
       </c>
       <c r="W7" t="n">
-        <v>121.4762516046213</v>
+        <v>115.0449293966624</v>
       </c>
       <c r="X7" t="n">
-        <v>4.874197689345315</v>
+        <v>5.206675224646983</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6161378401454218</v>
+        <v>0.578235336790496</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.3</v>
+        <v>118.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.722616812266775</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC7" t="n">
-        <v>116.5392386763017</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD7" t="n">
-        <v>113.8166218640349</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.625701230675739</v>
+        <v>0.6899162431082604</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46113</v>
+        <v>46116</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>1584.828</v>
+        <v>1600.377</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1629</v>
+        <v>1.6841</v>
       </c>
       <c r="I8" t="n">
-        <v>1497.981493333333</v>
+        <v>1499.056220779221</v>
       </c>
       <c r="J8" t="n">
-        <v>115.6583684984793</v>
+        <v>120.0434871013276</v>
       </c>
       <c r="K8" t="n">
-        <v>111.1578191183936</v>
+        <v>115.3455176711199</v>
       </c>
       <c r="L8" t="n">
-        <v>4.500549380085617</v>
+        <v>4.69796943020774</v>
       </c>
       <c r="M8" t="n">
-        <v>118.4645138426517</v>
+        <v>122.748813923288</v>
       </c>
       <c r="N8" t="n">
-        <v>111.5640511951537</v>
+        <v>114.5007062279897</v>
       </c>
       <c r="O8" t="n">
-        <v>6.900462647497992</v>
+        <v>8.248107695298286</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5433369960177337</v>
+        <v>0.5764441724580596</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1262942730836234</v>
+        <v>0.1082343933699723</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3446208856598313</v>
+        <v>0.2310408831414184</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5568142229719847</v>
+        <v>0.5979847670077997</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2624683941816954</v>
+        <v>0.3007825007792502</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3520606583910677</v>
+        <v>0.4092786877500528</v>
       </c>
       <c r="V8" t="n">
-        <v>99.086</v>
+        <v>101.520586270872</v>
       </c>
       <c r="W8" t="n">
-        <v>114.476</v>
+        <v>121.7944341372913</v>
       </c>
       <c r="X8" t="n">
-        <v>4.505000000000001</v>
+        <v>4.699814471243043</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5765287526009019</v>
+        <v>0.6160305043387976</v>
       </c>
       <c r="Z8" t="n">
-        <v>115.49</v>
+        <v>127.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.82</v>
+        <v>8.479999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.413694058608522</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC8" t="n">
-        <v>112.3850185369902</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD8" t="n">
-        <v>108.9713244783817</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.622974570303663</v>
+        <v>1.642995696320874</v>
       </c>
     </row>
     <row r="9">
@@ -1453,223 +1453,223 @@
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.570510599707363</v>
+        <v>0.8573136836434867</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1579.057</v>
+        <v>1586.524</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8065</v>
+        <v>1.4464</v>
       </c>
       <c r="I10" t="n">
-        <v>1500.461506666667</v>
+        <v>1494.794402597402</v>
       </c>
       <c r="J10" t="n">
-        <v>114.5510091728242</v>
+        <v>116.3669266270436</v>
       </c>
       <c r="K10" t="n">
-        <v>110.6393014336458</v>
+        <v>112.3490667342127</v>
       </c>
       <c r="L10" t="n">
-        <v>3.911707739178512</v>
+        <v>4.017859892830965</v>
       </c>
       <c r="M10" t="n">
-        <v>109.9760628138808</v>
+        <v>121.8413954266828</v>
       </c>
       <c r="N10" t="n">
-        <v>108.5662251088618</v>
+        <v>108.3940566068545</v>
       </c>
       <c r="O10" t="n">
-        <v>1.40983770501907</v>
+        <v>13.44733881982839</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5580554349269832</v>
+        <v>0.5552588991379335</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1246675148687783</v>
+        <v>0.1266827779873118</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2542267892037883</v>
+        <v>0.3039189967089364</v>
       </c>
       <c r="S10" t="n">
-        <v>0.543141722363614</v>
+        <v>0.5815656479262545</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2911943806214223</v>
+        <v>0.247510518858991</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4202932805961634</v>
+        <v>0.4844534904519965</v>
       </c>
       <c r="V10" t="n">
-        <v>103.0096</v>
+        <v>99.68479338842975</v>
       </c>
       <c r="W10" t="n">
-        <v>117.6495238095238</v>
+        <v>116.62062180244</v>
       </c>
       <c r="X10" t="n">
-        <v>3.587428571428572</v>
+        <v>5.371507280598189</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5917326719248989</v>
+        <v>0.5918599541037188</v>
       </c>
       <c r="Z10" t="n">
-        <v>114.12</v>
+        <v>120.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.74</v>
+        <v>15.24</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.250350764022217</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC10" t="n">
-        <v>114.1383305986051</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD10" t="n">
-        <v>109.8879798345829</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9803930014492847</v>
+        <v>0.5158824558467822</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>1582.953</v>
+        <v>1576.992</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7598</v>
+        <v>0.4902</v>
       </c>
       <c r="I11" t="n">
-        <v>1494.619</v>
+        <v>1502.843328947368</v>
       </c>
       <c r="J11" t="n">
-        <v>116.1936704899855</v>
+        <v>114.194094218518</v>
       </c>
       <c r="K11" t="n">
-        <v>112.3272523065444</v>
+        <v>110.7439747596146</v>
       </c>
       <c r="L11" t="n">
-        <v>3.866418183441092</v>
+        <v>3.450119458903405</v>
       </c>
       <c r="M11" t="n">
-        <v>120.8701470534281</v>
+        <v>107.321562320982</v>
       </c>
       <c r="N11" t="n">
-        <v>108.8115959964366</v>
+        <v>105.2637910007372</v>
       </c>
       <c r="O11" t="n">
-        <v>12.05855105699137</v>
+        <v>2.057771320244798</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5548254208961517</v>
+        <v>0.5555566428326241</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1274390415058646</v>
+        <v>0.1239187544974006</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3057836610503921</v>
+        <v>0.2556689823014835</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5777780135176525</v>
+        <v>0.5223269540097021</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2487142834544319</v>
+        <v>0.2886138601341515</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4844422156465903</v>
+        <v>0.4193944574858675</v>
       </c>
       <c r="V11" t="n">
-        <v>99.6992105263158</v>
+        <v>103.0392397660818</v>
       </c>
       <c r="W11" t="n">
-        <v>116.4329769736842</v>
+        <v>117.3914473684211</v>
       </c>
       <c r="X11" t="n">
-        <v>5.162828947368421</v>
+        <v>3.286915204678363</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5915768055953945</v>
+        <v>0.5888647949106643</v>
       </c>
       <c r="Z11" t="n">
-        <v>119.53</v>
+        <v>111.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>14.06</v>
+        <v>3.839999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>-10.13717477219789</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC11" t="n">
-        <v>104.7204689341547</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD11" t="n">
-        <v>114.8576437063525</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
       <c r="AG11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4622750115775418</v>
+        <v>0.9635141539133494</v>
       </c>
     </row>
     <row r="12">
@@ -1687,76 +1687,76 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1521.635</v>
+        <v>1529.831</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2789</v>
+        <v>2.5778</v>
       </c>
       <c r="I12" t="n">
-        <v>1486.017460526316</v>
+        <v>1486.427545454545</v>
       </c>
       <c r="J12" t="n">
-        <v>113.9707468270876</v>
+        <v>114.4632733608845</v>
       </c>
       <c r="K12" t="n">
-        <v>111.5643938317927</v>
+        <v>111.6189629785043</v>
       </c>
       <c r="L12" t="n">
-        <v>2.406352995294905</v>
+        <v>2.844310382380152</v>
       </c>
       <c r="M12" t="n">
-        <v>118.3840893776426</v>
+        <v>119.6784079793296</v>
       </c>
       <c r="N12" t="n">
-        <v>106.7715599768774</v>
+        <v>107.2761797473664</v>
       </c>
       <c r="O12" t="n">
-        <v>11.61252940076515</v>
+        <v>12.40222823196334</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5539635872810795</v>
+        <v>0.5569425538743025</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1167066689761772</v>
+        <v>0.1163580958759639</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2407859497037374</v>
+        <v>0.2395355623524018</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5691156447894506</v>
+        <v>0.579811614786908</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2385889869815702</v>
+        <v>0.2387114169812871</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4284885902688828</v>
+        <v>0.4289383837201488</v>
       </c>
       <c r="V12" t="n">
-        <v>103.9297960526316</v>
+        <v>103.8489393939394</v>
       </c>
       <c r="W12" t="n">
-        <v>118.4667763157894</v>
+        <v>118.9545454545454</v>
       </c>
       <c r="X12" t="n">
-        <v>2.623684210526316</v>
+        <v>3.17929292929293</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5848545178709627</v>
+        <v>0.5875932947369503</v>
       </c>
       <c r="Z12" t="n">
-        <v>122.35</v>
+        <v>124.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.63</v>
+        <v>12.67</v>
       </c>
       <c r="AB12" t="n">
         <v>-0.981113782848854</v>
@@ -1777,103 +1777,103 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.6777650584512972</v>
+        <v>0.7480774026203251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>1569.196</v>
+        <v>1510.535</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4652</v>
+        <v>-0.0224</v>
       </c>
       <c r="I13" t="n">
-        <v>1492.221013157895</v>
+        <v>1495.603684210526</v>
       </c>
       <c r="J13" t="n">
-        <v>116.4194087094877</v>
+        <v>113.7125816706429</v>
       </c>
       <c r="K13" t="n">
-        <v>114.5045932890717</v>
+        <v>111.2179325407423</v>
       </c>
       <c r="L13" t="n">
-        <v>1.914815420415977</v>
+        <v>2.494649129900552</v>
       </c>
       <c r="M13" t="n">
-        <v>118.0663825506114</v>
+        <v>119.3973070489987</v>
       </c>
       <c r="N13" t="n">
-        <v>112.2261586960545</v>
+        <v>113.3328387367582</v>
       </c>
       <c r="O13" t="n">
-        <v>5.840223854556848</v>
+        <v>6.064468312240596</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5712291588266269</v>
+        <v>0.5452656509846545</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1256972656006453</v>
+        <v>0.1157249163737343</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2376870464441672</v>
+        <v>0.2569178400193068</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5768626394342689</v>
+        <v>0.5849661390500662</v>
       </c>
       <c r="T13" t="n">
-        <v>0.324642865172263</v>
+        <v>0.2689314969160542</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3971457498802721</v>
+        <v>0.3658961111401283</v>
       </c>
       <c r="V13" t="n">
-        <v>100.3483313397129</v>
+        <v>100.8163881578948</v>
       </c>
       <c r="W13" t="n">
-        <v>116.3427033492823</v>
+        <v>114.6963815789473</v>
       </c>
       <c r="X13" t="n">
-        <v>1.093002392344498</v>
+        <v>2.801315789473685</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6082332378082067</v>
+        <v>0.5796257291996354</v>
       </c>
       <c r="Z13" t="n">
-        <v>117.6</v>
+        <v>120.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.989999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.827913300592181</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC13" t="n">
-        <v>114.1496737878887</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD13" t="n">
-        <v>112.3217604872965</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3006139480902592</v>
+        <v>0.4396779170072456</v>
       </c>
     </row>
     <row r="14">
@@ -1903,76 +1903,76 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46113</v>
+        <v>46116</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>1533.636</v>
+        <v>1528.663</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.7113</v>
+        <v>-2.1519</v>
       </c>
       <c r="I14" t="n">
-        <v>1505.278789473684</v>
+        <v>1507.300402597403</v>
       </c>
       <c r="J14" t="n">
-        <v>113.984454965129</v>
+        <v>114.5186265302597</v>
       </c>
       <c r="K14" t="n">
-        <v>112.2586812931816</v>
+        <v>112.3108720562382</v>
       </c>
       <c r="L14" t="n">
-        <v>1.725773671947434</v>
+        <v>2.207754474021498</v>
       </c>
       <c r="M14" t="n">
-        <v>115.7806766419599</v>
+        <v>118.0016236097122</v>
       </c>
       <c r="N14" t="n">
-        <v>122.3318716431754</v>
+        <v>124.1690508750568</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.551195001215493</v>
+        <v>-6.16742726534464</v>
       </c>
       <c r="P14" t="n">
-        <v>0.537712963923746</v>
+        <v>0.541255885793396</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1112415592742477</v>
+        <v>0.111679216630442</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2519334999041863</v>
+        <v>0.2525608849200953</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5383739776913999</v>
+        <v>0.5556618027941286</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2719616798845572</v>
+        <v>0.2751033216200673</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4063485241097721</v>
+        <v>0.4058415614538717</v>
       </c>
       <c r="V14" t="n">
-        <v>105.665911872705</v>
+        <v>105.8480047225502</v>
       </c>
       <c r="W14" t="n">
-        <v>120.4406364749082</v>
+        <v>121.3097205824478</v>
       </c>
       <c r="X14" t="n">
-        <v>1.946144430844553</v>
+        <v>2.575364029909485</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5760248946858337</v>
+        <v>0.579518941255972</v>
       </c>
       <c r="Z14" t="n">
-        <v>119.01</v>
+        <v>122.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>-8.280000000000001</v>
+        <v>-7.129999999999999</v>
       </c>
       <c r="AB14" t="n">
         <v>-1.094669144490311</v>
@@ -1984,30 +1984,30 @@
         <v>112.7751239908198</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1037886042391138</v>
+        <v>0.14984396897703</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612746</v>
+        <v>1610612747</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2017,79 +2017,79 @@
         <v>46114</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>1555.38</v>
+        <v>1569.196</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4326</v>
+        <v>2.4652</v>
       </c>
       <c r="I15" t="n">
-        <v>1495.794473684211</v>
+        <v>1492.221013157895</v>
       </c>
       <c r="J15" t="n">
-        <v>115.5308680528053</v>
+        <v>116.4194087094877</v>
       </c>
       <c r="K15" t="n">
-        <v>113.8324266773286</v>
+        <v>114.5045932890717</v>
       </c>
       <c r="L15" t="n">
-        <v>1.698441375476713</v>
+        <v>1.914815420415977</v>
       </c>
       <c r="M15" t="n">
-        <v>116.8446816593703</v>
+        <v>118.0663825506114</v>
       </c>
       <c r="N15" t="n">
-        <v>114.0963488752868</v>
+        <v>112.2261586960545</v>
       </c>
       <c r="O15" t="n">
-        <v>2.748332784083542</v>
+        <v>5.840223854556848</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5588537995811402</v>
+        <v>0.5712291588266269</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1249793680202745</v>
+        <v>0.1256972656006453</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2346421905870804</v>
+        <v>0.2376870464441672</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5730362557347206</v>
+        <v>0.5768626394342689</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3010272971365625</v>
+        <v>0.324642865172263</v>
       </c>
       <c r="U15" t="n">
-        <v>0.401287615049342</v>
+        <v>0.3971457498802721</v>
       </c>
       <c r="V15" t="n">
-        <v>98.74230769230769</v>
+        <v>100.3483313397129</v>
       </c>
       <c r="W15" t="n">
-        <v>113.4871794871795</v>
+        <v>116.3427033492823</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8205128205128207</v>
+        <v>1.093002392344498</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6023923312009145</v>
+        <v>0.6082332378082067</v>
       </c>
       <c r="Z15" t="n">
-        <v>114.57</v>
+        <v>117.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.34</v>
+        <v>2.989999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.815266446541752</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC15" t="n">
-        <v>113.8106821492749</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD15" t="n">
-        <v>108.9954157027332</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2101,115 +2101,115 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.4442511610787055</v>
+        <v>-0.4206675461378738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F16" t="n">
         <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>1513.967</v>
+        <v>1555.38</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5175</v>
+        <v>0.4326</v>
       </c>
       <c r="I16" t="n">
-        <v>1498.068306666667</v>
+        <v>1495.794473684211</v>
       </c>
       <c r="J16" t="n">
-        <v>113.3795012307266</v>
+        <v>115.5308680528053</v>
       </c>
       <c r="K16" t="n">
-        <v>111.8525989203726</v>
+        <v>113.8324266773286</v>
       </c>
       <c r="L16" t="n">
-        <v>1.526902310354019</v>
+        <v>1.698441375476713</v>
       </c>
       <c r="M16" t="n">
-        <v>119.0008012020616</v>
+        <v>116.8446816593703</v>
       </c>
       <c r="N16" t="n">
-        <v>115.837254644371</v>
+        <v>114.0963488752868</v>
       </c>
       <c r="O16" t="n">
-        <v>3.163546557690581</v>
+        <v>2.748332784083542</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5451942484259756</v>
+        <v>0.5588537995811402</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.115499508690161</v>
+        <v>0.1249793680202745</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2517852498832425</v>
+        <v>0.2346421905870804</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5887321211300018</v>
+        <v>0.5730362557347206</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2652380958826372</v>
+        <v>0.3010272971365625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3670760629041485</v>
+        <v>0.401287615049342</v>
       </c>
       <c r="V16" t="n">
-        <v>100.7690256410256</v>
+        <v>98.74230769230769</v>
       </c>
       <c r="W16" t="n">
-        <v>114.3634188034189</v>
+        <v>113.4871794871795</v>
       </c>
       <c r="X16" t="n">
-        <v>1.925470085470086</v>
+        <v>0.8205128205128207</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5790750032406927</v>
+        <v>0.6023923312009145</v>
       </c>
       <c r="Z16" t="n">
-        <v>119.86</v>
+        <v>114.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.05</v>
+        <v>1.34</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.536933640611859</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC16" t="n">
-        <v>108.3888858603967</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD16" t="n">
-        <v>112.9258195010085</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3959969550852299</v>
+        <v>0.4812833980178786</v>
       </c>
     </row>
     <row r="17">
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.05741170207757666</v>
+        <v>0.1179282646283339</v>
       </c>
     </row>
     <row r="18">
@@ -2335,76 +2335,76 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46113</v>
+        <v>46116</v>
       </c>
       <c r="F18" t="n">
         <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>1472.215</v>
+        <v>1478.324</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7292999999999999</v>
+        <v>1.0942</v>
       </c>
       <c r="I18" t="n">
-        <v>1498.929866666667</v>
+        <v>1496.806012987013</v>
       </c>
       <c r="J18" t="n">
-        <v>113.9844315618287</v>
+        <v>113.2493428398411</v>
       </c>
       <c r="K18" t="n">
-        <v>113.4156275902304</v>
+        <v>113.3819868113484</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5688039715983007</v>
+        <v>-0.1326439715072333</v>
       </c>
       <c r="M18" t="n">
-        <v>115.4172867081167</v>
+        <v>115.7695689062811</v>
       </c>
       <c r="N18" t="n">
-        <v>114.8869612042637</v>
+        <v>115.1084160252666</v>
       </c>
       <c r="O18" t="n">
-        <v>0.530325503852987</v>
+        <v>0.6611528810144534</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5351457441619317</v>
+        <v>0.532136619691546</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1131602468595699</v>
+        <v>0.1146932720129836</v>
       </c>
       <c r="R18" t="n">
-        <v>0.26060149308536</v>
+        <v>0.2597878208196118</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5464156884276465</v>
+        <v>0.5493479408686979</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2780537193113485</v>
+        <v>0.2793796375868643</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3933920893953691</v>
+        <v>0.3922524406850108</v>
       </c>
       <c r="V18" t="n">
-        <v>102.8899298245614</v>
+        <v>102.5863157894737</v>
       </c>
       <c r="W18" t="n">
-        <v>117.0515789473684</v>
+        <v>115.9258373205741</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1505263157894736</v>
+        <v>-0.5926179084073822</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5770440496152104</v>
+        <v>0.5744029824631754</v>
       </c>
       <c r="Z18" t="n">
-        <v>120.6</v>
+        <v>119.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
         <v>-6.382503892565079</v>
@@ -2416,138 +2416,138 @@
         <v>116.2614936572104</v>
       </c>
       <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1</v>
       </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5833372772122284</v>
+        <v>0.6764672843598126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>1474.991</v>
+        <v>1509.398</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0881</v>
+        <v>-3.4348</v>
       </c>
       <c r="I19" t="n">
-        <v>1506.411710526316</v>
+        <v>1490.914438356164</v>
       </c>
       <c r="J19" t="n">
-        <v>112.4327589050653</v>
+        <v>112.6547736710958</v>
       </c>
       <c r="K19" t="n">
-        <v>112.9572150915985</v>
+        <v>112.835522549035</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5244561865333028</v>
+        <v>-0.1807488779392295</v>
       </c>
       <c r="M19" t="n">
-        <v>109.9734404020988</v>
+        <v>109.5197158773527</v>
       </c>
       <c r="N19" t="n">
-        <v>116.3520023932743</v>
+        <v>120.6820638521788</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.378561991175575</v>
+        <v>-11.16234797482613</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498925907421595</v>
+        <v>0.5335801995109656</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1319571408514362</v>
+        <v>0.1189625874505289</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2563491495441706</v>
+        <v>0.2423104787828728</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5544058001170727</v>
+        <v>0.5254418415651094</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2386765745649697</v>
+        <v>0.3192610891449315</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4997351196251281</v>
+        <v>0.3867859130039036</v>
       </c>
       <c r="V19" t="n">
-        <v>102.0110453216374</v>
+        <v>102.6665675146771</v>
       </c>
       <c r="W19" t="n">
-        <v>114.7609649122807</v>
+        <v>115.7769080234834</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3991228070175439</v>
+        <v>0.473972602739726</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5837245340717334</v>
+        <v>0.5796255413826368</v>
       </c>
       <c r="Z19" t="n">
-        <v>112.35</v>
+        <v>114.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>-6.91</v>
+        <v>-9.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.402868486532558</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC19" t="n">
-        <v>112.5227430890375</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD19" t="n">
-        <v>110.1198746025049</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1</v>
       </c>
       <c r="AG19" t="n">
         <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.294446285740992</v>
+        <v>-0.1290390982058583</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2557,739 +2557,739 @@
         <v>46114</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>1467.509</v>
+        <v>1474.991</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6738</v>
+        <v>-1.0881</v>
       </c>
       <c r="I20" t="n">
-        <v>1503.88051948052</v>
+        <v>1506.411710526316</v>
       </c>
       <c r="J20" t="n">
-        <v>111.4731251846435</v>
+        <v>112.4327589050653</v>
       </c>
       <c r="K20" t="n">
-        <v>112.2064478325931</v>
+        <v>112.9572150915985</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7333226479496043</v>
+        <v>-0.5244561865333028</v>
       </c>
       <c r="M20" t="n">
-        <v>113.9996153916357</v>
+        <v>109.9734404020988</v>
       </c>
       <c r="N20" t="n">
-        <v>103.491548713392</v>
+        <v>116.3520023932743</v>
       </c>
       <c r="O20" t="n">
-        <v>10.50806667824366</v>
+        <v>-6.378561991175575</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5340566350449895</v>
+        <v>0.5498925907421595</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.140574133685937</v>
+        <v>0.1319571408514362</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3116283493387423</v>
+        <v>0.2563491495441706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5462692030856715</v>
+        <v>0.5544058001170727</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2844703452452553</v>
+        <v>0.2386765745649697</v>
       </c>
       <c r="U20" t="n">
-        <v>0.470120992747168</v>
+        <v>0.4997351196251281</v>
       </c>
       <c r="V20" t="n">
-        <v>103.3384809130263</v>
+        <v>102.0110453216374</v>
       </c>
       <c r="W20" t="n">
-        <v>115.4057457693821</v>
+        <v>114.7609649122807</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2786304604486423</v>
+        <v>-0.3991228070175439</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5707724847405173</v>
+        <v>0.5837245340717334</v>
       </c>
       <c r="Z20" t="n">
-        <v>116.02</v>
+        <v>112.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.37</v>
+        <v>-6.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.840928550668963</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC20" t="n">
-        <v>109.2995408403883</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD20" t="n">
-        <v>113.1404693910572</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1982377175155782</v>
+        <v>-0.2308641524389182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>1517.594</v>
+        <v>1467.509</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5061</v>
+        <v>1.6738</v>
       </c>
       <c r="I21" t="n">
-        <v>1490.487763888889</v>
+        <v>1503.88051948052</v>
       </c>
       <c r="J21" t="n">
-        <v>111.9487583735943</v>
+        <v>111.4731251846435</v>
       </c>
       <c r="K21" t="n">
-        <v>112.852901991738</v>
+        <v>112.2064478325931</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9041436181436305</v>
+        <v>-0.7333226479496043</v>
       </c>
       <c r="M21" t="n">
-        <v>107.8715998687121</v>
+        <v>113.9996153916357</v>
       </c>
       <c r="N21" t="n">
-        <v>120.5781407699248</v>
+        <v>103.491548713392</v>
       </c>
       <c r="O21" t="n">
-        <v>-12.7065409012127</v>
+        <v>10.50806667824366</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5290344421716072</v>
+        <v>0.5340566350449895</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1189425539863543</v>
+        <v>0.140574133685937</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2428295425858887</v>
+        <v>0.3116283493387423</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5150248708953298</v>
+        <v>0.5462692030856715</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3161902200269517</v>
+        <v>0.2844703452452553</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3887147877557122</v>
+        <v>0.470120992747168</v>
       </c>
       <c r="V21" t="n">
-        <v>102.5710810810811</v>
+        <v>103.3384809130263</v>
       </c>
       <c r="W21" t="n">
-        <v>114.9324324324324</v>
+        <v>115.4057457693821</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2297297297297297</v>
+        <v>-0.2786304604486423</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5753604355976911</v>
+        <v>0.5707724847405173</v>
       </c>
       <c r="Z21" t="n">
-        <v>112.34</v>
+        <v>116.02</v>
       </c>
       <c r="AA21" t="n">
-        <v>-10.46</v>
+        <v>11.37</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.5231111597400365</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC21" t="n">
-        <v>107.6152962364644</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD21" t="n">
-        <v>108.1384073962044</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.08494785297712305</v>
+        <v>-0.1525171291645537</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F22" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>1379.04</v>
+        <v>1374.163</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8052</v>
+        <v>0.0561</v>
       </c>
       <c r="I22" t="n">
-        <v>1498.586533333333</v>
+        <v>1508.346064935065</v>
       </c>
       <c r="J22" t="n">
-        <v>111.6466488854735</v>
+        <v>112.0847060341278</v>
       </c>
       <c r="K22" t="n">
-        <v>115.9903649027076</v>
+        <v>116.4267390859726</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.343716017234031</v>
+        <v>-4.342033051844718</v>
       </c>
       <c r="M22" t="n">
-        <v>111.997286104648</v>
+        <v>111.1122711135355</v>
       </c>
       <c r="N22" t="n">
-        <v>121.0023674622528</v>
+        <v>117.1696317867927</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.005081357604777</v>
+        <v>-6.057360673257184</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5496681499284022</v>
+        <v>0.5286202097307927</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1268731669476357</v>
+        <v>0.1175422585620949</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2296270604637786</v>
+        <v>0.2653158953191943</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5541231651861768</v>
+        <v>0.5345571135379749</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2469650628214027</v>
+        <v>0.2829825312227077</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4455523571143614</v>
+        <v>0.3598838294658352</v>
       </c>
       <c r="V22" t="n">
-        <v>104.6596727272727</v>
+        <v>102.586985645933</v>
       </c>
       <c r="W22" t="n">
-        <v>116.5660606060606</v>
+        <v>114.9094326725906</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.057575757575758</v>
+        <v>-4.505809979494191</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5821111599703364</v>
+        <v>0.5687822021558822</v>
       </c>
       <c r="Z22" t="n">
-        <v>121.41</v>
+        <v>110.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>-9.01</v>
+        <v>-4.989999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.9433805425336231</v>
+        <v>-9.447870926461551</v>
       </c>
       <c r="AC22" t="n">
-        <v>112.5644270515903</v>
+        <v>108.3910194524218</v>
       </c>
       <c r="AD22" t="n">
-        <v>113.5078075941239</v>
+        <v>117.8388903788833</v>
       </c>
       <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1</v>
       </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3551665353312072</v>
+        <v>-0.02486963518620396</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612740</v>
+        <v>1610612741</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>1375.739</v>
+        <v>1375.148</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7695</v>
+        <v>-1.0399</v>
       </c>
       <c r="I23" t="n">
-        <v>1508.883394736842</v>
+        <v>1496.483473684211</v>
       </c>
       <c r="J23" t="n">
-        <v>111.9147963701947</v>
+        <v>111.1740010832762</v>
       </c>
       <c r="K23" t="n">
-        <v>116.476910660563</v>
+        <v>116.5653401475512</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.562114290368302</v>
+        <v>-5.391339064274999</v>
       </c>
       <c r="M23" t="n">
-        <v>111.3630347239127</v>
+        <v>109.4117213630724</v>
       </c>
       <c r="N23" t="n">
-        <v>116.5494897145978</v>
+        <v>121.1424228191247</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.186454990685206</v>
+        <v>-11.73070145605227</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5274744140557101</v>
+        <v>0.5480481532241219</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1181034499933678</v>
+        <v>0.1272667615832913</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2680315069823698</v>
+        <v>0.2273181295936215</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5368460745769359</v>
+        <v>0.5431866486370721</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2842388138380912</v>
+        <v>0.2491531694043016</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3574637764393076</v>
+        <v>0.4455304885923183</v>
       </c>
       <c r="V23" t="n">
-        <v>102.6282503556187</v>
+        <v>104.3996943972835</v>
       </c>
       <c r="W23" t="n">
-        <v>114.8335704125178</v>
+        <v>115.8132427843803</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.625889046941679</v>
+        <v>-6.052631578947369</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5676001493215278</v>
+        <v>0.5800944130596322</v>
       </c>
       <c r="Z23" t="n">
-        <v>111.67</v>
+        <v>118.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>-3.72</v>
+        <v>-11.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>-9.447870926461551</v>
+        <v>-0.9433805425336231</v>
       </c>
       <c r="AC23" t="n">
-        <v>108.3910194524218</v>
+        <v>112.5644270515903</v>
       </c>
       <c r="AD23" t="n">
-        <v>117.8388903788833</v>
+        <v>113.5078075941239</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2102233229535417</v>
+        <v>-0.3791700871226604</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>1379.688</v>
+        <v>1364.459</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7918</v>
+        <v>-1.3373</v>
       </c>
       <c r="I24" t="n">
-        <v>1495.164917808219</v>
+        <v>1504.191213333333</v>
       </c>
       <c r="J24" t="n">
-        <v>110.8475367280819</v>
+        <v>108.621885813086</v>
       </c>
       <c r="K24" t="n">
-        <v>116.1182130038252</v>
+        <v>114.581491420867</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.270676275743345</v>
+        <v>-5.95960560778096</v>
       </c>
       <c r="M24" t="n">
-        <v>107.6057654648695</v>
+        <v>109.5012694983384</v>
       </c>
       <c r="N24" t="n">
-        <v>124.1558169866645</v>
+        <v>120.547631738542</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.55005152179498</v>
+        <v>-11.04636224020363</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5364854383330634</v>
+        <v>0.5275768362878875</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1271719235378404</v>
+        <v>0.1234620287682866</v>
       </c>
       <c r="R24" t="n">
-        <v>0.24756723582568</v>
+        <v>0.229826291876405</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5306987152229944</v>
+        <v>0.5214033132386693</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2609564692037231</v>
+        <v>0.2897338328214157</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4308478934060112</v>
+        <v>0.3506143378622698</v>
       </c>
       <c r="V24" t="n">
-        <v>103.5728462709285</v>
+        <v>104.6422704761905</v>
       </c>
       <c r="W24" t="n">
-        <v>115.031202435312</v>
+        <v>113.8274285714286</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.753805175038051</v>
+        <v>-5.741333333333334</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5740063892441803</v>
+        <v>0.5640763761976483</v>
       </c>
       <c r="Z24" t="n">
-        <v>110.81</v>
+        <v>116.74</v>
       </c>
       <c r="AA24" t="n">
-        <v>-15.59</v>
+        <v>-12.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.575252351995317</v>
+        <v>-0.6658146557452705</v>
       </c>
       <c r="AC24" t="n">
-        <v>114.5419381230804</v>
+        <v>113.1126313914285</v>
       </c>
       <c r="AD24" t="n">
-        <v>110.9666857710851</v>
+        <v>113.7784460471737</v>
       </c>
       <c r="AE24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.35523365668851</v>
+        <v>-0.8473140882554058</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>1392.794</v>
+        <v>1378.083</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9178</v>
+        <v>-1.8783</v>
       </c>
       <c r="I25" t="n">
-        <v>1494.676133333333</v>
+        <v>1497.221283783784</v>
       </c>
       <c r="J25" t="n">
-        <v>111.2462406419491</v>
+        <v>110.176484725517</v>
       </c>
       <c r="K25" t="n">
-        <v>117.1873068154184</v>
+        <v>116.2085953752688</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.941066173469398</v>
+        <v>-6.032110649751728</v>
       </c>
       <c r="M25" t="n">
-        <v>109.8699173762595</v>
+        <v>105.9966155718154</v>
       </c>
       <c r="N25" t="n">
-        <v>123.1000876756754</v>
+        <v>124.2697657572009</v>
       </c>
       <c r="O25" t="n">
-        <v>-13.23017029941586</v>
+        <v>-18.27315018538551</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5645626067479678</v>
+        <v>0.53337579656797</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1321159774411719</v>
+        <v>0.1283766451860904</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2082057821899348</v>
+        <v>0.2494386908066895</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5677341548638143</v>
+        <v>0.5249738569769165</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2254461079656181</v>
+        <v>0.2602609301110664</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4519929170250186</v>
+        <v>0.431946386363751</v>
       </c>
       <c r="V25" t="n">
-        <v>99.57681616161616</v>
+        <v>103.6124762600438</v>
       </c>
       <c r="W25" t="n">
-        <v>110.6727272727273</v>
+        <v>114.4601899196494</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.025858585858586</v>
+        <v>-5.401022644265888</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5884534757256186</v>
+        <v>0.5706164763232952</v>
       </c>
       <c r="Z25" t="n">
-        <v>108.41</v>
+        <v>109.32</v>
       </c>
       <c r="AA25" t="n">
-        <v>-12.66</v>
+        <v>-17.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.809266556998161</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC25" t="n">
-        <v>114.2499905834389</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD25" t="n">
-        <v>112.4407240264407</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="n">
         <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.616485613857187</v>
+        <v>-1.251641804852336</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>1367.445</v>
+        <v>1391.794</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.236</v>
+        <v>-1.896</v>
       </c>
       <c r="I26" t="n">
-        <v>1505.736932432432</v>
+        <v>1495.862342105263</v>
       </c>
       <c r="J26" t="n">
-        <v>108.1628123718708</v>
+        <v>111.0527318681116</v>
       </c>
       <c r="K26" t="n">
-        <v>114.241379265655</v>
+        <v>117.5001999205299</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.078566893784112</v>
+        <v>-6.447468052418269</v>
       </c>
       <c r="M26" t="n">
-        <v>109.5706664969746</v>
+        <v>110.4628275846109</v>
       </c>
       <c r="N26" t="n">
-        <v>118.7865677055872</v>
+        <v>124.8693374323362</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.21590120861258</v>
+        <v>-14.40650984772529</v>
       </c>
       <c r="P26" t="n">
-        <v>0.52533166245338</v>
+        <v>0.5641236039947805</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1237952040717519</v>
+        <v>0.131961988852083</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2296991213980427</v>
+        <v>0.2052295935424117</v>
       </c>
       <c r="S26" t="n">
-        <v>0.520652570454289</v>
+        <v>0.5659582220372983</v>
       </c>
       <c r="T26" t="n">
-        <v>0.288706923016706</v>
+        <v>0.224595822057458</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3483646601866096</v>
+        <v>0.45475777658069</v>
       </c>
       <c r="V26" t="n">
-        <v>104.5411764705882</v>
+        <v>99.55556390977443</v>
       </c>
       <c r="W26" t="n">
-        <v>113.2046899841017</v>
+        <v>110.4022556390977</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.886724960254372</v>
+        <v>-6.644736842105263</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5617402691419118</v>
+        <v>0.5879979228649672</v>
       </c>
       <c r="Z26" t="n">
-        <v>115.83</v>
+        <v>108.47</v>
       </c>
       <c r="AA26" t="n">
-        <v>-10.59</v>
+        <v>-13.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.6658146557452705</v>
+        <v>1.809266556998161</v>
       </c>
       <c r="AC26" t="n">
-        <v>113.1126313914285</v>
+        <v>114.2499905834389</v>
       </c>
       <c r="AD26" t="n">
-        <v>113.7784460471737</v>
+        <v>112.4407240264407</v>
       </c>
       <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1</v>
-      </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.9235057473697733</v>
+        <v>-1.140797122074303</v>
       </c>
     </row>
     <row r="27">
@@ -3307,76 +3307,76 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>1338.754</v>
+        <v>1342.647</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.346</v>
+        <v>0.3231</v>
       </c>
       <c r="I27" t="n">
-        <v>1502.63128</v>
+        <v>1501.005078947368</v>
       </c>
       <c r="J27" t="n">
-        <v>109.7168549128822</v>
+        <v>109.5233955549887</v>
       </c>
       <c r="K27" t="n">
-        <v>116.8433985310214</v>
+        <v>117.298815517779</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.12654361813933</v>
+        <v>-7.775419962790352</v>
       </c>
       <c r="M27" t="n">
-        <v>118.9171734093284</v>
+        <v>118.6714447434109</v>
       </c>
       <c r="N27" t="n">
-        <v>122.0742567182238</v>
+        <v>122.5921264826182</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.157083308895318</v>
+        <v>-3.920681739207278</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5357845505631168</v>
+        <v>0.5346186920761387</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1211021796219608</v>
+        <v>0.1206367915977383</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2143633248927037</v>
+        <v>0.2149051861033622</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6049063678783739</v>
+        <v>0.605345654529305</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2535873769257557</v>
+        <v>0.2508071215125294</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4205294228691061</v>
+        <v>0.4189866512388939</v>
       </c>
       <c r="V27" t="n">
-        <v>103.2823365079365</v>
+        <v>103.0407336523126</v>
       </c>
       <c r="W27" t="n">
-        <v>112.9939682539682</v>
+        <v>112.5039872408294</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.747619047619049</v>
+        <v>-8.432216905901116</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5708527815450193</v>
+        <v>0.5691850805661083</v>
       </c>
       <c r="Z27" t="n">
-        <v>120.43</v>
+        <v>120.06</v>
       </c>
       <c r="AA27" t="n">
-        <v>-4.67</v>
+        <v>-5.61</v>
       </c>
       <c r="AB27" t="n">
         <v>2.960186837728194</v>
@@ -3388,7 +3388,7 @@
         <v>111.9328051119554</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.5507618313038203</v>
+        <v>-1.060416690374951</v>
       </c>
     </row>
     <row r="28">
@@ -3415,76 +3415,76 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G28" t="n">
-        <v>1307.055</v>
+        <v>1305.68</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0144</v>
+        <v>-1.1603</v>
       </c>
       <c r="I28" t="n">
-        <v>1511.801605263158</v>
+        <v>1512.934064935065</v>
       </c>
       <c r="J28" t="n">
-        <v>112.010452041258</v>
+        <v>111.8213086722742</v>
       </c>
       <c r="K28" t="n">
-        <v>119.9901278243179</v>
+        <v>120.305120084665</v>
       </c>
       <c r="L28" t="n">
-        <v>-7.979675783060011</v>
+        <v>-8.483811412390832</v>
       </c>
       <c r="M28" t="n">
-        <v>110.9783569526622</v>
+        <v>110.9449599040905</v>
       </c>
       <c r="N28" t="n">
-        <v>120.126243683934</v>
+        <v>121.6793035616746</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.1478867312718</v>
+        <v>-10.7343436575841</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5380082744551464</v>
+        <v>0.5364249413533397</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1279663446181419</v>
+        <v>0.1278002542318371</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2601605462032421</v>
+        <v>0.262224634450693</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5395462824183588</v>
+        <v>0.5342333056830422</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2836730110498208</v>
+        <v>0.2824590958759929</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4077012239107814</v>
+        <v>0.4045139466865198</v>
       </c>
       <c r="V28" t="n">
-        <v>104.7084615384615</v>
+        <v>104.6601333801334</v>
       </c>
       <c r="W28" t="n">
-        <v>117.3205128205129</v>
+        <v>117.018603018603</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.179487179487179</v>
+        <v>-8.816426816426816</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5775856118857268</v>
+        <v>0.5758543531051435</v>
       </c>
       <c r="Z28" t="n">
-        <v>116.82</v>
+        <v>115.99</v>
       </c>
       <c r="AA28" t="n">
-        <v>-11.02</v>
+        <v>-13.39</v>
       </c>
       <c r="AB28" t="n">
         <v>-9.725925288085115</v>
@@ -3505,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1.243309197052991</v>
+        <v>-1.174410343692028</v>
       </c>
     </row>
     <row r="29">
@@ -3523,76 +3523,76 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="F29" t="n">
         <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>1310.757</v>
+        <v>1314.189</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8026</v>
+        <v>-1.0161</v>
       </c>
       <c r="I29" t="n">
-        <v>1516.76152631579</v>
+        <v>1516.725233766234</v>
       </c>
       <c r="J29" t="n">
-        <v>109.6506485001995</v>
+        <v>109.6211015792705</v>
       </c>
       <c r="K29" t="n">
-        <v>118.8173637638446</v>
+        <v>118.6918248311824</v>
       </c>
       <c r="L29" t="n">
-        <v>-9.166715263645051</v>
+        <v>-9.070723251911787</v>
       </c>
       <c r="M29" t="n">
-        <v>114.2082428854661</v>
+        <v>114.1515055397331</v>
       </c>
       <c r="N29" t="n">
-        <v>122.8110160291269</v>
+        <v>122.3204372854018</v>
       </c>
       <c r="O29" t="n">
-        <v>-8.602773143660794</v>
+        <v>-8.168931745668655</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5237406401578811</v>
+        <v>0.5248969501101631</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1203218403332457</v>
+        <v>0.1205539458726043</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2575512976501724</v>
+        <v>0.2564032936867319</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5521994378100236</v>
+        <v>0.5505161830518606</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2573159643465087</v>
+        <v>0.2556206896387418</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3379416451810295</v>
+        <v>0.3384209412786616</v>
       </c>
       <c r="V29" t="n">
-        <v>101.6028324099723</v>
+        <v>101.6102665755298</v>
       </c>
       <c r="W29" t="n">
-        <v>111.0339335180056</v>
+        <v>111.0314422419686</v>
       </c>
       <c r="X29" t="n">
-        <v>-9.936288088642662</v>
+        <v>-9.808612440191386</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.5600176911920542</v>
+        <v>0.5605017116959584</v>
       </c>
       <c r="Z29" t="n">
-        <v>112.2</v>
+        <v>112.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>-9.460000000000001</v>
+        <v>-8.42</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.1619477822758719</v>
@@ -3604,7 +3604,7 @@
         <v>114.7058177516698</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.648485861400802</v>
+        <v>-1.540916347109895</v>
       </c>
     </row>
     <row r="30">
@@ -3631,76 +3631,76 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>1294.032</v>
+        <v>1291.513</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4447</v>
+        <v>-1.2614</v>
       </c>
       <c r="I30" t="n">
-        <v>1501.72304</v>
+        <v>1502.758697368421</v>
       </c>
       <c r="J30" t="n">
-        <v>106.5735229248656</v>
+        <v>106.715785404944</v>
       </c>
       <c r="K30" t="n">
-        <v>117.0749205821124</v>
+        <v>117.4424674719294</v>
       </c>
       <c r="L30" t="n">
-        <v>-10.50139765724669</v>
+        <v>-10.7266820669854</v>
       </c>
       <c r="M30" t="n">
-        <v>99.88338055761382</v>
+        <v>100.4385313723269</v>
       </c>
       <c r="N30" t="n">
-        <v>113.3443506278637</v>
+        <v>115.6048841702255</v>
       </c>
       <c r="O30" t="n">
-        <v>-13.46097007024982</v>
+        <v>-15.16635279789852</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5198137615037446</v>
+        <v>0.5223500941779544</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1383904577161692</v>
+        <v>0.1391814215447868</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2391442090549466</v>
+        <v>0.2365836763688505</v>
       </c>
       <c r="S30" t="n">
-        <v>0.4960370991051177</v>
+        <v>0.4986840559284226</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2785091760612896</v>
+        <v>0.2765742877729097</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4588363798352281</v>
+        <v>0.4558027229868891</v>
       </c>
       <c r="V30" t="n">
-        <v>99.05321081081081</v>
+        <v>99.24521468144044</v>
       </c>
       <c r="W30" t="n">
-        <v>105.7578378378379</v>
+        <v>106.0647506925208</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.724324324324323</v>
+        <v>-10.06786703601108</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.559664431501391</v>
+        <v>0.5617081973308453</v>
       </c>
       <c r="Z30" t="n">
-        <v>99.95</v>
+        <v>101.06</v>
       </c>
       <c r="AA30" t="n">
-        <v>-12.91</v>
+        <v>-15.01</v>
       </c>
       <c r="AB30" t="n">
         <v>-6.499587896466165</v>
@@ -3712,7 +3712,7 @@
         <v>113.7332995772778</v>
       </c>
       <c r="AE30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.790471869380649</v>
+        <v>-2.213516287115717</v>
       </c>
     </row>
     <row r="31">
@@ -3739,76 +3739,76 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46113</v>
+        <v>46116</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.331</v>
+        <v>1255.304</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4749</v>
+        <v>-0.4642</v>
       </c>
       <c r="I31" t="n">
-        <v>1505.793133333333</v>
+        <v>1505.351315789474</v>
       </c>
       <c r="J31" t="n">
-        <v>108.9368258185659</v>
+        <v>109.0584664035398</v>
       </c>
       <c r="K31" t="n">
-        <v>120.6012009392548</v>
+        <v>120.4889590371514</v>
       </c>
       <c r="L31" t="n">
-        <v>-11.66437512068896</v>
+        <v>-11.43049263361158</v>
       </c>
       <c r="M31" t="n">
-        <v>108.5300715708885</v>
+        <v>110.4128168350798</v>
       </c>
       <c r="N31" t="n">
-        <v>124.1405019236009</v>
+        <v>125.9065550577442</v>
       </c>
       <c r="O31" t="n">
-        <v>-15.61043035271232</v>
+        <v>-15.49373822266436</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5362923003100211</v>
+        <v>0.5353375409717583</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.131173573577824</v>
+        <v>0.1304981876868936</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2366362148665032</v>
+        <v>0.2391686709529552</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5539569619436472</v>
+        <v>0.5554254030936923</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2351517579588084</v>
+        <v>0.2360732373108673</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4048352729941456</v>
+        <v>0.4039825934617253</v>
       </c>
       <c r="V31" t="n">
-        <v>103.7796129032258</v>
+        <v>103.8694078947368</v>
       </c>
       <c r="W31" t="n">
-        <v>113.0774193548387</v>
+        <v>113.2526913875598</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.80645161290323</v>
+        <v>-11.70514354066986</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5680913396971063</v>
+        <v>0.5671876016454752</v>
       </c>
       <c r="Z31" t="n">
-        <v>112.19</v>
+        <v>115.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>-15.07</v>
+        <v>-15.46</v>
       </c>
       <c r="AB31" t="n">
         <v>-12.72363327068823</v>
@@ -3820,16 +3820,16 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH31" t="n">
-        <v>-1.692094098696974</v>
+        <v>-1.592524154937978</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -865,7 +865,7 @@
         <v>3</v>
       </c>
       <c r="AH2">
-        <v>1.25154279983684</v>
+        <v>1.173118490651568</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -969,7 +969,7 @@
         <v>4</v>
       </c>
       <c r="AH3">
-        <v>1.222129230658837</v>
+        <v>1.102332312861675</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -1073,7 +1073,7 @@
         <v>4</v>
       </c>
       <c r="AH4">
-        <v>1.624174822598726</v>
+        <v>1.484579813677341</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1177,7 +1177,7 @@
         <v>4</v>
       </c>
       <c r="AH5">
-        <v>0.05805020187196448</v>
+        <v>-0.004423508931388254</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1281,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="AH6">
-        <v>1.216626398729362</v>
+        <v>1.097100459075389</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1385,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AH7">
-        <v>0.759278250226991</v>
+        <v>0.6622736875040652</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1489,7 +1489,7 @@
         <v>2</v>
       </c>
       <c r="AH8">
-        <v>0.09804251291223129</v>
+        <v>1.547792103199323</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="AH9">
-        <v>1.647129029299265</v>
+        <v>1.506403677240057</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="AH10">
-        <v>0.6173274251656873</v>
+        <v>0.5692923368339535</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -1801,7 +1801,7 @@
         <v>3</v>
       </c>
       <c r="AH11">
-        <v>0.3072368426177246</v>
+        <v>0.2324923348716186</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -1905,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="AH12">
-        <v>0.4869952456888546</v>
+        <v>0.4033988233447668</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -2009,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="AH13">
-        <v>0.4081626169002694</v>
+        <v>0.3284481810761377</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2113,7 +2113,7 @@
         <v>3</v>
       </c>
       <c r="AH14">
-        <v>0.9021167697812853</v>
+        <v>0.7980783529809151</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2217,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="AH15">
-        <v>-0.9196314600879388</v>
+        <v>-0.933960803630433</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2321,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>0.1742391725906169</v>
+        <v>0.1060439220513891</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="AH17">
-        <v>0.5678004203100421</v>
+        <v>0.6609678491339591</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -2529,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="AH18">
-        <v>0.09032896737096691</v>
+        <v>0.02626574046909616</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -2633,7 +2633,7 @@
         <v>4</v>
       </c>
       <c r="AH19">
-        <v>0.7151938732662206</v>
+        <v>0.6203601750664268</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2737,7 +2737,7 @@
         <v>3</v>
       </c>
       <c r="AH20">
-        <v>0.316936888625863</v>
+        <v>0.2417147176529283</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="AH21">
-        <v>-0.004102735849473581</v>
+        <v>-0.06351582479969299</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-0.6740726494428833</v>
+        <v>-0.8606278627813541</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>3</v>
       </c>
       <c r="AH23">
-        <v>-1.127591051751448</v>
+        <v>-1.131679758340197</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>3</v>
       </c>
       <c r="AH24">
-        <v>-0.4418045758069141</v>
+        <v>-0.4796637388182743</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.626226552039232</v>
+        <v>-1.605760752197909</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.151846139108159</v>
+        <v>-1.154740442775097</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>3</v>
       </c>
       <c r="AH27">
-        <v>-0.9008902030379061</v>
+        <v>-0.9161424297615558</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-1.011154642527419</v>
+        <v>-0.8521257029301433</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.574826173419692</v>
+        <v>-1.556891502883429</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>3</v>
       </c>
       <c r="AH30">
-        <v>-1.837485619139621</v>
+        <v>-1.806616704962209</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.193679666241059</v>
+        <v>-1.194513944878924</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -124,12 +124,12 @@
     <t>San Antonio Spurs</t>
   </si>
   <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
     <t>New York Knicks</t>
   </si>
   <si>
@@ -148,24 +148,24 @@
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
+    <t>Toronto Raptors</t>
+  </si>
+  <si>
+    <t>Atlanta Hawks</t>
+  </si>
+  <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
     <t>LA Clippers</t>
   </si>
   <si>
+    <t>Phoenix Suns</t>
+  </si>
+  <si>
     <t>Miami Heat</t>
   </si>
   <si>
-    <t>Atlanta Hawks</t>
-  </si>
-  <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>Phoenix Suns</t>
-  </si>
-  <si>
-    <t>Toronto Raptors</t>
-  </si>
-  <si>
     <t>Orlando Magic</t>
   </si>
   <si>
@@ -187,12 +187,12 @@
     <t>Dallas Mavericks</t>
   </si>
   <si>
+    <t>Memphis Grizzlies</t>
+  </si>
+  <si>
     <t>Milwaukee Bucks</t>
   </si>
   <si>
-    <t>Memphis Grizzlies</t>
-  </si>
-  <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>SAS</t>
   </si>
   <si>
+    <t>DET</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>DET</t>
-  </si>
-  <si>
     <t>NYK</t>
   </si>
   <si>
@@ -238,24 +238,24 @@
     <t>MIN</t>
   </si>
   <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
     <t>LAC</t>
   </si>
   <si>
+    <t>PHX</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
     <t>ORL</t>
   </si>
   <si>
@@ -277,10 +277,10 @@
     <t>DAL</t>
   </si>
   <si>
+    <t>MEM</t>
+  </si>
+  <si>
     <t>MIL</t>
-  </si>
-  <si>
-    <t>MEM</t>
   </si>
   <si>
     <t>IND</t>
@@ -775,76 +775,76 @@
         <v>64</v>
       </c>
       <c r="D2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E2" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>1762.395</v>
+        <v>1769.519</v>
       </c>
       <c r="H2">
-        <v>1.1556</v>
+        <v>1.6656</v>
       </c>
       <c r="I2">
-        <v>1499.931236842105</v>
+        <v>1498.208871794872</v>
       </c>
       <c r="J2">
-        <v>117.4606313221413</v>
+        <v>117.6484940385879</v>
       </c>
       <c r="K2">
-        <v>105.3653418509131</v>
+        <v>105.3702957725928</v>
       </c>
       <c r="L2">
-        <v>12.0952894712282</v>
+        <v>12.27819826599503</v>
       </c>
       <c r="M2">
-        <v>121.2619929960477</v>
+        <v>123.6262450758385</v>
       </c>
       <c r="N2">
-        <v>102.8172314560054</v>
+        <v>102.4591453767432</v>
       </c>
       <c r="O2">
-        <v>18.44476154004224</v>
+        <v>21.16709969909541</v>
       </c>
       <c r="P2">
-        <v>0.5649680316551817</v>
+        <v>0.5667742882617324</v>
       </c>
       <c r="Q2">
-        <v>0.1078396672830446</v>
+        <v>0.1080559262096478</v>
       </c>
       <c r="R2">
-        <v>0.2200956401192015</v>
+        <v>0.2195502668751287</v>
       </c>
       <c r="S2">
-        <v>0.5764248966394866</v>
+        <v>0.6024283188129468</v>
       </c>
       <c r="T2">
-        <v>0.2672108184561992</v>
+        <v>0.2674797075371117</v>
       </c>
       <c r="U2">
-        <v>0.4261943142865996</v>
+        <v>0.4254678923291795</v>
       </c>
       <c r="V2">
-        <v>102.0187719298245</v>
+        <v>101.8349321266968</v>
       </c>
       <c r="W2">
-        <v>119.6428571428571</v>
+        <v>119.6504524886878</v>
       </c>
       <c r="X2">
-        <v>12.12374686716792</v>
+        <v>12.35067873303167</v>
       </c>
       <c r="Y2">
-        <v>0.6035829749302591</v>
+        <v>0.6050630160415154</v>
       </c>
       <c r="Z2">
-        <v>123.41</v>
+        <v>125.21</v>
       </c>
       <c r="AA2">
-        <v>17.36</v>
+        <v>20.43</v>
       </c>
       <c r="AB2">
         <v>11.54061896828745</v>
@@ -856,16 +856,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2">
         <v>3</v>
       </c>
       <c r="AH2">
-        <v>1.173118490651568</v>
+        <v>-0.8684245964312617</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -879,76 +879,76 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E3" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>1737.73</v>
+        <v>1738.935</v>
       </c>
       <c r="H3">
-        <v>2.4638</v>
+        <v>2.1342</v>
       </c>
       <c r="I3">
-        <v>1508.850194805195</v>
+        <v>1508.406166666667</v>
       </c>
       <c r="J3">
-        <v>117.6125957592216</v>
+        <v>117.4767544571925</v>
       </c>
       <c r="K3">
-        <v>109.0494172313531</v>
+        <v>108.8080435002499</v>
       </c>
       <c r="L3">
-        <v>8.563178527868487</v>
+        <v>8.668710956942585</v>
       </c>
       <c r="M3">
-        <v>122.0589154262412</v>
+        <v>120.1399996005027</v>
       </c>
       <c r="N3">
-        <v>106.3582051488749</v>
+        <v>105.8519930993021</v>
       </c>
       <c r="O3">
-        <v>15.70071027736633</v>
+        <v>14.28800650120055</v>
       </c>
       <c r="P3">
-        <v>0.5609060505210923</v>
+        <v>0.5607256769333011</v>
       </c>
       <c r="Q3">
-        <v>0.1110140349714025</v>
+        <v>0.1119768579435056</v>
       </c>
       <c r="R3">
-        <v>0.2578436955828236</v>
+        <v>0.2582367857545545</v>
       </c>
       <c r="S3">
-        <v>0.5785450563361206</v>
+        <v>0.5695485078501739</v>
       </c>
       <c r="T3">
-        <v>0.2778903299650403</v>
+        <v>0.2767556546471427</v>
       </c>
       <c r="U3">
-        <v>0.4217800744551822</v>
+        <v>0.4203151483176745</v>
       </c>
       <c r="V3">
-        <v>101.9574094326725</v>
+        <v>102.01375</v>
       </c>
       <c r="W3">
-        <v>119.7546138072454</v>
+        <v>119.625</v>
       </c>
       <c r="X3">
-        <v>8.510936431989064</v>
+        <v>8.512499999999999</v>
       </c>
       <c r="Y3">
-        <v>0.5965694697178648</v>
+        <v>0.5963716228708283</v>
       </c>
       <c r="Z3">
-        <v>124.99</v>
+        <v>123.16</v>
       </c>
       <c r="AA3">
-        <v>16.78</v>
+        <v>15.23</v>
       </c>
       <c r="AB3">
         <v>-2.513643863094118</v>
@@ -969,12 +969,12 @@
         <v>4</v>
       </c>
       <c r="AH3">
-        <v>1.102332312861675</v>
+        <v>1.265811702660106</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -983,85 +983,85 @@
         <v>66</v>
       </c>
       <c r="D4">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E4" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>1669.327</v>
+        <v>1680.746</v>
       </c>
       <c r="H4">
-        <v>1.5256</v>
+        <v>0.8821</v>
       </c>
       <c r="I4">
-        <v>1489.920571428572</v>
+        <v>1496.208705128205</v>
       </c>
       <c r="J4">
-        <v>117.7739295921551</v>
+        <v>115.4609697176974</v>
       </c>
       <c r="K4">
-        <v>110.1885280156173</v>
+        <v>107.6627038123182</v>
       </c>
       <c r="L4">
-        <v>7.585401576537841</v>
+        <v>7.798265905379202</v>
       </c>
       <c r="M4">
-        <v>120.0077354343567</v>
+        <v>117.982948995146</v>
       </c>
       <c r="N4">
-        <v>109.7841497135124</v>
+        <v>106.3804728052524</v>
       </c>
       <c r="O4">
-        <v>10.22358572084431</v>
+        <v>11.60247618989356</v>
       </c>
       <c r="P4">
-        <v>0.5520833121684687</v>
+        <v>0.5488980195844952</v>
       </c>
       <c r="Q4">
-        <v>0.1042514427877992</v>
+        <v>0.1233378817507484</v>
       </c>
       <c r="R4">
-        <v>0.2917067604078712</v>
+        <v>0.3053339468968531</v>
       </c>
       <c r="S4">
-        <v>0.5650946639167389</v>
+        <v>0.5788210036565079</v>
       </c>
       <c r="T4">
-        <v>0.2121452454164453</v>
+        <v>0.2954211926033668</v>
       </c>
       <c r="U4">
-        <v>0.4615540790325772</v>
+        <v>0.3472563105733588</v>
       </c>
       <c r="V4">
-        <v>97.23471428571428</v>
+        <v>101.9793006993007</v>
       </c>
       <c r="W4">
-        <v>114.6454545454545</v>
+        <v>117.7176573426574</v>
       </c>
       <c r="X4">
-        <v>7.706818181818183</v>
+        <v>8.120920745920746</v>
       </c>
       <c r="Y4">
-        <v>0.5822893468519508</v>
+        <v>0.5853846825652759</v>
       </c>
       <c r="Z4">
-        <v>117.07</v>
+        <v>118.82</v>
       </c>
       <c r="AA4">
-        <v>10.04</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB4">
-        <v>9.220352523846751</v>
+        <v>1.549391602834736</v>
       </c>
       <c r="AC4">
-        <v>117.8084737243045</v>
+        <v>112.5216901085732</v>
       </c>
       <c r="AD4">
-        <v>108.5881212004577</v>
+        <v>110.9722985057385</v>
       </c>
       <c r="AE4">
         <v>1</v>
@@ -1070,15 +1070,15 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH4">
-        <v>1.484579813677341</v>
+        <v>0.8722884576791512</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -1087,85 +1087,85 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E5" s="2">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>1687.652</v>
+        <v>1673.996</v>
       </c>
       <c r="H5">
-        <v>1.1116</v>
+        <v>2.0279</v>
       </c>
       <c r="I5">
-        <v>1495.988701298701</v>
+        <v>1491.547227848101</v>
       </c>
       <c r="J5">
-        <v>114.5472314302991</v>
+        <v>117.9229440256062</v>
       </c>
       <c r="K5">
-        <v>107.6798910978373</v>
+        <v>110.7493992088959</v>
       </c>
       <c r="L5">
-        <v>6.867340332461835</v>
+        <v>7.173544816710401</v>
       </c>
       <c r="M5">
-        <v>114.8452421324196</v>
+        <v>120.327259301116</v>
       </c>
       <c r="N5">
-        <v>104.7707794084896</v>
+        <v>112.1552529601885</v>
       </c>
       <c r="O5">
-        <v>10.07446272393003</v>
+        <v>8.17200634092748</v>
       </c>
       <c r="P5">
-        <v>0.5465512713821925</v>
+        <v>0.5521274473984394</v>
       </c>
       <c r="Q5">
-        <v>0.1244554973072285</v>
+        <v>0.1038608322360771</v>
       </c>
       <c r="R5">
-        <v>0.3006525291433526</v>
+        <v>0.2931543819664709</v>
       </c>
       <c r="S5">
-        <v>0.5638742249450233</v>
+        <v>0.5640081718543285</v>
       </c>
       <c r="T5">
-        <v>0.2927380531086305</v>
+        <v>0.2110245087005032</v>
       </c>
       <c r="U5">
-        <v>0.3471311391546138</v>
+        <v>0.4648622155423958</v>
       </c>
       <c r="V5">
-        <v>102.171948051948</v>
+        <v>96.90247168554298</v>
       </c>
       <c r="W5">
-        <v>117.0873671782763</v>
+        <v>114.3934043970687</v>
       </c>
       <c r="X5">
-        <v>7.285320739866195</v>
+        <v>7.311125916055962</v>
       </c>
       <c r="Y5">
-        <v>0.5824398731513262</v>
+        <v>0.5823826303045305</v>
       </c>
       <c r="Z5">
-        <v>116.72</v>
+        <v>115.09</v>
       </c>
       <c r="AA5">
-        <v>8.84</v>
+        <v>7.68</v>
       </c>
       <c r="AB5">
-        <v>1.549391602834736</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC5">
-        <v>112.5216901085732</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD5">
-        <v>110.9722985057385</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE5">
         <v>1</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH5">
-        <v>-0.004423508931388254</v>
+        <v>1.63870366444443</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1191,76 +1191,76 @@
         <v>68</v>
       </c>
       <c r="D6">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E6" s="2">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="F6">
         <v>39</v>
       </c>
       <c r="G6">
-        <v>1650.995</v>
+        <v>1653.738</v>
       </c>
       <c r="H6">
-        <v>-1.3274</v>
+        <v>-1.3253</v>
       </c>
       <c r="I6">
-        <v>1487.807220779221</v>
+        <v>1488.382846153846</v>
       </c>
       <c r="J6">
-        <v>117.5906383621484</v>
+        <v>117.858857916099</v>
       </c>
       <c r="K6">
-        <v>110.7819964477277</v>
+        <v>111.0679353852492</v>
       </c>
       <c r="L6">
-        <v>6.808641914420648</v>
+        <v>6.790922530849887</v>
       </c>
       <c r="M6">
-        <v>121.6557986940841</v>
+        <v>122.5223398479738</v>
       </c>
       <c r="N6">
-        <v>114.0358508402555</v>
+        <v>114.9254668798314</v>
       </c>
       <c r="O6">
-        <v>7.619947853828603</v>
+        <v>7.596872968142457</v>
       </c>
       <c r="P6">
-        <v>0.5555159967392291</v>
+        <v>0.5573301994672366</v>
       </c>
       <c r="Q6">
-        <v>0.1163812154013237</v>
+        <v>0.1150007014141735</v>
       </c>
       <c r="R6">
-        <v>0.2959459148894727</v>
+        <v>0.2921701303425507</v>
       </c>
       <c r="S6">
-        <v>0.5706655389085561</v>
+        <v>0.5809929198609369</v>
       </c>
       <c r="T6">
-        <v>0.2386496091755298</v>
+        <v>0.2378030635145492</v>
       </c>
       <c r="U6">
-        <v>0.4282949207051554</v>
+        <v>0.4289852788646132</v>
       </c>
       <c r="V6">
-        <v>99.29560439560439</v>
+        <v>99.05668639053255</v>
       </c>
       <c r="W6">
-        <v>116.5161505161505</v>
+        <v>116.5095332018409</v>
       </c>
       <c r="X6">
-        <v>6.340659340659341</v>
+        <v>6.374753451676529</v>
       </c>
       <c r="Y6">
-        <v>0.5885643515890709</v>
+        <v>0.5900315981097985</v>
       </c>
       <c r="Z6">
-        <v>115.92</v>
+        <v>116.14</v>
       </c>
       <c r="AA6">
-        <v>7.41</v>
+        <v>7.71</v>
       </c>
       <c r="AB6">
         <v>2.775420617465777</v>
@@ -1278,10 +1278,10 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH6">
-        <v>1.097100459075389</v>
+        <v>1.286267411500424</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1295,76 +1295,76 @@
         <v>69</v>
       </c>
       <c r="D7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E7" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>1587.308</v>
+        <v>1593.669</v>
       </c>
       <c r="H7">
-        <v>1.5199</v>
+        <v>2.1301</v>
       </c>
       <c r="I7">
-        <v>1494.118</v>
+        <v>1494.003632911392</v>
       </c>
       <c r="J7">
-        <v>115.9895637116712</v>
+        <v>115.6933541325044</v>
       </c>
       <c r="K7">
-        <v>111.2428511199221</v>
+        <v>110.7700909988529</v>
       </c>
       <c r="L7">
-        <v>4.746712591749109</v>
+        <v>4.923263133651576</v>
       </c>
       <c r="M7">
-        <v>122.6482742860319</v>
+        <v>122.0238535344921</v>
       </c>
       <c r="N7">
-        <v>111.9290305106504</v>
+        <v>110.1191203896841</v>
       </c>
       <c r="O7">
-        <v>10.71924377538156</v>
+        <v>11.90473314480801</v>
       </c>
       <c r="P7">
-        <v>0.5466507978823559</v>
+        <v>0.5440089246782009</v>
       </c>
       <c r="Q7">
-        <v>0.1265366354218069</v>
+        <v>0.1266128899290344</v>
       </c>
       <c r="R7">
-        <v>0.3413592447553356</v>
+        <v>0.3439162304041541</v>
       </c>
       <c r="S7">
-        <v>0.580281116898439</v>
+        <v>0.5687663006501065</v>
       </c>
       <c r="T7">
-        <v>0.2626693570191851</v>
+        <v>0.2622670465377827</v>
       </c>
       <c r="U7">
-        <v>0.3507834593546368</v>
+        <v>0.3507746169168276</v>
       </c>
       <c r="V7">
-        <v>99.08733209647495</v>
+        <v>99.23696202531647</v>
       </c>
       <c r="W7">
-        <v>114.817439703154</v>
+        <v>114.7844585091421</v>
       </c>
       <c r="X7">
-        <v>4.759554730983302</v>
+        <v>5.105133614627285</v>
       </c>
       <c r="Y7">
-        <v>0.5796407592001069</v>
+        <v>0.5769914276758995</v>
       </c>
       <c r="Z7">
-        <v>120.69</v>
+        <v>120.56</v>
       </c>
       <c r="AA7">
-        <v>9.460000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="AB7">
         <v>3.413694058608522</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH7">
-        <v>0.6622736875040652</v>
+        <v>0.8282632983909106</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1399,76 +1399,76 @@
         <v>70</v>
       </c>
       <c r="D8">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E8" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>1605.173</v>
+        <v>1606.552</v>
       </c>
       <c r="H8">
-        <v>1.9093</v>
+        <v>2.3051</v>
       </c>
       <c r="I8">
-        <v>1502.177628205128</v>
+        <v>1501.758721518987</v>
       </c>
       <c r="J8">
-        <v>120.1657687408336</v>
+        <v>120.4507078756702</v>
       </c>
       <c r="K8">
-        <v>115.4961513534244</v>
+        <v>115.5572099086143</v>
       </c>
       <c r="L8">
-        <v>4.669617387409372</v>
+        <v>4.893497967055835</v>
       </c>
       <c r="M8">
-        <v>124.3700147720405</v>
+        <v>125.6183453136214</v>
       </c>
       <c r="N8">
-        <v>115.749613572756</v>
+        <v>118.3642586489945</v>
       </c>
       <c r="O8">
-        <v>8.620401199284521</v>
+        <v>7.254086664626874</v>
       </c>
       <c r="P8">
-        <v>0.5763483621028707</v>
+        <v>0.5790279656640467</v>
       </c>
       <c r="Q8">
-        <v>0.1088689593256973</v>
+        <v>0.1089699987072154</v>
       </c>
       <c r="R8">
-        <v>0.2354388453792781</v>
+        <v>0.2340902320474838</v>
       </c>
       <c r="S8">
-        <v>0.5989342198478205</v>
+        <v>0.6064862192338055</v>
       </c>
       <c r="T8">
-        <v>0.3005918340106732</v>
+        <v>0.2993117887150277</v>
       </c>
       <c r="U8">
-        <v>0.4077612609181785</v>
+        <v>0.4078825005605269</v>
       </c>
       <c r="V8">
-        <v>101.4950793650794</v>
+        <v>101.4071183916605</v>
       </c>
       <c r="W8">
-        <v>121.931623931624</v>
+        <v>122.1783320923306</v>
       </c>
       <c r="X8">
-        <v>4.74969474969475</v>
+        <v>5.1072226358898</v>
       </c>
       <c r="Y8">
-        <v>0.616008684090786</v>
+        <v>0.6180660018775607</v>
       </c>
       <c r="Z8">
-        <v>128.45</v>
+        <v>129.52</v>
       </c>
       <c r="AA8">
-        <v>9.140000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="AB8">
         <v>2.722616812266775</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH8">
-        <v>1.547792103199323</v>
+        <v>1.798225502042187</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1503,76 +1503,76 @@
         <v>71</v>
       </c>
       <c r="D9">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E9" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>1640.206</v>
+        <v>1642.167</v>
       </c>
       <c r="H9">
-        <v>-0.5363</v>
+        <v>-0.5165</v>
       </c>
       <c r="I9">
-        <v>1487.416756410256</v>
+        <v>1485.946151898734</v>
       </c>
       <c r="J9">
-        <v>117.4513045619505</v>
+        <v>117.1665092173712</v>
       </c>
       <c r="K9">
-        <v>113.026784764065</v>
+        <v>112.8161748740272</v>
       </c>
       <c r="L9">
-        <v>4.424519797885502</v>
+        <v>4.350334343343985</v>
       </c>
       <c r="M9">
-        <v>122.0375732909415</v>
+        <v>120.944599387484</v>
       </c>
       <c r="N9">
-        <v>117.5972259882529</v>
+        <v>116.5426102853361</v>
       </c>
       <c r="O9">
-        <v>4.440347302688653</v>
+        <v>4.401989102147839</v>
       </c>
       <c r="P9">
-        <v>0.563792193646707</v>
+        <v>0.5617467379738843</v>
       </c>
       <c r="Q9">
-        <v>0.1158553301066078</v>
+        <v>0.1155315095967123</v>
       </c>
       <c r="R9">
-        <v>0.2661712917981914</v>
+        <v>0.2639215667607245</v>
       </c>
       <c r="S9">
-        <v>0.580680295056611</v>
+        <v>0.5773399738935827</v>
       </c>
       <c r="T9">
-        <v>0.2707233851278056</v>
+        <v>0.271980493842378</v>
       </c>
       <c r="U9">
-        <v>0.4418084827497264</v>
+        <v>0.4412331763264081</v>
       </c>
       <c r="V9">
-        <v>102.1834511434512</v>
+        <v>102.2337508327782</v>
       </c>
       <c r="W9">
-        <v>119.9085239085239</v>
+        <v>119.6459027315124</v>
       </c>
       <c r="X9">
-        <v>4.474012474012474</v>
+        <v>4.348434377081945</v>
       </c>
       <c r="Y9">
-        <v>0.5967144252444975</v>
+        <v>0.5954192520569199</v>
       </c>
       <c r="Z9">
-        <v>122.83</v>
+        <v>122.54</v>
       </c>
       <c r="AA9">
-        <v>4.93</v>
+        <v>4.739999999999999</v>
       </c>
       <c r="AB9">
         <v>9.967224035556209</v>
@@ -1584,16 +1584,16 @@
         <v>110.1289876408569</v>
       </c>
       <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
         <v>0</v>
       </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
       <c r="AG9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9">
-        <v>1.506403677240057</v>
+        <v>0.6144762147516616</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1607,76 +1607,76 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E10" s="2">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>1587.89</v>
+        <v>1593.135</v>
       </c>
       <c r="H10">
-        <v>0.764</v>
+        <v>0.6887</v>
       </c>
       <c r="I10">
-        <v>1492.843794871795</v>
+        <v>1493.85729113924</v>
       </c>
       <c r="J10">
-        <v>116.3907140967677</v>
+        <v>116.0895593539149</v>
       </c>
       <c r="K10">
-        <v>112.3410030300366</v>
+        <v>112.7071454866825</v>
       </c>
       <c r="L10">
-        <v>4.049711066731184</v>
+        <v>3.382413867232365</v>
       </c>
       <c r="M10">
-        <v>123.7245250206069</v>
+        <v>122.2871234716915</v>
       </c>
       <c r="N10">
-        <v>107.7617226327901</v>
+        <v>110.1099658084995</v>
       </c>
       <c r="O10">
-        <v>15.96280238781681</v>
+        <v>12.17715766319199</v>
       </c>
       <c r="P10">
-        <v>0.5554952119280885</v>
+        <v>0.5538846716509681</v>
       </c>
       <c r="Q10">
-        <v>0.1276460028144167</v>
+        <v>0.1271439745227298</v>
       </c>
       <c r="R10">
-        <v>0.3069379886588396</v>
+        <v>0.3056206346965748</v>
       </c>
       <c r="S10">
-        <v>0.5921824665330802</v>
+        <v>0.5827500307623292</v>
       </c>
       <c r="T10">
-        <v>0.246623124170698</v>
+        <v>0.2450252490489063</v>
       </c>
       <c r="U10">
-        <v>0.4841367287670704</v>
+        <v>0.4862556116283863</v>
       </c>
       <c r="V10">
-        <v>99.63714932126697</v>
+        <v>99.42868431146913</v>
       </c>
       <c r="W10">
-        <v>116.5622171945701</v>
+        <v>116.0299194476409</v>
       </c>
       <c r="X10">
-        <v>5.351809954751131</v>
+        <v>4.711545838128116</v>
       </c>
       <c r="Y10">
-        <v>0.5920043669738166</v>
+        <v>0.5901087789255457</v>
       </c>
       <c r="Z10">
-        <v>122.36</v>
+        <v>119.1</v>
       </c>
       <c r="AA10">
-        <v>17.6</v>
+        <v>13.66</v>
       </c>
       <c r="AB10">
         <v>-10.13717477219789</v>
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="AH10">
-        <v>0.5692923368339535</v>
+        <v>0.7063220678784009</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -1711,76 +1711,76 @@
         <v>73</v>
       </c>
       <c r="D11">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E11" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11">
-        <v>1572.91</v>
+        <v>1570.012</v>
       </c>
       <c r="H11">
-        <v>0.2039</v>
+        <v>-0.905</v>
       </c>
       <c r="I11">
-        <v>1502.471883116883</v>
+        <v>1501.505493670886</v>
       </c>
       <c r="J11">
-        <v>114.4089222093157</v>
+        <v>114.5554676748872</v>
       </c>
       <c r="K11">
-        <v>111.0426868068074</v>
+        <v>111.2101462602894</v>
       </c>
       <c r="L11">
-        <v>3.366235402508212</v>
+        <v>3.345321414597836</v>
       </c>
       <c r="M11">
-        <v>105.884001050451</v>
+        <v>107.2444298025893</v>
       </c>
       <c r="N11">
-        <v>106.2939298505355</v>
+        <v>107.4449111718987</v>
       </c>
       <c r="O11">
-        <v>-0.4099288000845112</v>
+        <v>-0.2004813693092842</v>
       </c>
       <c r="P11">
-        <v>0.5568537555895298</v>
+        <v>0.5588211356774447</v>
       </c>
       <c r="Q11">
-        <v>0.1250569199032537</v>
+        <v>0.1255600858628708</v>
       </c>
       <c r="R11">
-        <v>0.2572447710466758</v>
+        <v>0.2561695785591078</v>
       </c>
       <c r="S11">
-        <v>0.5150152052033198</v>
+        <v>0.5229688650198807</v>
       </c>
       <c r="T11">
-        <v>0.2896700083237832</v>
+        <v>0.2850267298234933</v>
       </c>
       <c r="U11">
-        <v>0.4202612174120698</v>
+        <v>0.4220678452713819</v>
       </c>
       <c r="V11">
-        <v>102.8747012987013</v>
+        <v>102.9468614086336</v>
       </c>
       <c r="W11">
-        <v>117.3701298701299</v>
+        <v>117.6319376825706</v>
       </c>
       <c r="X11">
-        <v>3.081493506493507</v>
+        <v>3.108730931515742</v>
       </c>
       <c r="Y11">
-        <v>0.5904180417652891</v>
+        <v>0.5920846861513666</v>
       </c>
       <c r="Z11">
-        <v>110.16</v>
+        <v>112.53</v>
       </c>
       <c r="AA11">
-        <v>1.66</v>
+        <v>2.489999999999999</v>
       </c>
       <c r="AB11">
         <v>4.250350764022217</v>
@@ -1792,21 +1792,21 @@
         <v>109.8879798345829</v>
       </c>
       <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>1</v>
       </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
       <c r="AG11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11">
-        <v>0.2324923348716186</v>
+        <v>0.3583296958320634</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -1815,88 +1815,88 @@
         <v>74</v>
       </c>
       <c r="D12">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E12" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>1550.751</v>
+        <v>1518.378</v>
       </c>
       <c r="H12">
-        <v>0.7018</v>
+        <v>1.0632</v>
       </c>
       <c r="I12">
-        <v>1498.938675324675</v>
+        <v>1496.742974683544</v>
       </c>
       <c r="J12">
-        <v>116.1727233092147</v>
+        <v>113.9948372337364</v>
       </c>
       <c r="K12">
-        <v>113.5691200412739</v>
+        <v>111.4976321318984</v>
       </c>
       <c r="L12">
-        <v>2.603603267940854</v>
+        <v>2.497205101837976</v>
       </c>
       <c r="M12">
-        <v>119.2405851125806</v>
+        <v>117.5904677919006</v>
       </c>
       <c r="N12">
-        <v>112.8785588149168</v>
+        <v>112.1121132540146</v>
       </c>
       <c r="O12">
-        <v>6.362026297663785</v>
+        <v>5.478354537885998</v>
       </c>
       <c r="P12">
-        <v>0.5623693545465863</v>
+        <v>0.5459183717879508</v>
       </c>
       <c r="Q12">
-        <v>0.125324982041318</v>
+        <v>0.1136407089073855</v>
       </c>
       <c r="R12">
-        <v>0.2353897055698567</v>
+        <v>0.2547519243726641</v>
       </c>
       <c r="S12">
-        <v>0.5859896551870681</v>
+        <v>0.5773759482331312</v>
       </c>
       <c r="T12">
-        <v>0.3004187417972992</v>
+        <v>0.2678910505840704</v>
       </c>
       <c r="U12">
-        <v>0.40388881275768</v>
+        <v>0.3637633368786354</v>
       </c>
       <c r="V12">
-        <v>98.86135486135485</v>
+        <v>100.6705836849508</v>
       </c>
       <c r="W12">
-        <v>114.3327483327484</v>
+        <v>114.8196202531645</v>
       </c>
       <c r="X12">
-        <v>1.832572832572833</v>
+        <v>2.850210970464135</v>
       </c>
       <c r="Y12">
-        <v>0.6059457257591011</v>
+        <v>0.5800943248599566</v>
       </c>
       <c r="Z12">
-        <v>117.57</v>
+        <v>118.46</v>
       </c>
       <c r="AA12">
-        <v>5.24</v>
+        <v>6.71</v>
       </c>
       <c r="AB12">
-        <v>4.815266446541752</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC12">
-        <v>113.8106821492749</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD12">
-        <v>108.9954157027332</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -1905,12 +1905,12 @@
         <v>3</v>
       </c>
       <c r="AH12">
-        <v>0.4033988233447668</v>
+        <v>0.7361621007331843</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -1919,88 +1919,88 @@
         <v>75</v>
       </c>
       <c r="D13">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2">
-        <v>46116</v>
+        <v>46120</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G13">
-        <v>1528.663</v>
+        <v>1529.962</v>
       </c>
       <c r="H13">
-        <v>-2.1519</v>
+        <v>3.1913</v>
       </c>
       <c r="I13">
-        <v>1507.300402597403</v>
+        <v>1486.043405063291</v>
       </c>
       <c r="J13">
-        <v>114.5186265302597</v>
+        <v>113.9815883697026</v>
       </c>
       <c r="K13">
-        <v>112.3108720562382</v>
+        <v>111.894725872181</v>
       </c>
       <c r="L13">
-        <v>2.207754474021498</v>
+        <v>2.08686249752164</v>
       </c>
       <c r="M13">
-        <v>118.0016236097122</v>
+        <v>116.9280437848686</v>
       </c>
       <c r="N13">
-        <v>124.1690508750568</v>
+        <v>108.6742643129208</v>
       </c>
       <c r="O13">
-        <v>-6.16742726534464</v>
+        <v>8.253779471947798</v>
       </c>
       <c r="P13">
-        <v>0.541255885793396</v>
+        <v>0.5538521711168289</v>
       </c>
       <c r="Q13">
-        <v>0.111679216630442</v>
+        <v>0.1159032175082687</v>
       </c>
       <c r="R13">
-        <v>0.2525608849200953</v>
+        <v>0.2406821348973643</v>
       </c>
       <c r="S13">
-        <v>0.5556618027941286</v>
+        <v>0.566633695967994</v>
       </c>
       <c r="T13">
-        <v>0.2751033216200673</v>
+        <v>0.2354185471123148</v>
       </c>
       <c r="U13">
-        <v>0.4058415614538717</v>
+        <v>0.4269858063807782</v>
       </c>
       <c r="V13">
-        <v>105.8480047225502</v>
+        <v>103.7756962025316</v>
       </c>
       <c r="W13">
-        <v>121.3097205824478</v>
+        <v>118.3819620253164</v>
       </c>
       <c r="X13">
-        <v>2.575364029909485</v>
+        <v>2.417088607594937</v>
       </c>
       <c r="Y13">
-        <v>0.579518941255972</v>
+        <v>0.5841558182815482</v>
       </c>
       <c r="Z13">
-        <v>122.84</v>
+        <v>120.5</v>
       </c>
       <c r="AA13">
-        <v>-7.129999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AB13">
-        <v>-1.094669144490311</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC13">
-        <v>111.6804548463295</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD13">
-        <v>112.7751239908198</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2009,12 +2009,12 @@
         <v>3</v>
       </c>
       <c r="AH13">
-        <v>0.3284481810761377</v>
+        <v>0.9500062504210939</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
@@ -2023,88 +2023,88 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G14">
-        <v>1532.706</v>
+        <v>1554.931</v>
       </c>
       <c r="H14">
-        <v>3.0036</v>
+        <v>0.0144</v>
       </c>
       <c r="I14">
-        <v>1483.928641025641</v>
+        <v>1497.368734177215</v>
       </c>
       <c r="J14">
-        <v>113.9948166574949</v>
+        <v>116.6121868781616</v>
       </c>
       <c r="K14">
-        <v>111.8044566614023</v>
+        <v>114.667904140824</v>
       </c>
       <c r="L14">
-        <v>2.190359996092478</v>
+        <v>1.944282737337594</v>
       </c>
       <c r="M14">
-        <v>118.3585252198222</v>
+        <v>117.5524688319591</v>
       </c>
       <c r="N14">
-        <v>108.3433399292894</v>
+        <v>115.7926921721206</v>
       </c>
       <c r="O14">
-        <v>10.01518529053286</v>
+        <v>1.759776659838577</v>
       </c>
       <c r="P14">
-        <v>0.5531680632914214</v>
+        <v>0.5741367317698555</v>
       </c>
       <c r="Q14">
-        <v>0.1164898820687884</v>
+        <v>0.1264271211873373</v>
       </c>
       <c r="R14">
-        <v>0.243005371788464</v>
+        <v>0.2383772290777021</v>
       </c>
       <c r="S14">
-        <v>0.5721000509310318</v>
+        <v>0.5782957233927123</v>
       </c>
       <c r="T14">
-        <v>0.2366777154656576</v>
+        <v>0.3214101508321631</v>
       </c>
       <c r="U14">
-        <v>0.4292284581390172</v>
+        <v>0.3948219449260268</v>
       </c>
       <c r="V14">
-        <v>103.6313097713097</v>
+        <v>100.1393805548074</v>
       </c>
       <c r="W14">
-        <v>118.2474012474012</v>
+        <v>116.3735523835173</v>
       </c>
       <c r="X14">
-        <v>2.55093555093555</v>
+        <v>1.281982224616213</v>
       </c>
       <c r="Y14">
-        <v>0.5838595364400733</v>
+        <v>0.6098744967983302</v>
       </c>
       <c r="Z14">
-        <v>122.1</v>
+        <v>116.3</v>
       </c>
       <c r="AA14">
-        <v>10.95</v>
+        <v>-0.3800000000000003</v>
       </c>
       <c r="AB14">
-        <v>-0.981113782848854</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC14">
-        <v>112.8029837792552</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD14">
-        <v>113.7840975621041</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2113,12 +2113,12 @@
         <v>3</v>
       </c>
       <c r="AH14">
-        <v>0.7980783529809151</v>
+        <v>-0.3191452497382719</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -2127,97 +2127,97 @@
         <v>77</v>
       </c>
       <c r="D15">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F15">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G15">
-        <v>1564.567</v>
+        <v>1554.715</v>
       </c>
       <c r="H15">
-        <v>1.7293</v>
+        <v>0.8591</v>
       </c>
       <c r="I15">
-        <v>1495.669662337662</v>
+        <v>1494.93235443038</v>
       </c>
       <c r="J15">
-        <v>116.7098032574465</v>
+        <v>115.7260225809766</v>
       </c>
       <c r="K15">
-        <v>114.6779312834015</v>
+        <v>113.826921011303</v>
       </c>
       <c r="L15">
-        <v>2.031871974044946</v>
+        <v>1.899101569673513</v>
       </c>
       <c r="M15">
-        <v>119.0554685740454</v>
+        <v>118.1481196381175</v>
       </c>
       <c r="N15">
-        <v>113.9447334514994</v>
+        <v>110.9061386110401</v>
       </c>
       <c r="O15">
-        <v>5.110735122546025</v>
+        <v>7.241981027077427</v>
       </c>
       <c r="P15">
-        <v>0.571930255319983</v>
+        <v>0.5603432680682666</v>
       </c>
       <c r="Q15">
-        <v>0.124786978893855</v>
+        <v>0.1251170895455838</v>
       </c>
       <c r="R15">
-        <v>0.2389510051038383</v>
+        <v>0.2344714338398585</v>
       </c>
       <c r="S15">
-        <v>0.574933953583574</v>
+        <v>0.5815143524184105</v>
       </c>
       <c r="T15">
-        <v>0.3253202574121375</v>
+        <v>0.3009182287077203</v>
       </c>
       <c r="U15">
-        <v>0.3950832528924128</v>
+        <v>0.402444715390783</v>
       </c>
       <c r="V15">
-        <v>100.4206984126984</v>
+        <v>98.91327115256496</v>
       </c>
       <c r="W15">
-        <v>116.8</v>
+        <v>113.9070619586942</v>
       </c>
       <c r="X15">
-        <v>1.365079365079365</v>
+        <v>1.066955363091272</v>
       </c>
       <c r="Y15">
-        <v>0.6089754172349797</v>
+        <v>0.6033120529567449</v>
       </c>
       <c r="Z15">
-        <v>118.01</v>
+        <v>117.47</v>
       </c>
       <c r="AA15">
-        <v>2.64</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="AB15">
-        <v>1.827913300592181</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC15">
-        <v>114.1496737878887</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD15">
-        <v>112.3217604872965</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15">
         <v>3</v>
       </c>
       <c r="AH15">
-        <v>-0.933960803630433</v>
+        <v>0.6077258162467379</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2231,76 +2231,76 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E16" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G16">
-        <v>1504.555</v>
+        <v>1502.546</v>
       </c>
       <c r="H16">
-        <v>-0.1659</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I16">
-        <v>1513.861818181818</v>
+        <v>1513.040316455696</v>
       </c>
       <c r="J16">
-        <v>113.4058561296252</v>
+        <v>113.3352660535845</v>
       </c>
       <c r="K16">
-        <v>111.7153955839651</v>
+        <v>111.8528816532374</v>
       </c>
       <c r="L16">
-        <v>1.690460545660135</v>
+        <v>1.482384400347095</v>
       </c>
       <c r="M16">
-        <v>114.6920746752961</v>
+        <v>114.8930659672694</v>
       </c>
       <c r="N16">
-        <v>112.2812691384384</v>
+        <v>111.2948692026117</v>
       </c>
       <c r="O16">
-        <v>2.410805536857686</v>
+        <v>3.598196764657815</v>
       </c>
       <c r="P16">
-        <v>0.5401288446147492</v>
+        <v>0.5388445294613354</v>
       </c>
       <c r="Q16">
-        <v>0.1190824919669281</v>
+        <v>0.1187621351706715</v>
       </c>
       <c r="R16">
-        <v>0.2859232594584336</v>
+        <v>0.2852108843136527</v>
       </c>
       <c r="S16">
-        <v>0.5372940960572087</v>
+        <v>0.5404242336083667</v>
       </c>
       <c r="T16">
-        <v>0.2280677406485585</v>
+        <v>0.2303414216833181</v>
       </c>
       <c r="U16">
-        <v>0.4545600651147733</v>
+        <v>0.4531893621121109</v>
       </c>
       <c r="V16">
-        <v>99.76475572046999</v>
+        <v>99.6380910023948</v>
       </c>
       <c r="W16">
-        <v>112.9891774891775</v>
+        <v>112.7882312692439</v>
       </c>
       <c r="X16">
-        <v>1.69604205318491</v>
+        <v>1.502223742730071</v>
       </c>
       <c r="Y16">
-        <v>0.571284806611746</v>
+        <v>0.5707960992451045</v>
       </c>
       <c r="Z16">
-        <v>115.23</v>
+        <v>115.24</v>
       </c>
       <c r="AA16">
-        <v>3.07</v>
+        <v>4.01</v>
       </c>
       <c r="AB16">
         <v>-2.375203171419814</v>
@@ -2312,21 +2312,21 @@
         <v>117.0787009454136</v>
       </c>
       <c r="AE16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16">
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>0.1060439220513891</v>
+        <v>-0.2529282805341169</v>
       </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
-        <v>1610612761</v>
+        <v>1610612748</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -2335,85 +2335,85 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E17" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F17">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G17">
-        <v>1515.212</v>
+        <v>1524.132</v>
       </c>
       <c r="H17">
-        <v>0.1181</v>
+        <v>-1.5367</v>
       </c>
       <c r="I17">
-        <v>1494.077441558442</v>
+        <v>1504.184063291139</v>
       </c>
       <c r="J17">
-        <v>113.1478708252857</v>
+        <v>113.975491222297</v>
       </c>
       <c r="K17">
-        <v>111.6073878851994</v>
+        <v>112.6481839434607</v>
       </c>
       <c r="L17">
-        <v>1.540482940086275</v>
+        <v>1.327307278836367</v>
       </c>
       <c r="M17">
-        <v>116.7434002601146</v>
+        <v>117.7057537449918</v>
       </c>
       <c r="N17">
-        <v>113.9630507269146</v>
+        <v>125.5728210123456</v>
       </c>
       <c r="O17">
-        <v>2.780349533200059</v>
+        <v>-7.867067267353764</v>
       </c>
       <c r="P17">
-        <v>0.5442849459007095</v>
+        <v>0.5399200745859291</v>
       </c>
       <c r="Q17">
-        <v>0.1163483569264917</v>
+        <v>0.1122402158016417</v>
       </c>
       <c r="R17">
-        <v>0.2523962094028602</v>
+        <v>0.2496448119477591</v>
       </c>
       <c r="S17">
-        <v>0.5841007544346816</v>
+        <v>0.5641349455565928</v>
       </c>
       <c r="T17">
-        <v>0.2647882482196954</v>
+        <v>0.2703882610824863</v>
       </c>
       <c r="U17">
-        <v>0.3633065658906802</v>
+        <v>0.4070341328690104</v>
       </c>
       <c r="V17">
-        <v>100.7741919191919</v>
+        <v>105.5048945147679</v>
       </c>
       <c r="W17">
-        <v>114.1565656565656</v>
+        <v>120.287482419128</v>
       </c>
       <c r="X17">
-        <v>1.984848484848484</v>
+        <v>1.619690576652602</v>
       </c>
       <c r="Y17">
-        <v>0.5782159283779257</v>
+        <v>0.5775868212322989</v>
       </c>
       <c r="Z17">
-        <v>118.64</v>
+        <v>121.2</v>
       </c>
       <c r="AA17">
-        <v>4.989999999999999</v>
+        <v>-7.97</v>
       </c>
       <c r="AB17">
-        <v>-4.536933640611859</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC17">
-        <v>108.3888858603967</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD17">
-        <v>112.9258195010085</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE17">
         <v>1</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>0.6609678491339591</v>
+        <v>0.4521245350812307</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -2439,76 +2439,76 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E18" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F18">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G18">
-        <v>1513.149</v>
+        <v>1520.055</v>
       </c>
       <c r="H18">
-        <v>-2.5659</v>
+        <v>-1.671</v>
       </c>
       <c r="I18">
-        <v>1487.651613333333</v>
+        <v>1490.283197368421</v>
       </c>
       <c r="J18">
-        <v>112.4393911961566</v>
+        <v>112.8167169197776</v>
       </c>
       <c r="K18">
-        <v>112.3803059184035</v>
+        <v>112.6233282923196</v>
       </c>
       <c r="L18">
-        <v>0.05908527775312505</v>
+        <v>0.1933886274579631</v>
       </c>
       <c r="M18">
-        <v>110.6320394897256</v>
+        <v>112.8205096753761</v>
       </c>
       <c r="N18">
-        <v>118.1339663350956</v>
+        <v>117.478089187061</v>
       </c>
       <c r="O18">
-        <v>-7.501926845370112</v>
+        <v>-4.657579511684808</v>
       </c>
       <c r="P18">
-        <v>0.5322267007993768</v>
+        <v>0.5333074815659665</v>
       </c>
       <c r="Q18">
-        <v>0.1186756883612962</v>
+        <v>0.1189283469453214</v>
       </c>
       <c r="R18">
-        <v>0.2421198287379534</v>
+        <v>0.2479974665383406</v>
       </c>
       <c r="S18">
-        <v>0.5299588778835039</v>
+        <v>0.5397020081105051</v>
       </c>
       <c r="T18">
-        <v>0.3231871167465694</v>
+        <v>0.3186582051037913</v>
       </c>
       <c r="U18">
-        <v>0.3856928851133848</v>
+        <v>0.384630827647544</v>
       </c>
       <c r="V18">
-        <v>102.6774074074074</v>
+        <v>102.6353815789473</v>
       </c>
       <c r="W18">
-        <v>115.5981481481482</v>
+        <v>115.8996710526316</v>
       </c>
       <c r="X18">
-        <v>0.7944444444444445</v>
+        <v>0.8516447368421052</v>
       </c>
       <c r="Y18">
-        <v>0.5783941829517384</v>
+        <v>0.5789659443293773</v>
       </c>
       <c r="Z18">
-        <v>115.44</v>
+        <v>117.42</v>
       </c>
       <c r="AA18">
-        <v>-6.05</v>
+        <v>-3.3</v>
       </c>
       <c r="AB18">
         <v>-0.5231111597400365</v>
@@ -2520,16 +2520,16 @@
         <v>108.1384073962044</v>
       </c>
       <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
         <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>1</v>
       </c>
       <c r="AG18">
         <v>4</v>
       </c>
       <c r="AH18">
-        <v>0.02626574046909616</v>
+        <v>0.1736577293349261</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -2543,76 +2543,76 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E19" s="2">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="F19">
         <v>39</v>
       </c>
       <c r="G19">
-        <v>1474.216</v>
+        <v>1473.011</v>
       </c>
       <c r="H19">
-        <v>1.201</v>
+        <v>0.8465</v>
       </c>
       <c r="I19">
-        <v>1499.20008974359</v>
+        <v>1502.219455696202</v>
       </c>
       <c r="J19">
-        <v>113.275092179579</v>
+        <v>113.0560072108706</v>
       </c>
       <c r="K19">
-        <v>113.3016440661993</v>
+        <v>113.1555315700215</v>
       </c>
       <c r="L19">
-        <v>-0.02655188662032169</v>
+        <v>-0.09952435915094389</v>
       </c>
       <c r="M19">
-        <v>115.871163146587</v>
+        <v>116.7224960302648</v>
       </c>
       <c r="N19">
-        <v>116.6160660771393</v>
+        <v>115.6068470641571</v>
       </c>
       <c r="O19">
-        <v>-0.7449029305523116</v>
+        <v>1.11564896610778</v>
       </c>
       <c r="P19">
-        <v>0.5303751928025738</v>
+        <v>0.5310300147818446</v>
       </c>
       <c r="Q19">
-        <v>0.1138460417897567</v>
+        <v>0.1148191305560612</v>
       </c>
       <c r="R19">
-        <v>0.2610976153240557</v>
+        <v>0.2596557858223979</v>
       </c>
       <c r="S19">
-        <v>0.5446572488776669</v>
+        <v>0.5516678587308923</v>
       </c>
       <c r="T19">
-        <v>0.2811909101904267</v>
+        <v>0.2802912694598166</v>
       </c>
       <c r="U19">
-        <v>0.3915671480555979</v>
+        <v>0.3916902082975683</v>
       </c>
       <c r="V19">
-        <v>102.5726495726496</v>
+        <v>102.6283089905875</v>
       </c>
       <c r="W19">
-        <v>115.8783694937541</v>
+        <v>115.702693930542</v>
       </c>
       <c r="X19">
-        <v>-0.6081525312294542</v>
+        <v>-0.7137293086660175</v>
       </c>
       <c r="Y19">
-        <v>0.5732218412268369</v>
+        <v>0.5731423999687638</v>
       </c>
       <c r="Z19">
-        <v>119.01</v>
+        <v>119.55</v>
       </c>
       <c r="AA19">
-        <v>-0.5800000000000001</v>
+        <v>0.9699999999999998</v>
       </c>
       <c r="AB19">
         <v>-6.382503892565079</v>
@@ -2624,16 +2624,16 @@
         <v>116.2614936572104</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH19">
-        <v>0.6203601750664268</v>
+        <v>0.244041306718433</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2647,76 +2647,76 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G20">
-        <v>1472.717</v>
+        <v>1471.079</v>
       </c>
       <c r="H20">
-        <v>-1.2053</v>
+        <v>-1.1842</v>
       </c>
       <c r="I20">
-        <v>1508.112350649351</v>
+        <v>1506.643886075949</v>
       </c>
       <c r="J20">
-        <v>112.683905217068</v>
+        <v>112.6465355346359</v>
       </c>
       <c r="K20">
-        <v>113.1637810499641</v>
+        <v>113.3459725581583</v>
       </c>
       <c r="L20">
-        <v>-0.4798758328961982</v>
+        <v>-0.6994370235224284</v>
       </c>
       <c r="M20">
-        <v>110.8039231821918</v>
+        <v>111.6227110061938</v>
       </c>
       <c r="N20">
-        <v>117.053993054835</v>
+        <v>117.6579556089775</v>
       </c>
       <c r="O20">
-        <v>-6.250069872643262</v>
+        <v>-6.035244602783636</v>
       </c>
       <c r="P20">
-        <v>0.5514686673087634</v>
+        <v>0.5513714251681003</v>
       </c>
       <c r="Q20">
-        <v>0.1314969520718249</v>
+        <v>0.1333674969990142</v>
       </c>
       <c r="R20">
-        <v>0.2542012645605551</v>
+        <v>0.2589082396102088</v>
       </c>
       <c r="S20">
-        <v>0.5561537675967475</v>
+        <v>0.5654872432147759</v>
       </c>
       <c r="T20">
-        <v>0.2390463739618715</v>
+        <v>0.2375563605461833</v>
       </c>
       <c r="U20">
-        <v>0.499615968949041</v>
+        <v>0.4963734015555497</v>
       </c>
       <c r="V20">
-        <v>101.8584025974026</v>
+        <v>101.6188607594937</v>
       </c>
       <c r="W20">
-        <v>114.8477272727273</v>
+        <v>114.4918625678119</v>
       </c>
       <c r="X20">
-        <v>-0.3162337662337662</v>
+        <v>-0.615732368896926</v>
       </c>
       <c r="Y20">
-        <v>0.5854067192698214</v>
+        <v>0.5853122893114001</v>
       </c>
       <c r="Z20">
-        <v>113.21</v>
+        <v>112.09</v>
       </c>
       <c r="AA20">
-        <v>-6.67</v>
+        <v>-6.64</v>
       </c>
       <c r="AB20">
         <v>2.402868486532558</v>
@@ -2728,7 +2728,7 @@
         <v>110.1198746025049</v>
       </c>
       <c r="AE20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF20">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>3</v>
       </c>
       <c r="AH20">
-        <v>0.2417147176529283</v>
+        <v>0.2705080178603088</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2751,76 +2751,76 @@
         <v>83</v>
       </c>
       <c r="D21">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E21" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G21">
-        <v>1469.084</v>
+        <v>1467.705</v>
       </c>
       <c r="H21">
-        <v>1.5523</v>
+        <v>1.3562</v>
       </c>
       <c r="I21">
-        <v>1502.23767948718</v>
+        <v>1503.540658227848</v>
       </c>
       <c r="J21">
-        <v>111.7439938279652</v>
+        <v>111.1415390128851</v>
       </c>
       <c r="K21">
-        <v>112.8403974781441</v>
+        <v>112.541218772173</v>
       </c>
       <c r="L21">
-        <v>-1.096403650179004</v>
+        <v>-1.399679759287897</v>
       </c>
       <c r="M21">
-        <v>116.4470249377538</v>
+        <v>114.7722997425094</v>
       </c>
       <c r="N21">
-        <v>105.6578914589945</v>
+        <v>106.7861470826888</v>
       </c>
       <c r="O21">
-        <v>10.78913347875938</v>
+        <v>7.986152659820483</v>
       </c>
       <c r="P21">
-        <v>0.535814392799571</v>
+        <v>0.5339684415002349</v>
       </c>
       <c r="Q21">
-        <v>0.1406776936115804</v>
+        <v>0.1408861462567083</v>
       </c>
       <c r="R21">
-        <v>0.3108858344570422</v>
+        <v>0.3094710080163383</v>
       </c>
       <c r="S21">
-        <v>0.5583203755331556</v>
+        <v>0.5514971832533441</v>
       </c>
       <c r="T21">
-        <v>0.2869109022501392</v>
+        <v>0.2813212395213871</v>
       </c>
       <c r="U21">
-        <v>0.4720044560914031</v>
+        <v>0.4680032742722018</v>
       </c>
       <c r="V21">
-        <v>103.4615158371041</v>
+        <v>103.3604846292948</v>
       </c>
       <c r="W21">
-        <v>115.8484162895928</v>
+        <v>115.1533453887885</v>
       </c>
       <c r="X21">
-        <v>-0.6323529411764706</v>
+        <v>-0.8553345388788426</v>
       </c>
       <c r="Y21">
-        <v>0.5727992060974542</v>
+        <v>0.5699292362853535</v>
       </c>
       <c r="Z21">
-        <v>118.77</v>
+        <v>117.29</v>
       </c>
       <c r="AA21">
-        <v>11.29</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AB21">
         <v>-3.840928550668963</v>
@@ -2832,7 +2832,7 @@
         <v>113.1404693910572</v>
       </c>
       <c r="AE21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF21">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="AH21">
-        <v>-0.06351582479969299</v>
+        <v>0.1086756755568378</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2855,76 +2855,76 @@
         <v>84</v>
       </c>
       <c r="D22">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E22" s="2">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="F22">
         <v>39</v>
       </c>
       <c r="G22">
-        <v>1372.658</v>
+        <v>1370.931</v>
       </c>
       <c r="H22">
-        <v>-0.851</v>
+        <v>-1.6162</v>
       </c>
       <c r="I22">
-        <v>1505.856871794872</v>
+        <v>1505.927316455696</v>
       </c>
       <c r="J22">
-        <v>111.8031231018661</v>
+        <v>112.3385851645336</v>
       </c>
       <c r="K22">
-        <v>116.1595724670769</v>
+        <v>116.2291100095153</v>
       </c>
       <c r="L22">
-        <v>-4.356449365210761</v>
+        <v>-3.890524844981663</v>
       </c>
       <c r="M22">
-        <v>110.064257196725</v>
+        <v>111.448394454494</v>
       </c>
       <c r="N22">
-        <v>116.5050462230136</v>
+        <v>117.5741649604015</v>
       </c>
       <c r="O22">
-        <v>-6.440789026288607</v>
+        <v>-6.125770505907487</v>
       </c>
       <c r="P22">
-        <v>0.5268585159421868</v>
+        <v>0.5304560959855672</v>
       </c>
       <c r="Q22">
-        <v>0.117812373765015</v>
+        <v>0.1177304903746707</v>
       </c>
       <c r="R22">
-        <v>0.2644056326174869</v>
+        <v>0.2649757309657001</v>
       </c>
       <c r="S22">
-        <v>0.5299737802046415</v>
+        <v>0.5386786083126474</v>
       </c>
       <c r="T22">
-        <v>0.2871609967166655</v>
+        <v>0.2835256099653364</v>
       </c>
       <c r="U22">
-        <v>0.3595127366773336</v>
+        <v>0.3583951518507153</v>
       </c>
       <c r="V22">
-        <v>102.7050624589086</v>
+        <v>103.1421811100292</v>
       </c>
       <c r="W22">
-        <v>114.7580539119</v>
+        <v>115.9032781564427</v>
       </c>
       <c r="X22">
-        <v>-4.499671268902038</v>
+        <v>-3.903602726387536</v>
       </c>
       <c r="Y22">
-        <v>0.567564272013827</v>
+        <v>0.5705815300511676</v>
       </c>
       <c r="Z22">
-        <v>111.15</v>
+        <v>114.06</v>
       </c>
       <c r="AA22">
-        <v>-5.17</v>
+        <v>-4.85</v>
       </c>
       <c r="AB22">
         <v>-9.447870926461551</v>
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-0.8606278627813541</v>
+        <v>-1.125753642178619</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -2959,76 +2959,76 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G23">
-        <v>1373.094</v>
+        <v>1373.768</v>
       </c>
       <c r="H23">
-        <v>-1.3804</v>
+        <v>-1.3956</v>
       </c>
       <c r="I23">
-        <v>1498.463441558441</v>
+        <v>1495.444430379747</v>
       </c>
       <c r="J23">
-        <v>111.252180094363</v>
+        <v>111.4717734186185</v>
       </c>
       <c r="K23">
-        <v>116.1550504065502</v>
+        <v>115.5382265194303</v>
       </c>
       <c r="L23">
-        <v>-4.902870312187116</v>
+        <v>-4.066453100811755</v>
       </c>
       <c r="M23">
-        <v>109.3549035011661</v>
+        <v>109.6715970055938</v>
       </c>
       <c r="N23">
-        <v>121.003310630076</v>
+        <v>117.4606653266079</v>
       </c>
       <c r="O23">
-        <v>-11.64840712890994</v>
+        <v>-7.789068321014038</v>
       </c>
       <c r="P23">
-        <v>0.5476452546884372</v>
+        <v>0.5478840370761009</v>
       </c>
       <c r="Q23">
-        <v>0.1276205750134966</v>
+        <v>0.126928664795089</v>
       </c>
       <c r="R23">
-        <v>0.2310704398403645</v>
+        <v>0.2302365699782219</v>
       </c>
       <c r="S23">
-        <v>0.5432624149759964</v>
+        <v>0.5382272056121705</v>
       </c>
       <c r="T23">
-        <v>0.247879716442059</v>
+        <v>0.2487327655352116</v>
       </c>
       <c r="U23">
-        <v>0.4452596310243828</v>
+        <v>0.4433137232568473</v>
       </c>
       <c r="V23">
-        <v>104.4905600649351</v>
+        <v>104.5786351128233</v>
       </c>
       <c r="W23">
-        <v>116.0137987012987</v>
+        <v>116.3500275178866</v>
       </c>
       <c r="X23">
-        <v>-5.521103896103896</v>
+        <v>-4.627407815079802</v>
       </c>
       <c r="Y23">
-        <v>0.580137241377902</v>
+        <v>0.5809881961922844</v>
       </c>
       <c r="Z23">
-        <v>118.37</v>
+        <v>119.09</v>
       </c>
       <c r="AA23">
-        <v>-11.35</v>
+        <v>-6.91</v>
       </c>
       <c r="AB23">
         <v>-0.9433805425336231</v>
@@ -3049,7 +3049,7 @@
         <v>3</v>
       </c>
       <c r="AH23">
-        <v>-1.131679758340197</v>
+        <v>-1.037521012209358</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3063,76 +3063,76 @@
         <v>86</v>
       </c>
       <c r="D24">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E24" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F24">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G24">
-        <v>1362.435</v>
+        <v>1364.506</v>
       </c>
       <c r="H24">
-        <v>-1.7514</v>
+        <v>-1.0239</v>
       </c>
       <c r="I24">
-        <v>1504.25972368421</v>
+        <v>1505.664653846154</v>
       </c>
       <c r="J24">
-        <v>109.0684551789288</v>
+        <v>108.7200060056871</v>
       </c>
       <c r="K24">
-        <v>114.5400893188421</v>
+        <v>114.4475048869208</v>
       </c>
       <c r="L24">
-        <v>-5.471634139913344</v>
+        <v>-5.727498881233766</v>
       </c>
       <c r="M24">
-        <v>112.1692334137199</v>
+        <v>110.0150089926656</v>
       </c>
       <c r="N24">
-        <v>119.0913551269911</v>
+        <v>118.4869029729465</v>
       </c>
       <c r="O24">
-        <v>-6.922121713271194</v>
+        <v>-8.471893980280926</v>
       </c>
       <c r="P24">
-        <v>0.5293008979869331</v>
+        <v>0.5254793541560655</v>
       </c>
       <c r="Q24">
-        <v>0.1222109700964863</v>
+        <v>0.1209385704651931</v>
       </c>
       <c r="R24">
-        <v>0.2283632342554335</v>
+        <v>0.229300895320536</v>
       </c>
       <c r="S24">
-        <v>0.5322966476719313</v>
+        <v>0.5098708819227636</v>
       </c>
       <c r="T24">
-        <v>0.2921518294970483</v>
+        <v>0.2894011957409569</v>
       </c>
       <c r="U24">
-        <v>0.3495245054808123</v>
+        <v>0.3505996246563323</v>
       </c>
       <c r="V24">
-        <v>104.5609473684211</v>
+        <v>104.3595426195426</v>
       </c>
       <c r="W24">
-        <v>114.1279605263158</v>
+        <v>113.5613305613305</v>
       </c>
       <c r="X24">
-        <v>-5.366447368421053</v>
+        <v>-5.586278586278586</v>
       </c>
       <c r="Y24">
-        <v>0.5657891061305471</v>
+        <v>0.5628721515556713</v>
       </c>
       <c r="Z24">
-        <v>119.42</v>
+        <v>116.36</v>
       </c>
       <c r="AA24">
-        <v>-8.49</v>
+        <v>-9.5</v>
       </c>
       <c r="AB24">
         <v>-0.6658146557452705</v>
@@ -3144,21 +3144,21 @@
         <v>113.7784460471737</v>
       </c>
       <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
         <v>1</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
       </c>
       <c r="AG24">
         <v>3</v>
       </c>
       <c r="AH24">
-        <v>-0.4796637388182743</v>
+        <v>-0.4872142298054135</v>
       </c>
     </row>
     <row r="25" spans="1:34">
       <c r="A25">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
@@ -3167,85 +3167,85 @@
         <v>87</v>
       </c>
       <c r="D25">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E25" s="2">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="F25">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G25">
-        <v>1388.383</v>
+        <v>1369.278</v>
       </c>
       <c r="H25">
-        <v>-1.7607</v>
+        <v>-2.3429</v>
       </c>
       <c r="I25">
-        <v>1498.070844155844</v>
+        <v>1497.837649350649</v>
       </c>
       <c r="J25">
-        <v>111.5785899479371</v>
+        <v>110.8418883611541</v>
       </c>
       <c r="K25">
-        <v>117.0815591155853</v>
+        <v>116.8432644697368</v>
       </c>
       <c r="L25">
-        <v>-5.502969167648153</v>
+        <v>-6.00137610858276</v>
       </c>
       <c r="M25">
-        <v>109.3773209759907</v>
+        <v>108.3277680694841</v>
       </c>
       <c r="N25">
-        <v>123.4368102431064</v>
+        <v>128.2868272258588</v>
       </c>
       <c r="O25">
-        <v>-14.05948926711581</v>
+        <v>-19.95905915637476</v>
       </c>
       <c r="P25">
-        <v>0.568255954883955</v>
+        <v>0.535846242379462</v>
       </c>
       <c r="Q25">
-        <v>0.1333054706091563</v>
+        <v>0.1257434015764443</v>
       </c>
       <c r="R25">
-        <v>0.2090459786199414</v>
+        <v>0.2475893581274633</v>
       </c>
       <c r="S25">
-        <v>0.5698558123987442</v>
+        <v>0.5357043723334582</v>
       </c>
       <c r="T25">
-        <v>0.2272260463923873</v>
+        <v>0.2580094344861534</v>
       </c>
       <c r="U25">
-        <v>0.4515221602399083</v>
+        <v>0.437177180668999</v>
       </c>
       <c r="V25">
-        <v>99.70907563025212</v>
+        <v>103.5548495407032</v>
       </c>
       <c r="W25">
-        <v>111.109243697479</v>
+        <v>114.9708584098828</v>
       </c>
       <c r="X25">
-        <v>-5.705882352941177</v>
+        <v>-5.596769084573962</v>
       </c>
       <c r="Y25">
-        <v>0.5914968198464428</v>
+        <v>0.5725209119616749</v>
       </c>
       <c r="Z25">
-        <v>108.5</v>
+        <v>110.99</v>
       </c>
       <c r="AA25">
-        <v>-12.8</v>
+        <v>-19.43</v>
       </c>
       <c r="AB25">
-        <v>1.809266556998161</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC25">
-        <v>114.2499905834389</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD25">
-        <v>112.4407240264407</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE25">
         <v>1</v>
@@ -3257,12 +3257,12 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.605760752197909</v>
+        <v>-1.284739140581789</v>
       </c>
     </row>
     <row r="26" spans="1:34">
       <c r="A26">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
@@ -3271,85 +3271,85 @@
         <v>88</v>
       </c>
       <c r="D26">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E26" s="2">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="F26">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G26">
-        <v>1371.239</v>
+        <v>1388.975</v>
       </c>
       <c r="H26">
-        <v>-2.3774</v>
+        <v>-1.4014</v>
       </c>
       <c r="I26">
-        <v>1495.964381578947</v>
+        <v>1493.850518987342</v>
       </c>
       <c r="J26">
-        <v>110.7332058825077</v>
+        <v>111.1517692702001</v>
       </c>
       <c r="K26">
-        <v>116.7053150694251</v>
+        <v>117.8520076525522</v>
       </c>
       <c r="L26">
-        <v>-5.972109186917367</v>
+        <v>-6.700238382352076</v>
       </c>
       <c r="M26">
-        <v>107.5510202001732</v>
+        <v>108.5087612266326</v>
       </c>
       <c r="N26">
-        <v>127.2924571933358</v>
+        <v>123.1693603554744</v>
       </c>
       <c r="O26">
-        <v>-19.74143699316266</v>
+        <v>-14.66059912884175</v>
       </c>
       <c r="P26">
-        <v>0.5365676063230549</v>
+        <v>0.5640877973663239</v>
       </c>
       <c r="Q26">
-        <v>0.1273537531562534</v>
+        <v>0.1327352833107777</v>
       </c>
       <c r="R26">
-        <v>0.2482111385200751</v>
+        <v>0.2100535280990145</v>
       </c>
       <c r="S26">
-        <v>0.5350558986979356</v>
+        <v>0.5630755276015077</v>
       </c>
       <c r="T26">
-        <v>0.2561593791525417</v>
+        <v>0.227526093589286</v>
       </c>
       <c r="U26">
-        <v>0.4371278451152869</v>
+        <v>0.4577009404236284</v>
       </c>
       <c r="V26">
-        <v>103.641932132964</v>
+        <v>99.47620997766195</v>
       </c>
       <c r="W26">
-        <v>115.0204293628809</v>
+        <v>110.5208488458675</v>
       </c>
       <c r="X26">
-        <v>-5.456024930747922</v>
+        <v>-6.661950856291885</v>
       </c>
       <c r="Y26">
-        <v>0.5731856987969203</v>
+        <v>0.5881976546133644</v>
       </c>
       <c r="Z26">
-        <v>110.43</v>
+        <v>107.31</v>
       </c>
       <c r="AA26">
-        <v>-18.34</v>
+        <v>-12.59</v>
       </c>
       <c r="AB26">
-        <v>3.575252351995317</v>
+        <v>1.809266556998161</v>
       </c>
       <c r="AC26">
-        <v>114.5419381230804</v>
+        <v>114.2499905834389</v>
       </c>
       <c r="AD26">
-        <v>110.9666857710851</v>
+        <v>112.4407240264407</v>
       </c>
       <c r="AE26">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.154740442775097</v>
+        <v>-0.897464825056609</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3375,76 +3375,76 @@
         <v>89</v>
       </c>
       <c r="D27">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G27">
-        <v>1341.28</v>
+        <v>1338.362</v>
       </c>
       <c r="H27">
-        <v>0.778</v>
+        <v>1.0053</v>
       </c>
       <c r="I27">
-        <v>1502.115714285714</v>
+        <v>1504.686202531646</v>
       </c>
       <c r="J27">
-        <v>109.5613898132286</v>
+        <v>109.604642909582</v>
       </c>
       <c r="K27">
-        <v>117.0658996915581</v>
+        <v>116.4586351396482</v>
       </c>
       <c r="L27">
-        <v>-7.504509878329517</v>
+        <v>-6.853992230066176</v>
       </c>
       <c r="M27">
-        <v>120.3266862918008</v>
+        <v>118.711756459824</v>
       </c>
       <c r="N27">
-        <v>123.7731586659914</v>
+        <v>116.5214522098985</v>
       </c>
       <c r="O27">
-        <v>-3.446472374190611</v>
+        <v>2.19030424992541</v>
       </c>
       <c r="P27">
-        <v>0.5329420487239813</v>
+        <v>0.5344897290409717</v>
       </c>
       <c r="Q27">
-        <v>0.1201250253827643</v>
+        <v>0.121044222520725</v>
       </c>
       <c r="R27">
-        <v>0.2154556389282515</v>
+        <v>0.2152062697179775</v>
       </c>
       <c r="S27">
-        <v>0.6077219227536644</v>
+        <v>0.5937958518474428</v>
       </c>
       <c r="T27">
-        <v>0.2558316856084696</v>
+        <v>0.255010003468748</v>
       </c>
       <c r="U27">
-        <v>0.4222641072598058</v>
+        <v>0.4176671386014152</v>
       </c>
       <c r="V27">
-        <v>102.9876470588235</v>
+        <v>103.1289653274628</v>
       </c>
       <c r="W27">
-        <v>112.4495798319328</v>
+        <v>112.6477710511832</v>
       </c>
       <c r="X27">
-        <v>-8.231092436974789</v>
+        <v>-7.554760594386352</v>
       </c>
       <c r="Y27">
-        <v>0.5687821075328068</v>
+        <v>0.5697917319582749</v>
       </c>
       <c r="Z27">
-        <v>121.5</v>
+        <v>121.11</v>
       </c>
       <c r="AA27">
-        <v>-5.489999999999999</v>
+        <v>-0.9700000000000002</v>
       </c>
       <c r="AB27">
         <v>2.960186837728194</v>
@@ -3465,7 +3465,7 @@
         <v>3</v>
       </c>
       <c r="AH27">
-        <v>-0.9161424297615558</v>
+        <v>-1.104622051053789</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3479,76 +3479,76 @@
         <v>90</v>
       </c>
       <c r="D28">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G28">
-        <v>1304.2</v>
+        <v>1303.464</v>
       </c>
       <c r="H28">
-        <v>-1.3675</v>
+        <v>-1.6441</v>
       </c>
       <c r="I28">
-        <v>1513.868615384615</v>
+        <v>1517.014518987342</v>
       </c>
       <c r="J28">
-        <v>111.6888301670213</v>
+        <v>111.8513171648238</v>
       </c>
       <c r="K28">
-        <v>120.5577269595959</v>
+        <v>120.5130857087986</v>
       </c>
       <c r="L28">
-        <v>-8.868896792574599</v>
+        <v>-8.661768543974819</v>
       </c>
       <c r="M28">
-        <v>110.3293505008559</v>
+        <v>111.6252517777173</v>
       </c>
       <c r="N28">
-        <v>124.0123647529239</v>
+        <v>123.8249074608383</v>
       </c>
       <c r="O28">
-        <v>-13.68301425206802</v>
+        <v>-12.19965568312098</v>
       </c>
       <c r="P28">
-        <v>0.5364035993920134</v>
+        <v>0.5373487742905084</v>
       </c>
       <c r="Q28">
-        <v>0.1281278704792397</v>
+        <v>0.1279687305136955</v>
       </c>
       <c r="R28">
-        <v>0.2615665470619492</v>
+        <v>0.2602338060505711</v>
       </c>
       <c r="S28">
-        <v>0.5303076758380809</v>
+        <v>0.5360769066073117</v>
       </c>
       <c r="T28">
-        <v>0.279906295422698</v>
+        <v>0.2803697149988327</v>
       </c>
       <c r="U28">
-        <v>0.4059058972603802</v>
+        <v>0.4038185184287812</v>
       </c>
       <c r="V28">
-        <v>104.744</v>
+        <v>105.0981042095967</v>
       </c>
       <c r="W28">
-        <v>117.025</v>
+        <v>117.56402708272</v>
       </c>
       <c r="X28">
-        <v>-9.112500000000001</v>
+        <v>-9.022372681778039</v>
       </c>
       <c r="Y28">
-        <v>0.5755322592068655</v>
+        <v>0.576732073823026</v>
       </c>
       <c r="Z28">
-        <v>116.04</v>
+        <v>118.64</v>
       </c>
       <c r="AA28">
-        <v>-16.1</v>
+        <v>-14.41</v>
       </c>
       <c r="AB28">
         <v>-9.725925288085115</v>
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.8521257029301433</v>
+        <v>-0.984078192395561</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3583,76 +3583,76 @@
         <v>91</v>
       </c>
       <c r="D29">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E29" s="2">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="F29">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G29">
-        <v>1315.694</v>
+        <v>1312.908</v>
       </c>
       <c r="H29">
-        <v>-0.7466</v>
+        <v>-0.4694</v>
       </c>
       <c r="I29">
-        <v>1514.897512820513</v>
+        <v>1515.35135443038</v>
       </c>
       <c r="J29">
-        <v>109.4686484601757</v>
+        <v>109.5123257995211</v>
       </c>
       <c r="K29">
-        <v>119.0759022586879</v>
+        <v>118.7903909663357</v>
       </c>
       <c r="L29">
-        <v>-9.607253798512208</v>
+        <v>-9.27806516681464</v>
       </c>
       <c r="M29">
-        <v>112.9751201830539</v>
+        <v>112.7969310994889</v>
       </c>
       <c r="N29">
-        <v>124.5586619996969</v>
+        <v>124.845136565112</v>
       </c>
       <c r="O29">
-        <v>-11.58354181664297</v>
+        <v>-12.04820546562315</v>
       </c>
       <c r="P29">
-        <v>0.5258060961294203</v>
+        <v>0.5252883934522501</v>
       </c>
       <c r="Q29">
-        <v>0.1219210803286885</v>
+        <v>0.1214001847069728</v>
       </c>
       <c r="R29">
-        <v>0.257228453628124</v>
+        <v>0.258475482579947</v>
       </c>
       <c r="S29">
-        <v>0.543816517819914</v>
+        <v>0.5422059701525712</v>
       </c>
       <c r="T29">
-        <v>0.2555505293930385</v>
+        <v>0.2543099815435653</v>
       </c>
       <c r="U29">
-        <v>0.3390151252128361</v>
+        <v>0.3389611964379824</v>
       </c>
       <c r="V29">
-        <v>101.6807100591716</v>
+        <v>101.5152974683545</v>
       </c>
       <c r="W29">
-        <v>110.8987508218277</v>
+        <v>110.7759493670886</v>
       </c>
       <c r="X29">
-        <v>-10.48717948717949</v>
+        <v>-10.10949367088607</v>
       </c>
       <c r="Y29">
-        <v>0.5606011159865449</v>
+        <v>0.5602126035248454</v>
       </c>
       <c r="Z29">
-        <v>111.97</v>
+        <v>110.94</v>
       </c>
       <c r="AA29">
-        <v>-12.17</v>
+        <v>-12.83</v>
       </c>
       <c r="AB29">
         <v>-0.1619477822758719</v>
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.556891502883429</v>
+        <v>-1.499480788820034</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3687,76 +3687,76 @@
         <v>92</v>
       </c>
       <c r="D30">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E30" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F30">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G30">
-        <v>1288.637</v>
+        <v>1290.905</v>
       </c>
       <c r="H30">
-        <v>-1.1494</v>
+        <v>-0.8539</v>
       </c>
       <c r="I30">
-        <v>1503.110285714286</v>
+        <v>1498.539291139241</v>
       </c>
       <c r="J30">
-        <v>107.1550127280252</v>
+        <v>106.4414554831461</v>
       </c>
       <c r="K30">
-        <v>117.1535341213211</v>
+        <v>116.9457223329821</v>
       </c>
       <c r="L30">
-        <v>-9.998521393295933</v>
+        <v>-10.50426684983602</v>
       </c>
       <c r="M30">
-        <v>103.1490758876266</v>
+        <v>103.4042404205238</v>
       </c>
       <c r="N30">
-        <v>116.523495476974</v>
+        <v>114.8923576237037</v>
       </c>
       <c r="O30">
-        <v>-13.3744195893474</v>
+        <v>-11.48811720317985</v>
       </c>
       <c r="P30">
-        <v>0.5230756603255347</v>
+        <v>0.5197713512650058</v>
       </c>
       <c r="Q30">
-        <v>0.1377590162388956</v>
+        <v>0.1366221993410033</v>
       </c>
       <c r="R30">
-        <v>0.2389793770858647</v>
+        <v>0.2338726923229511</v>
       </c>
       <c r="S30">
-        <v>0.5104303968084217</v>
+        <v>0.5138521102632525</v>
       </c>
       <c r="T30">
-        <v>0.2764860305422571</v>
+        <v>0.2751443161454343</v>
       </c>
       <c r="U30">
-        <v>0.457120806280249</v>
+        <v>0.4542963205174071</v>
       </c>
       <c r="V30">
-        <v>99.19193438140806</v>
+        <v>99.26963877740043</v>
       </c>
       <c r="W30">
-        <v>106.4453178400546</v>
+        <v>105.8184624884224</v>
       </c>
       <c r="X30">
-        <v>-9.326042378673957</v>
+        <v>-9.821241123803643</v>
       </c>
       <c r="Y30">
-        <v>0.5625176402818755</v>
+        <v>0.5590774457794662</v>
       </c>
       <c r="Z30">
         <v>103.36</v>
       </c>
       <c r="AA30">
-        <v>-13.44</v>
+        <v>-11.54</v>
       </c>
       <c r="AB30">
         <v>-6.499587896466165</v>
@@ -3777,7 +3777,7 @@
         <v>3</v>
       </c>
       <c r="AH30">
-        <v>-1.806616704962209</v>
+        <v>-1.783479677857188</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3791,76 +3791,76 @@
         <v>93</v>
       </c>
       <c r="D31">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G31">
-        <v>1254.562</v>
+        <v>1251.266</v>
       </c>
       <c r="H31">
-        <v>-0.4957</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="I31">
-        <v>1505.654064935065</v>
+        <v>1501.204620253164</v>
       </c>
       <c r="J31">
-        <v>109.0243008059617</v>
+        <v>108.6144668824543</v>
       </c>
       <c r="K31">
-        <v>120.3753400076893</v>
+        <v>120.1501244813441</v>
       </c>
       <c r="L31">
-        <v>-11.35103920172752</v>
+        <v>-11.53565759888977</v>
       </c>
       <c r="M31">
-        <v>110.376192880436</v>
+        <v>108.7610623965598</v>
       </c>
       <c r="N31">
-        <v>125.9722269097043</v>
+        <v>124.4728035616271</v>
       </c>
       <c r="O31">
-        <v>-15.59603402926827</v>
+        <v>-15.71174116506733</v>
       </c>
       <c r="P31">
-        <v>0.5369226305407879</v>
+        <v>0.5337839548056479</v>
       </c>
       <c r="Q31">
-        <v>0.13216393349989</v>
+        <v>0.1324078153619469</v>
       </c>
       <c r="R31">
-        <v>0.2400163112822092</v>
+        <v>0.2406071873250716</v>
       </c>
       <c r="S31">
-        <v>0.5576450940786088</v>
+        <v>0.5402717412963134</v>
       </c>
       <c r="T31">
-        <v>0.2387975174692601</v>
+        <v>0.2386930964370224</v>
       </c>
       <c r="U31">
-        <v>0.4022970109964032</v>
+        <v>0.4034472436154499</v>
       </c>
       <c r="V31">
-        <v>103.7149206349207</v>
+        <v>103.8549636412604</v>
       </c>
       <c r="W31">
-        <v>113.0698412698412</v>
+        <v>112.7573390789119</v>
       </c>
       <c r="X31">
-        <v>-11.53650793650793</v>
+        <v>-11.81766765418798</v>
       </c>
       <c r="Y31">
-        <v>0.5684178407559159</v>
+        <v>0.5657368787383508</v>
       </c>
       <c r="Z31">
-        <v>115.09</v>
+        <v>114.48</v>
       </c>
       <c r="AA31">
-        <v>-15.18</v>
+        <v>-15.86</v>
       </c>
       <c r="AB31">
         <v>-12.72363327068823</v>
@@ -3872,16 +3872,16 @@
         <v>117.4454989237997</v>
       </c>
       <c r="AE31">
+        <v>1</v>
+      </c>
+      <c r="AF31">
         <v>0</v>
       </c>
-      <c r="AF31">
-        <v>1</v>
-      </c>
       <c r="AG31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH31">
-        <v>-1.194513944878924</v>
+        <v>-1.266737760470074</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -142,36 +142,36 @@
     <t>Cleveland Cavaliers</t>
   </si>
   <si>
+    <t>Minnesota Timberwolves</t>
+  </si>
+  <si>
     <t>Charlotte Hornets</t>
   </si>
   <si>
-    <t>Minnesota Timberwolves</t>
+    <t>Los Angeles Lakers</t>
   </si>
   <si>
     <t>Toronto Raptors</t>
   </si>
   <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>LA Clippers</t>
+  </si>
+  <si>
     <t>Atlanta Hawks</t>
   </si>
   <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>LA Clippers</t>
-  </si>
-  <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
-    <t>Miami Heat</t>
+    <t>Philadelphia 76ers</t>
   </si>
   <si>
     <t>Orlando Magic</t>
   </si>
   <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
     <t>Golden State Warriors</t>
   </si>
   <si>
@@ -187,12 +187,12 @@
     <t>Dallas Mavericks</t>
   </si>
   <si>
+    <t>Milwaukee Bucks</t>
+  </si>
+  <si>
     <t>Memphis Grizzlies</t>
   </si>
   <si>
-    <t>Milwaukee Bucks</t>
-  </si>
-  <si>
     <t>Indiana Pacers</t>
   </si>
   <si>
@@ -232,36 +232,36 @@
     <t>CLE</t>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>CHA</t>
   </si>
   <si>
-    <t>MIN</t>
+    <t>LAL</t>
   </si>
   <si>
     <t>TOR</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
     <t>PHX</t>
   </si>
   <si>
-    <t>MIA</t>
+    <t>PHI</t>
   </si>
   <si>
     <t>ORL</t>
   </si>
   <si>
-    <t>PHI</t>
-  </si>
-  <si>
     <t>GSW</t>
   </si>
   <si>
@@ -277,10 +277,10 @@
     <t>DAL</t>
   </si>
   <si>
+    <t>MIL</t>
+  </si>
+  <si>
     <t>MEM</t>
-  </si>
-  <si>
-    <t>MIL</t>
   </si>
   <si>
     <t>IND</t>
@@ -775,76 +775,76 @@
         <v>64</v>
       </c>
       <c r="D2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E2" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>1769.519</v>
+        <v>1764.102</v>
       </c>
       <c r="H2">
-        <v>1.6656</v>
+        <v>2.0618</v>
       </c>
       <c r="I2">
-        <v>1498.208871794872</v>
+        <v>1500.28485</v>
       </c>
       <c r="J2">
-        <v>117.6484940385879</v>
+        <v>116.9132749472211</v>
       </c>
       <c r="K2">
-        <v>105.3702957725928</v>
+        <v>106.2630499540704</v>
       </c>
       <c r="L2">
-        <v>12.27819826599503</v>
+        <v>10.65022499315071</v>
       </c>
       <c r="M2">
-        <v>123.6262450758385</v>
+        <v>119.8427936428078</v>
       </c>
       <c r="N2">
-        <v>102.4591453767432</v>
+        <v>108.1168925755339</v>
       </c>
       <c r="O2">
-        <v>21.16709969909541</v>
+        <v>11.7259010672738</v>
       </c>
       <c r="P2">
-        <v>0.5667742882617324</v>
+        <v>0.5632583602522824</v>
       </c>
       <c r="Q2">
-        <v>0.1080559262096478</v>
+        <v>0.1073938433911547</v>
       </c>
       <c r="R2">
-        <v>0.2195502668751287</v>
+        <v>0.2196580100677842</v>
       </c>
       <c r="S2">
-        <v>0.6024283188129468</v>
+        <v>0.5842705862967622</v>
       </c>
       <c r="T2">
-        <v>0.2674797075371117</v>
+        <v>0.260409154694913</v>
       </c>
       <c r="U2">
-        <v>0.4254678923291795</v>
+        <v>0.4276387920316667</v>
       </c>
       <c r="V2">
-        <v>101.8349321266968</v>
+        <v>101.8549714285714</v>
       </c>
       <c r="W2">
-        <v>119.6504524886878</v>
+        <v>118.8828571428571</v>
       </c>
       <c r="X2">
-        <v>12.35067873303167</v>
+        <v>10.59714285714286</v>
       </c>
       <c r="Y2">
-        <v>0.6050630160415154</v>
+        <v>0.6002190721862691</v>
       </c>
       <c r="Z2">
-        <v>125.21</v>
+        <v>121.09</v>
       </c>
       <c r="AA2">
-        <v>20.43</v>
+        <v>10.75</v>
       </c>
       <c r="AB2">
         <v>11.54061896828745</v>
@@ -856,16 +856,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
         <v>0</v>
       </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
       <c r="AG2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH2">
-        <v>-0.8684245964312617</v>
+        <v>-0.6662511097089785</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -879,76 +879,76 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E3" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>1738.935</v>
+        <v>1740.684</v>
       </c>
       <c r="H3">
-        <v>2.1342</v>
+        <v>1.2096</v>
       </c>
       <c r="I3">
-        <v>1508.406166666667</v>
+        <v>1506.0862875</v>
       </c>
       <c r="J3">
-        <v>117.4767544571925</v>
+        <v>117.7546797640171</v>
       </c>
       <c r="K3">
-        <v>108.8080435002499</v>
+        <v>109.5250557544995</v>
       </c>
       <c r="L3">
-        <v>8.668710956942585</v>
+        <v>8.229624009517593</v>
       </c>
       <c r="M3">
-        <v>120.1399996005027</v>
+        <v>121.8543160436847</v>
       </c>
       <c r="N3">
-        <v>105.8519930993021</v>
+        <v>108.5131608435764</v>
       </c>
       <c r="O3">
-        <v>14.28800650120055</v>
+        <v>13.34115520010841</v>
       </c>
       <c r="P3">
-        <v>0.5607256769333011</v>
+        <v>0.5607518815416633</v>
       </c>
       <c r="Q3">
-        <v>0.1119768579435056</v>
+        <v>0.1105675804191624</v>
       </c>
       <c r="R3">
-        <v>0.2582367857545545</v>
+        <v>0.2599241918883525</v>
       </c>
       <c r="S3">
-        <v>0.5695485078501739</v>
+        <v>0.573759506831634</v>
       </c>
       <c r="T3">
-        <v>0.2767556546471427</v>
+        <v>0.275386072016686</v>
       </c>
       <c r="U3">
-        <v>0.4203151483176745</v>
+        <v>0.421865700577073</v>
       </c>
       <c r="V3">
-        <v>102.01375</v>
+        <v>101.9809756097561</v>
       </c>
       <c r="W3">
-        <v>119.625</v>
+        <v>119.9146341463415</v>
       </c>
       <c r="X3">
-        <v>8.512499999999999</v>
+        <v>8.158536585365853</v>
       </c>
       <c r="Y3">
-        <v>0.5963716228708283</v>
+        <v>0.5963566573981414</v>
       </c>
       <c r="Z3">
-        <v>123.16</v>
+        <v>125.2</v>
       </c>
       <c r="AA3">
-        <v>15.23</v>
+        <v>14.39</v>
       </c>
       <c r="AB3">
         <v>-2.513643863094118</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH3">
-        <v>1.265811702660106</v>
+        <v>0.8493059619118966</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -983,76 +983,76 @@
         <v>66</v>
       </c>
       <c r="D4">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E4" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>1680.746</v>
+        <v>1687.659</v>
       </c>
       <c r="H4">
-        <v>0.8821</v>
+        <v>1.1559</v>
       </c>
       <c r="I4">
-        <v>1496.208705128205</v>
+        <v>1496.0478375</v>
       </c>
       <c r="J4">
-        <v>115.4609697176974</v>
+        <v>115.6103956612828</v>
       </c>
       <c r="K4">
-        <v>107.6627038123182</v>
+        <v>107.6945038484208</v>
       </c>
       <c r="L4">
-        <v>7.798265905379202</v>
+        <v>7.915891812861926</v>
       </c>
       <c r="M4">
-        <v>117.982948995146</v>
+        <v>119.8649433120767</v>
       </c>
       <c r="N4">
-        <v>106.3804728052524</v>
+        <v>106.4361929688154</v>
       </c>
       <c r="O4">
-        <v>11.60247618989356</v>
+        <v>13.42875034326124</v>
       </c>
       <c r="P4">
-        <v>0.5488980195844952</v>
+        <v>0.5507988638619832</v>
       </c>
       <c r="Q4">
-        <v>0.1233378817507484</v>
+        <v>0.1240593293444159</v>
       </c>
       <c r="R4">
-        <v>0.3053339468968531</v>
+        <v>0.3059060468335256</v>
       </c>
       <c r="S4">
-        <v>0.5788210036565079</v>
+        <v>0.5906929127225311</v>
       </c>
       <c r="T4">
-        <v>0.2954211926033668</v>
+        <v>0.2933532745723434</v>
       </c>
       <c r="U4">
-        <v>0.3472563105733588</v>
+        <v>0.3473183094591422</v>
       </c>
       <c r="V4">
-        <v>101.9793006993007</v>
+        <v>102.0868014705882</v>
       </c>
       <c r="W4">
-        <v>117.7176573426574</v>
+        <v>117.9801470588235</v>
       </c>
       <c r="X4">
-        <v>8.120920745920746</v>
+        <v>8.178308823529411</v>
       </c>
       <c r="Y4">
-        <v>0.5853846825652759</v>
+        <v>0.5868339963733044</v>
       </c>
       <c r="Z4">
-        <v>118.82</v>
+        <v>120.85</v>
       </c>
       <c r="AA4">
-        <v>9.619999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="AB4">
         <v>1.549391602834736</v>
@@ -1073,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="AH4">
-        <v>0.8722884576791512</v>
+        <v>1.140005843727795</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1087,76 +1087,76 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E5" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>1673.996</v>
+        <v>1672.097</v>
       </c>
       <c r="H5">
-        <v>2.0279</v>
+        <v>1.6605</v>
       </c>
       <c r="I5">
-        <v>1491.547227848101</v>
+        <v>1492.080469135802</v>
       </c>
       <c r="J5">
-        <v>117.9229440256062</v>
+        <v>117.8340667576958</v>
       </c>
       <c r="K5">
-        <v>110.7493992088959</v>
+        <v>110.2326502268895</v>
       </c>
       <c r="L5">
-        <v>7.173544816710401</v>
+        <v>7.601416530806378</v>
       </c>
       <c r="M5">
-        <v>120.327259301116</v>
+        <v>122.823052319119</v>
       </c>
       <c r="N5">
-        <v>112.1552529601885</v>
+        <v>111.2468541567881</v>
       </c>
       <c r="O5">
-        <v>8.17200634092748</v>
+        <v>11.57619816233083</v>
       </c>
       <c r="P5">
-        <v>0.5521274473984394</v>
+        <v>0.5531895830281515</v>
       </c>
       <c r="Q5">
-        <v>0.1038608322360771</v>
+        <v>0.1051189871210553</v>
       </c>
       <c r="R5">
-        <v>0.2931543819664709</v>
+        <v>0.2890820057519844</v>
       </c>
       <c r="S5">
-        <v>0.5640081718543285</v>
+        <v>0.5906896617872682</v>
       </c>
       <c r="T5">
-        <v>0.2110245087005032</v>
+        <v>0.211641895060464</v>
       </c>
       <c r="U5">
-        <v>0.4648622155423958</v>
+        <v>0.4686385426947525</v>
       </c>
       <c r="V5">
-        <v>96.90247168554298</v>
+        <v>97.39728982951205</v>
       </c>
       <c r="W5">
-        <v>114.3934043970687</v>
+        <v>114.8318636096413</v>
       </c>
       <c r="X5">
-        <v>7.311125916055962</v>
+        <v>7.663433274544386</v>
       </c>
       <c r="Y5">
-        <v>0.5823826303045305</v>
+        <v>0.5838723733985678</v>
       </c>
       <c r="Z5">
-        <v>115.09</v>
+        <v>119.48</v>
       </c>
       <c r="AA5">
-        <v>7.68</v>
+        <v>11.03</v>
       </c>
       <c r="AB5">
         <v>9.220352523846751</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH5">
-        <v>1.63870366444443</v>
+        <v>0.03038678962681212</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1191,76 +1191,76 @@
         <v>68</v>
       </c>
       <c r="D6">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E6" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>1653.738</v>
+        <v>1659.456</v>
       </c>
       <c r="H6">
-        <v>-1.3253</v>
+        <v>-0.4289</v>
       </c>
       <c r="I6">
-        <v>1488.382846153846</v>
+        <v>1491.1179625</v>
       </c>
       <c r="J6">
-        <v>117.858857916099</v>
+        <v>117.4821467291267</v>
       </c>
       <c r="K6">
-        <v>111.0679353852492</v>
+        <v>110.898988049768</v>
       </c>
       <c r="L6">
-        <v>6.790922530849887</v>
+        <v>6.583158679358667</v>
       </c>
       <c r="M6">
-        <v>122.5223398479738</v>
+        <v>121.0345935504245</v>
       </c>
       <c r="N6">
-        <v>114.9254668798314</v>
+        <v>115.6207584862354</v>
       </c>
       <c r="O6">
-        <v>7.596872968142457</v>
+        <v>5.413835064189071</v>
       </c>
       <c r="P6">
-        <v>0.5573301994672366</v>
+        <v>0.5556388603984453</v>
       </c>
       <c r="Q6">
-        <v>0.1150007014141735</v>
+        <v>0.1149244657950105</v>
       </c>
       <c r="R6">
-        <v>0.2921701303425507</v>
+        <v>0.2917389614411804</v>
       </c>
       <c r="S6">
-        <v>0.5809929198609369</v>
+        <v>0.58108860699544</v>
       </c>
       <c r="T6">
-        <v>0.2378030635145492</v>
+        <v>0.2363069559585412</v>
       </c>
       <c r="U6">
-        <v>0.4289852788646132</v>
+        <v>0.4290621510752881</v>
       </c>
       <c r="V6">
-        <v>99.05668639053255</v>
+        <v>98.99536585365854</v>
       </c>
       <c r="W6">
-        <v>116.5095332018409</v>
+        <v>116.0121951219512</v>
       </c>
       <c r="X6">
-        <v>6.374753451676529</v>
+        <v>6.012195121951219</v>
       </c>
       <c r="Y6">
-        <v>0.5900315981097985</v>
+        <v>0.5880973439850578</v>
       </c>
       <c r="Z6">
-        <v>116.14</v>
+        <v>114.09</v>
       </c>
       <c r="AA6">
-        <v>7.71</v>
+        <v>5.35</v>
       </c>
       <c r="AB6">
         <v>2.775420617465777</v>
@@ -1272,16 +1272,16 @@
         <v>112.335295999638</v>
       </c>
       <c r="AE6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF6">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6">
-        <v>1.286267411500424</v>
+        <v>-0.140115325253566</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1295,76 +1295,76 @@
         <v>69</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E7" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>1593.669</v>
+        <v>1591.505</v>
       </c>
       <c r="H7">
-        <v>2.1301</v>
+        <v>2.5318</v>
       </c>
       <c r="I7">
-        <v>1494.003632911392</v>
+        <v>1494.639592592593</v>
       </c>
       <c r="J7">
-        <v>115.6933541325044</v>
+        <v>116.1261142955221</v>
       </c>
       <c r="K7">
-        <v>110.7700909988529</v>
+        <v>110.8492473446616</v>
       </c>
       <c r="L7">
-        <v>4.923263133651576</v>
+        <v>5.276866950860388</v>
       </c>
       <c r="M7">
-        <v>122.0238535344921</v>
+        <v>123.3463153357207</v>
       </c>
       <c r="N7">
-        <v>110.1191203896841</v>
+        <v>108.6507235196123</v>
       </c>
       <c r="O7">
-        <v>11.90473314480801</v>
+        <v>14.69559181610846</v>
       </c>
       <c r="P7">
-        <v>0.5440089246782009</v>
+        <v>0.5451181025519822</v>
       </c>
       <c r="Q7">
-        <v>0.1266128899290344</v>
+        <v>0.1254588717427119</v>
       </c>
       <c r="R7">
-        <v>0.3439162304041541</v>
+        <v>0.3462547355904307</v>
       </c>
       <c r="S7">
-        <v>0.5687663006501065</v>
+        <v>0.5641559442031023</v>
       </c>
       <c r="T7">
-        <v>0.2622670465377827</v>
+        <v>0.2632562388546684</v>
       </c>
       <c r="U7">
-        <v>0.3507746169168276</v>
+        <v>0.351912753408883</v>
       </c>
       <c r="V7">
-        <v>99.23696202531647</v>
+        <v>99.39277777777779</v>
       </c>
       <c r="W7">
-        <v>114.7844585091421</v>
+        <v>115.4104938271605</v>
       </c>
       <c r="X7">
-        <v>5.105133614627285</v>
+        <v>5.49438832772166</v>
       </c>
       <c r="Y7">
-        <v>0.5769914276758995</v>
+        <v>0.5781705646770098</v>
       </c>
       <c r="Z7">
-        <v>120.56</v>
+        <v>122.28</v>
       </c>
       <c r="AA7">
-        <v>10.55</v>
+        <v>13.81</v>
       </c>
       <c r="AB7">
         <v>3.413694058608522</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH7">
-        <v>0.8282632983909106</v>
+        <v>-0.522833929919282</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1399,76 +1399,76 @@
         <v>70</v>
       </c>
       <c r="D8">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E8" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>1606.552</v>
+        <v>1616.966</v>
       </c>
       <c r="H8">
-        <v>2.3051</v>
+        <v>2.5671</v>
       </c>
       <c r="I8">
-        <v>1501.758721518987</v>
+        <v>1503.475345679012</v>
       </c>
       <c r="J8">
-        <v>120.4507078756702</v>
+        <v>120.4359953151273</v>
       </c>
       <c r="K8">
-        <v>115.5572099086143</v>
+        <v>115.3362286216927</v>
       </c>
       <c r="L8">
-        <v>4.893497967055835</v>
+        <v>5.099766693434593</v>
       </c>
       <c r="M8">
-        <v>125.6183453136214</v>
+        <v>126.6975204785679</v>
       </c>
       <c r="N8">
-        <v>118.3642586489945</v>
+        <v>117.0436639215076</v>
       </c>
       <c r="O8">
-        <v>7.254086664626874</v>
+        <v>9.653856557060355</v>
       </c>
       <c r="P8">
-        <v>0.5790279656640467</v>
+        <v>0.5773653575047751</v>
       </c>
       <c r="Q8">
-        <v>0.1089699987072154</v>
+        <v>0.1086484651027513</v>
       </c>
       <c r="R8">
-        <v>0.2340902320474838</v>
+        <v>0.2381079146426767</v>
       </c>
       <c r="S8">
-        <v>0.6064862192338055</v>
+        <v>0.6037980471907948</v>
       </c>
       <c r="T8">
-        <v>0.2993117887150277</v>
+        <v>0.2962978156392768</v>
       </c>
       <c r="U8">
-        <v>0.4078825005605269</v>
+        <v>0.4056715938787011</v>
       </c>
       <c r="V8">
-        <v>101.4071183916605</v>
+        <v>101.4497942386832</v>
       </c>
       <c r="W8">
-        <v>122.1783320923306</v>
+        <v>122.1666666666667</v>
       </c>
       <c r="X8">
-        <v>5.1072226358898</v>
+        <v>5.222908093278464</v>
       </c>
       <c r="Y8">
-        <v>0.6180660018775607</v>
+        <v>0.6162849962270014</v>
       </c>
       <c r="Z8">
-        <v>129.52</v>
+        <v>130.88</v>
       </c>
       <c r="AA8">
-        <v>8.27</v>
+        <v>10.99</v>
       </c>
       <c r="AB8">
         <v>2.722616812266775</v>
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="AH8">
-        <v>1.798225502042187</v>
+        <v>1.229413159416357</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1503,76 +1503,76 @@
         <v>71</v>
       </c>
       <c r="D9">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E9" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G9">
-        <v>1642.167</v>
+        <v>1636.739</v>
       </c>
       <c r="H9">
-        <v>-0.5165</v>
+        <v>-0.3377</v>
       </c>
       <c r="I9">
-        <v>1485.946151898734</v>
+        <v>1487.012209876543</v>
       </c>
       <c r="J9">
-        <v>117.1665092173712</v>
+        <v>117.2471280340223</v>
       </c>
       <c r="K9">
-        <v>112.8161748740272</v>
+        <v>112.9859451982325</v>
       </c>
       <c r="L9">
-        <v>4.350334343343985</v>
+        <v>4.261182835789736</v>
       </c>
       <c r="M9">
-        <v>120.944599387484</v>
+        <v>121.1617644513356</v>
       </c>
       <c r="N9">
-        <v>116.5426102853361</v>
+        <v>118.6730230740667</v>
       </c>
       <c r="O9">
-        <v>4.401989102147839</v>
+        <v>2.488741377268961</v>
       </c>
       <c r="P9">
-        <v>0.5617467379738843</v>
+        <v>0.5632306931627614</v>
       </c>
       <c r="Q9">
-        <v>0.1155315095967123</v>
+        <v>0.1175664044372691</v>
       </c>
       <c r="R9">
-        <v>0.2639215667607245</v>
+        <v>0.2677442248019539</v>
       </c>
       <c r="S9">
-        <v>0.5773399738935827</v>
+        <v>0.5849463272345193</v>
       </c>
       <c r="T9">
-        <v>0.271980493842378</v>
+        <v>0.2686276571501762</v>
       </c>
       <c r="U9">
-        <v>0.4412331763264081</v>
+        <v>0.4416279673178116</v>
       </c>
       <c r="V9">
-        <v>102.2337508327782</v>
+        <v>102.1880758807588</v>
       </c>
       <c r="W9">
-        <v>119.6459027315124</v>
+        <v>119.6537187594099</v>
       </c>
       <c r="X9">
-        <v>4.348434377081945</v>
+        <v>4.219512195121951</v>
       </c>
       <c r="Y9">
-        <v>0.5954192520569199</v>
+        <v>0.5964782171009012</v>
       </c>
       <c r="Z9">
-        <v>122.54</v>
+        <v>123.16</v>
       </c>
       <c r="AA9">
-        <v>4.739999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="AB9">
         <v>9.967224035556209</v>
@@ -1590,15 +1590,15 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH9">
-        <v>0.6144762147516616</v>
+        <v>-0.1608482777598297</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
@@ -1607,85 +1607,85 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E10" s="2">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G10">
-        <v>1593.135</v>
+        <v>1570.357</v>
       </c>
       <c r="H10">
-        <v>0.6887</v>
+        <v>-1.5468</v>
       </c>
       <c r="I10">
-        <v>1493.85729113924</v>
+        <v>1502.893111111111</v>
       </c>
       <c r="J10">
-        <v>116.0895593539149</v>
+        <v>115.0078782496342</v>
       </c>
       <c r="K10">
-        <v>112.7071454866825</v>
+        <v>111.234850723</v>
       </c>
       <c r="L10">
-        <v>3.382413867232365</v>
+        <v>3.773027526634123</v>
       </c>
       <c r="M10">
-        <v>122.2871234716915</v>
+        <v>109.9733259753153</v>
       </c>
       <c r="N10">
-        <v>110.1099658084995</v>
+        <v>110.5562272513674</v>
       </c>
       <c r="O10">
-        <v>12.17715766319199</v>
+        <v>-0.5829012760520715</v>
       </c>
       <c r="P10">
-        <v>0.5538846716509681</v>
+        <v>0.559544773828665</v>
       </c>
       <c r="Q10">
-        <v>0.1271439745227298</v>
+        <v>0.123807232665508</v>
       </c>
       <c r="R10">
-        <v>0.3056206346965748</v>
+        <v>0.2561480558681392</v>
       </c>
       <c r="S10">
-        <v>0.5827500307623292</v>
+        <v>0.5350634986166211</v>
       </c>
       <c r="T10">
-        <v>0.2450252490489063</v>
+        <v>0.2914917269685467</v>
       </c>
       <c r="U10">
-        <v>0.4862556116283863</v>
+        <v>0.42002124440607</v>
       </c>
       <c r="V10">
-        <v>99.42868431146913</v>
+        <v>103.0849202047576</v>
       </c>
       <c r="W10">
-        <v>116.0299194476409</v>
+        <v>118.1728395061729</v>
       </c>
       <c r="X10">
-        <v>4.711545838128116</v>
+        <v>3.386329418849745</v>
       </c>
       <c r="Y10">
-        <v>0.5901087789255457</v>
+        <v>0.5932044610718091</v>
       </c>
       <c r="Z10">
-        <v>119.1</v>
+        <v>114.18</v>
       </c>
       <c r="AA10">
-        <v>13.66</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="AB10">
-        <v>-10.13717477219789</v>
+        <v>4.250350764022217</v>
       </c>
       <c r="AC10">
-        <v>104.7204689341547</v>
+        <v>114.1383305986051</v>
       </c>
       <c r="AD10">
-        <v>114.8576437063525</v>
+        <v>109.8879798345829</v>
       </c>
       <c r="AE10">
         <v>1</v>
@@ -1697,12 +1697,12 @@
         <v>4</v>
       </c>
       <c r="AH10">
-        <v>0.7063220678784009</v>
+        <v>-0.3147776481839128</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -1711,102 +1711,102 @@
         <v>73</v>
       </c>
       <c r="D11">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E11" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11">
-        <v>1570.012</v>
+        <v>1585.093</v>
       </c>
       <c r="H11">
-        <v>-0.905</v>
+        <v>0.3172</v>
       </c>
       <c r="I11">
-        <v>1501.505493670886</v>
+        <v>1498.374555555556</v>
       </c>
       <c r="J11">
-        <v>114.5554676748872</v>
+        <v>115.9234470691132</v>
       </c>
       <c r="K11">
-        <v>111.2101462602894</v>
+        <v>112.4455710258942</v>
       </c>
       <c r="L11">
-        <v>3.345321414597836</v>
+        <v>3.477876043218948</v>
       </c>
       <c r="M11">
-        <v>107.2444298025893</v>
+        <v>119.0669956221712</v>
       </c>
       <c r="N11">
-        <v>107.4449111718987</v>
+        <v>111.4353271903156</v>
       </c>
       <c r="O11">
-        <v>-0.2004813693092842</v>
+        <v>7.631668431855641</v>
       </c>
       <c r="P11">
-        <v>0.5588211356774447</v>
+        <v>0.5536613514695621</v>
       </c>
       <c r="Q11">
-        <v>0.1255600858628708</v>
+        <v>0.128050566236857</v>
       </c>
       <c r="R11">
-        <v>0.2561695785591078</v>
+        <v>0.3055936785914721</v>
       </c>
       <c r="S11">
-        <v>0.5229688650198807</v>
+        <v>0.5592005655216874</v>
       </c>
       <c r="T11">
-        <v>0.2850267298234933</v>
+        <v>0.2459914206193677</v>
       </c>
       <c r="U11">
-        <v>0.4220678452713819</v>
+        <v>0.488251744191927</v>
       </c>
       <c r="V11">
-        <v>102.9468614086336</v>
+        <v>99.45064880483321</v>
       </c>
       <c r="W11">
-        <v>117.6319376825706</v>
+        <v>115.9569214604675</v>
       </c>
       <c r="X11">
-        <v>3.108730931515742</v>
+        <v>4.91358024691358</v>
       </c>
       <c r="Y11">
-        <v>0.5920846861513666</v>
+        <v>0.590049127530256</v>
       </c>
       <c r="Z11">
-        <v>112.53</v>
+        <v>115.22</v>
       </c>
       <c r="AA11">
-        <v>2.489999999999999</v>
+        <v>9.770000000000001</v>
       </c>
       <c r="AB11">
-        <v>4.250350764022217</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC11">
-        <v>114.1383305986051</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD11">
-        <v>109.8879798345829</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
         <v>0</v>
       </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
       <c r="AG11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH11">
-        <v>0.3583296958320634</v>
+        <v>1.367372555625685</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -1815,85 +1815,85 @@
         <v>74</v>
       </c>
       <c r="D12">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E12" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G12">
-        <v>1518.378</v>
+        <v>1563.113</v>
       </c>
       <c r="H12">
-        <v>1.0632</v>
+        <v>-0.2995</v>
       </c>
       <c r="I12">
-        <v>1496.742974683544</v>
+        <v>1497.120296296296</v>
       </c>
       <c r="J12">
-        <v>113.9948372337364</v>
+        <v>116.7427707903731</v>
       </c>
       <c r="K12">
-        <v>111.4976321318984</v>
+        <v>113.8631432395376</v>
       </c>
       <c r="L12">
-        <v>2.497205101837976</v>
+        <v>2.879627550835488</v>
       </c>
       <c r="M12">
-        <v>117.5904677919006</v>
+        <v>117.1221202324025</v>
       </c>
       <c r="N12">
-        <v>112.1121132540146</v>
+        <v>111.3731400442088</v>
       </c>
       <c r="O12">
-        <v>5.478354537885998</v>
+        <v>5.748980188193748</v>
       </c>
       <c r="P12">
-        <v>0.5459183717879508</v>
+        <v>0.5745583981687303</v>
       </c>
       <c r="Q12">
-        <v>0.1136407089073855</v>
+        <v>0.1260686327059639</v>
       </c>
       <c r="R12">
-        <v>0.2547519243726641</v>
+        <v>0.238906356375631</v>
       </c>
       <c r="S12">
-        <v>0.5773759482331312</v>
+        <v>0.5849052002403099</v>
       </c>
       <c r="T12">
-        <v>0.2678910505840704</v>
+        <v>0.3203340492940487</v>
       </c>
       <c r="U12">
-        <v>0.3637633368786354</v>
+        <v>0.3929304189189218</v>
       </c>
       <c r="V12">
-        <v>100.6705836849508</v>
+        <v>100.2376234567901</v>
       </c>
       <c r="W12">
-        <v>114.8196202531645</v>
+        <v>116.6242283950617</v>
       </c>
       <c r="X12">
-        <v>2.850210970464135</v>
+        <v>2.185185185185185</v>
       </c>
       <c r="Y12">
-        <v>0.5800943248599566</v>
+        <v>0.61036078125245</v>
       </c>
       <c r="Z12">
-        <v>118.46</v>
+        <v>115.79</v>
       </c>
       <c r="AA12">
-        <v>6.71</v>
+        <v>3.57</v>
       </c>
       <c r="AB12">
-        <v>-4.536933640611859</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC12">
-        <v>108.3888858603967</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD12">
-        <v>112.9258195010085</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE12">
         <v>1</v>
@@ -1902,15 +1902,15 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH12">
-        <v>0.7361621007331843</v>
+        <v>-0.1163171033675953</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -1919,85 +1919,85 @@
         <v>75</v>
       </c>
       <c r="D13">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E13" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G13">
-        <v>1529.962</v>
+        <v>1519.075</v>
       </c>
       <c r="H13">
-        <v>3.1913</v>
+        <v>1.4845</v>
       </c>
       <c r="I13">
-        <v>1486.043405063291</v>
+        <v>1499.059012345679</v>
       </c>
       <c r="J13">
-        <v>113.9815883697026</v>
+        <v>114.0721750810242</v>
       </c>
       <c r="K13">
-        <v>111.894725872181</v>
+        <v>111.2353680452117</v>
       </c>
       <c r="L13">
-        <v>2.08686249752164</v>
+        <v>2.836807035812536</v>
       </c>
       <c r="M13">
-        <v>116.9280437848686</v>
+        <v>118.2933190627534</v>
       </c>
       <c r="N13">
-        <v>108.6742643129208</v>
+        <v>109.9968480358148</v>
       </c>
       <c r="O13">
-        <v>8.253779471947798</v>
+        <v>8.29647102693859</v>
       </c>
       <c r="P13">
-        <v>0.5538521711168289</v>
+        <v>0.5493560462736199</v>
       </c>
       <c r="Q13">
-        <v>0.1159032175082687</v>
+        <v>0.1151105315578217</v>
       </c>
       <c r="R13">
-        <v>0.2406821348973643</v>
+        <v>0.2502841411495709</v>
       </c>
       <c r="S13">
-        <v>0.566633695967994</v>
+        <v>0.5780472549608094</v>
       </c>
       <c r="T13">
-        <v>0.2354185471123148</v>
+        <v>0.2682324169232653</v>
       </c>
       <c r="U13">
-        <v>0.4269858063807782</v>
+        <v>0.3631220135205512</v>
       </c>
       <c r="V13">
-        <v>103.7756962025316</v>
+        <v>100.6396037898363</v>
       </c>
       <c r="W13">
-        <v>118.3819620253164</v>
+        <v>114.8733850129199</v>
       </c>
       <c r="X13">
-        <v>2.417088607594937</v>
+        <v>3.189491817398794</v>
       </c>
       <c r="Y13">
-        <v>0.5841558182815482</v>
+        <v>0.5828432461013802</v>
       </c>
       <c r="Z13">
-        <v>120.5</v>
+        <v>117.64</v>
       </c>
       <c r="AA13">
-        <v>9.029999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="AB13">
-        <v>-0.981113782848854</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC13">
-        <v>112.8029837792552</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD13">
-        <v>113.7840975621041</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE13">
         <v>1</v>
@@ -2006,15 +2006,15 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH13">
-        <v>0.9500062504210939</v>
+        <v>1.435180330083925</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
-        <v>1610612747</v>
+        <v>1610612748</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
@@ -2023,85 +2023,85 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E14" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F14">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G14">
-        <v>1554.931</v>
+        <v>1522.559</v>
       </c>
       <c r="H14">
-        <v>0.0144</v>
+        <v>-1.8059</v>
       </c>
       <c r="I14">
-        <v>1497.368734177215</v>
+        <v>1501.222209876543</v>
       </c>
       <c r="J14">
-        <v>116.6121868781616</v>
+        <v>114.8839319698021</v>
       </c>
       <c r="K14">
-        <v>114.667904140824</v>
+        <v>112.4185007824804</v>
       </c>
       <c r="L14">
-        <v>1.944282737337594</v>
+        <v>2.465431187321614</v>
       </c>
       <c r="M14">
-        <v>117.5524688319591</v>
+        <v>120.2678077962238</v>
       </c>
       <c r="N14">
-        <v>115.7926921721206</v>
+        <v>121.6671133267305</v>
       </c>
       <c r="O14">
-        <v>1.759776659838577</v>
+        <v>-1.399305530506721</v>
       </c>
       <c r="P14">
-        <v>0.5741367317698555</v>
+        <v>0.5438015913268103</v>
       </c>
       <c r="Q14">
-        <v>0.1264271211873373</v>
+        <v>0.1109409230900582</v>
       </c>
       <c r="R14">
-        <v>0.2383772290777021</v>
+        <v>0.2519821426815509</v>
       </c>
       <c r="S14">
-        <v>0.5782957233927123</v>
+        <v>0.5805133860074695</v>
       </c>
       <c r="T14">
-        <v>0.3214101508321631</v>
+        <v>0.2688891523044427</v>
       </c>
       <c r="U14">
-        <v>0.3948219449260268</v>
+        <v>0.406009179457376</v>
       </c>
       <c r="V14">
-        <v>100.1393805548074</v>
+        <v>105.5325220458554</v>
       </c>
       <c r="W14">
-        <v>116.3735523835173</v>
+        <v>121.2328042328042</v>
       </c>
       <c r="X14">
-        <v>1.281982224616213</v>
+        <v>2.721693121693122</v>
       </c>
       <c r="Y14">
-        <v>0.6098744967983302</v>
+        <v>0.5809746418805888</v>
       </c>
       <c r="Z14">
-        <v>116.3</v>
+        <v>124.64</v>
       </c>
       <c r="AA14">
-        <v>-0.3800000000000003</v>
+        <v>-2.35</v>
       </c>
       <c r="AB14">
-        <v>1.827913300592181</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC14">
-        <v>114.1496737878887</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD14">
-        <v>112.3217604872965</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE14">
         <v>1</v>
@@ -2113,7 +2113,7 @@
         <v>3</v>
       </c>
       <c r="AH14">
-        <v>-0.3191452497382719</v>
+        <v>1.038374839997535</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2127,76 +2127,76 @@
         <v>77</v>
       </c>
       <c r="D15">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15">
-        <v>1554.715</v>
+        <v>1546.063</v>
       </c>
       <c r="H15">
-        <v>0.8591</v>
+        <v>-0.6596</v>
       </c>
       <c r="I15">
-        <v>1494.93235443038</v>
+        <v>1497.973962962963</v>
       </c>
       <c r="J15">
-        <v>115.7260225809766</v>
+        <v>115.7044466103971</v>
       </c>
       <c r="K15">
-        <v>113.826921011303</v>
+        <v>113.8180777013727</v>
       </c>
       <c r="L15">
-        <v>1.899101569673513</v>
+        <v>1.886368909024496</v>
       </c>
       <c r="M15">
-        <v>118.1481196381175</v>
+        <v>116.7735953178043</v>
       </c>
       <c r="N15">
-        <v>110.9061386110401</v>
+        <v>111.3520914765397</v>
       </c>
       <c r="O15">
-        <v>7.241981027077427</v>
+        <v>5.42150384126453</v>
       </c>
       <c r="P15">
-        <v>0.5603432680682666</v>
+        <v>0.5597003803540067</v>
       </c>
       <c r="Q15">
-        <v>0.1251170895455838</v>
+        <v>0.1247261155085186</v>
       </c>
       <c r="R15">
-        <v>0.2344714338398585</v>
+        <v>0.2351137530798637</v>
       </c>
       <c r="S15">
-        <v>0.5815143524184105</v>
+        <v>0.5683213322113877</v>
       </c>
       <c r="T15">
-        <v>0.3009182287077203</v>
+        <v>0.2970940051711752</v>
       </c>
       <c r="U15">
-        <v>0.402444715390783</v>
+        <v>0.4047321285737012</v>
       </c>
       <c r="V15">
-        <v>98.91327115256496</v>
+        <v>98.76594491927825</v>
       </c>
       <c r="W15">
-        <v>113.9070619586942</v>
+        <v>113.7850585628364</v>
       </c>
       <c r="X15">
-        <v>1.066955363091272</v>
+        <v>1.186767964545743</v>
       </c>
       <c r="Y15">
-        <v>0.6033120529567449</v>
+        <v>0.6027976413905946</v>
       </c>
       <c r="Z15">
-        <v>117.47</v>
+        <v>115.27</v>
       </c>
       <c r="AA15">
-        <v>6.029999999999999</v>
+        <v>4.91</v>
       </c>
       <c r="AB15">
         <v>4.815266446541752</v>
@@ -2208,21 +2208,21 @@
         <v>108.9954157027332</v>
       </c>
       <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
         <v>0</v>
       </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
       <c r="AG15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH15">
-        <v>0.6077258162467379</v>
+        <v>1.160493279997867</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16">
-        <v>1610612756</v>
+        <v>1610612737</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
@@ -2231,102 +2231,102 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F16">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16">
-        <v>1502.546</v>
+        <v>1535.39</v>
       </c>
       <c r="H16">
-        <v>0.008800000000000001</v>
+        <v>2.5282</v>
       </c>
       <c r="I16">
-        <v>1513.040316455696</v>
+        <v>1489.919061728395</v>
       </c>
       <c r="J16">
-        <v>113.3352660535845</v>
+        <v>114.1025562679364</v>
       </c>
       <c r="K16">
-        <v>111.8528816532374</v>
+        <v>112.34244268759</v>
       </c>
       <c r="L16">
-        <v>1.482384400347095</v>
+        <v>1.760113580346285</v>
       </c>
       <c r="M16">
-        <v>114.8930659672694</v>
+        <v>118.9250544663896</v>
       </c>
       <c r="N16">
-        <v>111.2948692026117</v>
+        <v>110.2068309552473</v>
       </c>
       <c r="O16">
-        <v>3.598196764657815</v>
+        <v>8.718223511142231</v>
       </c>
       <c r="P16">
-        <v>0.5388445294613354</v>
+        <v>0.5544793872465036</v>
       </c>
       <c r="Q16">
-        <v>0.1187621351706715</v>
+        <v>0.1164525757798825</v>
       </c>
       <c r="R16">
-        <v>0.2852108843136527</v>
+        <v>0.2431098219155935</v>
       </c>
       <c r="S16">
-        <v>0.5404242336083667</v>
+        <v>0.5709727556948205</v>
       </c>
       <c r="T16">
-        <v>0.2303414216833181</v>
+        <v>0.2357627984158827</v>
       </c>
       <c r="U16">
-        <v>0.4531893621121109</v>
+        <v>0.4297112087313593</v>
       </c>
       <c r="V16">
-        <v>99.6380910023948</v>
+        <v>103.7428236783793</v>
       </c>
       <c r="W16">
-        <v>112.7882312692439</v>
+        <v>118.4434947768281</v>
       </c>
       <c r="X16">
-        <v>1.502223742730071</v>
+        <v>2.027856916745805</v>
       </c>
       <c r="Y16">
-        <v>0.5707960992451045</v>
+        <v>0.5845510108149552</v>
       </c>
       <c r="Z16">
-        <v>115.24</v>
+        <v>122.31</v>
       </c>
       <c r="AA16">
-        <v>4.01</v>
+        <v>9.010000000000002</v>
       </c>
       <c r="AB16">
-        <v>-2.375203171419814</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC16">
-        <v>114.7034977739938</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD16">
-        <v>117.0787009454136</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
         <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>1</v>
       </c>
       <c r="AG16">
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>-0.2529282805341169</v>
+        <v>1.038021081879212</v>
       </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
-        <v>1610612748</v>
+        <v>1610612756</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -2335,85 +2335,85 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E17" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F17">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G17">
-        <v>1524.132</v>
+        <v>1499.249</v>
       </c>
       <c r="H17">
-        <v>-1.5367</v>
+        <v>-0.6829</v>
       </c>
       <c r="I17">
-        <v>1504.184063291139</v>
+        <v>1511.771839506173</v>
       </c>
       <c r="J17">
-        <v>113.975491222297</v>
+        <v>113.3579866792698</v>
       </c>
       <c r="K17">
-        <v>112.6481839434607</v>
+        <v>111.676625634198</v>
       </c>
       <c r="L17">
-        <v>1.327307278836367</v>
+        <v>1.681361045071835</v>
       </c>
       <c r="M17">
-        <v>117.7057537449918</v>
+        <v>115.212368268558</v>
       </c>
       <c r="N17">
-        <v>125.5728210123456</v>
+        <v>111.1045719057573</v>
       </c>
       <c r="O17">
-        <v>-7.867067267353764</v>
+        <v>4.107796362800745</v>
       </c>
       <c r="P17">
-        <v>0.5399200745859291</v>
+        <v>0.5397023215257585</v>
       </c>
       <c r="Q17">
-        <v>0.1122402158016417</v>
+        <v>0.1197078111198993</v>
       </c>
       <c r="R17">
-        <v>0.2496448119477591</v>
+        <v>0.2874150724826931</v>
       </c>
       <c r="S17">
-        <v>0.5641349455565928</v>
+        <v>0.5438109864705895</v>
       </c>
       <c r="T17">
-        <v>0.2703882610824863</v>
+        <v>0.2274089467613819</v>
       </c>
       <c r="U17">
-        <v>0.4070341328690104</v>
+        <v>0.4538504459758578</v>
       </c>
       <c r="V17">
-        <v>105.5048945147679</v>
+        <v>99.59627278071723</v>
       </c>
       <c r="W17">
-        <v>120.287482419128</v>
+        <v>112.8489124044679</v>
       </c>
       <c r="X17">
-        <v>1.619690576652602</v>
+        <v>1.822457378012934</v>
       </c>
       <c r="Y17">
-        <v>0.5775868212322989</v>
+        <v>0.5709653419910864</v>
       </c>
       <c r="Z17">
-        <v>121.2</v>
+        <v>115.74</v>
       </c>
       <c r="AA17">
-        <v>-7.97</v>
+        <v>5</v>
       </c>
       <c r="AB17">
-        <v>-1.094669144490311</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC17">
-        <v>111.6804548463295</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD17">
-        <v>112.7751239908198</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE17">
         <v>1</v>
@@ -2422,15 +2422,15 @@
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH17">
-        <v>0.4521245350812307</v>
+        <v>0.6911417331988822</v>
       </c>
     </row>
     <row r="18" spans="1:34">
       <c r="A18">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
@@ -2439,85 +2439,85 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E18" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F18">
         <v>40</v>
       </c>
       <c r="G18">
-        <v>1520.055</v>
+        <v>1473.102</v>
       </c>
       <c r="H18">
-        <v>-1.671</v>
+        <v>0.4413</v>
       </c>
       <c r="I18">
-        <v>1490.283197368421</v>
+        <v>1501.363333333333</v>
       </c>
       <c r="J18">
-        <v>112.8167169197776</v>
+        <v>113.3364274064839</v>
       </c>
       <c r="K18">
-        <v>112.6233282923196</v>
+        <v>112.6139686884808</v>
       </c>
       <c r="L18">
-        <v>0.1933886274579631</v>
+        <v>0.7224587180030148</v>
       </c>
       <c r="M18">
-        <v>112.8205096753761</v>
+        <v>114.5501181806482</v>
       </c>
       <c r="N18">
-        <v>117.478089187061</v>
+        <v>112.2888021156216</v>
       </c>
       <c r="O18">
-        <v>-4.657579511684808</v>
+        <v>2.261316065026615</v>
       </c>
       <c r="P18">
-        <v>0.5333074815659665</v>
+        <v>0.5318727944427831</v>
       </c>
       <c r="Q18">
-        <v>0.1189283469453214</v>
+        <v>0.1136606510374349</v>
       </c>
       <c r="R18">
-        <v>0.2479974665383406</v>
+        <v>0.2600054390419136</v>
       </c>
       <c r="S18">
-        <v>0.5397020081105051</v>
+        <v>0.5450646048875489</v>
       </c>
       <c r="T18">
-        <v>0.3186582051037913</v>
+        <v>0.2780044326762062</v>
       </c>
       <c r="U18">
-        <v>0.384630827647544</v>
+        <v>0.3920010435106439</v>
       </c>
       <c r="V18">
-        <v>102.6353815789473</v>
+        <v>102.678574074074</v>
       </c>
       <c r="W18">
-        <v>115.8996710526316</v>
+        <v>116.0092592592593</v>
       </c>
       <c r="X18">
-        <v>0.8516447368421052</v>
+        <v>0.0787037037037038</v>
       </c>
       <c r="Y18">
-        <v>0.5789659443293773</v>
+        <v>0.5737317169306106</v>
       </c>
       <c r="Z18">
-        <v>117.42</v>
+        <v>116.73</v>
       </c>
       <c r="AA18">
-        <v>-3.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB18">
-        <v>-0.5231111597400365</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC18">
-        <v>107.6152962364644</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD18">
-        <v>108.1384073962044</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE18">
         <v>1</v>
@@ -2526,15 +2526,15 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH18">
-        <v>0.1736577293349261</v>
+        <v>0.8011081820896432</v>
       </c>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -2543,97 +2543,97 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E19" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F19">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G19">
-        <v>1473.011</v>
+        <v>1527.008</v>
       </c>
       <c r="H19">
-        <v>0.8465</v>
+        <v>0.2441</v>
       </c>
       <c r="I19">
-        <v>1502.219455696202</v>
+        <v>1489.826794871795</v>
       </c>
       <c r="J19">
-        <v>113.0560072108706</v>
+        <v>112.3618046206719</v>
       </c>
       <c r="K19">
-        <v>113.1555315700215</v>
+        <v>112.2198305215782</v>
       </c>
       <c r="L19">
-        <v>-0.09952435915094389</v>
+        <v>0.1419740990936243</v>
       </c>
       <c r="M19">
-        <v>116.7224960302648</v>
+        <v>111.8649203009325</v>
       </c>
       <c r="N19">
-        <v>115.6068470641571</v>
+        <v>113.5765262526615</v>
       </c>
       <c r="O19">
-        <v>1.11564896610778</v>
+        <v>-1.711605951729009</v>
       </c>
       <c r="P19">
-        <v>0.5310300147818446</v>
+        <v>0.5314800403153312</v>
       </c>
       <c r="Q19">
-        <v>0.1148191305560612</v>
+        <v>0.1196222682343991</v>
       </c>
       <c r="R19">
-        <v>0.2596557858223979</v>
+        <v>0.2465242137565519</v>
       </c>
       <c r="S19">
-        <v>0.5516678587308923</v>
+        <v>0.5362920244771173</v>
       </c>
       <c r="T19">
-        <v>0.2802912694598166</v>
+        <v>0.3190429672900122</v>
       </c>
       <c r="U19">
-        <v>0.3916902082975683</v>
+        <v>0.3878288537136768</v>
       </c>
       <c r="V19">
-        <v>102.6283089905875</v>
+        <v>102.8133583489681</v>
       </c>
       <c r="W19">
-        <v>115.702693930542</v>
+        <v>115.65478424015</v>
       </c>
       <c r="X19">
-        <v>-0.7137293086660175</v>
+        <v>0.8661663539712321</v>
       </c>
       <c r="Y19">
-        <v>0.5731423999687638</v>
+        <v>0.5772590404186486</v>
       </c>
       <c r="Z19">
-        <v>119.55</v>
+        <v>117.63</v>
       </c>
       <c r="AA19">
-        <v>0.9699999999999998</v>
+        <v>-1.49</v>
       </c>
       <c r="AB19">
-        <v>-6.382503892565079</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC19">
-        <v>109.8789897646453</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD19">
-        <v>116.2614936572104</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH19">
-        <v>0.244041306718433</v>
+        <v>0.6664103782363974</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2647,76 +2647,76 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E20" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20">
-        <v>1471.079</v>
+        <v>1465.009</v>
       </c>
       <c r="H20">
-        <v>-1.1842</v>
+        <v>-1.8002</v>
       </c>
       <c r="I20">
-        <v>1506.643886075949</v>
+        <v>1504.838530864198</v>
       </c>
       <c r="J20">
-        <v>112.6465355346359</v>
+        <v>112.7778777455463</v>
       </c>
       <c r="K20">
-        <v>113.3459725581583</v>
+        <v>113.3577573917064</v>
       </c>
       <c r="L20">
-        <v>-0.6994370235224284</v>
+        <v>-0.5798796461601849</v>
       </c>
       <c r="M20">
-        <v>111.6227110061938</v>
+        <v>114.0444443399996</v>
       </c>
       <c r="N20">
-        <v>117.6579556089775</v>
+        <v>118.2284876497019</v>
       </c>
       <c r="O20">
-        <v>-6.035244602783636</v>
+        <v>-4.184043309702345</v>
       </c>
       <c r="P20">
-        <v>0.5513714251681003</v>
+        <v>0.5498546901292588</v>
       </c>
       <c r="Q20">
-        <v>0.1333674969990142</v>
+        <v>0.1318149452976943</v>
       </c>
       <c r="R20">
-        <v>0.2589082396102088</v>
+        <v>0.2577646107997965</v>
       </c>
       <c r="S20">
-        <v>0.5654872432147759</v>
+        <v>0.5574525454327377</v>
       </c>
       <c r="T20">
-        <v>0.2375563605461833</v>
+        <v>0.242988171994435</v>
       </c>
       <c r="U20">
-        <v>0.4963734015555497</v>
+        <v>0.496158125901545</v>
       </c>
       <c r="V20">
-        <v>101.6188607594937</v>
+        <v>101.608630490956</v>
       </c>
       <c r="W20">
-        <v>114.4918625678119</v>
+        <v>114.5581395348838</v>
       </c>
       <c r="X20">
-        <v>-0.615732368896926</v>
+        <v>-0.6106804478897502</v>
       </c>
       <c r="Y20">
-        <v>0.5853122893114001</v>
+        <v>0.5849172096355714</v>
       </c>
       <c r="Z20">
-        <v>112.09</v>
+        <v>113.69</v>
       </c>
       <c r="AA20">
-        <v>-6.64</v>
+        <v>-4.82</v>
       </c>
       <c r="AB20">
         <v>2.402868486532558</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH20">
-        <v>0.2705080178603088</v>
+        <v>1.077792710122442</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2751,76 +2751,76 @@
         <v>83</v>
       </c>
       <c r="D21">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E21" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21">
-        <v>1467.705</v>
+        <v>1471.6</v>
       </c>
       <c r="H21">
-        <v>1.3562</v>
+        <v>1.2858</v>
       </c>
       <c r="I21">
-        <v>1503.540658227848</v>
+        <v>1507.032037037037</v>
       </c>
       <c r="J21">
-        <v>111.1415390128851</v>
+        <v>111.6839894968333</v>
       </c>
       <c r="K21">
-        <v>112.541218772173</v>
+        <v>112.4435626374769</v>
       </c>
       <c r="L21">
-        <v>-1.399679759287897</v>
+        <v>-0.759573140643502</v>
       </c>
       <c r="M21">
-        <v>114.7722997425094</v>
+        <v>115.891950349308</v>
       </c>
       <c r="N21">
-        <v>106.7861470826888</v>
+        <v>106.3211056799474</v>
       </c>
       <c r="O21">
-        <v>7.986152659820483</v>
+        <v>9.570844669360605</v>
       </c>
       <c r="P21">
-        <v>0.5339684415002349</v>
+        <v>0.5343550965743989</v>
       </c>
       <c r="Q21">
-        <v>0.1408861462567083</v>
+        <v>0.1394660755341611</v>
       </c>
       <c r="R21">
-        <v>0.3094710080163383</v>
+        <v>0.3125017781001434</v>
       </c>
       <c r="S21">
-        <v>0.5514971832533441</v>
+        <v>0.5576357739010501</v>
       </c>
       <c r="T21">
-        <v>0.2813212395213871</v>
+        <v>0.2820778387585565</v>
       </c>
       <c r="U21">
-        <v>0.4680032742722018</v>
+        <v>0.468791430854873</v>
       </c>
       <c r="V21">
-        <v>103.3604846292948</v>
+        <v>103.1977777777778</v>
       </c>
       <c r="W21">
-        <v>115.1533453887885</v>
+        <v>115.5785322359397</v>
       </c>
       <c r="X21">
-        <v>-0.8553345388788426</v>
+        <v>-0.09876543209876543</v>
       </c>
       <c r="Y21">
-        <v>0.5699292362853535</v>
+        <v>0.5708968808747181</v>
       </c>
       <c r="Z21">
-        <v>117.29</v>
+        <v>117.77</v>
       </c>
       <c r="AA21">
-        <v>8.529999999999999</v>
+        <v>10.47</v>
       </c>
       <c r="AB21">
         <v>-3.840928550668963</v>
@@ -2838,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.1086756755568378</v>
+        <v>0.6009843904787218</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2855,76 +2855,76 @@
         <v>84</v>
       </c>
       <c r="D22">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E22" s="2">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="F22">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G22">
-        <v>1370.931</v>
+        <v>1371.233</v>
       </c>
       <c r="H22">
-        <v>-1.6162</v>
+        <v>-1.6519</v>
       </c>
       <c r="I22">
-        <v>1505.927316455696</v>
+        <v>1505.463</v>
       </c>
       <c r="J22">
-        <v>112.3385851645336</v>
+        <v>112.0850938793152</v>
       </c>
       <c r="K22">
-        <v>116.2291100095153</v>
+        <v>116.6704370218488</v>
       </c>
       <c r="L22">
-        <v>-3.890524844981663</v>
+        <v>-4.585343142533532</v>
       </c>
       <c r="M22">
-        <v>111.448394454494</v>
+        <v>109.8108292856906</v>
       </c>
       <c r="N22">
-        <v>117.5741649604015</v>
+        <v>121.3107155542834</v>
       </c>
       <c r="O22">
-        <v>-6.125770505907487</v>
+        <v>-11.49988626859275</v>
       </c>
       <c r="P22">
-        <v>0.5304560959855672</v>
+        <v>0.526546629887776</v>
       </c>
       <c r="Q22">
-        <v>0.1177304903746707</v>
+        <v>0.1163021487939905</v>
       </c>
       <c r="R22">
-        <v>0.2649757309657001</v>
+        <v>0.2679655633187853</v>
       </c>
       <c r="S22">
-        <v>0.5386786083126474</v>
+        <v>0.5155469374765284</v>
       </c>
       <c r="T22">
-        <v>0.2835256099653364</v>
+        <v>0.2865289752514886</v>
       </c>
       <c r="U22">
-        <v>0.3583951518507153</v>
+        <v>0.3545289938005295</v>
       </c>
       <c r="V22">
-        <v>103.1421811100292</v>
+        <v>103.124037037037</v>
       </c>
       <c r="W22">
-        <v>115.9032781564427</v>
+        <v>115.6601851851852</v>
       </c>
       <c r="X22">
-        <v>-3.903602726387536</v>
+        <v>-4.519444444444445</v>
       </c>
       <c r="Y22">
-        <v>0.5705815300511676</v>
+        <v>0.567369262511092</v>
       </c>
       <c r="Z22">
-        <v>114.06</v>
+        <v>115.11</v>
       </c>
       <c r="AA22">
-        <v>-4.85</v>
+        <v>-9.870000000000001</v>
       </c>
       <c r="AB22">
         <v>-9.447870926461551</v>
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-1.125753642178619</v>
+        <v>-0.9477176015193129</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -2959,76 +2959,76 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E23" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F23">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G23">
-        <v>1373.768</v>
+        <v>1371.504</v>
       </c>
       <c r="H23">
-        <v>-1.3956</v>
+        <v>-1.2134</v>
       </c>
       <c r="I23">
-        <v>1495.444430379747</v>
+        <v>1492.776950617284</v>
       </c>
       <c r="J23">
-        <v>111.4717734186185</v>
+        <v>111.2810167920214</v>
       </c>
       <c r="K23">
-        <v>115.5382265194303</v>
+        <v>116.1591569938408</v>
       </c>
       <c r="L23">
-        <v>-4.066453100811755</v>
+        <v>-4.87814020181945</v>
       </c>
       <c r="M23">
-        <v>109.6715970055938</v>
+        <v>108.0373418581318</v>
       </c>
       <c r="N23">
-        <v>117.4606653266079</v>
+        <v>120.1538428982576</v>
       </c>
       <c r="O23">
-        <v>-7.789068321014038</v>
+        <v>-12.1165010401258</v>
       </c>
       <c r="P23">
-        <v>0.5478840370761009</v>
+        <v>0.547270327027616</v>
       </c>
       <c r="Q23">
-        <v>0.126928664795089</v>
+        <v>0.1266854088142798</v>
       </c>
       <c r="R23">
-        <v>0.2302365699782219</v>
+        <v>0.2299284128404735</v>
       </c>
       <c r="S23">
-        <v>0.5382272056121705</v>
+        <v>0.5294824052355236</v>
       </c>
       <c r="T23">
-        <v>0.2487327655352116</v>
+        <v>0.2470454055324363</v>
       </c>
       <c r="U23">
-        <v>0.4433137232568473</v>
+        <v>0.4418947820820854</v>
       </c>
       <c r="V23">
-        <v>104.5786351128233</v>
+        <v>104.8949494949495</v>
       </c>
       <c r="W23">
-        <v>116.3500275178866</v>
+        <v>116.519266741489</v>
       </c>
       <c r="X23">
-        <v>-4.627407815079802</v>
+        <v>-5.496820052375608</v>
       </c>
       <c r="Y23">
-        <v>0.5809881961922844</v>
+        <v>0.5797291449308587</v>
       </c>
       <c r="Z23">
-        <v>119.09</v>
+        <v>118.19</v>
       </c>
       <c r="AA23">
-        <v>-6.91</v>
+        <v>-11.55</v>
       </c>
       <c r="AB23">
         <v>-0.9433805425336231</v>
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23">
-        <v>-1.037521012209358</v>
+        <v>-0.5852165804675344</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3063,76 +3063,76 @@
         <v>86</v>
       </c>
       <c r="D24">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E24" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G24">
-        <v>1364.506</v>
+        <v>1362.759</v>
       </c>
       <c r="H24">
-        <v>-1.0239</v>
+        <v>-0.7974</v>
       </c>
       <c r="I24">
-        <v>1505.664653846154</v>
+        <v>1508.553925</v>
       </c>
       <c r="J24">
-        <v>108.7200060056871</v>
+        <v>109.4062000245472</v>
       </c>
       <c r="K24">
-        <v>114.4475048869208</v>
+        <v>114.6438663248674</v>
       </c>
       <c r="L24">
-        <v>-5.727498881233766</v>
+        <v>-5.237666300320275</v>
       </c>
       <c r="M24">
-        <v>110.0150089926656</v>
+        <v>111.7089980700899</v>
       </c>
       <c r="N24">
-        <v>118.4869029729465</v>
+        <v>117.5138264402058</v>
       </c>
       <c r="O24">
-        <v>-8.471893980280926</v>
+        <v>-5.804828370115862</v>
       </c>
       <c r="P24">
-        <v>0.5254793541560655</v>
+        <v>0.5288057295113444</v>
       </c>
       <c r="Q24">
-        <v>0.1209385704651931</v>
+        <v>0.1213231660728197</v>
       </c>
       <c r="R24">
-        <v>0.229300895320536</v>
+        <v>0.2332540995204987</v>
       </c>
       <c r="S24">
-        <v>0.5098708819227636</v>
+        <v>0.5183999895679121</v>
       </c>
       <c r="T24">
-        <v>0.2894011957409569</v>
+        <v>0.2883400816451441</v>
       </c>
       <c r="U24">
-        <v>0.3505996246563323</v>
+        <v>0.3541092766207404</v>
       </c>
       <c r="V24">
-        <v>104.3595426195426</v>
+        <v>104.6687179487179</v>
       </c>
       <c r="W24">
-        <v>113.5613305613305</v>
+        <v>114.6416666666667</v>
       </c>
       <c r="X24">
-        <v>-5.586278586278586</v>
+        <v>-5.076282051282051</v>
       </c>
       <c r="Y24">
-        <v>0.5628721515556713</v>
+        <v>0.5658232650250469</v>
       </c>
       <c r="Z24">
-        <v>116.36</v>
+        <v>118.4</v>
       </c>
       <c r="AA24">
-        <v>-9.5</v>
+        <v>-7.079999999999999</v>
       </c>
       <c r="AB24">
         <v>-0.6658146557452705</v>
@@ -3144,21 +3144,21 @@
         <v>113.7784460471737</v>
       </c>
       <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
         <v>0</v>
       </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
       <c r="AG24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24">
-        <v>-0.4872142298054135</v>
+        <v>-1.225296356118726</v>
       </c>
     </row>
     <row r="25" spans="1:34">
       <c r="A25">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
@@ -3167,85 +3167,85 @@
         <v>87</v>
       </c>
       <c r="D25">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E25" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F25">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G25">
-        <v>1369.278</v>
+        <v>1388.819</v>
       </c>
       <c r="H25">
-        <v>-2.3429</v>
+        <v>-0.6724</v>
       </c>
       <c r="I25">
-        <v>1497.837649350649</v>
+        <v>1493.614567901235</v>
       </c>
       <c r="J25">
-        <v>110.8418883611541</v>
+        <v>111.1158061312331</v>
       </c>
       <c r="K25">
-        <v>116.8432644697368</v>
+        <v>117.5761914884467</v>
       </c>
       <c r="L25">
-        <v>-6.00137610858276</v>
+        <v>-6.460385357213616</v>
       </c>
       <c r="M25">
-        <v>108.3277680694841</v>
+        <v>110.0541586299186</v>
       </c>
       <c r="N25">
-        <v>128.2868272258588</v>
+        <v>123.142419684016</v>
       </c>
       <c r="O25">
-        <v>-19.95905915637476</v>
+        <v>-13.08826105409746</v>
       </c>
       <c r="P25">
-        <v>0.535846242379462</v>
+        <v>0.5652573279805296</v>
       </c>
       <c r="Q25">
-        <v>0.1257434015764443</v>
+        <v>0.1336431729270692</v>
       </c>
       <c r="R25">
-        <v>0.2475893581274633</v>
+        <v>0.2098926481219327</v>
       </c>
       <c r="S25">
-        <v>0.5357043723334582</v>
+        <v>0.5693449429406905</v>
       </c>
       <c r="T25">
-        <v>0.2580094344861534</v>
+        <v>0.2258900271470669</v>
       </c>
       <c r="U25">
-        <v>0.437177180668999</v>
+        <v>0.4586816993093407</v>
       </c>
       <c r="V25">
-        <v>103.5548495407032</v>
+        <v>99.53005212620027</v>
       </c>
       <c r="W25">
-        <v>114.9708584098828</v>
+        <v>110.5871056241427</v>
       </c>
       <c r="X25">
-        <v>-5.596769084573962</v>
+        <v>-6.347325102880658</v>
       </c>
       <c r="Y25">
-        <v>0.5725209119616749</v>
+        <v>0.5888103819932251</v>
       </c>
       <c r="Z25">
-        <v>110.99</v>
+        <v>109.69</v>
       </c>
       <c r="AA25">
-        <v>-19.43</v>
+        <v>-10.1</v>
       </c>
       <c r="AB25">
-        <v>3.575252351995317</v>
+        <v>1.809266556998161</v>
       </c>
       <c r="AC25">
-        <v>114.5419381230804</v>
+        <v>114.2499905834389</v>
       </c>
       <c r="AD25">
-        <v>110.9666857710851</v>
+        <v>112.4407240264407</v>
       </c>
       <c r="AE25">
         <v>1</v>
@@ -3257,12 +3257,12 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.284739140581789</v>
+        <v>-1.259238547880103</v>
       </c>
     </row>
     <row r="26" spans="1:34">
       <c r="A26">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
@@ -3271,97 +3271,97 @@
         <v>88</v>
       </c>
       <c r="D26">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E26" s="2">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="F26">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G26">
-        <v>1388.975</v>
+        <v>1363.711</v>
       </c>
       <c r="H26">
-        <v>-1.4014</v>
+        <v>-2.39</v>
       </c>
       <c r="I26">
-        <v>1493.850518987342</v>
+        <v>1496.732873417722</v>
       </c>
       <c r="J26">
-        <v>111.1517692702001</v>
+        <v>110.0057254487443</v>
       </c>
       <c r="K26">
-        <v>117.8520076525522</v>
+        <v>116.8325082803325</v>
       </c>
       <c r="L26">
-        <v>-6.700238382352076</v>
+        <v>-6.826782831588231</v>
       </c>
       <c r="M26">
-        <v>108.5087612266326</v>
+        <v>106.0814258569361</v>
       </c>
       <c r="N26">
-        <v>123.1693603554744</v>
+        <v>125.955261737259</v>
       </c>
       <c r="O26">
-        <v>-14.66059912884175</v>
+        <v>-19.87383588032283</v>
       </c>
       <c r="P26">
-        <v>0.5640877973663239</v>
+        <v>0.5328680422635065</v>
       </c>
       <c r="Q26">
-        <v>0.1327352833107777</v>
+        <v>0.1265316231044593</v>
       </c>
       <c r="R26">
-        <v>0.2100535280990145</v>
+        <v>0.244381293811856</v>
       </c>
       <c r="S26">
-        <v>0.5630755276015077</v>
+        <v>0.5258536098267521</v>
       </c>
       <c r="T26">
-        <v>0.227526093589286</v>
+        <v>0.2522962748234502</v>
       </c>
       <c r="U26">
-        <v>0.4577009404236284</v>
+        <v>0.4383267500787908</v>
       </c>
       <c r="V26">
-        <v>99.47620997766195</v>
+        <v>103.9008800482218</v>
       </c>
       <c r="W26">
-        <v>110.5208488458675</v>
+        <v>114.4195298372514</v>
       </c>
       <c r="X26">
-        <v>-6.661950856291885</v>
+        <v>-6.570524412296563</v>
       </c>
       <c r="Y26">
-        <v>0.5881976546133644</v>
+        <v>0.5693198082598562</v>
       </c>
       <c r="Z26">
-        <v>107.31</v>
+        <v>110.27</v>
       </c>
       <c r="AA26">
-        <v>-12.59</v>
+        <v>-20.92</v>
       </c>
       <c r="AB26">
-        <v>1.809266556998161</v>
+        <v>3.575252351995317</v>
       </c>
       <c r="AC26">
-        <v>114.2499905834389</v>
+        <v>114.5419381230804</v>
       </c>
       <c r="AD26">
-        <v>112.4407240264407</v>
+        <v>110.9666857710851</v>
       </c>
       <c r="AE26">
+        <v>1</v>
+      </c>
+      <c r="AF26">
         <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>1</v>
       </c>
       <c r="AG26">
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-0.897464825056609</v>
+        <v>-0.9521540538361646</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3375,76 +3375,76 @@
         <v>89</v>
       </c>
       <c r="D27">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E27" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F27">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27">
-        <v>1338.362</v>
+        <v>1339.648</v>
       </c>
       <c r="H27">
-        <v>1.0053</v>
+        <v>0.6471</v>
       </c>
       <c r="I27">
-        <v>1504.686202531646</v>
+        <v>1501.635086419753</v>
       </c>
       <c r="J27">
-        <v>109.604642909582</v>
+        <v>109.3500004710919</v>
       </c>
       <c r="K27">
-        <v>116.4586351396482</v>
+        <v>116.7825435865277</v>
       </c>
       <c r="L27">
-        <v>-6.853992230066176</v>
+        <v>-7.432543115435855</v>
       </c>
       <c r="M27">
-        <v>118.711756459824</v>
+        <v>115.181307464374</v>
       </c>
       <c r="N27">
-        <v>116.5214522098985</v>
+        <v>114.5950199147631</v>
       </c>
       <c r="O27">
-        <v>2.19030424992541</v>
+        <v>0.5862875496109257</v>
       </c>
       <c r="P27">
-        <v>0.5344897290409717</v>
+        <v>0.534318915764955</v>
       </c>
       <c r="Q27">
-        <v>0.121044222520725</v>
+        <v>0.1224044549954639</v>
       </c>
       <c r="R27">
-        <v>0.2152062697179775</v>
+        <v>0.2137618205728044</v>
       </c>
       <c r="S27">
-        <v>0.5937958518474428</v>
+        <v>0.5809386362339246</v>
       </c>
       <c r="T27">
-        <v>0.255010003468748</v>
+        <v>0.2540792723934914</v>
       </c>
       <c r="U27">
-        <v>0.4176671386014152</v>
+        <v>0.4242904078856247</v>
       </c>
       <c r="V27">
-        <v>103.1289653274628</v>
+        <v>103.1759810874704</v>
       </c>
       <c r="W27">
-        <v>112.6477710511832</v>
+        <v>112.5056474914631</v>
       </c>
       <c r="X27">
-        <v>-7.554760594386352</v>
+        <v>-8.024691358024691</v>
       </c>
       <c r="Y27">
-        <v>0.5697917319582749</v>
+        <v>0.5696888654212232</v>
       </c>
       <c r="Z27">
-        <v>121.11</v>
+        <v>119.02</v>
       </c>
       <c r="AA27">
-        <v>-0.9700000000000002</v>
+        <v>-1.38</v>
       </c>
       <c r="AB27">
         <v>2.960186837728194</v>
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27">
-        <v>-1.104622051053789</v>
+        <v>-0.7998378263709043</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3479,76 +3479,76 @@
         <v>90</v>
       </c>
       <c r="D28">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E28" s="2">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="F28">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G28">
-        <v>1303.464</v>
+        <v>1306.184</v>
       </c>
       <c r="H28">
-        <v>-1.6441</v>
+        <v>-1.0451</v>
       </c>
       <c r="I28">
-        <v>1517.014518987342</v>
+        <v>1513.371938271605</v>
       </c>
       <c r="J28">
-        <v>111.8513171648238</v>
+        <v>111.6767382634197</v>
       </c>
       <c r="K28">
-        <v>120.5130857087986</v>
+        <v>120.1235742154271</v>
       </c>
       <c r="L28">
-        <v>-8.661768543974819</v>
+        <v>-8.446835952007435</v>
       </c>
       <c r="M28">
-        <v>111.6252517777173</v>
+        <v>110.131838994038</v>
       </c>
       <c r="N28">
-        <v>123.8249074608383</v>
+        <v>123.2809515428013</v>
       </c>
       <c r="O28">
-        <v>-12.19965568312098</v>
+        <v>-13.14911254876331</v>
       </c>
       <c r="P28">
-        <v>0.5373487742905084</v>
+        <v>0.536540036220296</v>
       </c>
       <c r="Q28">
-        <v>0.1279687305136955</v>
+        <v>0.1280181812720871</v>
       </c>
       <c r="R28">
-        <v>0.2602338060505711</v>
+        <v>0.2619805510452017</v>
       </c>
       <c r="S28">
-        <v>0.5360769066073117</v>
+        <v>0.5362823459877377</v>
       </c>
       <c r="T28">
-        <v>0.2803697149988327</v>
+        <v>0.2795687076861887</v>
       </c>
       <c r="U28">
-        <v>0.4038185184287812</v>
+        <v>0.4026687771043674</v>
       </c>
       <c r="V28">
-        <v>105.0981042095967</v>
+        <v>105.1085885885886</v>
       </c>
       <c r="W28">
-        <v>117.56402708272</v>
+        <v>117.4264264264265</v>
       </c>
       <c r="X28">
-        <v>-9.022372681778039</v>
+        <v>-8.66066066066066</v>
       </c>
       <c r="Y28">
-        <v>0.576732073823026</v>
+        <v>0.5751642216574683</v>
       </c>
       <c r="Z28">
-        <v>118.64</v>
+        <v>119.24</v>
       </c>
       <c r="AA28">
-        <v>-14.41</v>
+        <v>-14.46</v>
       </c>
       <c r="AB28">
         <v>-9.725925288085115</v>
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.984078192395561</v>
+        <v>-0.7506031220141877</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3583,76 +3583,76 @@
         <v>91</v>
       </c>
       <c r="D29">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="F29">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G29">
-        <v>1312.908</v>
+        <v>1314.296</v>
       </c>
       <c r="H29">
-        <v>-0.4694</v>
+        <v>-0.1616</v>
       </c>
       <c r="I29">
-        <v>1515.35135443038</v>
+        <v>1514.200407407408</v>
       </c>
       <c r="J29">
-        <v>109.5123257995211</v>
+        <v>109.7010125757129</v>
       </c>
       <c r="K29">
-        <v>118.7903909663357</v>
+        <v>118.8268052692938</v>
       </c>
       <c r="L29">
-        <v>-9.27806516681464</v>
+        <v>-9.125792693580875</v>
       </c>
       <c r="M29">
-        <v>112.7969310994889</v>
+        <v>113.8650104956569</v>
       </c>
       <c r="N29">
-        <v>124.845136565112</v>
+        <v>122.1147884139038</v>
       </c>
       <c r="O29">
-        <v>-12.04820546562315</v>
+        <v>-8.249777918246924</v>
       </c>
       <c r="P29">
-        <v>0.5252883934522501</v>
+        <v>0.5255178116719339</v>
       </c>
       <c r="Q29">
-        <v>0.1214001847069728</v>
+        <v>0.1219534170184018</v>
       </c>
       <c r="R29">
-        <v>0.258475482579947</v>
+        <v>0.2608308673214755</v>
       </c>
       <c r="S29">
-        <v>0.5422059701525712</v>
+        <v>0.5433247861948836</v>
       </c>
       <c r="T29">
-        <v>0.2543099815435653</v>
+        <v>0.2594828597735084</v>
       </c>
       <c r="U29">
-        <v>0.3389611964379824</v>
+        <v>0.3385223890126498</v>
       </c>
       <c r="V29">
-        <v>101.5152974683545</v>
+        <v>101.5625474254742</v>
       </c>
       <c r="W29">
-        <v>110.7759493670886</v>
+        <v>110.9876543209876</v>
       </c>
       <c r="X29">
-        <v>-10.10949367088607</v>
+        <v>-10.02469135802469</v>
       </c>
       <c r="Y29">
-        <v>0.5602126035248454</v>
+        <v>0.5609216554477084</v>
       </c>
       <c r="Z29">
-        <v>110.94</v>
+        <v>112.07</v>
       </c>
       <c r="AA29">
-        <v>-12.83</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="AB29">
         <v>-0.1619477822758719</v>
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.499480788820034</v>
+        <v>-1.632423740711327</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3687,76 +3687,76 @@
         <v>92</v>
       </c>
       <c r="D30">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E30" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F30">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30">
-        <v>1290.905</v>
+        <v>1286.566</v>
       </c>
       <c r="H30">
-        <v>-0.8539</v>
+        <v>-0.7705</v>
       </c>
       <c r="I30">
-        <v>1498.539291139241</v>
+        <v>1495.191456790124</v>
       </c>
       <c r="J30">
-        <v>106.4414554831461</v>
+        <v>106.6946689558687</v>
       </c>
       <c r="K30">
-        <v>116.9457223329821</v>
+        <v>117.5335836909019</v>
       </c>
       <c r="L30">
-        <v>-10.50426684983602</v>
+        <v>-10.83891473503323</v>
       </c>
       <c r="M30">
-        <v>103.4042404205238</v>
+        <v>103.6249406768065</v>
       </c>
       <c r="N30">
-        <v>114.8923576237037</v>
+        <v>118.2205232375353</v>
       </c>
       <c r="O30">
-        <v>-11.48811720317985</v>
+        <v>-14.5955825607287</v>
       </c>
       <c r="P30">
-        <v>0.5197713512650058</v>
+        <v>0.5198998237003548</v>
       </c>
       <c r="Q30">
-        <v>0.1366221993410033</v>
+        <v>0.1363005591376335</v>
       </c>
       <c r="R30">
-        <v>0.2338726923229511</v>
+        <v>0.2351133645570815</v>
       </c>
       <c r="S30">
-        <v>0.5138521102632525</v>
+        <v>0.5087571301464701</v>
       </c>
       <c r="T30">
-        <v>0.2751443161454343</v>
+        <v>0.276509115091956</v>
       </c>
       <c r="U30">
-        <v>0.4542963205174071</v>
+        <v>0.4545610025684944</v>
       </c>
       <c r="V30">
-        <v>99.26963877740043</v>
+        <v>99.14328630217518</v>
       </c>
       <c r="W30">
-        <v>105.8184624884224</v>
+        <v>105.8689006466785</v>
       </c>
       <c r="X30">
-        <v>-9.821241123803643</v>
+        <v>-10.28189300411523</v>
       </c>
       <c r="Y30">
-        <v>0.5590774457794662</v>
+        <v>0.5596288678358861</v>
       </c>
       <c r="Z30">
-        <v>103.36</v>
+        <v>102.98</v>
       </c>
       <c r="AA30">
-        <v>-11.54</v>
+        <v>-15.83</v>
       </c>
       <c r="AB30">
         <v>-6.499587896466165</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.783479677857188</v>
+        <v>-1.921377186539993</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3791,76 +3791,76 @@
         <v>93</v>
       </c>
       <c r="D31">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E31" s="2">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="F31">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G31">
-        <v>1251.266</v>
+        <v>1248.453</v>
       </c>
       <c r="H31">
-        <v>-0.7727000000000001</v>
+        <v>-1.3493</v>
       </c>
       <c r="I31">
-        <v>1501.204620253164</v>
+        <v>1499.87487654321</v>
       </c>
       <c r="J31">
-        <v>108.6144668824543</v>
+        <v>108.7888914910984</v>
       </c>
       <c r="K31">
-        <v>120.1501244813441</v>
+        <v>120.6129392352695</v>
       </c>
       <c r="L31">
-        <v>-11.53565759888977</v>
+        <v>-11.82404774417107</v>
       </c>
       <c r="M31">
-        <v>108.7610623965598</v>
+        <v>109.4454469371932</v>
       </c>
       <c r="N31">
-        <v>124.4728035616271</v>
+        <v>124.3688794725477</v>
       </c>
       <c r="O31">
-        <v>-15.71174116506733</v>
+        <v>-14.92343253535458</v>
       </c>
       <c r="P31">
-        <v>0.5337839548056479</v>
+        <v>0.5357116104225234</v>
       </c>
       <c r="Q31">
-        <v>0.1324078153619469</v>
+        <v>0.1317054380895965</v>
       </c>
       <c r="R31">
-        <v>0.2406071873250716</v>
+        <v>0.2371661937124714</v>
       </c>
       <c r="S31">
-        <v>0.5402717412963134</v>
+        <v>0.5432612592588102</v>
       </c>
       <c r="T31">
-        <v>0.2386930964370224</v>
+        <v>0.2367146385541855</v>
       </c>
       <c r="U31">
-        <v>0.4034472436154499</v>
+        <v>0.4037726157400284</v>
       </c>
       <c r="V31">
-        <v>103.8549636412604</v>
+        <v>103.7986092214663</v>
       </c>
       <c r="W31">
-        <v>112.7573390789119</v>
+        <v>112.9365079365079</v>
       </c>
       <c r="X31">
-        <v>-11.81766765418798</v>
+        <v>-11.98412698412698</v>
       </c>
       <c r="Y31">
-        <v>0.5657368787383508</v>
+        <v>0.567260147620279</v>
       </c>
       <c r="Z31">
-        <v>114.48</v>
+        <v>115.47</v>
       </c>
       <c r="AA31">
-        <v>-15.86</v>
+        <v>-14.35</v>
       </c>
       <c r="AB31">
         <v>-12.72363327068823</v>
@@ -3878,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="AG31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.266737760470074</v>
+        <v>-1.130982826741756</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -145,15 +145,15 @@
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
+    <t>Los Angeles Lakers</t>
+  </si>
+  <si>
+    <t>Toronto Raptors</t>
+  </si>
+  <si>
     <t>Charlotte Hornets</t>
   </si>
   <si>
-    <t>Los Angeles Lakers</t>
-  </si>
-  <si>
-    <t>Toronto Raptors</t>
-  </si>
-  <si>
     <t>Miami Heat</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Phoenix Suns</t>
   </si>
   <si>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
     <t>Philadelphia 76ers</t>
   </si>
   <si>
-    <t>Orlando Magic</t>
+    <t>Portland Trail Blazers</t>
   </si>
   <si>
     <t>Golden State Warriors</t>
   </si>
   <si>
-    <t>Portland Trail Blazers</t>
-  </si>
-  <si>
     <t>New Orleans Pelicans</t>
   </si>
   <si>
@@ -235,15 +235,15 @@
     <t>MIN</t>
   </si>
   <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>CHA</t>
   </si>
   <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
@@ -256,16 +256,16 @@
     <t>PHX</t>
   </si>
   <si>
+    <t>ORL</t>
+  </si>
+  <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>ORL</t>
+    <t>POR</t>
   </si>
   <si>
     <t>GSW</t>
-  </si>
-  <si>
-    <t>POR</t>
   </si>
   <si>
     <t>NOP</t>
@@ -865,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="AH2">
-        <v>-0.6662511097089785</v>
+        <v>-0.7710635982193697</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -969,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="AH3">
-        <v>0.8493059619118966</v>
+        <v>0.3409857680820598</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -1073,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="AH4">
-        <v>1.140005843727795</v>
+        <v>0.5654538617262683</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1177,7 +1177,7 @@
         <v>4</v>
       </c>
       <c r="AH5">
-        <v>0.03038678962681212</v>
+        <v>1.177202809186422</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1281,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="AH6">
-        <v>-0.140115325253566</v>
+        <v>1.366245995995082</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1385,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AH7">
-        <v>-0.522833929919282</v>
+        <v>0.3005155364075296</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="AH8">
-        <v>1.229413159416357</v>
+        <v>1.756720663233555</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="AH9">
-        <v>-0.1608482777598297</v>
+        <v>1.758131410677385</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1697,12 +1697,12 @@
         <v>4</v>
       </c>
       <c r="AH10">
-        <v>-0.3147776481839128</v>
+        <v>0.5860951280523858</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11">
-        <v>1610612766</v>
+        <v>1610612747</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -1717,79 +1717,79 @@
         <v>46124</v>
       </c>
       <c r="F11">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G11">
-        <v>1585.093</v>
+        <v>1563.113</v>
       </c>
       <c r="H11">
-        <v>0.3172</v>
+        <v>-0.2995</v>
       </c>
       <c r="I11">
-        <v>1498.374555555556</v>
+        <v>1497.120296296296</v>
       </c>
       <c r="J11">
-        <v>115.9234470691132</v>
+        <v>116.7427707903731</v>
       </c>
       <c r="K11">
-        <v>112.4455710258942</v>
+        <v>113.8631432395376</v>
       </c>
       <c r="L11">
-        <v>3.477876043218948</v>
+        <v>2.879627550835488</v>
       </c>
       <c r="M11">
-        <v>119.0669956221712</v>
+        <v>117.1221202324025</v>
       </c>
       <c r="N11">
-        <v>111.4353271903156</v>
+        <v>111.3731400442088</v>
       </c>
       <c r="O11">
-        <v>7.631668431855641</v>
+        <v>5.748980188193748</v>
       </c>
       <c r="P11">
-        <v>0.5536613514695621</v>
+        <v>0.5745583981687303</v>
       </c>
       <c r="Q11">
-        <v>0.128050566236857</v>
+        <v>0.1260686327059639</v>
       </c>
       <c r="R11">
-        <v>0.3055936785914721</v>
+        <v>0.238906356375631</v>
       </c>
       <c r="S11">
-        <v>0.5592005655216874</v>
+        <v>0.5849052002403099</v>
       </c>
       <c r="T11">
-        <v>0.2459914206193677</v>
+        <v>0.3203340492940487</v>
       </c>
       <c r="U11">
-        <v>0.488251744191927</v>
+        <v>0.3929304189189218</v>
       </c>
       <c r="V11">
-        <v>99.45064880483321</v>
+        <v>100.2376234567901</v>
       </c>
       <c r="W11">
-        <v>115.9569214604675</v>
+        <v>116.6242283950617</v>
       </c>
       <c r="X11">
-        <v>4.91358024691358</v>
+        <v>2.185185185185185</v>
       </c>
       <c r="Y11">
-        <v>0.590049127530256</v>
+        <v>0.61036078125245</v>
       </c>
       <c r="Z11">
-        <v>115.22</v>
+        <v>115.79</v>
       </c>
       <c r="AA11">
-        <v>9.770000000000001</v>
+        <v>3.57</v>
       </c>
       <c r="AB11">
-        <v>-10.13717477219789</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC11">
-        <v>104.7204689341547</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD11">
-        <v>114.8576437063525</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE11">
         <v>1</v>
@@ -1798,15 +1798,15 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11">
-        <v>1.367372555625685</v>
+        <v>-0.05212589690184837</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -1821,79 +1821,79 @@
         <v>46124</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G12">
-        <v>1563.113</v>
+        <v>1519.075</v>
       </c>
       <c r="H12">
-        <v>-0.2995</v>
+        <v>1.4845</v>
       </c>
       <c r="I12">
-        <v>1497.120296296296</v>
+        <v>1499.059012345679</v>
       </c>
       <c r="J12">
-        <v>116.7427707903731</v>
+        <v>114.0721750810242</v>
       </c>
       <c r="K12">
-        <v>113.8631432395376</v>
+        <v>111.2353680452117</v>
       </c>
       <c r="L12">
-        <v>2.879627550835488</v>
+        <v>2.836807035812536</v>
       </c>
       <c r="M12">
-        <v>117.1221202324025</v>
+        <v>118.2933190627534</v>
       </c>
       <c r="N12">
-        <v>111.3731400442088</v>
+        <v>109.9968480358148</v>
       </c>
       <c r="O12">
-        <v>5.748980188193748</v>
+        <v>8.29647102693859</v>
       </c>
       <c r="P12">
-        <v>0.5745583981687303</v>
+        <v>0.5493560462736199</v>
       </c>
       <c r="Q12">
-        <v>0.1260686327059639</v>
+        <v>0.1151105315578217</v>
       </c>
       <c r="R12">
-        <v>0.238906356375631</v>
+        <v>0.2502841411495709</v>
       </c>
       <c r="S12">
-        <v>0.5849052002403099</v>
+        <v>0.5780472549608094</v>
       </c>
       <c r="T12">
-        <v>0.3203340492940487</v>
+        <v>0.2682324169232653</v>
       </c>
       <c r="U12">
-        <v>0.3929304189189218</v>
+        <v>0.3631220135205512</v>
       </c>
       <c r="V12">
-        <v>100.2376234567901</v>
+        <v>100.6396037898363</v>
       </c>
       <c r="W12">
-        <v>116.6242283950617</v>
+        <v>114.8733850129199</v>
       </c>
       <c r="X12">
-        <v>2.185185185185185</v>
+        <v>3.189491817398794</v>
       </c>
       <c r="Y12">
-        <v>0.61036078125245</v>
+        <v>0.5828432461013802</v>
       </c>
       <c r="Z12">
-        <v>115.79</v>
+        <v>117.64</v>
       </c>
       <c r="AA12">
-        <v>3.57</v>
+        <v>9.08</v>
       </c>
       <c r="AB12">
-        <v>1.827913300592181</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC12">
-        <v>114.1496737878887</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD12">
-        <v>112.3217604872965</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE12">
         <v>1</v>
@@ -1905,12 +1905,12 @@
         <v>4</v>
       </c>
       <c r="AH12">
-        <v>-0.1163171033675953</v>
+        <v>0.7761682313291499</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -1919,97 +1919,97 @@
         <v>75</v>
       </c>
       <c r="D13">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E13" s="2">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="F13">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G13">
-        <v>1519.075</v>
+        <v>1595.901</v>
       </c>
       <c r="H13">
-        <v>1.4845</v>
+        <v>1.1766</v>
       </c>
       <c r="I13">
-        <v>1499.059012345679</v>
+        <v>1500.667987951807</v>
       </c>
       <c r="J13">
-        <v>114.0721750810242</v>
+        <v>115.181340119533</v>
       </c>
       <c r="K13">
-        <v>111.2353680452117</v>
+        <v>112.7471716506547</v>
       </c>
       <c r="L13">
-        <v>2.836807035812536</v>
+        <v>2.434168468878287</v>
       </c>
       <c r="M13">
-        <v>118.2933190627534</v>
+        <v>114.3450585426628</v>
       </c>
       <c r="N13">
-        <v>109.9968480358148</v>
+        <v>114.519081716883</v>
       </c>
       <c r="O13">
-        <v>8.29647102693859</v>
+        <v>-0.1740231742202818</v>
       </c>
       <c r="P13">
-        <v>0.5493560462736199</v>
+        <v>0.5490265642552472</v>
       </c>
       <c r="Q13">
-        <v>0.1151105315578217</v>
+        <v>0.1273777560431238</v>
       </c>
       <c r="R13">
-        <v>0.2502841411495709</v>
+        <v>0.3014656305607926</v>
       </c>
       <c r="S13">
-        <v>0.5780472549608094</v>
+        <v>0.5265069721753005</v>
       </c>
       <c r="T13">
-        <v>0.2682324169232653</v>
+        <v>0.2460316087241722</v>
       </c>
       <c r="U13">
-        <v>0.3631220135205512</v>
+        <v>0.4887780357010577</v>
       </c>
       <c r="V13">
-        <v>100.6396037898363</v>
+        <v>99.6657969018933</v>
       </c>
       <c r="W13">
-        <v>114.8733850129199</v>
+        <v>115.3975903614458</v>
       </c>
       <c r="X13">
-        <v>3.189491817398794</v>
+        <v>3.760757314974183</v>
       </c>
       <c r="Y13">
-        <v>0.5828432461013802</v>
+        <v>0.5862751795663363</v>
       </c>
       <c r="Z13">
-        <v>117.64</v>
+        <v>112.23</v>
       </c>
       <c r="AA13">
-        <v>9.08</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>-4.536933640611859</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC13">
-        <v>108.3888858603967</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD13">
-        <v>112.9258195010085</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH13">
-        <v>1.435180330083925</v>
+        <v>0.7410183375666578</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2023,76 +2023,76 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E14" s="2">
-        <v>46124</v>
+        <v>46126</v>
       </c>
       <c r="F14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14">
-        <v>1522.559</v>
+        <v>1527.648</v>
       </c>
       <c r="H14">
-        <v>-1.8059</v>
+        <v>-1.8362</v>
       </c>
       <c r="I14">
-        <v>1501.222209876543</v>
+        <v>1501.638890243902</v>
       </c>
       <c r="J14">
-        <v>114.8839319698021</v>
+        <v>114.6709319067504</v>
       </c>
       <c r="K14">
-        <v>112.4185007824804</v>
+        <v>112.6223580741253</v>
       </c>
       <c r="L14">
-        <v>2.465431187321614</v>
+        <v>2.048573832625117</v>
       </c>
       <c r="M14">
-        <v>120.2678077962238</v>
+        <v>121.8006871479158</v>
       </c>
       <c r="N14">
-        <v>121.6671133267305</v>
+        <v>121.5315734581696</v>
       </c>
       <c r="O14">
-        <v>-1.399305530506721</v>
+        <v>0.2691136897462759</v>
       </c>
       <c r="P14">
-        <v>0.5438015913268103</v>
+        <v>0.5425583298740713</v>
       </c>
       <c r="Q14">
-        <v>0.1109409230900582</v>
+        <v>0.1105072050709512</v>
       </c>
       <c r="R14">
-        <v>0.2519821426815509</v>
+        <v>0.2512834002215163</v>
       </c>
       <c r="S14">
-        <v>0.5805133860074695</v>
+        <v>0.5859150211633202</v>
       </c>
       <c r="T14">
-        <v>0.2688891523044427</v>
+        <v>0.2668975444299984</v>
       </c>
       <c r="U14">
-        <v>0.406009179457376</v>
+        <v>0.4065551262287586</v>
       </c>
       <c r="V14">
-        <v>105.5325220458554</v>
+        <v>105.549430894309</v>
       </c>
       <c r="W14">
-        <v>121.2328042328042</v>
+        <v>121.0084688346884</v>
       </c>
       <c r="X14">
-        <v>2.721693121693122</v>
+        <v>2.236788617886179</v>
       </c>
       <c r="Y14">
-        <v>0.5809746418805888</v>
+        <v>0.5797829519539587</v>
       </c>
       <c r="Z14">
-        <v>124.64</v>
+        <v>125.82</v>
       </c>
       <c r="AA14">
-        <v>-2.35</v>
+        <v>-0.46</v>
       </c>
       <c r="AB14">
         <v>-1.094669144490311</v>
@@ -2110,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14">
-        <v>1.038374839997535</v>
+        <v>0.2021263012905594</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2127,76 +2127,76 @@
         <v>77</v>
       </c>
       <c r="D15">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="F15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G15">
-        <v>1546.063</v>
+        <v>1547.576</v>
       </c>
       <c r="H15">
-        <v>-0.6596</v>
+        <v>-1.1818</v>
       </c>
       <c r="I15">
-        <v>1497.973962962963</v>
+        <v>1497.571951219512</v>
       </c>
       <c r="J15">
-        <v>115.7044466103971</v>
+        <v>115.7559971917994</v>
       </c>
       <c r="K15">
-        <v>113.8180777013727</v>
+        <v>113.9836636742961</v>
       </c>
       <c r="L15">
-        <v>1.886368909024496</v>
+        <v>1.772333517503413</v>
       </c>
       <c r="M15">
-        <v>116.7735953178043</v>
+        <v>115.5369920979726</v>
       </c>
       <c r="N15">
-        <v>111.3520914765397</v>
+        <v>113.7634557004086</v>
       </c>
       <c r="O15">
-        <v>5.42150384126453</v>
+        <v>1.773536397563934</v>
       </c>
       <c r="P15">
-        <v>0.5597003803540067</v>
+        <v>0.5608937445510744</v>
       </c>
       <c r="Q15">
-        <v>0.1247261155085186</v>
+        <v>0.1258455536109729</v>
       </c>
       <c r="R15">
-        <v>0.2351137530798637</v>
+        <v>0.2355198616052937</v>
       </c>
       <c r="S15">
-        <v>0.5683213322113877</v>
+        <v>0.5616141638462627</v>
       </c>
       <c r="T15">
-        <v>0.2970940051711752</v>
+        <v>0.2958532089187961</v>
       </c>
       <c r="U15">
-        <v>0.4047321285737012</v>
+        <v>0.4043346898788371</v>
       </c>
       <c r="V15">
-        <v>98.76594491927825</v>
+        <v>98.88738095238094</v>
       </c>
       <c r="W15">
-        <v>113.7850585628364</v>
+        <v>113.9404761904762</v>
       </c>
       <c r="X15">
-        <v>1.186767964545743</v>
+        <v>0.9880952380952385</v>
       </c>
       <c r="Y15">
-        <v>0.6027976413905946</v>
+        <v>0.6040192047046427</v>
       </c>
       <c r="Z15">
-        <v>115.27</v>
+        <v>114.61</v>
       </c>
       <c r="AA15">
-        <v>4.91</v>
+        <v>1.39</v>
       </c>
       <c r="AB15">
         <v>4.815266446541752</v>
@@ -2208,16 +2208,16 @@
         <v>108.9954157027332</v>
       </c>
       <c r="AE15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH15">
-        <v>1.160493279997867</v>
+        <v>0.5644096808070423</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2321,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>1.038021081879212</v>
+        <v>1.006657396874706</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -2335,76 +2335,76 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E17" s="2">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="F17">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17">
-        <v>1499.249</v>
+        <v>1506.998</v>
       </c>
       <c r="H17">
-        <v>-0.6829</v>
+        <v>-0.0965</v>
       </c>
       <c r="I17">
-        <v>1511.771839506173</v>
+        <v>1514.33956626506</v>
       </c>
       <c r="J17">
-        <v>113.3579866792698</v>
+        <v>113.3693251323049</v>
       </c>
       <c r="K17">
-        <v>111.676625634198</v>
+        <v>111.6097938829175</v>
       </c>
       <c r="L17">
-        <v>1.681361045071835</v>
+        <v>1.759531249387505</v>
       </c>
       <c r="M17">
-        <v>115.212368268558</v>
+        <v>113.749090710574</v>
       </c>
       <c r="N17">
-        <v>111.1045719057573</v>
+        <v>109.92578595288</v>
       </c>
       <c r="O17">
-        <v>4.107796362800745</v>
+        <v>3.82330475769396</v>
       </c>
       <c r="P17">
-        <v>0.5397023215257585</v>
+        <v>0.53988387817215</v>
       </c>
       <c r="Q17">
-        <v>0.1197078111198993</v>
+        <v>0.1200330816043692</v>
       </c>
       <c r="R17">
-        <v>0.2874150724826931</v>
+        <v>0.2854315642327104</v>
       </c>
       <c r="S17">
-        <v>0.5438109864705895</v>
+        <v>0.5424408688965603</v>
       </c>
       <c r="T17">
-        <v>0.2274089467613819</v>
+        <v>0.2303359461455696</v>
       </c>
       <c r="U17">
-        <v>0.4538504459758578</v>
+        <v>0.4566602881617265</v>
       </c>
       <c r="V17">
-        <v>99.59627278071723</v>
+        <v>99.35960457213469</v>
       </c>
       <c r="W17">
-        <v>112.8489124044679</v>
+        <v>112.5143651529194</v>
       </c>
       <c r="X17">
-        <v>1.822457378012934</v>
+        <v>1.746370095767686</v>
       </c>
       <c r="Y17">
-        <v>0.5709653419910864</v>
+        <v>0.5718842837859359</v>
       </c>
       <c r="Z17">
-        <v>115.74</v>
+        <v>113.52</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>4.02</v>
       </c>
       <c r="AB17">
         <v>-2.375203171419814</v>
@@ -2416,21 +2416,21 @@
         <v>117.0787009454136</v>
       </c>
       <c r="AE17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17">
-        <v>0.6911417331988822</v>
+        <v>0.2188569846778717</v>
       </c>
     </row>
     <row r="18" spans="1:34">
       <c r="A18">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
@@ -2439,85 +2439,85 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G18">
-        <v>1473.102</v>
+        <v>1518.584</v>
       </c>
       <c r="H18">
-        <v>0.4413</v>
+        <v>1.3156</v>
       </c>
       <c r="I18">
-        <v>1501.363333333333</v>
+        <v>1491.9238875</v>
       </c>
       <c r="J18">
-        <v>113.3364274064839</v>
+        <v>112.4488476125274</v>
       </c>
       <c r="K18">
-        <v>112.6139686884808</v>
+        <v>111.6504448775219</v>
       </c>
       <c r="L18">
-        <v>0.7224587180030148</v>
+        <v>0.7984027350055121</v>
       </c>
       <c r="M18">
-        <v>114.5501181806482</v>
+        <v>107.4637355676158</v>
       </c>
       <c r="N18">
-        <v>112.2888021156216</v>
+        <v>107.1936242807708</v>
       </c>
       <c r="O18">
-        <v>2.261316065026615</v>
+        <v>0.2701112868450855</v>
       </c>
       <c r="P18">
-        <v>0.5318727944427831</v>
+        <v>0.5316883653351835</v>
       </c>
       <c r="Q18">
-        <v>0.1136606510374349</v>
+        <v>0.1194026517819761</v>
       </c>
       <c r="R18">
-        <v>0.2600054390419136</v>
+        <v>0.2468902134060437</v>
       </c>
       <c r="S18">
-        <v>0.5450646048875489</v>
+        <v>0.5190114746965675</v>
       </c>
       <c r="T18">
-        <v>0.2780044326762062</v>
+        <v>0.3225880025447687</v>
       </c>
       <c r="U18">
-        <v>0.3920010435106439</v>
+        <v>0.3846010709395101</v>
       </c>
       <c r="V18">
-        <v>102.678574074074</v>
+        <v>102.7309761904762</v>
       </c>
       <c r="W18">
-        <v>116.0092592592593</v>
+        <v>115.6431547619048</v>
       </c>
       <c r="X18">
-        <v>0.0787037037037038</v>
+        <v>1.494642857142857</v>
       </c>
       <c r="Y18">
-        <v>0.5737317169306106</v>
+        <v>0.5777729492695108</v>
       </c>
       <c r="Z18">
-        <v>116.73</v>
+        <v>114.7</v>
       </c>
       <c r="AA18">
-        <v>1.28</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="AB18">
-        <v>-6.382503892565079</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC18">
-        <v>109.8789897646453</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD18">
-        <v>116.2614936572104</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE18">
         <v>1</v>
@@ -2529,12 +2529,12 @@
         <v>3</v>
       </c>
       <c r="AH18">
-        <v>0.8011081820896432</v>
+        <v>0.1825651873351112</v>
       </c>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -2543,102 +2543,102 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E19" s="2">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="F19">
         <v>41</v>
       </c>
       <c r="G19">
-        <v>1527.008</v>
+        <v>1475.324</v>
       </c>
       <c r="H19">
-        <v>0.2441</v>
+        <v>0.1877</v>
       </c>
       <c r="I19">
-        <v>1489.826794871795</v>
+        <v>1499.990841463415</v>
       </c>
       <c r="J19">
-        <v>112.3618046206719</v>
+        <v>113.0881776309462</v>
       </c>
       <c r="K19">
-        <v>112.2198305215782</v>
+        <v>112.3871525051826</v>
       </c>
       <c r="L19">
-        <v>0.1419740990936243</v>
+        <v>0.7010251257636451</v>
       </c>
       <c r="M19">
-        <v>111.8649203009325</v>
+        <v>115.1137501098109</v>
       </c>
       <c r="N19">
-        <v>113.5765262526615</v>
+        <v>109.7612384232032</v>
       </c>
       <c r="O19">
-        <v>-1.711605951729009</v>
+        <v>5.352511686607764</v>
       </c>
       <c r="P19">
-        <v>0.5314800403153312</v>
+        <v>0.5305965987775721</v>
       </c>
       <c r="Q19">
-        <v>0.1196222682343991</v>
+        <v>0.1134822954828032</v>
       </c>
       <c r="R19">
-        <v>0.2465242137565519</v>
+        <v>0.2581697776036243</v>
       </c>
       <c r="S19">
-        <v>0.5362920244771173</v>
+        <v>0.5433917377046693</v>
       </c>
       <c r="T19">
-        <v>0.3190429672900122</v>
+        <v>0.2790026571671177</v>
       </c>
       <c r="U19">
-        <v>0.3878288537136768</v>
+        <v>0.3917329099854188</v>
       </c>
       <c r="V19">
-        <v>102.8133583489681</v>
+        <v>102.605246876859</v>
       </c>
       <c r="W19">
-        <v>115.65478424015</v>
+        <v>115.7102914931588</v>
       </c>
       <c r="X19">
-        <v>0.8661663539712321</v>
+        <v>0.1142177275431291</v>
       </c>
       <c r="Y19">
-        <v>0.5772590404186486</v>
+        <v>0.5728831727331063</v>
       </c>
       <c r="Z19">
-        <v>117.63</v>
+        <v>117.1</v>
       </c>
       <c r="AA19">
-        <v>-1.49</v>
+        <v>4.08</v>
       </c>
       <c r="AB19">
-        <v>-0.5231111597400365</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC19">
-        <v>107.6152962364644</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD19">
-        <v>108.1384073962044</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH19">
-        <v>0.6664103782363974</v>
+        <v>0.321213283069761</v>
       </c>
     </row>
     <row r="20" spans="1:34">
       <c r="A20">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B20" t="s">
         <v>52</v>
@@ -2647,85 +2647,85 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2">
-        <v>46124</v>
+        <v>46126</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G20">
-        <v>1465.009</v>
+        <v>1472.563</v>
       </c>
       <c r="H20">
-        <v>-1.8002</v>
+        <v>1.2276</v>
       </c>
       <c r="I20">
-        <v>1504.838530864198</v>
+        <v>1504.681597560976</v>
       </c>
       <c r="J20">
-        <v>112.7778777455463</v>
+        <v>111.611977985623</v>
       </c>
       <c r="K20">
-        <v>113.3577573917064</v>
+        <v>112.4635866111893</v>
       </c>
       <c r="L20">
-        <v>-0.5798796461601849</v>
+        <v>-0.8516086255663559</v>
       </c>
       <c r="M20">
-        <v>114.0444443399996</v>
+        <v>116.0015297319025</v>
       </c>
       <c r="N20">
-        <v>118.2284876497019</v>
+        <v>105.2001729121645</v>
       </c>
       <c r="O20">
-        <v>-4.184043309702345</v>
+        <v>10.80135681973795</v>
       </c>
       <c r="P20">
-        <v>0.5498546901292588</v>
+        <v>0.5346495885056282</v>
       </c>
       <c r="Q20">
-        <v>0.1318149452976943</v>
+        <v>0.1398908202848756</v>
       </c>
       <c r="R20">
-        <v>0.2577646107997965</v>
+        <v>0.311680572475506</v>
       </c>
       <c r="S20">
-        <v>0.5574525454327377</v>
+        <v>0.5609121131329114</v>
       </c>
       <c r="T20">
-        <v>0.242988171994435</v>
+        <v>0.2836008686676942</v>
       </c>
       <c r="U20">
-        <v>0.496158125901545</v>
+        <v>0.4707644065611628</v>
       </c>
       <c r="V20">
-        <v>101.608630490956</v>
+        <v>103.1293078444298</v>
       </c>
       <c r="W20">
-        <v>114.5581395348838</v>
+        <v>115.4357284113382</v>
       </c>
       <c r="X20">
-        <v>-0.6106804478897502</v>
+        <v>-0.1766644693473961</v>
       </c>
       <c r="Y20">
-        <v>0.5849172096355714</v>
+        <v>0.5712299157036377</v>
       </c>
       <c r="Z20">
-        <v>113.69</v>
+        <v>117.87</v>
       </c>
       <c r="AA20">
-        <v>-4.82</v>
+        <v>12.19</v>
       </c>
       <c r="AB20">
-        <v>2.402868486532558</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC20">
-        <v>112.5227430890375</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD20">
-        <v>110.1198746025049</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE20">
         <v>1</v>
@@ -2734,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH20">
-        <v>1.077792710122442</v>
+        <v>0.3304416016302762</v>
       </c>
     </row>
     <row r="21" spans="1:34">
       <c r="A21">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
@@ -2751,85 +2751,85 @@
         <v>83</v>
       </c>
       <c r="D21">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E21" s="2">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G21">
-        <v>1471.6</v>
+        <v>1471.569</v>
       </c>
       <c r="H21">
-        <v>1.2858</v>
+        <v>-1.5085</v>
       </c>
       <c r="I21">
-        <v>1507.032037037037</v>
+        <v>1505.850120481928</v>
       </c>
       <c r="J21">
-        <v>111.6839894968333</v>
+        <v>112.6221838412012</v>
       </c>
       <c r="K21">
-        <v>112.4435626374769</v>
+        <v>113.6097028971402</v>
       </c>
       <c r="L21">
-        <v>-0.759573140643502</v>
+        <v>-0.9875190559389955</v>
       </c>
       <c r="M21">
-        <v>115.891950349308</v>
+        <v>114.3428494363806</v>
       </c>
       <c r="N21">
-        <v>106.3211056799474</v>
+        <v>120.1535355097058</v>
       </c>
       <c r="O21">
-        <v>9.570844669360605</v>
+        <v>-5.810686073325223</v>
       </c>
       <c r="P21">
-        <v>0.5343550965743989</v>
+        <v>0.5513659943192487</v>
       </c>
       <c r="Q21">
-        <v>0.1394660755341611</v>
+        <v>0.1344422423758589</v>
       </c>
       <c r="R21">
-        <v>0.3125017781001434</v>
+        <v>0.258513203243472</v>
       </c>
       <c r="S21">
-        <v>0.5576357739010501</v>
+        <v>0.559296308148711</v>
       </c>
       <c r="T21">
-        <v>0.2820778387585565</v>
+        <v>0.2434375477815177</v>
       </c>
       <c r="U21">
-        <v>0.468791430854873</v>
+        <v>0.495310148563981</v>
       </c>
       <c r="V21">
-        <v>103.1977777777778</v>
+        <v>101.41843682422</v>
       </c>
       <c r="W21">
-        <v>115.5785322359397</v>
+        <v>114.2662959530429</v>
       </c>
       <c r="X21">
-        <v>-0.09876543209876543</v>
+        <v>-0.8659252394192152</v>
       </c>
       <c r="Y21">
-        <v>0.5708968808747181</v>
+        <v>0.5860872916743576</v>
       </c>
       <c r="Z21">
-        <v>117.77</v>
+        <v>111.39</v>
       </c>
       <c r="AA21">
-        <v>10.47</v>
+        <v>-6.63</v>
       </c>
       <c r="AB21">
-        <v>-3.840928550668963</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC21">
-        <v>109.2995408403883</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD21">
-        <v>113.1404693910572</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE21">
         <v>1</v>
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.6009843904787218</v>
+        <v>0.5174150960659849</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-0.9477176015193129</v>
+        <v>-1.230770811879907</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="AH23">
-        <v>-0.5852165804675344</v>
+        <v>-0.7667014396529654</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="AH24">
-        <v>-1.225296356118726</v>
+        <v>-1.165658227677184</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.259238547880103</v>
+        <v>-1.287157193381943</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-0.9521540538361646</v>
+        <v>-1.050037485815659</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="AH27">
-        <v>-0.7998378263709043</v>
+        <v>-0.9324243206618551</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.7506031220141877</v>
+        <v>-0.8944070357594571</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.632423740711327</v>
+        <v>-1.575317505962057</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.921377186539993</v>
+        <v>-1.798437063947162</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.130982826741756</v>
+        <v>-1.188122694148399</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -865,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="AH2">
-        <v>-0.7710635982193697</v>
+        <v>-0.7568777193517886</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -969,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="AH3">
-        <v>0.3409857680820598</v>
+        <v>0.360595027182989</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -1073,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="AH4">
-        <v>0.5654538617262683</v>
+        <v>0.586404346312513</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1177,7 +1177,7 @@
         <v>4</v>
       </c>
       <c r="AH5">
-        <v>1.177202809186422</v>
+        <v>1.201729063033445</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1281,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="AH6">
-        <v>1.366245995995082</v>
+        <v>1.391693207210217</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1385,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AH7">
-        <v>0.3005155364075296</v>
+        <v>0.3198264469894737</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="AH8">
-        <v>1.756720663233555</v>
+        <v>1.78460558663419</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="AH9">
-        <v>1.758131410677385</v>
+        <v>1.785988337793205</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="AH10">
-        <v>0.5860951280523858</v>
+        <v>0.607000438145785</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -1801,7 +1801,7 @@
         <v>4</v>
       </c>
       <c r="AH11">
-        <v>-0.05212589690184837</v>
+        <v>-0.03484281697181366</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -1905,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="AH12">
-        <v>0.7761682313291499</v>
+        <v>0.6585782419471469</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -2009,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="AH13">
-        <v>0.7410183375666578</v>
+        <v>0.7867139442025407</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2113,7 +2113,7 @@
         <v>4</v>
       </c>
       <c r="AH14">
-        <v>0.2021263012905594</v>
+        <v>0.2226849113213537</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2217,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="AH15">
-        <v>0.5644096808070423</v>
+        <v>0.5612931716368992</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2321,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>1.006657396874706</v>
+        <v>1.030107321918117</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="AH17">
-        <v>0.2188569846778717</v>
+        <v>0.222318185787201</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -2529,7 +2529,7 @@
         <v>3</v>
       </c>
       <c r="AH18">
-        <v>0.1825651873351112</v>
+        <v>0.1311049722384743</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -2633,7 +2633,7 @@
         <v>3</v>
       </c>
       <c r="AH19">
-        <v>0.321213283069761</v>
+        <v>0.3474586977253006</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2737,7 +2737,7 @@
         <v>3</v>
       </c>
       <c r="AH20">
-        <v>0.3304416016302762</v>
+        <v>0.02644865279800278</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.5174150960659849</v>
+        <v>0.5444201825156062</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-1.230770811879907</v>
+        <v>-1.219764322489436</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="AH23">
-        <v>-0.7667014396529654</v>
+        <v>-0.753461922250703</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="AH24">
-        <v>-1.165658227677184</v>
+        <v>-1.154670231892047</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.287157193381943</v>
+        <v>-1.273884398444201</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.050037485815659</v>
+        <v>-1.037728995491819</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="AH27">
-        <v>-0.9324243206618551</v>
+        <v>-0.9200683304860611</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.8944070357594571</v>
+        <v>-0.8821469189446238</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.575317505962057</v>
+        <v>-1.567292597074853</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.798437063947162</v>
+        <v>-1.790824006364488</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.188122694148399</v>
+        <v>-1.177408475630625</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -124,54 +124,54 @@
     <t>San Antonio Spurs</t>
   </si>
   <si>
+    <t>Boston Celtics</t>
+  </si>
+  <si>
     <t>Detroit Pistons</t>
   </si>
   <si>
-    <t>Boston Celtics</t>
-  </si>
-  <si>
     <t>New York Knicks</t>
   </si>
   <si>
+    <t>Denver Nuggets</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
     <t>Houston Rockets</t>
   </si>
   <si>
-    <t>Denver Nuggets</t>
-  </si>
-  <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
     <t>Los Angeles Lakers</t>
   </si>
   <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
+    <t>Miami Heat</t>
+  </si>
+  <si>
+    <t>Atlanta Hawks</t>
+  </si>
+  <si>
     <t>Toronto Raptors</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
-    <t>Miami Heat</t>
-  </si>
-  <si>
     <t>LA Clippers</t>
   </si>
   <si>
-    <t>Atlanta Hawks</t>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
   </si>
   <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
     <t>Portland Trail Blazers</t>
   </si>
   <si>
@@ -214,52 +214,52 @@
     <t>SAS</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
     <t>DET</t>
   </si>
   <si>
-    <t>BOS</t>
-  </si>
-  <si>
     <t>NYK</t>
   </si>
   <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
     <t>LAL</t>
   </si>
   <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>ATL</t>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>PHI</t>
   </si>
   <si>
     <t>PHX</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>PHI</t>
   </si>
   <si>
     <t>POR</t>
@@ -775,76 +775,76 @@
         <v>64</v>
       </c>
       <c r="D2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E2" s="2">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>1764.102</v>
+        <v>1749.147</v>
       </c>
       <c r="H2">
-        <v>2.0618</v>
+        <v>1.2057</v>
       </c>
       <c r="I2">
-        <v>1500.28485</v>
+        <v>1500.272061728395</v>
       </c>
       <c r="J2">
-        <v>116.9132749472211</v>
+        <v>117.5589013231487</v>
       </c>
       <c r="K2">
-        <v>106.2630499540704</v>
+        <v>105.3643959793545</v>
       </c>
       <c r="L2">
-        <v>10.65022499315071</v>
+        <v>12.19450534379416</v>
       </c>
       <c r="M2">
-        <v>119.8427936428078</v>
+        <v>120.7669975454074</v>
       </c>
       <c r="N2">
-        <v>108.1168925755339</v>
+        <v>106.6406565741449</v>
       </c>
       <c r="O2">
-        <v>11.7259010672738</v>
+        <v>14.12634097126251</v>
       </c>
       <c r="P2">
-        <v>0.5632583602522824</v>
+        <v>0.5628478086594806</v>
       </c>
       <c r="Q2">
-        <v>0.1073938433911547</v>
+        <v>0.1061916568324137</v>
       </c>
       <c r="R2">
-        <v>0.2196580100677842</v>
+        <v>0.2247559608916612</v>
       </c>
       <c r="S2">
-        <v>0.5842705862967622</v>
+        <v>0.5746956004450361</v>
       </c>
       <c r="T2">
-        <v>0.260409154694913</v>
+        <v>0.2627356937233273</v>
       </c>
       <c r="U2">
-        <v>0.4276387920316667</v>
+        <v>0.4285808139687929</v>
       </c>
       <c r="V2">
-        <v>101.8549714285714</v>
+        <v>101.5989094650206</v>
       </c>
       <c r="W2">
-        <v>118.8828571428571</v>
+        <v>119.1440329218107</v>
       </c>
       <c r="X2">
-        <v>10.59714285714286</v>
+        <v>11.96673525377229</v>
       </c>
       <c r="Y2">
-        <v>0.6002190721862691</v>
+        <v>0.6008700161511308</v>
       </c>
       <c r="Z2">
-        <v>121.09</v>
+        <v>120.89</v>
       </c>
       <c r="AA2">
-        <v>10.75</v>
+        <v>12.77</v>
       </c>
       <c r="AB2">
         <v>11.54061896828745</v>
@@ -856,16 +856,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF2">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH2">
-        <v>-0.7568777193517886</v>
+        <v>1.221332954544052</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -879,76 +879,76 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E3" s="2">
-        <v>46124</v>
+        <v>46133</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>1740.684</v>
+        <v>1737.41</v>
       </c>
       <c r="H3">
-        <v>1.2096</v>
+        <v>0.1702</v>
       </c>
       <c r="I3">
-        <v>1506.0862875</v>
+        <v>1507.117536585366</v>
       </c>
       <c r="J3">
-        <v>117.7546797640171</v>
+        <v>117.3385438578281</v>
       </c>
       <c r="K3">
-        <v>109.5250557544995</v>
+        <v>109.1329793659553</v>
       </c>
       <c r="L3">
-        <v>8.229624009517593</v>
+        <v>8.205564491872869</v>
       </c>
       <c r="M3">
-        <v>121.8543160436847</v>
+        <v>119.2492500944585</v>
       </c>
       <c r="N3">
-        <v>108.5131608435764</v>
+        <v>109.231178061518</v>
       </c>
       <c r="O3">
-        <v>13.34115520010841</v>
+        <v>10.01807203294055</v>
       </c>
       <c r="P3">
-        <v>0.5607518815416633</v>
+        <v>0.559164856289013</v>
       </c>
       <c r="Q3">
-        <v>0.1105675804191624</v>
+        <v>0.1118647634360532</v>
       </c>
       <c r="R3">
-        <v>0.2599241918883525</v>
+        <v>0.2610009906273514</v>
       </c>
       <c r="S3">
-        <v>0.573759506831634</v>
+        <v>0.5635429605073611</v>
       </c>
       <c r="T3">
-        <v>0.275386072016686</v>
+        <v>0.2772003821165557</v>
       </c>
       <c r="U3">
-        <v>0.421865700577073</v>
+        <v>0.4172312105430142</v>
       </c>
       <c r="V3">
-        <v>101.9809756097561</v>
+        <v>101.8894684177611</v>
       </c>
       <c r="W3">
-        <v>119.9146341463415</v>
+        <v>119.3977485928705</v>
       </c>
       <c r="X3">
-        <v>8.158536585365853</v>
+        <v>8.145716072545341</v>
       </c>
       <c r="Y3">
-        <v>0.5963566573981414</v>
+        <v>0.5950795943644354</v>
       </c>
       <c r="Z3">
-        <v>125.2</v>
+        <v>121</v>
       </c>
       <c r="AA3">
-        <v>14.39</v>
+        <v>10.86</v>
       </c>
       <c r="AB3">
         <v>-2.513643863094118</v>
@@ -966,15 +966,15 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>0.360595027182989</v>
+        <v>1.059605115926468</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -983,85 +983,85 @@
         <v>66</v>
       </c>
       <c r="D4">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2">
-        <v>46124</v>
+        <v>46133</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>1687.659</v>
+        <v>1680.208</v>
       </c>
       <c r="H4">
-        <v>1.1559</v>
+        <v>1.5486</v>
       </c>
       <c r="I4">
-        <v>1496.0478375</v>
+        <v>1492.383397590361</v>
       </c>
       <c r="J4">
-        <v>115.6103956612828</v>
+        <v>117.7265517285943</v>
       </c>
       <c r="K4">
-        <v>107.6945038484208</v>
+        <v>110.4458779575985</v>
       </c>
       <c r="L4">
-        <v>7.915891812861926</v>
+        <v>7.280673770995797</v>
       </c>
       <c r="M4">
-        <v>119.8649433120767</v>
+        <v>122.0516609007653</v>
       </c>
       <c r="N4">
-        <v>106.4361929688154</v>
+        <v>110.1415847651288</v>
       </c>
       <c r="O4">
-        <v>13.42875034326124</v>
+        <v>11.91007613563649</v>
       </c>
       <c r="P4">
-        <v>0.5507988638619832</v>
+        <v>0.5517264180966418</v>
       </c>
       <c r="Q4">
-        <v>0.1240593293444159</v>
+        <v>0.1041665093381238</v>
       </c>
       <c r="R4">
-        <v>0.3059060468335256</v>
+        <v>0.29084626977922</v>
       </c>
       <c r="S4">
-        <v>0.5906929127225311</v>
+        <v>0.5828667679907207</v>
       </c>
       <c r="T4">
-        <v>0.2933532745723434</v>
+        <v>0.2113138591529365</v>
       </c>
       <c r="U4">
-        <v>0.3473183094591422</v>
+        <v>0.4700501041216564</v>
       </c>
       <c r="V4">
-        <v>102.0868014705882</v>
+        <v>97.15411801050355</v>
       </c>
       <c r="W4">
-        <v>117.9801470588235</v>
+        <v>114.4915044794563</v>
       </c>
       <c r="X4">
-        <v>8.178308823529411</v>
+        <v>7.424158171146123</v>
       </c>
       <c r="Y4">
-        <v>0.5868339963733044</v>
+        <v>0.5821149070408982</v>
       </c>
       <c r="Z4">
-        <v>120.85</v>
+        <v>118.6</v>
       </c>
       <c r="AA4">
-        <v>10.65</v>
+        <v>10.93</v>
       </c>
       <c r="AB4">
-        <v>1.549391602834736</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC4">
-        <v>112.5216901085732</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD4">
-        <v>110.9722985057385</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE4">
         <v>1</v>
@@ -1070,15 +1070,15 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH4">
-        <v>0.586404346312513</v>
+        <v>1.385938306503901</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -1087,97 +1087,97 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>1672.097</v>
+        <v>1688.714</v>
       </c>
       <c r="H5">
-        <v>1.6605</v>
+        <v>1.0394</v>
       </c>
       <c r="I5">
-        <v>1492.080469135802</v>
+        <v>1494.116975308642</v>
       </c>
       <c r="J5">
-        <v>117.8340667576958</v>
+        <v>114.9277646145556</v>
       </c>
       <c r="K5">
-        <v>110.2326502268895</v>
+        <v>107.7424536074891</v>
       </c>
       <c r="L5">
-        <v>7.601416530806378</v>
+        <v>7.185311007066583</v>
       </c>
       <c r="M5">
-        <v>122.823052319119</v>
+        <v>117.9912515778412</v>
       </c>
       <c r="N5">
-        <v>111.2468541567881</v>
+        <v>106.3552500880781</v>
       </c>
       <c r="O5">
-        <v>11.57619816233083</v>
+        <v>11.63600148976311</v>
       </c>
       <c r="P5">
-        <v>0.5531895830281515</v>
+        <v>0.5467925550246744</v>
       </c>
       <c r="Q5">
-        <v>0.1051189871210553</v>
+        <v>0.1238369938908686</v>
       </c>
       <c r="R5">
-        <v>0.2890820057519844</v>
+        <v>0.30082043179818</v>
       </c>
       <c r="S5">
-        <v>0.5906896617872682</v>
+        <v>0.5811325441420039</v>
       </c>
       <c r="T5">
-        <v>0.211641895060464</v>
+        <v>0.2998604291982057</v>
       </c>
       <c r="U5">
-        <v>0.4686385426947525</v>
+        <v>0.3488679124333923</v>
       </c>
       <c r="V5">
-        <v>97.39728982951205</v>
+        <v>101.9887477954144</v>
       </c>
       <c r="W5">
-        <v>114.8318636096413</v>
+        <v>117.2384479717814</v>
       </c>
       <c r="X5">
-        <v>7.663433274544386</v>
+        <v>7.565079365079365</v>
       </c>
       <c r="Y5">
-        <v>0.5838723733985678</v>
+        <v>0.5839756293687143</v>
       </c>
       <c r="Z5">
-        <v>119.48</v>
+        <v>118.01</v>
       </c>
       <c r="AA5">
-        <v>11.03</v>
+        <v>9.52</v>
       </c>
       <c r="AB5">
-        <v>9.220352523846751</v>
+        <v>1.549391602834736</v>
       </c>
       <c r="AC5">
-        <v>117.8084737243045</v>
+        <v>112.5216901085732</v>
       </c>
       <c r="AD5">
-        <v>108.5881212004577</v>
+        <v>110.9722985057385</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH5">
-        <v>1.201729063033445</v>
+        <v>0.7466211640355485</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1191,76 +1191,76 @@
         <v>68</v>
       </c>
       <c r="D6">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E6" s="2">
-        <v>46124</v>
+        <v>46132</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>1659.456</v>
+        <v>1657.279</v>
       </c>
       <c r="H6">
-        <v>-0.4289</v>
+        <v>0.5225</v>
       </c>
       <c r="I6">
-        <v>1491.1179625</v>
+        <v>1492.741841463415</v>
       </c>
       <c r="J6">
-        <v>117.4821467291267</v>
+        <v>117.3394362270218</v>
       </c>
       <c r="K6">
-        <v>110.898988049768</v>
+        <v>110.7887201296264</v>
       </c>
       <c r="L6">
-        <v>6.583158679358667</v>
+        <v>6.550716097395441</v>
       </c>
       <c r="M6">
-        <v>121.0345935504245</v>
+        <v>116.9344475705151</v>
       </c>
       <c r="N6">
-        <v>115.6207584862354</v>
+        <v>113.7441118504646</v>
       </c>
       <c r="O6">
-        <v>5.413835064189071</v>
+        <v>3.190335720050509</v>
       </c>
       <c r="P6">
-        <v>0.5556388603984453</v>
+        <v>0.5550350552301679</v>
       </c>
       <c r="Q6">
-        <v>0.1149244657950105</v>
+        <v>0.1152643701100042</v>
       </c>
       <c r="R6">
-        <v>0.2917389614411804</v>
+        <v>0.291193392577663</v>
       </c>
       <c r="S6">
-        <v>0.58108860699544</v>
+        <v>0.5624140161515211</v>
       </c>
       <c r="T6">
-        <v>0.2363069559585412</v>
+        <v>0.2416050571767059</v>
       </c>
       <c r="U6">
-        <v>0.4290621510752881</v>
+        <v>0.4265133680028778</v>
       </c>
       <c r="V6">
-        <v>98.99536585365854</v>
+        <v>99.0078799249531</v>
       </c>
       <c r="W6">
-        <v>116.0121951219512</v>
+        <v>115.9574734208881</v>
       </c>
       <c r="X6">
-        <v>6.012195121951219</v>
+        <v>6.129455909943715</v>
       </c>
       <c r="Y6">
-        <v>0.5880973439850578</v>
+        <v>0.5878662352946638</v>
       </c>
       <c r="Z6">
-        <v>114.09</v>
+        <v>109.96</v>
       </c>
       <c r="AA6">
-        <v>5.35</v>
+        <v>3.05</v>
       </c>
       <c r="AB6">
         <v>2.775420617465777</v>
@@ -1278,15 +1278,15 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH6">
-        <v>1.391693207210217</v>
+        <v>1.075207595206764</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
@@ -1295,85 +1295,85 @@
         <v>69</v>
       </c>
       <c r="D7">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E7" s="2">
-        <v>46124</v>
+        <v>46132</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>1591.505</v>
+        <v>1628.839</v>
       </c>
       <c r="H7">
-        <v>2.5318</v>
+        <v>3.7056</v>
       </c>
       <c r="I7">
-        <v>1494.639592592593</v>
+        <v>1507.148915662651</v>
       </c>
       <c r="J7">
-        <v>116.1261142955221</v>
+        <v>119.9280599431096</v>
       </c>
       <c r="K7">
-        <v>110.8492473446616</v>
+        <v>115.1030109853419</v>
       </c>
       <c r="L7">
-        <v>5.276866950860388</v>
+        <v>4.825048957767701</v>
       </c>
       <c r="M7">
-        <v>123.3463153357207</v>
+        <v>123.2540605180378</v>
       </c>
       <c r="N7">
-        <v>108.6507235196123</v>
+        <v>115.0746647345575</v>
       </c>
       <c r="O7">
-        <v>14.69559181610846</v>
+        <v>8.17939578348026</v>
       </c>
       <c r="P7">
-        <v>0.5451181025519822</v>
+        <v>0.5754303583246921</v>
       </c>
       <c r="Q7">
-        <v>0.1254588717427119</v>
+        <v>0.1084037766481807</v>
       </c>
       <c r="R7">
-        <v>0.3462547355904307</v>
+        <v>0.2318296053812003</v>
       </c>
       <c r="S7">
-        <v>0.5641559442031023</v>
+        <v>0.5849673280102159</v>
       </c>
       <c r="T7">
-        <v>0.2632562388546684</v>
+        <v>0.2998664243573962</v>
       </c>
       <c r="U7">
-        <v>0.351912753408883</v>
+        <v>0.409315740892408</v>
       </c>
       <c r="V7">
-        <v>99.39277777777779</v>
+        <v>101.5691370888961</v>
       </c>
       <c r="W7">
-        <v>115.4104938271605</v>
+        <v>121.7837837837838</v>
       </c>
       <c r="X7">
-        <v>5.49438832772166</v>
+        <v>4.940735916639531</v>
       </c>
       <c r="Y7">
-        <v>0.5781705646770098</v>
+        <v>0.6151360057647196</v>
       </c>
       <c r="Z7">
-        <v>122.28</v>
+        <v>128.67</v>
       </c>
       <c r="AA7">
-        <v>13.81</v>
+        <v>9.76</v>
       </c>
       <c r="AB7">
-        <v>3.413694058608522</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC7">
-        <v>112.3850185369902</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD7">
-        <v>108.9713244783817</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE7">
         <v>1</v>
@@ -1382,15 +1382,15 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH7">
-        <v>0.3198264469894737</v>
+        <v>1.473429233530684</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
@@ -1399,85 +1399,85 @@
         <v>70</v>
       </c>
       <c r="D8">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2">
-        <v>46124</v>
+        <v>46132</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G8">
-        <v>1616.966</v>
+        <v>1642.052</v>
       </c>
       <c r="H8">
-        <v>2.5671</v>
+        <v>-0.1592</v>
       </c>
       <c r="I8">
-        <v>1503.475345679012</v>
+        <v>1484.54234939759</v>
       </c>
       <c r="J8">
-        <v>120.4359953151273</v>
+        <v>117.2213020019621</v>
       </c>
       <c r="K8">
-        <v>115.3362286216927</v>
+        <v>112.7895091370545</v>
       </c>
       <c r="L8">
-        <v>5.099766693434593</v>
+        <v>4.431792864907528</v>
       </c>
       <c r="M8">
-        <v>126.6975204785679</v>
+        <v>120.668250262103</v>
       </c>
       <c r="N8">
-        <v>117.0436639215076</v>
+        <v>114.9759488648647</v>
       </c>
       <c r="O8">
-        <v>9.653856557060355</v>
+        <v>5.692301397238248</v>
       </c>
       <c r="P8">
-        <v>0.5773653575047751</v>
+        <v>0.5643021974490076</v>
       </c>
       <c r="Q8">
-        <v>0.1086484651027513</v>
+        <v>0.1172061706953217</v>
       </c>
       <c r="R8">
-        <v>0.2381079146426767</v>
+        <v>0.2640814000885438</v>
       </c>
       <c r="S8">
-        <v>0.6037980471907948</v>
+        <v>0.5904963174575838</v>
       </c>
       <c r="T8">
-        <v>0.2962978156392768</v>
+        <v>0.2698428252727614</v>
       </c>
       <c r="U8">
-        <v>0.4056715938787011</v>
+        <v>0.4415392882472934</v>
       </c>
       <c r="V8">
-        <v>101.4497942386832</v>
+        <v>102.0853471026965</v>
       </c>
       <c r="W8">
-        <v>122.1666666666667</v>
+        <v>119.4928284566839</v>
       </c>
       <c r="X8">
-        <v>5.222908093278464</v>
+        <v>4.354561101549054</v>
       </c>
       <c r="Y8">
-        <v>0.6162849962270014</v>
+        <v>0.5971871707768338</v>
       </c>
       <c r="Z8">
-        <v>130.88</v>
+        <v>123.19</v>
       </c>
       <c r="AA8">
-        <v>10.99</v>
+        <v>6.22</v>
       </c>
       <c r="AB8">
-        <v>2.722616812266775</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC8">
-        <v>116.5392386763017</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD8">
-        <v>113.8166218640349</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE8">
         <v>1</v>
@@ -1486,15 +1486,15 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH8">
-        <v>1.78460558663419</v>
+        <v>1.397380316794549</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9">
-        <v>1610612739</v>
+        <v>1610612745</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -1503,97 +1503,97 @@
         <v>71</v>
       </c>
       <c r="D9">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E9" s="2">
-        <v>46124</v>
+        <v>46133</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G9">
-        <v>1636.739</v>
+        <v>1587.025</v>
       </c>
       <c r="H9">
-        <v>-0.3377</v>
+        <v>1.1706</v>
       </c>
       <c r="I9">
-        <v>1487.012209876543</v>
+        <v>1493.901168674699</v>
       </c>
       <c r="J9">
-        <v>117.2471280340223</v>
+        <v>115.4262986005273</v>
       </c>
       <c r="K9">
-        <v>112.9859451982325</v>
+        <v>111.2018708324444</v>
       </c>
       <c r="L9">
-        <v>4.261182835789736</v>
+        <v>4.224427768082892</v>
       </c>
       <c r="M9">
-        <v>121.1617644513356</v>
+        <v>121.0957433947555</v>
       </c>
       <c r="N9">
-        <v>118.6730230740667</v>
+        <v>110.5715281461097</v>
       </c>
       <c r="O9">
-        <v>2.488741377268961</v>
+        <v>10.52421524864574</v>
       </c>
       <c r="P9">
-        <v>0.5632306931627614</v>
+        <v>0.5413158732898051</v>
       </c>
       <c r="Q9">
-        <v>0.1175664044372691</v>
+        <v>0.1259256820064917</v>
       </c>
       <c r="R9">
-        <v>0.2677442248019539</v>
+        <v>0.347095889045974</v>
       </c>
       <c r="S9">
-        <v>0.5849463272345193</v>
+        <v>0.5529772907917559</v>
       </c>
       <c r="T9">
-        <v>0.2686276571501762</v>
+        <v>0.2617435552976827</v>
       </c>
       <c r="U9">
-        <v>0.4416279673178116</v>
+        <v>0.3500536664840906</v>
       </c>
       <c r="V9">
-        <v>102.1880758807588</v>
+        <v>99.032582220775</v>
       </c>
       <c r="W9">
-        <v>119.6537187594099</v>
+        <v>114.4558775643113</v>
       </c>
       <c r="X9">
-        <v>4.219512195121951</v>
+        <v>4.722565939433409</v>
       </c>
       <c r="Y9">
-        <v>0.5964782171009012</v>
+        <v>0.5745420351749058</v>
       </c>
       <c r="Z9">
-        <v>123.16</v>
+        <v>118.75</v>
       </c>
       <c r="AA9">
-        <v>3.1</v>
+        <v>11.27</v>
       </c>
       <c r="AB9">
-        <v>9.967224035556209</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC9">
-        <v>120.0962116764131</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD9">
-        <v>110.1289876408569</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF9">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH9">
-        <v>1.785988337793205</v>
+        <v>0.684919795558695</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1607,76 +1607,76 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E10" s="2">
-        <v>46124</v>
+        <v>46132</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10">
-        <v>1570.357</v>
+        <v>1565.336</v>
       </c>
       <c r="H10">
-        <v>-1.5468</v>
+        <v>-1.168</v>
       </c>
       <c r="I10">
-        <v>1502.893111111111</v>
+        <v>1502.753951807229</v>
       </c>
       <c r="J10">
-        <v>115.0078782496342</v>
+        <v>114.7013870828077</v>
       </c>
       <c r="K10">
-        <v>111.234850723</v>
+        <v>111.1824707545871</v>
       </c>
       <c r="L10">
-        <v>3.773027526634123</v>
+        <v>3.518916328220537</v>
       </c>
       <c r="M10">
-        <v>109.9733259753153</v>
+        <v>111.1634740183666</v>
       </c>
       <c r="N10">
-        <v>110.5562272513674</v>
+        <v>112.9972705892531</v>
       </c>
       <c r="O10">
-        <v>-0.5829012760520715</v>
+        <v>-1.833796570886449</v>
       </c>
       <c r="P10">
-        <v>0.559544773828665</v>
+        <v>0.5589926815883727</v>
       </c>
       <c r="Q10">
-        <v>0.123807232665508</v>
+        <v>0.1236719049247095</v>
       </c>
       <c r="R10">
-        <v>0.2561480558681392</v>
+        <v>0.2531858203374175</v>
       </c>
       <c r="S10">
-        <v>0.5350634986166211</v>
+        <v>0.5446478809891669</v>
       </c>
       <c r="T10">
-        <v>0.2914917269685467</v>
+        <v>0.2893177286477721</v>
       </c>
       <c r="U10">
-        <v>0.42002124440607</v>
+        <v>0.4187235493789284</v>
       </c>
       <c r="V10">
-        <v>103.0849202047576</v>
+        <v>103.0522375215146</v>
       </c>
       <c r="W10">
-        <v>118.1728395061729</v>
+        <v>117.8709122203098</v>
       </c>
       <c r="X10">
-        <v>3.386329418849745</v>
+        <v>3.22403901319564</v>
       </c>
       <c r="Y10">
-        <v>0.5932044610718091</v>
+        <v>0.5920848746253627</v>
       </c>
       <c r="Z10">
-        <v>114.18</v>
+        <v>115.13</v>
       </c>
       <c r="AA10">
-        <v>0.6900000000000001</v>
+        <v>-0.9400000000000002</v>
       </c>
       <c r="AB10">
         <v>4.250350764022217</v>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <v>0.607000438145785</v>
+        <v>0.8243614366531509</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -1711,76 +1711,76 @@
         <v>73</v>
       </c>
       <c r="D11">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E11" s="2">
-        <v>46124</v>
+        <v>46133</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11">
-        <v>1563.113</v>
+        <v>1570.585</v>
       </c>
       <c r="H11">
-        <v>-0.2995</v>
+        <v>0.1104</v>
       </c>
       <c r="I11">
-        <v>1497.120296296296</v>
+        <v>1495.979012048193</v>
       </c>
       <c r="J11">
-        <v>116.7427707903731</v>
+        <v>116.5357560994516</v>
       </c>
       <c r="K11">
-        <v>113.8631432395376</v>
+        <v>113.485349022595</v>
       </c>
       <c r="L11">
-        <v>2.879627550835488</v>
+        <v>3.050407076856565</v>
       </c>
       <c r="M11">
-        <v>117.1221202324025</v>
+        <v>116.2880254326737</v>
       </c>
       <c r="N11">
-        <v>111.3731400442088</v>
+        <v>108.3570805923215</v>
       </c>
       <c r="O11">
-        <v>5.748980188193748</v>
+        <v>7.930944840352239</v>
       </c>
       <c r="P11">
-        <v>0.5745583981687303</v>
+        <v>0.5739987538430139</v>
       </c>
       <c r="Q11">
-        <v>0.1260686327059639</v>
+        <v>0.1266821693873879</v>
       </c>
       <c r="R11">
-        <v>0.238906356375631</v>
+        <v>0.2369891261007327</v>
       </c>
       <c r="S11">
-        <v>0.5849052002403099</v>
+        <v>0.5918791643180277</v>
       </c>
       <c r="T11">
-        <v>0.3203340492940487</v>
+        <v>0.3258631388458821</v>
       </c>
       <c r="U11">
-        <v>0.3929304189189218</v>
+        <v>0.3920957884198234</v>
       </c>
       <c r="V11">
-        <v>100.2376234567901</v>
+        <v>99.81398320554949</v>
       </c>
       <c r="W11">
-        <v>116.6242283950617</v>
+        <v>115.767433369843</v>
       </c>
       <c r="X11">
-        <v>2.185185185185185</v>
+        <v>1.999634903249362</v>
       </c>
       <c r="Y11">
-        <v>0.61036078125245</v>
+        <v>0.6101719986715327</v>
       </c>
       <c r="Z11">
-        <v>115.79</v>
+        <v>111.98</v>
       </c>
       <c r="AA11">
-        <v>3.57</v>
+        <v>4.48</v>
       </c>
       <c r="AB11">
         <v>1.827913300592181</v>
@@ -1792,21 +1792,21 @@
         <v>112.3217604872965</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF11">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <v>-0.03484281697181366</v>
+        <v>-0.1747857011179423</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -1815,102 +1815,102 @@
         <v>74</v>
       </c>
       <c r="D12">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E12" s="2">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G12">
-        <v>1519.075</v>
+        <v>1595.901</v>
       </c>
       <c r="H12">
-        <v>1.4845</v>
+        <v>1.1766</v>
       </c>
       <c r="I12">
-        <v>1499.059012345679</v>
+        <v>1500.667987951807</v>
       </c>
       <c r="J12">
-        <v>114.0721750810242</v>
+        <v>115.181340119533</v>
       </c>
       <c r="K12">
-        <v>111.2353680452117</v>
+        <v>112.7471716506547</v>
       </c>
       <c r="L12">
-        <v>2.836807035812536</v>
+        <v>2.434168468878287</v>
       </c>
       <c r="M12">
-        <v>118.2933190627534</v>
+        <v>114.3450585426628</v>
       </c>
       <c r="N12">
-        <v>109.9968480358148</v>
+        <v>114.519081716883</v>
       </c>
       <c r="O12">
-        <v>8.29647102693859</v>
+        <v>-0.1740231742202818</v>
       </c>
       <c r="P12">
-        <v>0.5493560462736199</v>
+        <v>0.5490265642552472</v>
       </c>
       <c r="Q12">
-        <v>0.1151105315578217</v>
+        <v>0.1273777560431238</v>
       </c>
       <c r="R12">
-        <v>0.2502841411495709</v>
+        <v>0.3014656305607926</v>
       </c>
       <c r="S12">
-        <v>0.5780472549608094</v>
+        <v>0.5265069721753005</v>
       </c>
       <c r="T12">
-        <v>0.2682324169232653</v>
+        <v>0.2460316087241722</v>
       </c>
       <c r="U12">
-        <v>0.3631220135205512</v>
+        <v>0.4887780357010577</v>
       </c>
       <c r="V12">
-        <v>100.6396037898363</v>
+        <v>99.6657969018933</v>
       </c>
       <c r="W12">
-        <v>114.8733850129199</v>
+        <v>115.3975903614458</v>
       </c>
       <c r="X12">
-        <v>3.189491817398794</v>
+        <v>3.760757314974183</v>
       </c>
       <c r="Y12">
-        <v>0.5828432461013802</v>
+        <v>0.5862751795663363</v>
       </c>
       <c r="Z12">
-        <v>117.64</v>
+        <v>112.23</v>
       </c>
       <c r="AA12">
-        <v>9.08</v>
+        <v>1.67</v>
       </c>
       <c r="AB12">
-        <v>-4.536933640611859</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC12">
-        <v>108.3888858603967</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD12">
-        <v>112.9258195010085</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12">
-        <v>0.6585782419471469</v>
+        <v>0.5508324885604984</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -1919,102 +1919,102 @@
         <v>75</v>
       </c>
       <c r="D13">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E13" s="2">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13">
-        <v>1595.901</v>
+        <v>1527.648</v>
       </c>
       <c r="H13">
-        <v>1.1766</v>
+        <v>-1.8362</v>
       </c>
       <c r="I13">
-        <v>1500.667987951807</v>
+        <v>1501.638890243902</v>
       </c>
       <c r="J13">
-        <v>115.181340119533</v>
+        <v>114.6709319067504</v>
       </c>
       <c r="K13">
-        <v>112.7471716506547</v>
+        <v>112.6223580741253</v>
       </c>
       <c r="L13">
-        <v>2.434168468878287</v>
+        <v>2.048573832625117</v>
       </c>
       <c r="M13">
-        <v>114.3450585426628</v>
+        <v>121.8006871479158</v>
       </c>
       <c r="N13">
-        <v>114.519081716883</v>
+        <v>121.5315734581696</v>
       </c>
       <c r="O13">
-        <v>-0.1740231742202818</v>
+        <v>0.2691136897462759</v>
       </c>
       <c r="P13">
-        <v>0.5490265642552472</v>
+        <v>0.5425583298740713</v>
       </c>
       <c r="Q13">
-        <v>0.1273777560431238</v>
+        <v>0.1105072050709512</v>
       </c>
       <c r="R13">
-        <v>0.3014656305607926</v>
+        <v>0.2512834002215163</v>
       </c>
       <c r="S13">
-        <v>0.5265069721753005</v>
+        <v>0.5859150211633202</v>
       </c>
       <c r="T13">
-        <v>0.2460316087241722</v>
+        <v>0.2668975444299984</v>
       </c>
       <c r="U13">
-        <v>0.4887780357010577</v>
+        <v>0.4065551262287586</v>
       </c>
       <c r="V13">
-        <v>99.6657969018933</v>
+        <v>105.549430894309</v>
       </c>
       <c r="W13">
-        <v>115.3975903614458</v>
+        <v>121.0084688346884</v>
       </c>
       <c r="X13">
-        <v>3.760757314974183</v>
+        <v>2.236788617886179</v>
       </c>
       <c r="Y13">
-        <v>0.5862751795663363</v>
+        <v>0.5797829519539587</v>
       </c>
       <c r="Z13">
-        <v>112.23</v>
+        <v>125.82</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>-0.46</v>
       </c>
       <c r="AB13">
-        <v>-10.13717477219789</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC13">
-        <v>104.7204689341547</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD13">
-        <v>114.8576437063525</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH13">
-        <v>0.7867139442025407</v>
+        <v>0.03077288067253913</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
@@ -2023,85 +2023,85 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="F14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G14">
-        <v>1527.648</v>
+        <v>1525.972</v>
       </c>
       <c r="H14">
-        <v>-1.8362</v>
+        <v>1.4977</v>
       </c>
       <c r="I14">
-        <v>1501.638890243902</v>
+        <v>1492.276542168675</v>
       </c>
       <c r="J14">
-        <v>114.6709319067504</v>
+        <v>113.9186722150754</v>
       </c>
       <c r="K14">
-        <v>112.6223580741253</v>
+        <v>111.9023583811811</v>
       </c>
       <c r="L14">
-        <v>2.048573832625117</v>
+        <v>2.01631383389426</v>
       </c>
       <c r="M14">
-        <v>121.8006871479158</v>
+        <v>115.0677585583131</v>
       </c>
       <c r="N14">
-        <v>121.5315734581696</v>
+        <v>110.5819435217274</v>
       </c>
       <c r="O14">
-        <v>0.2691136897462759</v>
+        <v>4.485815036585638</v>
       </c>
       <c r="P14">
-        <v>0.5425583298740713</v>
+        <v>0.5537811211979</v>
       </c>
       <c r="Q14">
-        <v>0.1105072050709512</v>
+        <v>0.1159081276847225</v>
       </c>
       <c r="R14">
-        <v>0.2512834002215163</v>
+        <v>0.2394133845239067</v>
       </c>
       <c r="S14">
-        <v>0.5859150211633202</v>
+        <v>0.5560831180976777</v>
       </c>
       <c r="T14">
-        <v>0.2668975444299984</v>
+        <v>0.2373245664378666</v>
       </c>
       <c r="U14">
-        <v>0.4065551262287586</v>
+        <v>0.4275987260802998</v>
       </c>
       <c r="V14">
-        <v>105.549430894309</v>
+        <v>103.5290240963855</v>
       </c>
       <c r="W14">
-        <v>121.0084688346884</v>
+        <v>117.9834337349398</v>
       </c>
       <c r="X14">
-        <v>2.236788617886179</v>
+        <v>2.221686746987952</v>
       </c>
       <c r="Y14">
-        <v>0.5797829519539587</v>
+        <v>0.5840963589351857</v>
       </c>
       <c r="Z14">
-        <v>125.82</v>
+        <v>116.18</v>
       </c>
       <c r="AA14">
-        <v>-0.46</v>
+        <v>4.78</v>
       </c>
       <c r="AB14">
-        <v>-1.094669144490311</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC14">
-        <v>111.6804548463295</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD14">
-        <v>112.7751239908198</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE14">
         <v>1</v>
@@ -2110,15 +2110,15 @@
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH14">
-        <v>0.2226849113213537</v>
+        <v>0.6962511020720954</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -2127,102 +2127,102 @@
         <v>77</v>
       </c>
       <c r="D15">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G15">
-        <v>1547.576</v>
+        <v>1515.647</v>
       </c>
       <c r="H15">
-        <v>-1.1818</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="I15">
-        <v>1497.571951219512</v>
+        <v>1498.162313253012</v>
       </c>
       <c r="J15">
-        <v>115.7559971917994</v>
+        <v>113.6066748047661</v>
       </c>
       <c r="K15">
-        <v>113.9836636742961</v>
+        <v>111.6854325433788</v>
       </c>
       <c r="L15">
-        <v>1.772333517503413</v>
+        <v>1.921242261387412</v>
       </c>
       <c r="M15">
-        <v>115.5369920979726</v>
+        <v>118.262850594387</v>
       </c>
       <c r="N15">
-        <v>113.7634557004086</v>
+        <v>111.1578252009957</v>
       </c>
       <c r="O15">
-        <v>1.773536397563934</v>
+        <v>7.105025393391172</v>
       </c>
       <c r="P15">
-        <v>0.5608937445510744</v>
+        <v>0.5482914525119978</v>
       </c>
       <c r="Q15">
-        <v>0.1258455536109729</v>
+        <v>0.1177146628733298</v>
       </c>
       <c r="R15">
-        <v>0.2355198616052937</v>
+        <v>0.2517768629649567</v>
       </c>
       <c r="S15">
-        <v>0.5616141638462627</v>
+        <v>0.5874045545590205</v>
       </c>
       <c r="T15">
-        <v>0.2958532089187961</v>
+        <v>0.2684065485338847</v>
       </c>
       <c r="U15">
-        <v>0.4043346898788371</v>
+        <v>0.362470805790394</v>
       </c>
       <c r="V15">
-        <v>98.88738095238094</v>
+        <v>100.5936527929901</v>
       </c>
       <c r="W15">
-        <v>113.9404761904762</v>
+        <v>114.3959474260679</v>
       </c>
       <c r="X15">
-        <v>0.9880952380952385</v>
+        <v>2.3513143483023</v>
       </c>
       <c r="Y15">
-        <v>0.6040192047046427</v>
+        <v>0.5819785842415984</v>
       </c>
       <c r="Z15">
-        <v>114.61</v>
+        <v>117.78</v>
       </c>
       <c r="AA15">
-        <v>1.39</v>
+        <v>7.64</v>
       </c>
       <c r="AB15">
-        <v>4.815266446541752</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC15">
-        <v>113.8106821492749</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD15">
-        <v>108.9954157027332</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH15">
-        <v>0.5612931716368992</v>
+        <v>0.4834732949576475</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16">
-        <v>1610612737</v>
+        <v>1610612746</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
@@ -2231,88 +2231,88 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G16">
-        <v>1535.39</v>
+        <v>1547.576</v>
       </c>
       <c r="H16">
-        <v>2.5282</v>
+        <v>-1.1818</v>
       </c>
       <c r="I16">
-        <v>1489.919061728395</v>
+        <v>1497.571951219512</v>
       </c>
       <c r="J16">
-        <v>114.1025562679364</v>
+        <v>115.7559971917994</v>
       </c>
       <c r="K16">
-        <v>112.34244268759</v>
+        <v>113.9836636742961</v>
       </c>
       <c r="L16">
-        <v>1.760113580346285</v>
+        <v>1.772333517503413</v>
       </c>
       <c r="M16">
-        <v>118.9250544663896</v>
+        <v>115.5369920979726</v>
       </c>
       <c r="N16">
-        <v>110.2068309552473</v>
+        <v>113.7634557004086</v>
       </c>
       <c r="O16">
-        <v>8.718223511142231</v>
+        <v>1.773536397563934</v>
       </c>
       <c r="P16">
-        <v>0.5544793872465036</v>
+        <v>0.5608937445510744</v>
       </c>
       <c r="Q16">
-        <v>0.1164525757798825</v>
+        <v>0.1258455536109729</v>
       </c>
       <c r="R16">
-        <v>0.2431098219155935</v>
+        <v>0.2355198616052937</v>
       </c>
       <c r="S16">
-        <v>0.5709727556948205</v>
+        <v>0.5616141638462627</v>
       </c>
       <c r="T16">
-        <v>0.2357627984158827</v>
+        <v>0.2958532089187961</v>
       </c>
       <c r="U16">
-        <v>0.4297112087313593</v>
+        <v>0.4043346898788371</v>
       </c>
       <c r="V16">
-        <v>103.7428236783793</v>
+        <v>98.88738095238094</v>
       </c>
       <c r="W16">
-        <v>118.4434947768281</v>
+        <v>113.9404761904762</v>
       </c>
       <c r="X16">
-        <v>2.027856916745805</v>
+        <v>0.9880952380952385</v>
       </c>
       <c r="Y16">
-        <v>0.5845510108149552</v>
+        <v>0.6040192047046427</v>
       </c>
       <c r="Z16">
-        <v>122.31</v>
+        <v>114.61</v>
       </c>
       <c r="AA16">
-        <v>9.010000000000002</v>
+        <v>1.39</v>
       </c>
       <c r="AB16">
-        <v>-0.981113782848854</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC16">
-        <v>112.8029837792552</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD16">
-        <v>113.7840975621041</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -2321,12 +2321,12 @@
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>1.030107321918117</v>
+        <v>0.34273987099214</v>
       </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -2335,88 +2335,88 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E17" s="2">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17">
-        <v>1506.998</v>
+        <v>1535.812</v>
       </c>
       <c r="H17">
-        <v>-0.0965</v>
+        <v>2.0849</v>
       </c>
       <c r="I17">
-        <v>1514.33956626506</v>
+        <v>1493.207555555556</v>
       </c>
       <c r="J17">
-        <v>113.3693251323049</v>
+        <v>112.4021827637863</v>
       </c>
       <c r="K17">
-        <v>111.6097938829175</v>
+        <v>111.6027610609452</v>
       </c>
       <c r="L17">
-        <v>1.759531249387505</v>
+        <v>0.7994217028411874</v>
       </c>
       <c r="M17">
-        <v>113.749090710574</v>
+        <v>110.3383912288006</v>
       </c>
       <c r="N17">
-        <v>109.92578595288</v>
+        <v>104.522396165093</v>
       </c>
       <c r="O17">
-        <v>3.82330475769396</v>
+        <v>5.815995063707557</v>
       </c>
       <c r="P17">
-        <v>0.53988387817215</v>
+        <v>0.5318418936334627</v>
       </c>
       <c r="Q17">
-        <v>0.1200330816043692</v>
+        <v>0.1190864389944169</v>
       </c>
       <c r="R17">
-        <v>0.2854315642327104</v>
+        <v>0.2464851329206768</v>
       </c>
       <c r="S17">
-        <v>0.5424408688965603</v>
+        <v>0.5290163140306751</v>
       </c>
       <c r="T17">
-        <v>0.2303359461455696</v>
+        <v>0.3183064179583552</v>
       </c>
       <c r="U17">
-        <v>0.4566602881617265</v>
+        <v>0.3851438510168819</v>
       </c>
       <c r="V17">
-        <v>99.35960457213469</v>
+        <v>102.6686419753087</v>
       </c>
       <c r="W17">
-        <v>112.5143651529194</v>
+        <v>115.4860298895387</v>
       </c>
       <c r="X17">
-        <v>1.746370095767686</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="Y17">
-        <v>0.5718842837859359</v>
+        <v>0.5772589444760052</v>
       </c>
       <c r="Z17">
-        <v>113.52</v>
+        <v>116.86</v>
       </c>
       <c r="AA17">
-        <v>4.02</v>
+        <v>6.14</v>
       </c>
       <c r="AB17">
-        <v>-2.375203171419814</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC17">
-        <v>114.7034977739938</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD17">
-        <v>117.0787009454136</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -2425,12 +2425,12 @@
         <v>3</v>
       </c>
       <c r="AH17">
-        <v>0.222318185787201</v>
+        <v>-0.03775391307332655</v>
       </c>
     </row>
     <row r="18" spans="1:34">
       <c r="A18">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
@@ -2439,85 +2439,85 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E18" s="2">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18">
-        <v>1518.584</v>
+        <v>1475.637</v>
       </c>
       <c r="H18">
-        <v>1.3156</v>
+        <v>0.407</v>
       </c>
       <c r="I18">
-        <v>1491.9238875</v>
+        <v>1502.361369047619</v>
       </c>
       <c r="J18">
-        <v>112.4488476125274</v>
+        <v>113.1047537424116</v>
       </c>
       <c r="K18">
-        <v>111.6504448775219</v>
+        <v>112.5464171722857</v>
       </c>
       <c r="L18">
-        <v>0.7984027350055121</v>
+        <v>0.5583365701259333</v>
       </c>
       <c r="M18">
-        <v>107.4637355676158</v>
+        <v>110.9855999327527</v>
       </c>
       <c r="N18">
-        <v>107.1936242807708</v>
+        <v>109.1399112268853</v>
       </c>
       <c r="O18">
-        <v>0.2701112868450855</v>
+        <v>1.845688705867384</v>
       </c>
       <c r="P18">
-        <v>0.5316883653351835</v>
+        <v>0.5306530293449634</v>
       </c>
       <c r="Q18">
-        <v>0.1194026517819761</v>
+        <v>0.1126279321969136</v>
       </c>
       <c r="R18">
-        <v>0.2468902134060437</v>
+        <v>0.2590932094978946</v>
       </c>
       <c r="S18">
-        <v>0.5190114746965675</v>
+        <v>0.5214481978923438</v>
       </c>
       <c r="T18">
-        <v>0.3225880025447687</v>
+        <v>0.2747220909141312</v>
       </c>
       <c r="U18">
-        <v>0.3846010709395101</v>
+        <v>0.3909216457451049</v>
       </c>
       <c r="V18">
-        <v>102.7309761904762</v>
+        <v>102.3322648083624</v>
       </c>
       <c r="W18">
-        <v>115.6431547619048</v>
+        <v>115.390243902439</v>
       </c>
       <c r="X18">
-        <v>1.494642857142857</v>
+        <v>-0.0650406504065041</v>
       </c>
       <c r="Y18">
-        <v>0.5777729492695108</v>
+        <v>0.5718711199090792</v>
       </c>
       <c r="Z18">
-        <v>114.7</v>
+        <v>110.55</v>
       </c>
       <c r="AA18">
-        <v>0.6699999999999999</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AB18">
-        <v>-0.5231111597400365</v>
+        <v>-6.382503892565079</v>
       </c>
       <c r="AC18">
-        <v>107.6152962364644</v>
+        <v>109.8789897646453</v>
       </c>
       <c r="AD18">
-        <v>108.1384073962044</v>
+        <v>116.2614936572104</v>
       </c>
       <c r="AE18">
         <v>1</v>
@@ -2526,15 +2526,15 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH18">
-        <v>0.1311049722384743</v>
+        <v>0.08222977259284869</v>
       </c>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
-        <v>1610612755</v>
+        <v>1610612756</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -2543,88 +2543,88 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E19" s="2">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>1475.324</v>
+        <v>1513.032</v>
       </c>
       <c r="H19">
-        <v>0.1877</v>
+        <v>0.259</v>
       </c>
       <c r="I19">
-        <v>1499.990841463415</v>
+        <v>1513.830392857143</v>
       </c>
       <c r="J19">
-        <v>113.0881776309462</v>
+        <v>112.6994027516088</v>
       </c>
       <c r="K19">
-        <v>112.3871525051826</v>
+        <v>112.1761801059456</v>
       </c>
       <c r="L19">
-        <v>0.7010251257636451</v>
+        <v>0.5232226456632106</v>
       </c>
       <c r="M19">
-        <v>115.1137501098109</v>
+        <v>109.8982519861314</v>
       </c>
       <c r="N19">
-        <v>109.7612384232032</v>
+        <v>112.5971839738885</v>
       </c>
       <c r="O19">
-        <v>5.352511686607764</v>
+        <v>-2.698931987757137</v>
       </c>
       <c r="P19">
-        <v>0.5305965987775721</v>
+        <v>0.5366083050811778</v>
       </c>
       <c r="Q19">
-        <v>0.1134822954828032</v>
+        <v>0.1208789661147309</v>
       </c>
       <c r="R19">
-        <v>0.2581697776036243</v>
+        <v>0.2859261424663591</v>
       </c>
       <c r="S19">
-        <v>0.5433917377046693</v>
+        <v>0.5269302580772146</v>
       </c>
       <c r="T19">
-        <v>0.2790026571671177</v>
+        <v>0.2306519018460218</v>
       </c>
       <c r="U19">
-        <v>0.3917329099854188</v>
+        <v>0.4549178488526007</v>
       </c>
       <c r="V19">
-        <v>102.605246876859</v>
+        <v>99.30300865800868</v>
       </c>
       <c r="W19">
-        <v>115.7102914931588</v>
+        <v>111.8871753246754</v>
       </c>
       <c r="X19">
-        <v>0.1142177275431291</v>
+        <v>0.7286255411255415</v>
       </c>
       <c r="Y19">
-        <v>0.5728831727331063</v>
+        <v>0.5685359038247572</v>
       </c>
       <c r="Z19">
-        <v>117.1</v>
+        <v>108.75</v>
       </c>
       <c r="AA19">
-        <v>4.08</v>
+        <v>-1.88</v>
       </c>
       <c r="AB19">
-        <v>-6.382503892565079</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC19">
-        <v>109.8789897646453</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD19">
-        <v>116.2614936572104</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>3</v>
       </c>
       <c r="AH19">
-        <v>0.3474586977253006</v>
+        <v>0.1005397791958908</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2647,76 +2647,76 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E20" s="2">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G20">
-        <v>1472.563</v>
+        <v>1477.005</v>
       </c>
       <c r="H20">
-        <v>1.2276</v>
+        <v>1.7664</v>
       </c>
       <c r="I20">
-        <v>1504.681597560976</v>
+        <v>1507.532630952381</v>
       </c>
       <c r="J20">
-        <v>111.611977985623</v>
+        <v>111.3362118824537</v>
       </c>
       <c r="K20">
-        <v>112.4635866111893</v>
+        <v>112.2490095221067</v>
       </c>
       <c r="L20">
-        <v>-0.8516086255663559</v>
+        <v>-0.9127976396529216</v>
       </c>
       <c r="M20">
-        <v>116.0015297319025</v>
+        <v>111.9684807372938</v>
       </c>
       <c r="N20">
-        <v>105.2001729121645</v>
+        <v>107.6890223086083</v>
       </c>
       <c r="O20">
-        <v>10.80135681973795</v>
+        <v>4.279458428685526</v>
       </c>
       <c r="P20">
-        <v>0.5346495885056282</v>
+        <v>0.5330391797254368</v>
       </c>
       <c r="Q20">
-        <v>0.1398908202848756</v>
+        <v>0.1392783216004193</v>
       </c>
       <c r="R20">
-        <v>0.311680572475506</v>
+        <v>0.3103200161554104</v>
       </c>
       <c r="S20">
-        <v>0.5609121131329114</v>
+        <v>0.5313547330130314</v>
       </c>
       <c r="T20">
-        <v>0.2836008686676942</v>
+        <v>0.2816059952278737</v>
       </c>
       <c r="U20">
-        <v>0.4707644065611628</v>
+        <v>0.4682301722160147</v>
       </c>
       <c r="V20">
-        <v>103.1293078444298</v>
+        <v>103.0638730158731</v>
       </c>
       <c r="W20">
-        <v>115.4357284113382</v>
+        <v>115.0444444444445</v>
       </c>
       <c r="X20">
-        <v>-0.1766644693473961</v>
+        <v>-0.3174603174603174</v>
       </c>
       <c r="Y20">
-        <v>0.5712299157036377</v>
+        <v>0.5695489561935217</v>
       </c>
       <c r="Z20">
-        <v>117.87</v>
+        <v>112.39</v>
       </c>
       <c r="AA20">
-        <v>12.19</v>
+        <v>5.34</v>
       </c>
       <c r="AB20">
         <v>-3.840928550668963</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>0.02644865279800278</v>
+        <v>0.1362503721686791</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.5444201825156062</v>
+        <v>0.3272715046115803</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-1.219764322489436</v>
+        <v>-1.121559683245019</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="AH23">
-        <v>-0.753461922250703</v>
+        <v>-0.8669392015446223</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="AH24">
-        <v>-1.154670231892047</v>
+        <v>-1.237099687171615</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.273884398444201</v>
+        <v>-1.346290698518558</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.037728995491819</v>
+        <v>-1.127746207974089</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="AH27">
-        <v>-0.9200683304860611</v>
+        <v>-1.02100457772906</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.8821469189446238</v>
+        <v>-0.9869360164415191</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.567292597074853</v>
+        <v>-1.618239121139825</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.790824006364488</v>
+        <v>-1.822324198014627</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.177408475630625</v>
+        <v>-1.258477978607528</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -124,12 +124,12 @@
     <t>San Antonio Spurs</t>
   </si>
   <si>
+    <t>Detroit Pistons</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
-    <t>Detroit Pistons</t>
-  </si>
-  <si>
     <t>New York Knicks</t>
   </si>
   <si>
@@ -163,15 +163,15 @@
     <t>LA Clippers</t>
   </si>
   <si>
+    <t>Phoenix Suns</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
+  </si>
+  <si>
     <t>Orlando Magic</t>
   </si>
   <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
-    <t>Phoenix Suns</t>
-  </si>
-  <si>
     <t>Portland Trail Blazers</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>SAS</t>
   </si>
   <si>
+    <t>DET</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>DET</t>
-  </si>
-  <si>
     <t>NYK</t>
   </si>
   <si>
@@ -253,13 +253,13 @@
     <t>LAC</t>
   </si>
   <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
     <t>ORL</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>PHX</t>
   </si>
   <si>
     <t>POR</t>
@@ -775,76 +775,76 @@
         <v>64</v>
       </c>
       <c r="D2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E2" s="2">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="F2">
         <v>36</v>
       </c>
       <c r="G2">
-        <v>1749.147</v>
+        <v>1755.522</v>
       </c>
       <c r="H2">
-        <v>1.2057</v>
+        <v>0.3888</v>
       </c>
       <c r="I2">
-        <v>1500.272061728395</v>
+        <v>1500.427670731707</v>
       </c>
       <c r="J2">
-        <v>117.5589013231487</v>
+        <v>117.4009596433833</v>
       </c>
       <c r="K2">
-        <v>105.3643959793545</v>
+        <v>105.6379331815748</v>
       </c>
       <c r="L2">
-        <v>12.19450534379416</v>
+        <v>11.7630264618085</v>
       </c>
       <c r="M2">
-        <v>120.7669975454074</v>
+        <v>121.0589882893597</v>
       </c>
       <c r="N2">
-        <v>106.6406565741449</v>
+        <v>105.638243968227</v>
       </c>
       <c r="O2">
-        <v>14.12634097126251</v>
+        <v>15.42074432113272</v>
       </c>
       <c r="P2">
-        <v>0.5628478086594806</v>
+        <v>0.5630361097446496</v>
       </c>
       <c r="Q2">
-        <v>0.1061916568324137</v>
+        <v>0.106519977771528</v>
       </c>
       <c r="R2">
-        <v>0.2247559608916612</v>
+        <v>0.2242237066260447</v>
       </c>
       <c r="S2">
-        <v>0.5746956004450361</v>
+        <v>0.5748718381857899</v>
       </c>
       <c r="T2">
-        <v>0.2627356937233273</v>
+        <v>0.2633090824317998</v>
       </c>
       <c r="U2">
-        <v>0.4285808139687929</v>
+        <v>0.4278566806927213</v>
       </c>
       <c r="V2">
-        <v>101.5989094650206</v>
+        <v>101.7132046070461</v>
       </c>
       <c r="W2">
-        <v>119.1440329218107</v>
+        <v>119.170054200542</v>
       </c>
       <c r="X2">
-        <v>11.96673525377229</v>
+        <v>11.63651761517615</v>
       </c>
       <c r="Y2">
-        <v>0.6008700161511308</v>
+        <v>0.6008910461633065</v>
       </c>
       <c r="Z2">
-        <v>120.89</v>
+        <v>121.89</v>
       </c>
       <c r="AA2">
-        <v>12.77</v>
+        <v>14.62</v>
       </c>
       <c r="AB2">
         <v>11.54061896828745</v>
@@ -856,7 +856,7 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="AH2">
-        <v>1.221332954544052</v>
+        <v>1.229117999530472</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -969,12 +969,12 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>1.059605115926468</v>
+        <v>1.05960719863679</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -983,88 +983,88 @@
         <v>66</v>
       </c>
       <c r="D4">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E4" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>1680.208</v>
+        <v>1674.955</v>
       </c>
       <c r="H4">
-        <v>1.5486</v>
+        <v>0.0895</v>
       </c>
       <c r="I4">
-        <v>1492.383397590361</v>
+        <v>1494.625451219512</v>
       </c>
       <c r="J4">
-        <v>117.7265517285943</v>
+        <v>114.8057598373368</v>
       </c>
       <c r="K4">
-        <v>110.4458779575985</v>
+        <v>107.1577853327808</v>
       </c>
       <c r="L4">
-        <v>7.280673770995797</v>
+        <v>7.647974504555963</v>
       </c>
       <c r="M4">
-        <v>122.0516609007653</v>
+        <v>115.5931599816501</v>
       </c>
       <c r="N4">
-        <v>110.1415847651288</v>
+        <v>104.3944175916681</v>
       </c>
       <c r="O4">
-        <v>11.91007613563649</v>
+        <v>11.19874238998203</v>
       </c>
       <c r="P4">
-        <v>0.5517264180966418</v>
+        <v>0.5469545648933447</v>
       </c>
       <c r="Q4">
-        <v>0.1041665093381238</v>
+        <v>0.1251120272287007</v>
       </c>
       <c r="R4">
-        <v>0.29084626977922</v>
+        <v>0.3048021365848963</v>
       </c>
       <c r="S4">
-        <v>0.5828667679907207</v>
+        <v>0.5671042782902086</v>
       </c>
       <c r="T4">
-        <v>0.2113138591529365</v>
+        <v>0.2962863204197715</v>
       </c>
       <c r="U4">
-        <v>0.4700501041216564</v>
+        <v>0.3468331895213101</v>
       </c>
       <c r="V4">
-        <v>97.15411801050355</v>
+        <v>101.9546235418876</v>
       </c>
       <c r="W4">
-        <v>114.4915044794563</v>
+        <v>117.0880169671262</v>
       </c>
       <c r="X4">
-        <v>7.424158171146123</v>
+        <v>8.032873806998939</v>
       </c>
       <c r="Y4">
-        <v>0.5821149070408982</v>
+        <v>0.5831719808713391</v>
       </c>
       <c r="Z4">
-        <v>118.6</v>
+        <v>115.19</v>
       </c>
       <c r="AA4">
-        <v>10.93</v>
+        <v>9.24</v>
       </c>
       <c r="AB4">
-        <v>9.220352523846751</v>
+        <v>1.549391602834736</v>
       </c>
       <c r="AC4">
-        <v>117.8084737243045</v>
+        <v>112.5216901085732</v>
       </c>
       <c r="AD4">
-        <v>108.5881212004577</v>
+        <v>110.9722985057385</v>
       </c>
       <c r="AE4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1073,12 +1073,12 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>1.385938306503901</v>
+        <v>0.7255523948316555</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -1087,88 +1087,88 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E5" s="2">
-        <v>46131</v>
+        <v>46133</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>1688.714</v>
+        <v>1680.208</v>
       </c>
       <c r="H5">
-        <v>1.0394</v>
+        <v>1.5486</v>
       </c>
       <c r="I5">
-        <v>1494.116975308642</v>
+        <v>1492.383397590361</v>
       </c>
       <c r="J5">
-        <v>114.9277646145556</v>
+        <v>117.7506714011724</v>
       </c>
       <c r="K5">
-        <v>107.7424536074891</v>
+        <v>110.4137920209438</v>
       </c>
       <c r="L5">
-        <v>7.185311007066583</v>
+        <v>7.336879380228604</v>
       </c>
       <c r="M5">
-        <v>117.9912515778412</v>
+        <v>122.0516609007653</v>
       </c>
       <c r="N5">
-        <v>106.3552500880781</v>
+        <v>110.1415847651288</v>
       </c>
       <c r="O5">
-        <v>11.63600148976311</v>
+        <v>11.91007613563649</v>
       </c>
       <c r="P5">
-        <v>0.5467925550246744</v>
+        <v>0.5519355595489434</v>
       </c>
       <c r="Q5">
-        <v>0.1238369938908686</v>
+        <v>0.1041719907475311</v>
       </c>
       <c r="R5">
-        <v>0.30082043179818</v>
+        <v>0.290640263095693</v>
       </c>
       <c r="S5">
-        <v>0.5811325441420039</v>
+        <v>0.5828667679907207</v>
       </c>
       <c r="T5">
-        <v>0.2998604291982057</v>
+        <v>0.2113360541789872</v>
       </c>
       <c r="U5">
-        <v>0.3488679124333923</v>
+        <v>0.4698255076744414</v>
       </c>
       <c r="V5">
-        <v>101.9887477954144</v>
+        <v>97.17192490893808</v>
       </c>
       <c r="W5">
-        <v>117.2384479717814</v>
+        <v>114.5343233398712</v>
       </c>
       <c r="X5">
-        <v>7.565079365079365</v>
+        <v>7.476604090781733</v>
       </c>
       <c r="Y5">
-        <v>0.5839756293687143</v>
+        <v>0.5823149124155034</v>
       </c>
       <c r="Z5">
-        <v>118.01</v>
+        <v>118.6</v>
       </c>
       <c r="AA5">
-        <v>9.52</v>
+        <v>10.93</v>
       </c>
       <c r="AB5">
-        <v>1.549391602834736</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC5">
-        <v>112.5216901085732</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD5">
-        <v>110.9722985057385</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="AH5">
-        <v>0.7466211640355485</v>
+        <v>1.38843080822267</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1197,7 +1197,7 @@
         <v>46132</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>1657.279</v>
@@ -1209,13 +1209,13 @@
         <v>1492.741841463415</v>
       </c>
       <c r="J6">
-        <v>117.3394362270218</v>
+        <v>117.3584941010403</v>
       </c>
       <c r="K6">
-        <v>110.7887201296264</v>
+        <v>110.7877230164248</v>
       </c>
       <c r="L6">
-        <v>6.550716097395441</v>
+        <v>6.570771084615547</v>
       </c>
       <c r="M6">
         <v>116.9344475705151</v>
@@ -1227,34 +1227,34 @@
         <v>3.190335720050509</v>
       </c>
       <c r="P6">
-        <v>0.5550350552301679</v>
+        <v>0.5551168988436201</v>
       </c>
       <c r="Q6">
-        <v>0.1152643701100042</v>
+        <v>0.1152479017947599</v>
       </c>
       <c r="R6">
-        <v>0.291193392577663</v>
+        <v>0.2911426624543469</v>
       </c>
       <c r="S6">
         <v>0.5624140161515211</v>
       </c>
       <c r="T6">
-        <v>0.2416050571767059</v>
+        <v>0.2414758470819512</v>
       </c>
       <c r="U6">
-        <v>0.4265133680028778</v>
+        <v>0.4265804897515652</v>
       </c>
       <c r="V6">
-        <v>99.0078799249531</v>
+        <v>99.01071428571429</v>
       </c>
       <c r="W6">
-        <v>115.9574734208881</v>
+        <v>115.9761904761905</v>
       </c>
       <c r="X6">
-        <v>6.129455909943715</v>
+        <v>6.142857142857143</v>
       </c>
       <c r="Y6">
-        <v>0.5878662352946638</v>
+        <v>0.5879637221349808</v>
       </c>
       <c r="Z6">
         <v>109.96</v>
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>1.075207595206764</v>
+        <v>1.075289060552672</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>1.473429233530684</v>
+        <v>1.47656357185103</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1405,7 +1405,7 @@
         <v>46132</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>1642.052</v>
@@ -1417,13 +1417,13 @@
         <v>1484.54234939759</v>
       </c>
       <c r="J8">
-        <v>117.2213020019621</v>
+        <v>117.2234090854567</v>
       </c>
       <c r="K8">
-        <v>112.7895091370545</v>
+        <v>112.7793980376719</v>
       </c>
       <c r="L8">
-        <v>4.431792864907528</v>
+        <v>4.444011047784725</v>
       </c>
       <c r="M8">
         <v>120.668250262103</v>
@@ -1435,34 +1435,34 @@
         <v>5.692301397238248</v>
       </c>
       <c r="P8">
-        <v>0.5643021974490076</v>
+        <v>0.564356016397167</v>
       </c>
       <c r="Q8">
-        <v>0.1172061706953217</v>
+        <v>0.1172030352168323</v>
       </c>
       <c r="R8">
-        <v>0.2640814000885438</v>
+        <v>0.2640160890101303</v>
       </c>
       <c r="S8">
         <v>0.5904963174575838</v>
       </c>
       <c r="T8">
-        <v>0.2698428252727614</v>
+        <v>0.2698369928528724</v>
       </c>
       <c r="U8">
-        <v>0.4415392882472934</v>
+        <v>0.4415885424211911</v>
       </c>
       <c r="V8">
-        <v>102.0853471026965</v>
+        <v>102.0810722891567</v>
       </c>
       <c r="W8">
-        <v>119.4928284566839</v>
+        <v>119.4873493975904</v>
       </c>
       <c r="X8">
-        <v>4.354561101549054</v>
+        <v>4.36144578313253</v>
       </c>
       <c r="Y8">
-        <v>0.5971871707768338</v>
+        <v>0.5972154965793909</v>
       </c>
       <c r="Z8">
         <v>123.19</v>
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>1.397380316794549</v>
+        <v>1.399972253296977</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -1593,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="AH9">
-        <v>0.684919795558695</v>
+        <v>0.6820093687253893</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="AH10">
-        <v>0.8243614366531509</v>
+        <v>0.8225072050563602</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="AH11">
-        <v>-0.1747857011179423</v>
+        <v>-0.1841754891464818</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -1905,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="AH12">
-        <v>0.5508324885604984</v>
+        <v>0.5469710369449039</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -2009,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="AH13">
-        <v>0.03077288067253913</v>
+        <v>0.02290300967776139</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2029,7 +2029,7 @@
         <v>46132</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G14">
         <v>1525.972</v>
@@ -2041,13 +2041,13 @@
         <v>1492.276542168675</v>
       </c>
       <c r="J14">
-        <v>113.9186722150754</v>
+        <v>113.9218461929291</v>
       </c>
       <c r="K14">
-        <v>111.9023583811811</v>
+        <v>111.9080991762141</v>
       </c>
       <c r="L14">
-        <v>2.01631383389426</v>
+        <v>2.013747016715009</v>
       </c>
       <c r="M14">
         <v>115.0677585583131</v>
@@ -2059,34 +2059,34 @@
         <v>4.485815036585638</v>
       </c>
       <c r="P14">
-        <v>0.5537811211979</v>
+        <v>0.5537864916559568</v>
       </c>
       <c r="Q14">
-        <v>0.1159081276847225</v>
+        <v>0.1159181297794972</v>
       </c>
       <c r="R14">
-        <v>0.2394133845239067</v>
+        <v>0.2395178622170419</v>
       </c>
       <c r="S14">
         <v>0.5560831180976777</v>
       </c>
       <c r="T14">
-        <v>0.2373245664378666</v>
+        <v>0.2372676359728531</v>
       </c>
       <c r="U14">
-        <v>0.4275987260802998</v>
+        <v>0.4276686019724975</v>
       </c>
       <c r="V14">
-        <v>103.5290240963855</v>
+        <v>103.5363855421686</v>
       </c>
       <c r="W14">
-        <v>117.9834337349398</v>
+        <v>117.996844520941</v>
       </c>
       <c r="X14">
-        <v>2.221686746987952</v>
+        <v>2.223178427997705</v>
       </c>
       <c r="Y14">
-        <v>0.5840963589351857</v>
+        <v>0.5840926452828347</v>
       </c>
       <c r="Z14">
         <v>116.18</v>
@@ -2113,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="AH14">
-        <v>0.6962511020720954</v>
+        <v>0.6934733560005515</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2133,7 +2133,7 @@
         <v>46132</v>
       </c>
       <c r="F15">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G15">
         <v>1515.647</v>
@@ -2145,13 +2145,13 @@
         <v>1498.162313253012</v>
       </c>
       <c r="J15">
-        <v>113.6066748047661</v>
+        <v>113.5732295153116</v>
       </c>
       <c r="K15">
-        <v>111.6854325433788</v>
+        <v>111.7121045553402</v>
       </c>
       <c r="L15">
-        <v>1.921242261387412</v>
+        <v>1.861124959971512</v>
       </c>
       <c r="M15">
         <v>118.262850594387</v>
@@ -2163,34 +2163,34 @@
         <v>7.105025393391172</v>
       </c>
       <c r="P15">
-        <v>0.5482914525119978</v>
+        <v>0.5482910901566943</v>
       </c>
       <c r="Q15">
-        <v>0.1177146628733298</v>
+        <v>0.1180006200249673</v>
       </c>
       <c r="R15">
-        <v>0.2517768629649567</v>
+        <v>0.2519821828354366</v>
       </c>
       <c r="S15">
         <v>0.5874045545590205</v>
       </c>
       <c r="T15">
-        <v>0.2684065485338847</v>
+        <v>0.2681730579411352</v>
       </c>
       <c r="U15">
-        <v>0.362470805790394</v>
+        <v>0.362290079497583</v>
       </c>
       <c r="V15">
-        <v>100.5936527929901</v>
+        <v>100.5862587190868</v>
       </c>
       <c r="W15">
-        <v>114.3959474260679</v>
+        <v>114.3614457831325</v>
       </c>
       <c r="X15">
-        <v>2.3513143483023</v>
+        <v>2.305960684844642</v>
       </c>
       <c r="Y15">
-        <v>0.5819785842415984</v>
+        <v>0.5819721955361474</v>
       </c>
       <c r="Z15">
         <v>117.78</v>
@@ -2217,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="AH15">
-        <v>0.4834732949576475</v>
+        <v>0.4790746633360264</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2321,12 +2321,12 @@
         <v>3</v>
       </c>
       <c r="AH16">
-        <v>0.34273987099214</v>
+        <v>0.3372477207784098</v>
       </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -2335,97 +2335,97 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="F17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G17">
-        <v>1535.812</v>
+        <v>1506.657</v>
       </c>
       <c r="H17">
-        <v>2.0849</v>
+        <v>0.4811</v>
       </c>
       <c r="I17">
-        <v>1493.207555555556</v>
+        <v>1516.598823529412</v>
       </c>
       <c r="J17">
-        <v>112.4021827637863</v>
+        <v>112.8084528572326</v>
       </c>
       <c r="K17">
-        <v>111.6027610609452</v>
+        <v>112.1361682042551</v>
       </c>
       <c r="L17">
-        <v>0.7994217028411874</v>
+        <v>0.6722846529775324</v>
       </c>
       <c r="M17">
-        <v>110.3383912288006</v>
+        <v>108.1314101343386</v>
       </c>
       <c r="N17">
-        <v>104.522396165093</v>
+        <v>113.8077844913904</v>
       </c>
       <c r="O17">
-        <v>5.815995063707557</v>
+        <v>-5.676374357051831</v>
       </c>
       <c r="P17">
-        <v>0.5318418936334627</v>
+        <v>0.537504853209016</v>
       </c>
       <c r="Q17">
-        <v>0.1190864389944169</v>
+        <v>0.1218557938279784</v>
       </c>
       <c r="R17">
-        <v>0.2464851329206768</v>
+        <v>0.28735826193371</v>
       </c>
       <c r="S17">
-        <v>0.5290163140306751</v>
+        <v>0.5225748981593997</v>
       </c>
       <c r="T17">
-        <v>0.3183064179583552</v>
+        <v>0.2314432788657317</v>
       </c>
       <c r="U17">
-        <v>0.3851438510168819</v>
+        <v>0.452703558587767</v>
       </c>
       <c r="V17">
-        <v>102.6686419753087</v>
+        <v>99.40641711229947</v>
       </c>
       <c r="W17">
-        <v>115.4860298895387</v>
+        <v>112.0818181818182</v>
       </c>
       <c r="X17">
-        <v>1.407407407407407</v>
+        <v>0.8082887700534755</v>
       </c>
       <c r="Y17">
-        <v>0.5772589444760052</v>
+        <v>0.5696254492825312</v>
       </c>
       <c r="Z17">
-        <v>116.86</v>
+        <v>106.82</v>
       </c>
       <c r="AA17">
-        <v>6.14</v>
+        <v>-5.17</v>
       </c>
       <c r="AB17">
-        <v>-0.5231111597400365</v>
+        <v>-2.375203171419814</v>
       </c>
       <c r="AC17">
-        <v>107.6152962364644</v>
+        <v>114.7034977739938</v>
       </c>
       <c r="AD17">
-        <v>108.1384073962044</v>
+        <v>117.0787009454136</v>
       </c>
       <c r="AE17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>-0.03775391307332655</v>
+        <v>0.05415775570613952</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -2445,7 +2445,7 @@
         <v>46133</v>
       </c>
       <c r="F18">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18">
         <v>1475.637</v>
@@ -2457,13 +2457,13 @@
         <v>1502.361369047619</v>
       </c>
       <c r="J18">
-        <v>113.1047537424116</v>
+        <v>113.0985345582815</v>
       </c>
       <c r="K18">
-        <v>112.5464171722857</v>
+        <v>112.5491985721023</v>
       </c>
       <c r="L18">
-        <v>0.5583365701259333</v>
+        <v>0.5493359861792191</v>
       </c>
       <c r="M18">
         <v>110.9855999327527</v>
@@ -2475,34 +2475,34 @@
         <v>1.845688705867384</v>
       </c>
       <c r="P18">
-        <v>0.5306530293449634</v>
+        <v>0.5306216720211607</v>
       </c>
       <c r="Q18">
-        <v>0.1126279321969136</v>
+        <v>0.1126540587809514</v>
       </c>
       <c r="R18">
-        <v>0.2590932094978946</v>
+        <v>0.2590850939840675</v>
       </c>
       <c r="S18">
         <v>0.5214481978923438</v>
       </c>
       <c r="T18">
-        <v>0.2747220909141312</v>
+        <v>0.2748128646454954</v>
       </c>
       <c r="U18">
-        <v>0.3909216457451049</v>
+        <v>0.390896400692969</v>
       </c>
       <c r="V18">
-        <v>102.3322648083624</v>
+        <v>102.3396768707483</v>
       </c>
       <c r="W18">
-        <v>115.390243902439</v>
+        <v>115.3928571428571</v>
       </c>
       <c r="X18">
-        <v>-0.0650406504065041</v>
+        <v>-0.07341269841269847</v>
       </c>
       <c r="Y18">
-        <v>0.5718711199090792</v>
+        <v>0.5718631883615367</v>
       </c>
       <c r="Z18">
         <v>110.55</v>
@@ -2529,12 +2529,12 @@
         <v>2</v>
       </c>
       <c r="AH18">
-        <v>0.08222977259284869</v>
+        <v>0.07478552016411476</v>
       </c>
     </row>
     <row r="19" spans="1:34">
       <c r="A19">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -2543,88 +2543,88 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E19" s="2">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19">
-        <v>1513.032</v>
+        <v>1549.571</v>
       </c>
       <c r="H19">
-        <v>0.259</v>
+        <v>3.5116</v>
       </c>
       <c r="I19">
-        <v>1513.830392857143</v>
+        <v>1495.591780487805</v>
       </c>
       <c r="J19">
-        <v>112.6994027516088</v>
+        <v>111.7516750590107</v>
       </c>
       <c r="K19">
-        <v>112.1761801059456</v>
+        <v>111.4481060651044</v>
       </c>
       <c r="L19">
-        <v>0.5232226456632106</v>
+        <v>0.3035689939062091</v>
       </c>
       <c r="M19">
-        <v>109.8982519861314</v>
+        <v>108.517605711177</v>
       </c>
       <c r="N19">
-        <v>112.5971839738885</v>
+        <v>104.3869996797991</v>
       </c>
       <c r="O19">
-        <v>-2.698931987757137</v>
+        <v>4.130606031377861</v>
       </c>
       <c r="P19">
-        <v>0.5366083050811778</v>
+        <v>0.528015892045394</v>
       </c>
       <c r="Q19">
-        <v>0.1208789661147309</v>
+        <v>0.120022750915836</v>
       </c>
       <c r="R19">
-        <v>0.2859261424663591</v>
+        <v>0.2464073885322829</v>
       </c>
       <c r="S19">
-        <v>0.5269302580772146</v>
+        <v>0.515502249333066</v>
       </c>
       <c r="T19">
-        <v>0.2306519018460218</v>
+        <v>0.3217246949659747</v>
       </c>
       <c r="U19">
-        <v>0.4549178488526007</v>
+        <v>0.3855936836069132</v>
       </c>
       <c r="V19">
-        <v>99.30300865800868</v>
+        <v>102.6209188882587</v>
       </c>
       <c r="W19">
-        <v>111.8871753246754</v>
+        <v>114.7799205899036</v>
       </c>
       <c r="X19">
-        <v>0.7286255411255415</v>
+        <v>0.8899602949517865</v>
       </c>
       <c r="Y19">
-        <v>0.5685359038247572</v>
+        <v>0.5742049945787354</v>
       </c>
       <c r="Z19">
-        <v>108.75</v>
+        <v>113.69</v>
       </c>
       <c r="AA19">
-        <v>-1.88</v>
+        <v>4.17</v>
       </c>
       <c r="AB19">
-        <v>-2.375203171419814</v>
+        <v>-0.5231111597400365</v>
       </c>
       <c r="AC19">
-        <v>114.7034977739938</v>
+        <v>107.6152962364644</v>
       </c>
       <c r="AD19">
-        <v>117.0787009454136</v>
+        <v>108.1384073962044</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>3</v>
       </c>
       <c r="AH19">
-        <v>0.1005397791958908</v>
+        <v>-0.04171231231847827</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -2737,7 +2737,7 @@
         <v>2</v>
       </c>
       <c r="AH20">
-        <v>0.1362503721686791</v>
+        <v>0.1291403514190761</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.3272715046115803</v>
+        <v>0.3216699062552075</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-1.121559683245019</v>
+        <v>-1.138072553268783</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="AH23">
-        <v>-0.8669392015446223</v>
+        <v>-0.593214857815052</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="AH24">
-        <v>-1.237099687171615</v>
+        <v>-1.254510821408037</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.346290698518558</v>
+        <v>-1.364463527011031</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.127746207974089</v>
+        <v>-1.144147103625029</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="AH27">
-        <v>-1.02100457772906</v>
+        <v>-1.036774025958877</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-0.9869360164415191</v>
+        <v>-1.002541067708509</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.618239121139825</v>
+        <v>-1.63866277384436</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.822324198014627</v>
+        <v>-1.844099574165216</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.258477978607528</v>
+        <v>-1.276099074716355</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_snapshot.xlsx
+++ b/nba/public/data/nba_snapshot.xlsx
@@ -127,10 +127,13 @@
     <t>Detroit Pistons</t>
   </si>
   <si>
+    <t>New York Knicks</t>
+  </si>
+  <si>
     <t>Boston Celtics</t>
   </si>
   <si>
-    <t>New York Knicks</t>
+    <t>Houston Rockets</t>
   </si>
   <si>
     <t>Denver Nuggets</t>
@@ -139,30 +142,27 @@
     <t>Cleveland Cavaliers</t>
   </si>
   <si>
-    <t>Houston Rockets</t>
-  </si>
-  <si>
     <t>Minnesota Timberwolves</t>
   </si>
   <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
     <t>Los Angeles Lakers</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
+    <t>Toronto Raptors</t>
   </si>
   <si>
     <t>Miami Heat</t>
   </si>
   <si>
+    <t>LA Clippers</t>
+  </si>
+  <si>
     <t>Atlanta Hawks</t>
   </si>
   <si>
-    <t>Toronto Raptors</t>
-  </si>
-  <si>
-    <t>LA Clippers</t>
-  </si>
-  <si>
     <t>Phoenix Suns</t>
   </si>
   <si>
@@ -172,12 +172,12 @@
     <t>Orlando Magic</t>
   </si>
   <si>
+    <t>Golden State Warriors</t>
+  </si>
+  <si>
     <t>Portland Trail Blazers</t>
   </si>
   <si>
-    <t>Golden State Warriors</t>
-  </si>
-  <si>
     <t>New Orleans Pelicans</t>
   </si>
   <si>
@@ -217,10 +217,13 @@
     <t>DET</t>
   </si>
   <si>
+    <t>NYK</t>
+  </si>
+  <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>NYK</t>
+    <t>HOU</t>
   </si>
   <si>
     <t>DEN</t>
@@ -229,30 +232,27 @@
     <t>CLE</t>
   </si>
   <si>
-    <t>HOU</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
+    <t>CHA</t>
+  </si>
+  <si>
     <t>LAL</t>
   </si>
   <si>
-    <t>CHA</t>
+    <t>TOR</t>
   </si>
   <si>
     <t>MIA</t>
   </si>
   <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
     <t>PHX</t>
   </si>
   <si>
@@ -262,10 +262,10 @@
     <t>ORL</t>
   </si>
   <si>
+    <t>GSW</t>
+  </si>
+  <si>
     <t>POR</t>
-  </si>
-  <si>
-    <t>GSW</t>
   </si>
   <si>
     <t>NOP</t>
@@ -775,76 +775,76 @@
         <v>64</v>
       </c>
       <c r="D2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E2" s="2">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G2">
-        <v>1755.522</v>
+        <v>1763.436</v>
       </c>
       <c r="H2">
-        <v>0.3888</v>
+        <v>-0.5121</v>
       </c>
       <c r="I2">
-        <v>1500.427670731707</v>
+        <v>1500.540357142857</v>
       </c>
       <c r="J2">
-        <v>117.4009596433833</v>
+        <v>117.7608513280508</v>
       </c>
       <c r="K2">
-        <v>105.6379331815748</v>
+        <v>106.0597632437028</v>
       </c>
       <c r="L2">
-        <v>11.7630264618085</v>
+        <v>11.70108808434789</v>
       </c>
       <c r="M2">
-        <v>121.0589882893597</v>
+        <v>122.5457774451886</v>
       </c>
       <c r="N2">
-        <v>105.638243968227</v>
+        <v>107.749209958365</v>
       </c>
       <c r="O2">
-        <v>15.42074432113272</v>
+        <v>14.79656748682356</v>
       </c>
       <c r="P2">
-        <v>0.5630361097446496</v>
+        <v>0.564896763437255</v>
       </c>
       <c r="Q2">
-        <v>0.106519977771528</v>
+        <v>0.1071214354680645</v>
       </c>
       <c r="R2">
-        <v>0.2242237066260447</v>
+        <v>0.2259693760129766</v>
       </c>
       <c r="S2">
-        <v>0.5748718381857899</v>
+        <v>0.5877224714935593</v>
       </c>
       <c r="T2">
-        <v>0.2633090824317998</v>
+        <v>0.2649808181658934</v>
       </c>
       <c r="U2">
-        <v>0.4278566806927213</v>
+        <v>0.4271385694999947</v>
       </c>
       <c r="V2">
-        <v>101.7132046070461</v>
+        <v>101.6379347826087</v>
       </c>
       <c r="W2">
-        <v>119.170054200542</v>
+        <v>119.4355590062112</v>
       </c>
       <c r="X2">
-        <v>11.63651761517615</v>
+        <v>11.56211180124224</v>
       </c>
       <c r="Y2">
-        <v>0.6008910461633065</v>
+        <v>0.6030141719782672</v>
       </c>
       <c r="Z2">
-        <v>121.89</v>
+        <v>122.9</v>
       </c>
       <c r="AA2">
-        <v>14.62</v>
+        <v>13.86</v>
       </c>
       <c r="AB2">
         <v>11.54061896828745</v>
@@ -856,16 +856,16 @@
         <v>105.5005634449357</v>
       </c>
       <c r="AE2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF2">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>1.229117999530472</v>
+        <v>1.156832820901875</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -879,76 +879,76 @@
         <v>65</v>
       </c>
       <c r="D3">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E3" s="2">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>1737.41</v>
+        <v>1737.158</v>
       </c>
       <c r="H3">
-        <v>0.1702</v>
+        <v>-1.1472</v>
       </c>
       <c r="I3">
-        <v>1507.117536585366</v>
+        <v>1506.295188235294</v>
       </c>
       <c r="J3">
-        <v>117.3385438578281</v>
+        <v>117.6775875929438</v>
       </c>
       <c r="K3">
-        <v>109.1329793659553</v>
+        <v>108.6913472948693</v>
       </c>
       <c r="L3">
-        <v>8.205564491872869</v>
+        <v>8.986240298074462</v>
       </c>
       <c r="M3">
-        <v>119.2492500944585</v>
+        <v>118.2358878159023</v>
       </c>
       <c r="N3">
-        <v>109.231178061518</v>
+        <v>107.4737065601434</v>
       </c>
       <c r="O3">
-        <v>10.01807203294055</v>
+        <v>10.76218125575889</v>
       </c>
       <c r="P3">
-        <v>0.559164856289013</v>
+        <v>0.5619441928750737</v>
       </c>
       <c r="Q3">
-        <v>0.1118647634360532</v>
+        <v>0.1121293067703514</v>
       </c>
       <c r="R3">
-        <v>0.2610009906273514</v>
+        <v>0.2599474246458524</v>
       </c>
       <c r="S3">
-        <v>0.5635429605073611</v>
+        <v>0.5648299157215618</v>
       </c>
       <c r="T3">
-        <v>0.2772003821165557</v>
+        <v>0.2786169370496939</v>
       </c>
       <c r="U3">
-        <v>0.4172312105430142</v>
+        <v>0.4178069159408146</v>
       </c>
       <c r="V3">
-        <v>101.8894684177611</v>
+        <v>101.712770053476</v>
       </c>
       <c r="W3">
-        <v>119.3977485928705</v>
+        <v>119.4382352941176</v>
       </c>
       <c r="X3">
-        <v>8.145716072545341</v>
+        <v>8.732887700534759</v>
       </c>
       <c r="Y3">
-        <v>0.5950795943644354</v>
+        <v>0.5974636569832278</v>
       </c>
       <c r="Z3">
-        <v>121</v>
+        <v>117.96</v>
       </c>
       <c r="AA3">
-        <v>10.86</v>
+        <v>10.27</v>
       </c>
       <c r="AB3">
         <v>-2.513643863094118</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH3">
-        <v>1.05960719863679</v>
+        <v>1.278516201174989</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -983,76 +983,76 @@
         <v>66</v>
       </c>
       <c r="D4">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E4" s="2">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="F4">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>1674.955</v>
+        <v>1663.006</v>
       </c>
       <c r="H4">
-        <v>0.0895</v>
+        <v>-1.9272</v>
       </c>
       <c r="I4">
-        <v>1494.625451219512</v>
+        <v>1496.536635294118</v>
       </c>
       <c r="J4">
-        <v>114.8057598373368</v>
+        <v>114.6580404842605</v>
       </c>
       <c r="K4">
-        <v>107.1577853327808</v>
+        <v>107.2467648092241</v>
       </c>
       <c r="L4">
-        <v>7.647974504555963</v>
+        <v>7.411275675036313</v>
       </c>
       <c r="M4">
-        <v>115.5931599816501</v>
+        <v>112.8199135425051</v>
       </c>
       <c r="N4">
-        <v>104.3944175916681</v>
+        <v>104.7896784769884</v>
       </c>
       <c r="O4">
-        <v>11.19874238998203</v>
+        <v>8.030235065516756</v>
       </c>
       <c r="P4">
-        <v>0.5469545648933447</v>
+        <v>0.5454820483108135</v>
       </c>
       <c r="Q4">
-        <v>0.1251120272287007</v>
+        <v>0.1260145874873382</v>
       </c>
       <c r="R4">
-        <v>0.3048021365848963</v>
+        <v>0.3049870737084054</v>
       </c>
       <c r="S4">
-        <v>0.5671042782902086</v>
+        <v>0.5390730566627078</v>
       </c>
       <c r="T4">
-        <v>0.2962863204197715</v>
+        <v>0.3005916827500988</v>
       </c>
       <c r="U4">
-        <v>0.3468331895213101</v>
+        <v>0.3478611726347328</v>
       </c>
       <c r="V4">
-        <v>101.9546235418876</v>
+        <v>101.8972591414945</v>
       </c>
       <c r="W4">
-        <v>117.0880169671262</v>
+        <v>116.7669316375198</v>
       </c>
       <c r="X4">
-        <v>8.032873806998939</v>
+        <v>7.59523052464229</v>
       </c>
       <c r="Y4">
-        <v>0.5831719808713391</v>
+        <v>0.5827825318299502</v>
       </c>
       <c r="Z4">
-        <v>115.19</v>
+        <v>112.04</v>
       </c>
       <c r="AA4">
-        <v>9.24</v>
+        <v>5.92</v>
       </c>
       <c r="AB4">
         <v>1.549391602834736</v>
@@ -1064,21 +1064,21 @@
         <v>110.9722985057385</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH4">
-        <v>0.7255523948316555</v>
+        <v>0.7155710062877992</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
-        <v>1610612738</v>
+        <v>1610612752</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -1087,102 +1087,102 @@
         <v>67</v>
       </c>
       <c r="D5">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E5" s="2">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="F5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>1680.208</v>
+        <v>1648.79</v>
       </c>
       <c r="H5">
-        <v>1.5486</v>
+        <v>-0.7923</v>
       </c>
       <c r="I5">
-        <v>1492.383397590361</v>
+        <v>1494.262611764706</v>
       </c>
       <c r="J5">
-        <v>117.7506714011724</v>
+        <v>117.6696084620531</v>
       </c>
       <c r="K5">
-        <v>110.4137920209438</v>
+        <v>110.3845619218085</v>
       </c>
       <c r="L5">
-        <v>7.336879380228604</v>
+        <v>7.285046540244495</v>
       </c>
       <c r="M5">
-        <v>122.0516609007653</v>
+        <v>119.883373211194</v>
       </c>
       <c r="N5">
-        <v>110.1415847651288</v>
+        <v>107.8257251898533</v>
       </c>
       <c r="O5">
-        <v>11.91007613563649</v>
+        <v>12.05764802134065</v>
       </c>
       <c r="P5">
-        <v>0.5519355595489434</v>
+        <v>0.5571178828888824</v>
       </c>
       <c r="Q5">
-        <v>0.1041719907475311</v>
+        <v>0.1152209047901232</v>
       </c>
       <c r="R5">
-        <v>0.290640263095693</v>
+        <v>0.2906697939101423</v>
       </c>
       <c r="S5">
-        <v>0.5828667679907207</v>
+        <v>0.5735298906371852</v>
       </c>
       <c r="T5">
-        <v>0.2113360541789872</v>
+        <v>0.2453985134748788</v>
       </c>
       <c r="U5">
-        <v>0.4698255076744414</v>
+        <v>0.4234279677700207</v>
       </c>
       <c r="V5">
-        <v>97.17192490893808</v>
+        <v>98.97328550932568</v>
       </c>
       <c r="W5">
-        <v>114.5343233398712</v>
+        <v>116.2209469153515</v>
       </c>
       <c r="X5">
-        <v>7.476604090781733</v>
+        <v>6.81348637015782</v>
       </c>
       <c r="Y5">
-        <v>0.5823149124155034</v>
+        <v>0.5901902223320261</v>
       </c>
       <c r="Z5">
-        <v>118.6</v>
+        <v>114.75</v>
       </c>
       <c r="AA5">
-        <v>10.93</v>
+        <v>10.82</v>
       </c>
       <c r="AB5">
-        <v>9.220352523846751</v>
+        <v>2.775420617465777</v>
       </c>
       <c r="AC5">
-        <v>117.8084737243045</v>
+        <v>115.1107166171038</v>
       </c>
       <c r="AD5">
-        <v>108.5881212004577</v>
+        <v>112.335295999638</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH5">
-        <v>1.38843080822267</v>
+        <v>1.096087321162811</v>
       </c>
     </row>
     <row r="6" spans="1:34">
       <c r="A6">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -1191,85 +1191,85 @@
         <v>68</v>
       </c>
       <c r="D6">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>1657.279</v>
+        <v>1680.591</v>
       </c>
       <c r="H6">
-        <v>0.5225</v>
+        <v>0.3701</v>
       </c>
       <c r="I6">
-        <v>1492.741841463415</v>
+        <v>1492.123523255814</v>
       </c>
       <c r="J6">
-        <v>117.3584941010403</v>
+        <v>117.6611216658405</v>
       </c>
       <c r="K6">
-        <v>110.7877230164248</v>
+        <v>110.444019606804</v>
       </c>
       <c r="L6">
-        <v>6.570771084615547</v>
+        <v>7.217102059036431</v>
       </c>
       <c r="M6">
-        <v>116.9344475705151</v>
+        <v>120.0290575117532</v>
       </c>
       <c r="N6">
-        <v>113.7441118504646</v>
+        <v>109.2496149436501</v>
       </c>
       <c r="O6">
-        <v>3.190335720050509</v>
+        <v>10.7794425681031</v>
       </c>
       <c r="P6">
-        <v>0.5551168988436201</v>
+        <v>0.5519461343259705</v>
       </c>
       <c r="Q6">
-        <v>0.1152479017947599</v>
+        <v>0.1049710134546151</v>
       </c>
       <c r="R6">
-        <v>0.2911426624543469</v>
+        <v>0.2910460317910489</v>
       </c>
       <c r="S6">
-        <v>0.5624140161515211</v>
+        <v>0.5718593718464045</v>
       </c>
       <c r="T6">
-        <v>0.2414758470819512</v>
+        <v>0.2137231656592584</v>
       </c>
       <c r="U6">
-        <v>0.4265804897515652</v>
+        <v>0.4709419908557567</v>
       </c>
       <c r="V6">
-        <v>99.01071428571429</v>
+        <v>97.09244444444444</v>
       </c>
       <c r="W6">
-        <v>115.9761904761905</v>
+        <v>114.4180878552972</v>
       </c>
       <c r="X6">
-        <v>6.142857142857143</v>
+        <v>7.478036175710593</v>
       </c>
       <c r="Y6">
-        <v>0.5879637221349808</v>
+        <v>0.5821809929650195</v>
       </c>
       <c r="Z6">
-        <v>109.96</v>
+        <v>115.9</v>
       </c>
       <c r="AA6">
-        <v>3.05</v>
+        <v>11</v>
       </c>
       <c r="AB6">
-        <v>2.775420617465777</v>
+        <v>9.220352523846751</v>
       </c>
       <c r="AC6">
-        <v>115.1107166171038</v>
+        <v>117.8084737243045</v>
       </c>
       <c r="AD6">
-        <v>112.335295999638</v>
+        <v>108.5881212004577</v>
       </c>
       <c r="AE6">
         <v>1</v>
@@ -1278,15 +1278,15 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6">
-        <v>1.075289060552672</v>
+        <v>1.461301142524003</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
@@ -1295,102 +1295,102 @@
         <v>69</v>
       </c>
       <c r="D7">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E7" s="2">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>1628.839</v>
+        <v>1583.429</v>
       </c>
       <c r="H7">
-        <v>3.7056</v>
+        <v>-1.4546</v>
       </c>
       <c r="I7">
-        <v>1507.148915662651</v>
+        <v>1496.811686046512</v>
       </c>
       <c r="J7">
-        <v>119.9280599431096</v>
+        <v>115.457509565832</v>
       </c>
       <c r="K7">
-        <v>115.1030109853419</v>
+        <v>110.7998517461486</v>
       </c>
       <c r="L7">
-        <v>4.825048957767701</v>
+        <v>4.65765781968346</v>
       </c>
       <c r="M7">
-        <v>123.2540605180378</v>
+        <v>115.6309540532214</v>
       </c>
       <c r="N7">
-        <v>115.0746647345575</v>
+        <v>109.3917323153685</v>
       </c>
       <c r="O7">
-        <v>8.17939578348026</v>
+        <v>6.239221737852925</v>
       </c>
       <c r="P7">
-        <v>0.5754303583246921</v>
+        <v>0.5418800234562926</v>
       </c>
       <c r="Q7">
-        <v>0.1084037766481807</v>
+        <v>0.1252449690389614</v>
       </c>
       <c r="R7">
-        <v>0.2318296053812003</v>
+        <v>0.3421973010380045</v>
       </c>
       <c r="S7">
-        <v>0.5849673280102159</v>
+        <v>0.5351043279029077</v>
       </c>
       <c r="T7">
-        <v>0.2998664243573962</v>
+        <v>0.2650526785411991</v>
       </c>
       <c r="U7">
-        <v>0.409315740892408</v>
+        <v>0.3550893608838158</v>
       </c>
       <c r="V7">
-        <v>101.5691370888961</v>
+        <v>98.98727362691736</v>
       </c>
       <c r="W7">
-        <v>121.7837837837838</v>
+        <v>114.3636813458683</v>
       </c>
       <c r="X7">
-        <v>4.940735916639531</v>
+        <v>4.987135081642751</v>
       </c>
       <c r="Y7">
-        <v>0.6151360057647196</v>
+        <v>0.5754492491366751</v>
       </c>
       <c r="Z7">
-        <v>128.67</v>
+        <v>115.02</v>
       </c>
       <c r="AA7">
-        <v>9.76</v>
+        <v>8.34</v>
       </c>
       <c r="AB7">
-        <v>2.722616812266775</v>
+        <v>3.413694058608522</v>
       </c>
       <c r="AC7">
-        <v>116.5392386763017</v>
+        <v>112.3850185369902</v>
       </c>
       <c r="AD7">
-        <v>113.8166218640349</v>
+        <v>108.9713244783817</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH7">
-        <v>1.47656357185103</v>
+        <v>0.09080986668194704</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8">
-        <v>1610612739</v>
+        <v>1610612743</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
@@ -1399,85 +1399,85 @@
         <v>70</v>
       </c>
       <c r="D8">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E8" s="2">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8">
-        <v>1642.052</v>
+        <v>1597.68</v>
       </c>
       <c r="H8">
-        <v>-0.1592</v>
+        <v>0.763</v>
       </c>
       <c r="I8">
-        <v>1484.54234939759</v>
+        <v>1509.536872093023</v>
       </c>
       <c r="J8">
-        <v>117.2234090854567</v>
+        <v>119.4954156053259</v>
       </c>
       <c r="K8">
-        <v>112.7793980376719</v>
+        <v>114.8864142028959</v>
       </c>
       <c r="L8">
-        <v>4.444011047784725</v>
+        <v>4.609001402429919</v>
       </c>
       <c r="M8">
-        <v>120.668250262103</v>
+        <v>117.1028580628416</v>
       </c>
       <c r="N8">
-        <v>114.9759488648647</v>
+        <v>113.3955803218321</v>
       </c>
       <c r="O8">
-        <v>5.692301397238248</v>
+        <v>3.707277741009438</v>
       </c>
       <c r="P8">
-        <v>0.564356016397167</v>
+        <v>0.5736507754272646</v>
       </c>
       <c r="Q8">
-        <v>0.1172030352168323</v>
+        <v>0.1093406521616943</v>
       </c>
       <c r="R8">
-        <v>0.2640160890101303</v>
+        <v>0.2305904129817437</v>
       </c>
       <c r="S8">
-        <v>0.5904963174575838</v>
+        <v>0.5485509941755198</v>
       </c>
       <c r="T8">
-        <v>0.2698369928528724</v>
+        <v>0.3015546262304304</v>
       </c>
       <c r="U8">
-        <v>0.4415885424211911</v>
+        <v>0.4055748333229622</v>
       </c>
       <c r="V8">
-        <v>102.0810722891567</v>
+        <v>101.5888252832439</v>
       </c>
       <c r="W8">
-        <v>119.4873493975904</v>
+        <v>121.397137745975</v>
       </c>
       <c r="X8">
-        <v>4.36144578313253</v>
+        <v>4.782945736434108</v>
       </c>
       <c r="Y8">
-        <v>0.5972154965793909</v>
+        <v>0.6140084412614211</v>
       </c>
       <c r="Z8">
-        <v>123.19</v>
+        <v>121.94</v>
       </c>
       <c r="AA8">
-        <v>6.22</v>
+        <v>4.8</v>
       </c>
       <c r="AB8">
-        <v>9.967224035556209</v>
+        <v>2.722616812266775</v>
       </c>
       <c r="AC8">
-        <v>120.0962116764131</v>
+        <v>116.5392386763017</v>
       </c>
       <c r="AD8">
-        <v>110.1289876408569</v>
+        <v>113.8166218640349</v>
       </c>
       <c r="AE8">
         <v>1</v>
@@ -1486,15 +1486,15 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH8">
-        <v>1.399972253296977</v>
+        <v>1.475359295435947</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -1503,85 +1503,85 @@
         <v>71</v>
       </c>
       <c r="D9">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G9">
-        <v>1587.025</v>
+        <v>1621.574</v>
       </c>
       <c r="H9">
-        <v>1.1706</v>
+        <v>-1.3677</v>
       </c>
       <c r="I9">
-        <v>1493.901168674699</v>
+        <v>1485.731744186046</v>
       </c>
       <c r="J9">
-        <v>115.4262986005273</v>
+        <v>116.9002875705497</v>
       </c>
       <c r="K9">
-        <v>111.2018708324444</v>
+        <v>112.8735877261384</v>
       </c>
       <c r="L9">
-        <v>4.224427768082892</v>
+        <v>4.026699844411326</v>
       </c>
       <c r="M9">
-        <v>121.0957433947555</v>
+        <v>116.5586308262305</v>
       </c>
       <c r="N9">
-        <v>110.5715281461097</v>
+        <v>112.8407675590231</v>
       </c>
       <c r="O9">
-        <v>10.52421524864574</v>
+        <v>3.717863267207385</v>
       </c>
       <c r="P9">
-        <v>0.5413158732898051</v>
+        <v>0.5636808786519771</v>
       </c>
       <c r="Q9">
-        <v>0.1259256820064917</v>
+        <v>0.1186245399701173</v>
       </c>
       <c r="R9">
-        <v>0.347095889045974</v>
+        <v>0.2628989758834306</v>
       </c>
       <c r="S9">
-        <v>0.5529772907917559</v>
+        <v>0.5763943985972998</v>
       </c>
       <c r="T9">
-        <v>0.2617435552976827</v>
+        <v>0.2718020513871829</v>
       </c>
       <c r="U9">
-        <v>0.3500536664840906</v>
+        <v>0.4426399694593818</v>
       </c>
       <c r="V9">
-        <v>99.032582220775</v>
+        <v>102.0845736434109</v>
       </c>
       <c r="W9">
-        <v>114.4558775643113</v>
+        <v>119.1542081949058</v>
       </c>
       <c r="X9">
-        <v>4.722565939433409</v>
+        <v>3.910299003322259</v>
       </c>
       <c r="Y9">
-        <v>0.5745420351749058</v>
+        <v>0.5967658761442574</v>
       </c>
       <c r="Z9">
-        <v>118.75</v>
+        <v>117.35</v>
       </c>
       <c r="AA9">
-        <v>11.27</v>
+        <v>2.84</v>
       </c>
       <c r="AB9">
-        <v>3.413694058608522</v>
+        <v>9.967224035556209</v>
       </c>
       <c r="AC9">
-        <v>112.3850185369902</v>
+        <v>120.0962116764131</v>
       </c>
       <c r="AD9">
-        <v>108.9713244783817</v>
+        <v>110.1289876408569</v>
       </c>
       <c r="AE9">
         <v>2</v>
@@ -1590,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>0.6820093687253893</v>
+        <v>1.396553555826033</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -1607,76 +1607,76 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E10" s="2">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>1565.336</v>
+        <v>1596.495</v>
       </c>
       <c r="H10">
-        <v>-1.168</v>
+        <v>2.2183</v>
       </c>
       <c r="I10">
-        <v>1502.753951807229</v>
+        <v>1506.794104651163</v>
       </c>
       <c r="J10">
-        <v>114.7013870828077</v>
+        <v>114.5167266836142</v>
       </c>
       <c r="K10">
-        <v>111.1824707545871</v>
+        <v>111.0166519873391</v>
       </c>
       <c r="L10">
-        <v>3.518916328220537</v>
+        <v>3.500074696275218</v>
       </c>
       <c r="M10">
-        <v>111.1634740183666</v>
+        <v>113.629998919173</v>
       </c>
       <c r="N10">
-        <v>112.9972705892531</v>
+        <v>112.999347481156</v>
       </c>
       <c r="O10">
-        <v>-1.833796570886449</v>
+        <v>0.6306514380170913</v>
       </c>
       <c r="P10">
-        <v>0.5589926815883727</v>
+        <v>0.5582916984118952</v>
       </c>
       <c r="Q10">
-        <v>0.1236719049247095</v>
+        <v>0.1253957774777632</v>
       </c>
       <c r="R10">
-        <v>0.2531858203374175</v>
+        <v>0.255887348298599</v>
       </c>
       <c r="S10">
-        <v>0.5446478809891669</v>
+        <v>0.5537435560892165</v>
       </c>
       <c r="T10">
-        <v>0.2893177286477721</v>
+        <v>0.287993665545852</v>
       </c>
       <c r="U10">
-        <v>0.4187235493789284</v>
+        <v>0.4153701238151429</v>
       </c>
       <c r="V10">
-        <v>103.0522375215146</v>
+        <v>103.0184090909091</v>
       </c>
       <c r="W10">
-        <v>117.8709122203098</v>
+        <v>117.625</v>
       </c>
       <c r="X10">
-        <v>3.22403901319564</v>
+        <v>3.159090909090909</v>
       </c>
       <c r="Y10">
-        <v>0.5920848746253627</v>
+        <v>0.5920606117918757</v>
       </c>
       <c r="Z10">
-        <v>115.13</v>
+        <v>116.78</v>
       </c>
       <c r="AA10">
-        <v>-0.9400000000000002</v>
+        <v>0.5099999999999998</v>
       </c>
       <c r="AB10">
         <v>4.250350764022217</v>
@@ -1694,15 +1694,15 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH10">
-        <v>0.8225072050563602</v>
+        <v>0.2347910037947659</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11">
-        <v>1610612747</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -1711,85 +1711,85 @@
         <v>73</v>
       </c>
       <c r="D11">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E11" s="2">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G11">
-        <v>1570.585</v>
+        <v>1595.901</v>
       </c>
       <c r="H11">
-        <v>0.1104</v>
+        <v>1.1766</v>
       </c>
       <c r="I11">
-        <v>1495.979012048193</v>
+        <v>1500.667987951807</v>
       </c>
       <c r="J11">
-        <v>116.5357560994516</v>
+        <v>115.4149762484644</v>
       </c>
       <c r="K11">
-        <v>113.485349022595</v>
+        <v>112.710112232192</v>
       </c>
       <c r="L11">
-        <v>3.050407076856565</v>
+        <v>2.704864016272356</v>
       </c>
       <c r="M11">
-        <v>116.2880254326737</v>
+        <v>114.3450585426628</v>
       </c>
       <c r="N11">
-        <v>108.3570805923215</v>
+        <v>114.519081716883</v>
       </c>
       <c r="O11">
-        <v>7.930944840352239</v>
+        <v>-0.1740231742202818</v>
       </c>
       <c r="P11">
-        <v>0.5739987538430139</v>
+        <v>0.5501978920706958</v>
       </c>
       <c r="Q11">
-        <v>0.1266821693873879</v>
+        <v>0.1272258502497506</v>
       </c>
       <c r="R11">
-        <v>0.2369891261007327</v>
+        <v>0.3026917656448702</v>
       </c>
       <c r="S11">
-        <v>0.5918791643180277</v>
+        <v>0.5265069721753005</v>
       </c>
       <c r="T11">
-        <v>0.3258631388458821</v>
+        <v>0.2455679682993576</v>
       </c>
       <c r="U11">
-        <v>0.3920957884198234</v>
+        <v>0.4883293748691439</v>
       </c>
       <c r="V11">
-        <v>99.81398320554949</v>
+        <v>99.63660191787559</v>
       </c>
       <c r="W11">
-        <v>115.767433369843</v>
+        <v>115.6110154905335</v>
       </c>
       <c r="X11">
-        <v>1.999634903249362</v>
+        <v>4.052864519301696</v>
       </c>
       <c r="Y11">
-        <v>0.6101719986715327</v>
+        <v>0.5871789759975214</v>
       </c>
       <c r="Z11">
-        <v>111.98</v>
+        <v>112.23</v>
       </c>
       <c r="AA11">
-        <v>4.48</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>1.827913300592181</v>
+        <v>-10.13717477219789</v>
       </c>
       <c r="AC11">
-        <v>114.1496737878887</v>
+        <v>104.7204689341547</v>
       </c>
       <c r="AD11">
-        <v>112.3217604872965</v>
+        <v>114.8576437063525</v>
       </c>
       <c r="AE11">
         <v>2</v>
@@ -1798,15 +1798,15 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH11">
-        <v>-0.1841754891464818</v>
+        <v>0.6096539178485425</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>1610612766</v>
+        <v>1610612747</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -1815,85 +1815,85 @@
         <v>74</v>
       </c>
       <c r="D12">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E12" s="2">
-        <v>46129</v>
+        <v>46141</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G12">
-        <v>1595.901</v>
+        <v>1574.18</v>
       </c>
       <c r="H12">
-        <v>1.1766</v>
+        <v>2.3992</v>
       </c>
       <c r="I12">
-        <v>1500.667987951807</v>
+        <v>1498.919511627907</v>
       </c>
       <c r="J12">
-        <v>115.181340119533</v>
+        <v>116.0022759811882</v>
       </c>
       <c r="K12">
-        <v>112.7471716506547</v>
+        <v>113.6282789432858</v>
       </c>
       <c r="L12">
-        <v>2.434168468878287</v>
+        <v>2.37399703790248</v>
       </c>
       <c r="M12">
-        <v>114.3450585426628</v>
+        <v>110.4544653868969</v>
       </c>
       <c r="N12">
-        <v>114.519081716883</v>
+        <v>110.7330110852719</v>
       </c>
       <c r="O12">
-        <v>-0.1740231742202818</v>
+        <v>-0.2785456983749446</v>
       </c>
       <c r="P12">
-        <v>0.5490265642552472</v>
+        <v>0.5717113969465225</v>
       </c>
       <c r="Q12">
-        <v>0.1273777560431238</v>
+        <v>0.1286910573046844</v>
       </c>
       <c r="R12">
-        <v>0.3014656305607926</v>
+        <v>0.2385704116837887</v>
       </c>
       <c r="S12">
-        <v>0.5265069721753005</v>
+        <v>0.5653848333685474</v>
       </c>
       <c r="T12">
-        <v>0.2460316087241722</v>
+        <v>0.3257176935752966</v>
       </c>
       <c r="U12">
-        <v>0.4887780357010577</v>
+        <v>0.3900660711338779</v>
       </c>
       <c r="V12">
-        <v>99.6657969018933</v>
+        <v>99.79043319653442</v>
       </c>
       <c r="W12">
-        <v>115.3975903614458</v>
+        <v>115.3210214318285</v>
       </c>
       <c r="X12">
-        <v>3.760757314974183</v>
+        <v>1.535339717282262</v>
       </c>
       <c r="Y12">
-        <v>0.5862751795663363</v>
+        <v>0.6083080478568764</v>
       </c>
       <c r="Z12">
-        <v>112.23</v>
+        <v>106.32</v>
       </c>
       <c r="AA12">
-        <v>1.67</v>
+        <v>-2.04</v>
       </c>
       <c r="AB12">
-        <v>-10.13717477219789</v>
+        <v>1.827913300592181</v>
       </c>
       <c r="AC12">
-        <v>104.7204689341547</v>
+        <v>114.1496737878887</v>
       </c>
       <c r="AD12">
-        <v>114.8576437063525</v>
+        <v>112.3217604872965</v>
       </c>
       <c r="AE12">
         <v>2</v>
@@ -1902,15 +1902,15 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>0.5469710369449039</v>
+        <v>0.3706437152686696</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>1610612748</v>
+        <v>1610612761</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -1919,102 +1919,102 @@
         <v>75</v>
       </c>
       <c r="D13">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2">
-        <v>46126</v>
+        <v>46141</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G13">
-        <v>1527.648</v>
+        <v>1536.125</v>
       </c>
       <c r="H13">
-        <v>-1.8362</v>
+        <v>1.4941</v>
       </c>
       <c r="I13">
-        <v>1501.638890243902</v>
+        <v>1503.077372093023</v>
       </c>
       <c r="J13">
-        <v>114.6709319067504</v>
+        <v>113.6532849978209</v>
       </c>
       <c r="K13">
-        <v>112.6223580741253</v>
+        <v>111.5767786132529</v>
       </c>
       <c r="L13">
-        <v>2.048573832625117</v>
+        <v>2.07650638456793</v>
       </c>
       <c r="M13">
-        <v>121.8006871479158</v>
+        <v>115.9088207542528</v>
       </c>
       <c r="N13">
-        <v>121.5315734581696</v>
+        <v>109.8761801386304</v>
       </c>
       <c r="O13">
-        <v>0.2691136897462759</v>
+        <v>6.032640615622364</v>
       </c>
       <c r="P13">
-        <v>0.5425583298740713</v>
+        <v>0.5469904641006763</v>
       </c>
       <c r="Q13">
-        <v>0.1105072050709512</v>
+        <v>0.1163679745727197</v>
       </c>
       <c r="R13">
-        <v>0.2512834002215163</v>
+        <v>0.2546095189292202</v>
       </c>
       <c r="S13">
-        <v>0.5859150211633202</v>
+        <v>0.5649017199981372</v>
       </c>
       <c r="T13">
-        <v>0.2668975444299984</v>
+        <v>0.2698041682872999</v>
       </c>
       <c r="U13">
-        <v>0.4065551262287586</v>
+        <v>0.3622128302441839</v>
       </c>
       <c r="V13">
-        <v>105.549430894309</v>
+        <v>100.6470523255814</v>
       </c>
       <c r="W13">
-        <v>121.0084688346884</v>
+        <v>114.5241279069768</v>
       </c>
       <c r="X13">
-        <v>2.236788617886179</v>
+        <v>2.539244186046512</v>
       </c>
       <c r="Y13">
-        <v>0.5797829519539587</v>
+        <v>0.5804958027403524</v>
       </c>
       <c r="Z13">
-        <v>125.82</v>
+        <v>115.14</v>
       </c>
       <c r="AA13">
-        <v>-0.46</v>
+        <v>6.61</v>
       </c>
       <c r="AB13">
-        <v>-1.094669144490311</v>
+        <v>-4.536933640611859</v>
       </c>
       <c r="AC13">
-        <v>111.6804548463295</v>
+        <v>108.3888858603967</v>
       </c>
       <c r="AD13">
-        <v>112.7751239908198</v>
+        <v>112.9258195010085</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>0.02290300967776139</v>
+        <v>0.5065194094335951</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
-        <v>1610612737</v>
+        <v>1610612748</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
@@ -2023,85 +2023,85 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E14" s="2">
-        <v>46132</v>
+        <v>46126</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G14">
-        <v>1525.972</v>
+        <v>1527.648</v>
       </c>
       <c r="H14">
-        <v>1.4977</v>
+        <v>-1.8362</v>
       </c>
       <c r="I14">
-        <v>1492.276542168675</v>
+        <v>1501.638890243902</v>
       </c>
       <c r="J14">
-        <v>113.9218461929291</v>
+        <v>114.6318212854539</v>
       </c>
       <c r="K14">
-        <v>111.9080991762141</v>
+        <v>112.577425207248</v>
       </c>
       <c r="L14">
-        <v>2.013747016715009</v>
+        <v>2.054396078205957</v>
       </c>
       <c r="M14">
-        <v>115.0677585583131</v>
+        <v>121.8006871479158</v>
       </c>
       <c r="N14">
-        <v>110.5819435217274</v>
+        <v>121.5315734581696</v>
       </c>
       <c r="O14">
-        <v>4.485815036585638</v>
+        <v>0.2691136897462759</v>
       </c>
       <c r="P14">
-        <v>0.5537864916559568</v>
+        <v>0.5424910023686157</v>
       </c>
       <c r="Q14">
-        <v>0.1159181297794972</v>
+        <v>0.1108192889037584</v>
       </c>
       <c r="R14">
-        <v>0.2395178622170419</v>
+        <v>0.2513230613459749</v>
       </c>
       <c r="S14">
-        <v>0.5560831180976777</v>
+        <v>0.5859150211633202</v>
       </c>
       <c r="T14">
-        <v>0.2372676359728531</v>
+        <v>0.2677110550780289</v>
       </c>
       <c r="U14">
-        <v>0.4276686019724975</v>
+        <v>0.406607901842433</v>
       </c>
       <c r="V14">
-        <v>103.5363855421686</v>
+        <v>105.5524708377519</v>
       </c>
       <c r="W14">
-        <v>117.996844520941</v>
+        <v>120.9774655355249</v>
       </c>
       <c r="X14">
-        <v>2.223178427997705</v>
+        <v>2.256892895015907</v>
       </c>
       <c r="Y14">
-        <v>0.5840926452828347</v>
+        <v>0.5797994020810326</v>
       </c>
       <c r="Z14">
-        <v>116.18</v>
+        <v>125.82</v>
       </c>
       <c r="AA14">
-        <v>4.78</v>
+        <v>-0.46</v>
       </c>
       <c r="AB14">
-        <v>-0.981113782848854</v>
+        <v>-1.094669144490311</v>
       </c>
       <c r="AC14">
-        <v>112.8029837792552</v>
+        <v>111.6804548463295</v>
       </c>
       <c r="AD14">
-        <v>113.7840975621041</v>
+        <v>112.7751239908198</v>
       </c>
       <c r="AE14">
         <v>1</v>
@@ -2110,15 +2110,15 @@
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH14">
-        <v>0.6934733560005515</v>
+        <v>-0.0878761004765552</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -2127,102 +2127,102 @@
         <v>77</v>
       </c>
       <c r="D15">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15">
-        <v>1515.647</v>
+        <v>1547.576</v>
       </c>
       <c r="H15">
-        <v>0.6798999999999999</v>
+        <v>-1.1818</v>
       </c>
       <c r="I15">
-        <v>1498.162313253012</v>
+        <v>1497.571951219512</v>
       </c>
       <c r="J15">
-        <v>113.5732295153116</v>
+        <v>115.7602402651069</v>
       </c>
       <c r="K15">
-        <v>111.7121045553402</v>
+        <v>113.9949512022783</v>
       </c>
       <c r="L15">
-        <v>1.861124959971512</v>
+        <v>1.765289062828634</v>
       </c>
       <c r="M15">
-        <v>118.262850594387</v>
+        <v>115.5369920979726</v>
       </c>
       <c r="N15">
-        <v>111.1578252009957</v>
+        <v>113.7634557004086</v>
       </c>
       <c r="O15">
-        <v>7.105025393391172</v>
+        <v>1.773536397563934</v>
       </c>
       <c r="P15">
-        <v>0.5482910901566943</v>
+        <v>0.5609471072562446</v>
       </c>
       <c r="Q15">
-        <v>0.1180006200249673</v>
+        <v>0.1258797346484531</v>
       </c>
       <c r="R15">
-        <v>0.2519821828354366</v>
+        <v>0.2355462311120468</v>
       </c>
       <c r="S15">
-        <v>0.5874045545590205</v>
+        <v>0.5616141638462627</v>
       </c>
       <c r="T15">
-        <v>0.2681730579411352</v>
+        <v>0.2957334786867056</v>
       </c>
       <c r="U15">
-        <v>0.362290079497583</v>
+        <v>0.4043379118962849</v>
       </c>
       <c r="V15">
-        <v>100.5862587190868</v>
+        <v>98.89100609756098</v>
       </c>
       <c r="W15">
-        <v>114.3614457831325</v>
+        <v>113.9490853658536</v>
       </c>
       <c r="X15">
-        <v>2.305960684844642</v>
+        <v>0.9807926829268296</v>
       </c>
       <c r="Y15">
-        <v>0.5819721955361474</v>
+        <v>0.6040718608714009</v>
       </c>
       <c r="Z15">
-        <v>117.78</v>
+        <v>114.61</v>
       </c>
       <c r="AA15">
-        <v>7.64</v>
+        <v>1.39</v>
       </c>
       <c r="AB15">
-        <v>-4.536933640611859</v>
+        <v>4.815266446541752</v>
       </c>
       <c r="AC15">
-        <v>108.3888858603967</v>
+        <v>113.8106821492749</v>
       </c>
       <c r="AD15">
-        <v>112.9258195010085</v>
+        <v>108.9954157027332</v>
       </c>
       <c r="AE15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH15">
-        <v>0.4790746633360264</v>
+        <v>0.4095082711228584</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16">
-        <v>1610612746</v>
+        <v>1610612737</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
@@ -2231,85 +2231,85 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="F16">
         <v>42</v>
       </c>
       <c r="G16">
-        <v>1547.576</v>
+        <v>1534.461</v>
       </c>
       <c r="H16">
-        <v>-1.1818</v>
+        <v>0.8975</v>
       </c>
       <c r="I16">
-        <v>1497.571951219512</v>
+        <v>1497.688534883721</v>
       </c>
       <c r="J16">
-        <v>115.7559971917994</v>
+        <v>113.4165229456221</v>
       </c>
       <c r="K16">
-        <v>113.9836636742961</v>
+        <v>112.4047993404294</v>
       </c>
       <c r="L16">
-        <v>1.772333517503413</v>
+        <v>1.011723605192716</v>
       </c>
       <c r="M16">
-        <v>115.5369920979726</v>
+        <v>111.4366157739386</v>
       </c>
       <c r="N16">
-        <v>113.7634557004086</v>
+        <v>112.7548500969661</v>
       </c>
       <c r="O16">
-        <v>1.773536397563934</v>
+        <v>-1.318234323027534</v>
       </c>
       <c r="P16">
-        <v>0.5608937445510744</v>
+        <v>0.5518977978132055</v>
       </c>
       <c r="Q16">
-        <v>0.1258455536109729</v>
+        <v>0.1164168069441013</v>
       </c>
       <c r="R16">
-        <v>0.2355198616052937</v>
+        <v>0.2384661101030415</v>
       </c>
       <c r="S16">
-        <v>0.5616141638462627</v>
+        <v>0.5469756511738948</v>
       </c>
       <c r="T16">
-        <v>0.2958532089187961</v>
+        <v>0.2374164610560177</v>
       </c>
       <c r="U16">
-        <v>0.4043346898788371</v>
+        <v>0.4304542728121414</v>
       </c>
       <c r="V16">
-        <v>98.88738095238094</v>
+        <v>103.3427851605759</v>
       </c>
       <c r="W16">
-        <v>113.9404761904762</v>
+        <v>117.2956810631229</v>
       </c>
       <c r="X16">
-        <v>0.9880952380952385</v>
+        <v>1.273255813953488</v>
       </c>
       <c r="Y16">
-        <v>0.6040192047046427</v>
+        <v>0.581918648579929</v>
       </c>
       <c r="Z16">
-        <v>114.61</v>
+        <v>113.11</v>
       </c>
       <c r="AA16">
-        <v>1.39</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="AB16">
-        <v>4.815266446541752</v>
+        <v>-0.981113782848854</v>
       </c>
       <c r="AC16">
-        <v>113.8106821492749</v>
+        <v>112.8029837792552</v>
       </c>
       <c r="AD16">
-        <v>108.9954157027332</v>
+        <v>113.7840975621041</v>
       </c>
       <c r="AE16">
         <v>2</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>0.3372477207784098</v>
+        <v>0.7289412242246355</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -2335,76 +2335,76 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G17">
-        <v>1506.657</v>
+        <v>1498.742</v>
       </c>
       <c r="H17">
-        <v>0.4811</v>
+        <v>-0.0733</v>
       </c>
       <c r="I17">
-        <v>1516.598823529412</v>
+        <v>1522.125701149425</v>
       </c>
       <c r="J17">
-        <v>112.8084528572326</v>
+        <v>113.1011602463513</v>
       </c>
       <c r="K17">
-        <v>112.1361682042551</v>
+        <v>112.6784840359227</v>
       </c>
       <c r="L17">
-        <v>0.6722846529775324</v>
+        <v>0.4226762104286177</v>
       </c>
       <c r="M17">
-        <v>108.1314101343386</v>
+        <v>110.6095009513796</v>
       </c>
       <c r="N17">
-        <v>113.8077844913904</v>
+        <v>116.1729614697779</v>
       </c>
       <c r="O17">
-        <v>-5.676374357051831</v>
+        <v>-5.563460518398324</v>
       </c>
       <c r="P17">
-        <v>0.537504853209016</v>
+        <v>0.5391615220262829</v>
       </c>
       <c r="Q17">
-        <v>0.1218557938279784</v>
+        <v>0.1206886145104707</v>
       </c>
       <c r="R17">
-        <v>0.28735826193371</v>
+        <v>0.2855225505254233</v>
       </c>
       <c r="S17">
-        <v>0.5225748981593997</v>
+        <v>0.5320801030063896</v>
       </c>
       <c r="T17">
-        <v>0.2314432788657317</v>
+        <v>0.2302036777648242</v>
       </c>
       <c r="U17">
-        <v>0.452703558587767</v>
+        <v>0.4534031020466724</v>
       </c>
       <c r="V17">
-        <v>99.40641711229947</v>
+        <v>99.37447154471543</v>
       </c>
       <c r="W17">
-        <v>112.0818181818182</v>
+        <v>112.3448275862069</v>
       </c>
       <c r="X17">
-        <v>0.8082887700534755</v>
+        <v>0.5766750770955986</v>
       </c>
       <c r="Y17">
-        <v>0.5696254492825312</v>
+        <v>0.5710190954596031</v>
       </c>
       <c r="Z17">
-        <v>106.82</v>
+        <v>108.14</v>
       </c>
       <c r="AA17">
-        <v>-5.17</v>
+        <v>-4.86</v>
       </c>
       <c r="AB17">
         <v>-2.375203171419814</v>
@@ -2416,7 +2416,7 @@
         <v>117.0787009454136</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>2</v>
       </c>
       <c r="AH17">
-        <v>0.05415775570613952</v>
+        <v>-0.06261797187047512</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -2439,76 +2439,76 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18">
-        <v>1475.637</v>
+        <v>1475.254</v>
       </c>
       <c r="H18">
-        <v>0.407</v>
+        <v>1.372</v>
       </c>
       <c r="I18">
-        <v>1502.361369047619</v>
+        <v>1508.173436781609</v>
       </c>
       <c r="J18">
-        <v>113.0985345582815</v>
+        <v>113.0426460886211</v>
       </c>
       <c r="K18">
-        <v>112.5491985721023</v>
+        <v>112.6232418763137</v>
       </c>
       <c r="L18">
-        <v>0.5493359861792191</v>
+        <v>0.4194042123073966</v>
       </c>
       <c r="M18">
-        <v>110.9855999327527</v>
+        <v>108.4267171001996</v>
       </c>
       <c r="N18">
-        <v>109.1399112268853</v>
+        <v>110.6137491202432</v>
       </c>
       <c r="O18">
-        <v>1.845688705867384</v>
+        <v>-2.187032020043509</v>
       </c>
       <c r="P18">
-        <v>0.5306216720211607</v>
+        <v>0.5305511223317256</v>
       </c>
       <c r="Q18">
-        <v>0.1126540587809514</v>
+        <v>0.1122638773991905</v>
       </c>
       <c r="R18">
-        <v>0.2590850939840675</v>
+        <v>0.2550240176089325</v>
       </c>
       <c r="S18">
-        <v>0.5214481978923438</v>
+        <v>0.5066891479816433</v>
       </c>
       <c r="T18">
-        <v>0.2748128646454954</v>
+        <v>0.2763382364559998</v>
       </c>
       <c r="U18">
-        <v>0.390896400692969</v>
+        <v>0.3937780168173592</v>
       </c>
       <c r="V18">
-        <v>102.3396768707483</v>
+        <v>102.0877626303127</v>
       </c>
       <c r="W18">
-        <v>115.3928571428571</v>
+        <v>114.9983961507619</v>
       </c>
       <c r="X18">
-        <v>-0.07341269841269847</v>
+        <v>-0.3127506014434644</v>
       </c>
       <c r="Y18">
-        <v>0.5718631883615367</v>
+        <v>0.5723973746393636</v>
       </c>
       <c r="Z18">
-        <v>110.55</v>
+        <v>104.45</v>
       </c>
       <c r="AA18">
-        <v>0.3200000000000001</v>
+        <v>-3.98</v>
       </c>
       <c r="AB18">
         <v>-6.382503892565079</v>
@@ -2526,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH18">
-        <v>0.07478552016411476</v>
+        <v>0.6229870569101851</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -2543,76 +2543,76 @@
         <v>81</v>
       </c>
       <c r="D19">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E19" s="2">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="F19">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G19">
-        <v>1549.571</v>
+        <v>1561.52</v>
       </c>
       <c r="H19">
-        <v>3.5116</v>
+        <v>4.5579</v>
       </c>
       <c r="I19">
-        <v>1495.591780487805</v>
+        <v>1501.950317647059</v>
       </c>
       <c r="J19">
-        <v>111.7516750590107</v>
+        <v>111.7032852116154</v>
       </c>
       <c r="K19">
-        <v>111.4481060651044</v>
+        <v>111.4387614338783</v>
       </c>
       <c r="L19">
-        <v>0.3035689939062091</v>
+        <v>0.2645237777369683</v>
       </c>
       <c r="M19">
-        <v>108.517605711177</v>
+        <v>107.6867865043865</v>
       </c>
       <c r="N19">
-        <v>104.3869996797991</v>
+        <v>102.3284630841294</v>
       </c>
       <c r="O19">
-        <v>4.130606031377861</v>
+        <v>5.358323420257033</v>
       </c>
       <c r="P19">
-        <v>0.528015892045394</v>
+        <v>0.5288129228595819</v>
       </c>
       <c r="Q19">
-        <v>0.120022750915836</v>
+        <v>0.1199182021455129</v>
       </c>
       <c r="R19">
-        <v>0.2464073885322829</v>
+        <v>0.2464385279286851</v>
       </c>
       <c r="S19">
-        <v>0.515502249333066</v>
+        <v>0.5087984599636823</v>
       </c>
       <c r="T19">
-        <v>0.3217246949659747</v>
+        <v>0.3233129961081564</v>
       </c>
       <c r="U19">
-        <v>0.3855936836069132</v>
+        <v>0.387442439047905</v>
       </c>
       <c r="V19">
-        <v>102.6209188882587</v>
+        <v>102.5492764705883</v>
       </c>
       <c r="W19">
-        <v>114.7799205899036</v>
+        <v>114.7238235294117</v>
       </c>
       <c r="X19">
-        <v>0.8899602949517865</v>
+        <v>1.006470588235294</v>
       </c>
       <c r="Y19">
-        <v>0.5742049945787354</v>
+        <v>0.5740508453966218</v>
       </c>
       <c r="Z19">
-        <v>113.69</v>
+        <v>110.8</v>
       </c>
       <c r="AA19">
-        <v>4.17</v>
+        <v>6.14</v>
       </c>
       <c r="AB19">
         <v>-0.5231111597400365</v>
@@ -2624,7 +2624,7 @@
         <v>108.1384073962044</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -2633,12 +2633,12 @@
         <v>3</v>
       </c>
       <c r="AH19">
-        <v>-0.04171231231847827</v>
+        <v>-0.05914799654191899</v>
       </c>
     </row>
     <row r="20" spans="1:34">
       <c r="A20">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="B20" t="s">
         <v>52</v>
@@ -2647,85 +2647,85 @@
         <v>82</v>
       </c>
       <c r="D20">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E20" s="2">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="F20">
         <v>45</v>
       </c>
       <c r="G20">
-        <v>1477.005</v>
+        <v>1471.569</v>
       </c>
       <c r="H20">
-        <v>1.7664</v>
+        <v>-1.5085</v>
       </c>
       <c r="I20">
-        <v>1507.532630952381</v>
+        <v>1505.850120481928</v>
       </c>
       <c r="J20">
-        <v>111.3362118824537</v>
+        <v>112.6516936177494</v>
       </c>
       <c r="K20">
-        <v>112.2490095221067</v>
+        <v>113.5784507799674</v>
       </c>
       <c r="L20">
-        <v>-0.9127976396529216</v>
+        <v>-0.9267571622179978</v>
       </c>
       <c r="M20">
-        <v>111.9684807372938</v>
+        <v>114.3428494363806</v>
       </c>
       <c r="N20">
-        <v>107.6890223086083</v>
+        <v>120.1535355097058</v>
       </c>
       <c r="O20">
-        <v>4.279458428685526</v>
+        <v>-5.810686073325223</v>
       </c>
       <c r="P20">
-        <v>0.5330391797254368</v>
+        <v>0.5514751021229293</v>
       </c>
       <c r="Q20">
-        <v>0.1392783216004193</v>
+        <v>0.1342399833857656</v>
       </c>
       <c r="R20">
-        <v>0.3103200161554104</v>
+        <v>0.258340644982248</v>
       </c>
       <c r="S20">
-        <v>0.5313547330130314</v>
+        <v>0.559296308148711</v>
       </c>
       <c r="T20">
-        <v>0.2816059952278737</v>
+        <v>0.2432011503673799</v>
       </c>
       <c r="U20">
-        <v>0.4682301722160147</v>
+        <v>0.4954833562924654</v>
       </c>
       <c r="V20">
-        <v>103.0638730158731</v>
+        <v>101.4537295850067</v>
       </c>
       <c r="W20">
-        <v>115.0444444444445</v>
+        <v>114.3303882195448</v>
       </c>
       <c r="X20">
-        <v>-0.3174603174603174</v>
+        <v>-0.8163319946452476</v>
       </c>
       <c r="Y20">
-        <v>0.5695489561935217</v>
+        <v>0.5861415859980742</v>
       </c>
       <c r="Z20">
-        <v>112.39</v>
+        <v>111.39</v>
       </c>
       <c r="AA20">
-        <v>5.34</v>
+        <v>-6.63</v>
       </c>
       <c r="AB20">
-        <v>-3.840928550668963</v>
+        <v>2.402868486532558</v>
       </c>
       <c r="AC20">
-        <v>109.2995408403883</v>
+        <v>112.5227430890375</v>
       </c>
       <c r="AD20">
-        <v>113.1404693910572</v>
+        <v>110.1198746025049</v>
       </c>
       <c r="AE20">
         <v>1</v>
@@ -2734,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH20">
-        <v>0.1291403514190761</v>
+        <v>0.3774518194945357</v>
       </c>
     </row>
     <row r="21" spans="1:34">
       <c r="A21">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
@@ -2751,85 +2751,85 @@
         <v>83</v>
       </c>
       <c r="D21">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E21" s="2">
-        <v>46129</v>
+        <v>46140</v>
       </c>
       <c r="F21">
         <v>39</v>
       </c>
       <c r="G21">
-        <v>1471.569</v>
+        <v>1477.256</v>
       </c>
       <c r="H21">
-        <v>-1.5085</v>
+        <v>2.0064</v>
       </c>
       <c r="I21">
-        <v>1505.850120481928</v>
+        <v>1515.224505747127</v>
       </c>
       <c r="J21">
-        <v>112.6221838412012</v>
+        <v>110.7699538905747</v>
       </c>
       <c r="K21">
-        <v>113.6097028971402</v>
+        <v>112.7358789076591</v>
       </c>
       <c r="L21">
-        <v>-0.9875190559389955</v>
+        <v>-1.965925017084302</v>
       </c>
       <c r="M21">
-        <v>114.3428494363806</v>
+        <v>109.1724515799799</v>
       </c>
       <c r="N21">
-        <v>120.1535355097058</v>
+        <v>113.7113652025218</v>
       </c>
       <c r="O21">
-        <v>-5.810686073325223</v>
+        <v>-4.538913622541832</v>
       </c>
       <c r="P21">
-        <v>0.5513659943192487</v>
+        <v>0.5289253346583457</v>
       </c>
       <c r="Q21">
-        <v>0.1344422423758589</v>
+        <v>0.1375649523058483</v>
       </c>
       <c r="R21">
-        <v>0.258513203243472</v>
+        <v>0.3082251088118518</v>
       </c>
       <c r="S21">
-        <v>0.559296308148711</v>
+        <v>0.5127711477376412</v>
       </c>
       <c r="T21">
-        <v>0.2434375477815177</v>
+        <v>0.2814160840446617</v>
       </c>
       <c r="U21">
-        <v>0.495310148563981</v>
+        <v>0.4680454996156455</v>
       </c>
       <c r="V21">
-        <v>101.41843682422</v>
+        <v>102.8266961391099</v>
       </c>
       <c r="W21">
-        <v>114.2662959530429</v>
+        <v>114.296787503684</v>
       </c>
       <c r="X21">
-        <v>-0.8659252394192152</v>
+        <v>-1.192749778956676</v>
       </c>
       <c r="Y21">
-        <v>0.5860872916743576</v>
+        <v>0.5659041101216474</v>
       </c>
       <c r="Z21">
-        <v>111.39</v>
+        <v>109.22</v>
       </c>
       <c r="AA21">
-        <v>-6.63</v>
+        <v>-2.98</v>
       </c>
       <c r="AB21">
-        <v>2.402868486532558</v>
+        <v>-3.840928550668963</v>
       </c>
       <c r="AC21">
-        <v>112.5227430890375</v>
+        <v>109.2995408403883</v>
       </c>
       <c r="AD21">
-        <v>110.1198746025049</v>
+        <v>113.1404693910572</v>
       </c>
       <c r="AE21">
         <v>1</v>
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="AH21">
-        <v>0.3216699062552075</v>
+        <v>-0.1501860934310909</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -2945,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>-1.138072553268783</v>
+        <v>-1.123397315804866</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3049,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="AH23">
-        <v>-0.593214857815052</v>
+        <v>-0.5615201740178595</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="AH24">
-        <v>-1.254510821408037</v>
+        <v>-1.243391525026527</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3257,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="AH25">
-        <v>-1.364463527011031</v>
+        <v>-1.35584327929742</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="AH26">
-        <v>-1.144147103625029</v>
+        <v>-1.128081021050644</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="AH27">
-        <v>-1.036774025958877</v>
+        <v>-1.019382795225623</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AH28">
-        <v>-1.002541067708509</v>
+        <v>-0.9850937856415628</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3673,7 +3673,7 @@
         <v>3</v>
       </c>
       <c r="AH29">
-        <v>-1.63866277384436</v>
+        <v>-1.639761242688036</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3777,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="AH30">
-        <v>-1.844099574165216</v>
+        <v>-1.849158350700011</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -3881,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="AH31">
-        <v>-1.276099074716355</v>
+        <v>-1.266069976320604</v>
       </c>
     </row>
   </sheetData>
